--- a/JsonConverter/ExcelFiles/SoundData.xlsx
+++ b/JsonConverter/ExcelFiles/SoundData.xlsx
@@ -47,19 +47,19 @@
     <t>string</t>
   </si>
   <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
     <t>SoundType</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>bool</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>Name</t>
   </si>
   <si>
     <t>Volume</t>
@@ -1373,24 +1373,24 @@
         <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:5">
       <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>11</v>

--- a/JsonConverter/ExcelFiles/SoundData.xlsx
+++ b/JsonConverter/ExcelFiles/SoundData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13128" windowHeight="9000"/>
+    <workbookView windowWidth="14592" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="시트1" sheetId="1" r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/SoundData.xlsx
+++ b/JsonConverter/ExcelFiles/SoundData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14592" windowHeight="9000"/>
+    <workbookView windowWidth="14568" windowHeight="8424"/>
   </bookViews>
   <sheets>
     <sheet name="시트1" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>SoundType</t>
+    <t>StringSoundType</t>
   </si>
   <si>
     <t>Volume</t>

--- a/JsonConverter/ExcelFiles/SoundData.xlsx
+++ b/JsonConverter/ExcelFiles/SoundData.xlsx
@@ -40,7 +40,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Volumn</t>
+    <t>Volume</t>
   </si>
   <si>
     <t>IsLoop</t>
@@ -49,7 +49,7 @@
     <t>Sound_BGM_01</t>
   </si>
   <si>
-    <t>BGM_01</t>
+    <t>PlayTheme</t>
   </si>
   <si>
     <t>true</t>
@@ -64,7 +64,7 @@
     <t>Sound_SFX_001</t>
   </si>
   <si>
-    <t>AlertLevelUp</t>
+    <t>AlertUp_01</t>
   </si>
   <si>
     <t>false</t>
@@ -530,7 +530,7 @@
         <v>12</v>
       </c>
       <c r="C4" s="1">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>13</v>
@@ -544,7 +544,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="1">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>13</v>
@@ -558,7 +558,7 @@
         <v>17</v>
       </c>
       <c r="C6" s="1">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>18</v>
@@ -572,7 +572,7 @@
         <v>20</v>
       </c>
       <c r="C7" s="1">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>18</v>
@@ -586,7 +586,7 @@
         <v>22</v>
       </c>
       <c r="C8" s="1">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>18</v>
@@ -600,7 +600,7 @@
         <v>24</v>
       </c>
       <c r="C9" s="1">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>18</v>
@@ -614,7 +614,7 @@
         <v>26</v>
       </c>
       <c r="C10" s="1">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>18</v>
@@ -628,7 +628,7 @@
         <v>28</v>
       </c>
       <c r="C11" s="1">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>18</v>
@@ -642,7 +642,7 @@
         <v>30</v>
       </c>
       <c r="C12" s="1">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>18</v>
@@ -656,7 +656,7 @@
         <v>32</v>
       </c>
       <c r="C13" s="1">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>18</v>
@@ -670,7 +670,7 @@
         <v>34</v>
       </c>
       <c r="C14" s="1">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>18</v>
@@ -684,7 +684,7 @@
         <v>36</v>
       </c>
       <c r="C15" s="1">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>18</v>
@@ -698,7 +698,7 @@
         <v>38</v>
       </c>
       <c r="C16" s="1">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>18</v>
@@ -712,7 +712,7 @@
         <v>40</v>
       </c>
       <c r="C17" s="1">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>13</v>
@@ -726,7 +726,7 @@
         <v>42</v>
       </c>
       <c r="C18" s="1">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>18</v>
@@ -740,7 +740,7 @@
         <v>44</v>
       </c>
       <c r="C19" s="1">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>18</v>
@@ -754,7 +754,7 @@
         <v>46</v>
       </c>
       <c r="C20" s="1">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>18</v>
@@ -768,7 +768,7 @@
         <v>48</v>
       </c>
       <c r="C21" s="1">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>18</v>
@@ -782,7 +782,7 @@
         <v>50</v>
       </c>
       <c r="C22" s="1">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>18</v>
@@ -796,7 +796,7 @@
         <v>52</v>
       </c>
       <c r="C23" s="1">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>18</v>
@@ -810,7 +810,7 @@
         <v>54</v>
       </c>
       <c r="C24" s="1">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>18</v>
@@ -824,7 +824,7 @@
         <v>56</v>
       </c>
       <c r="C25" s="1">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>18</v>
@@ -838,7 +838,7 @@
         <v>58</v>
       </c>
       <c r="C26" s="1">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>18</v>
@@ -852,7 +852,7 @@
         <v>60</v>
       </c>
       <c r="C27" s="1">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>18</v>
@@ -866,7 +866,7 @@
         <v>62</v>
       </c>
       <c r="C28" s="1">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>18</v>

--- a/JsonConverter/ExcelFiles/SoundData.xlsx
+++ b/JsonConverter/ExcelFiles/SoundData.xlsx
@@ -1,12 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="시트1" sheetId="1" r:id="rId5"/>
+    <sheet name="시트1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -49,7 +65,7 @@
     <t>Sound_BGM_01</t>
   </si>
   <si>
-    <t>BGM_01</t>
+    <t>PlayTheme</t>
   </si>
   <si>
     <t>true</t>
@@ -205,71 +221,915 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
-    <border/>
+  <borders count="9">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="18">
     <dxf>
-      <font/>
       <fill>
         <patternFill patternType="none"/>
       </fill>
-      <border/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
     </dxf>
   </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="totalRow" dxfId="5"/>
+      <tableStyleElement type="firstColumn" dxfId="4"/>
+      <tableStyleElement type="lastColumn" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="totalRow" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
+      <tableStyleElement type="pageFieldValues" dxfId="8"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -459,28 +1319,30 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:D1001"/>
+  <sheetFormatPr defaultColWidth="12.6296296296296" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="3"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.75"/>
-    <col customWidth="1" min="2" max="2" width="14.5"/>
-    <col customWidth="1" min="3" max="3" width="13.5"/>
-    <col customWidth="1" min="4" max="4" width="12.75"/>
-    <col customWidth="1" min="5" max="5" width="16.5"/>
-    <col customWidth="1" min="6" max="6" width="16.25"/>
-    <col customWidth="1" min="7" max="7" width="23.75"/>
-    <col customWidth="1" min="8" max="8" width="29.63"/>
-    <col customWidth="1" min="9" max="9" width="17.25"/>
+    <col min="1" max="1" width="14.75" customWidth="1"/>
+    <col min="2" max="2" width="14.5" customWidth="1"/>
+    <col min="3" max="3" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="12.75" customWidth="1"/>
+    <col min="5" max="5" width="16.5" customWidth="1"/>
+    <col min="6" max="6" width="16.25" customWidth="1"/>
+    <col min="7" max="7" width="23.75" customWidth="1"/>
+    <col min="8" max="8" width="29.6296296296296" customWidth="1"/>
+    <col min="9" max="9" width="17.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -494,7 +1356,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" customHeight="1" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -508,7 +1370,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" customHeight="1" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -522,7 +1384,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" customHeight="1" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -530,13 +1392,13 @@
         <v>12</v>
       </c>
       <c r="C4" s="1">
-        <v>100.0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" customHeight="1" spans="1:4">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -544,13 +1406,13 @@
         <v>15</v>
       </c>
       <c r="C5" s="1">
-        <v>100.0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" customHeight="1" spans="1:4">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -558,13 +1420,13 @@
         <v>17</v>
       </c>
       <c r="C6" s="1">
-        <v>100.0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" customHeight="1" spans="1:4">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -572,13 +1434,13 @@
         <v>20</v>
       </c>
       <c r="C7" s="1">
-        <v>100.0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" customHeight="1" spans="1:4">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -586,13 +1448,13 @@
         <v>22</v>
       </c>
       <c r="C8" s="1">
-        <v>100.0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" customHeight="1" spans="1:4">
       <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
@@ -600,13 +1462,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="1">
-        <v>100.0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" customHeight="1" spans="1:4">
       <c r="A10" s="1" t="s">
         <v>25</v>
       </c>
@@ -614,13 +1476,13 @@
         <v>26</v>
       </c>
       <c r="C10" s="1">
-        <v>100.0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" customHeight="1" spans="1:4">
       <c r="A11" s="1" t="s">
         <v>27</v>
       </c>
@@ -628,13 +1490,13 @@
         <v>28</v>
       </c>
       <c r="C11" s="1">
-        <v>100.0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" customHeight="1" spans="1:4">
       <c r="A12" s="1" t="s">
         <v>29</v>
       </c>
@@ -642,13 +1504,13 @@
         <v>30</v>
       </c>
       <c r="C12" s="1">
-        <v>100.0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" customHeight="1" spans="1:4">
       <c r="A13" s="1" t="s">
         <v>31</v>
       </c>
@@ -656,13 +1518,13 @@
         <v>32</v>
       </c>
       <c r="C13" s="1">
-        <v>100.0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" customHeight="1" spans="1:4">
       <c r="A14" s="1" t="s">
         <v>33</v>
       </c>
@@ -670,13 +1532,13 @@
         <v>34</v>
       </c>
       <c r="C14" s="1">
-        <v>100.0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" customHeight="1" spans="1:4">
       <c r="A15" s="1" t="s">
         <v>35</v>
       </c>
@@ -684,13 +1546,13 @@
         <v>36</v>
       </c>
       <c r="C15" s="1">
-        <v>100.0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" customHeight="1" spans="1:4">
       <c r="A16" s="1" t="s">
         <v>37</v>
       </c>
@@ -698,13 +1560,13 @@
         <v>38</v>
       </c>
       <c r="C16" s="1">
-        <v>100.0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" customHeight="1" spans="1:4">
       <c r="A17" s="1" t="s">
         <v>39</v>
       </c>
@@ -712,13 +1574,13 @@
         <v>40</v>
       </c>
       <c r="C17" s="1">
-        <v>100.0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" customHeight="1" spans="1:4">
       <c r="A18" s="1" t="s">
         <v>41</v>
       </c>
@@ -726,13 +1588,13 @@
         <v>42</v>
       </c>
       <c r="C18" s="1">
-        <v>100.0</v>
+        <v>1</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" customHeight="1" spans="1:4">
       <c r="A19" s="1" t="s">
         <v>43</v>
       </c>
@@ -740,13 +1602,13 @@
         <v>44</v>
       </c>
       <c r="C19" s="1">
-        <v>100.0</v>
+        <v>1</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" customHeight="1" spans="1:4">
       <c r="A20" s="1" t="s">
         <v>45</v>
       </c>
@@ -754,13 +1616,13 @@
         <v>46</v>
       </c>
       <c r="C20" s="1">
-        <v>100.0</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" customHeight="1" spans="1:4">
       <c r="A21" s="1" t="s">
         <v>47</v>
       </c>
@@ -768,13 +1630,13 @@
         <v>48</v>
       </c>
       <c r="C21" s="1">
-        <v>100.0</v>
+        <v>1</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" customHeight="1" spans="1:4">
       <c r="A22" s="1" t="s">
         <v>49</v>
       </c>
@@ -782,13 +1644,13 @@
         <v>50</v>
       </c>
       <c r="C22" s="1">
-        <v>100.0</v>
+        <v>1</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" customHeight="1" spans="1:4">
       <c r="A23" s="1" t="s">
         <v>51</v>
       </c>
@@ -796,13 +1658,13 @@
         <v>52</v>
       </c>
       <c r="C23" s="1">
-        <v>100.0</v>
+        <v>1</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" customHeight="1" spans="1:4">
       <c r="A24" s="1" t="s">
         <v>53</v>
       </c>
@@ -810,13 +1672,13 @@
         <v>54</v>
       </c>
       <c r="C24" s="1">
-        <v>100.0</v>
+        <v>1</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" customHeight="1" spans="1:4">
       <c r="A25" s="1" t="s">
         <v>55</v>
       </c>
@@ -824,13 +1686,13 @@
         <v>56</v>
       </c>
       <c r="C25" s="1">
-        <v>100.0</v>
+        <v>1</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" customHeight="1" spans="1:4">
       <c r="A26" s="1" t="s">
         <v>57</v>
       </c>
@@ -838,13 +1700,13 @@
         <v>58</v>
       </c>
       <c r="C26" s="1">
-        <v>100.0</v>
+        <v>1</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" customHeight="1" spans="1:4">
       <c r="A27" s="1" t="s">
         <v>59</v>
       </c>
@@ -852,13 +1714,13 @@
         <v>60</v>
       </c>
       <c r="C27" s="1">
-        <v>100.0</v>
+        <v>1</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" customHeight="1" spans="1:4">
       <c r="A28" s="1" t="s">
         <v>61</v>
       </c>
@@ -866,2929 +1728,2929 @@
         <v>62</v>
       </c>
       <c r="C28" s="1">
-        <v>100.0</v>
+        <v>1</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" customHeight="1" spans="1:4">
       <c r="D29" s="3"/>
     </row>
-    <row r="30">
+    <row r="30" customHeight="1" spans="1:4">
       <c r="D30" s="3"/>
     </row>
-    <row r="31">
+    <row r="31" customHeight="1" spans="1:4">
       <c r="D31" s="3"/>
     </row>
-    <row r="32">
+    <row r="32" customHeight="1" spans="1:4">
       <c r="D32" s="3"/>
     </row>
-    <row r="33">
+    <row r="33" customHeight="1" spans="4:4">
       <c r="D33" s="3"/>
     </row>
-    <row r="34">
+    <row r="34" customHeight="1" spans="4:4">
       <c r="D34" s="3"/>
     </row>
-    <row r="35">
+    <row r="35" customHeight="1" spans="4:4">
       <c r="D35" s="3"/>
     </row>
-    <row r="36">
+    <row r="36" customHeight="1" spans="4:4">
       <c r="D36" s="3"/>
     </row>
-    <row r="37">
+    <row r="37" customHeight="1" spans="4:4">
       <c r="D37" s="3"/>
     </row>
-    <row r="38">
+    <row r="38" customHeight="1" spans="4:4">
       <c r="D38" s="3"/>
     </row>
-    <row r="39">
+    <row r="39" customHeight="1" spans="4:4">
       <c r="D39" s="3"/>
     </row>
-    <row r="40">
+    <row r="40" customHeight="1" spans="4:4">
       <c r="D40" s="3"/>
     </row>
-    <row r="41">
+    <row r="41" customHeight="1" spans="4:4">
       <c r="D41" s="3"/>
     </row>
-    <row r="42">
+    <row r="42" customHeight="1" spans="4:4">
       <c r="D42" s="3"/>
     </row>
-    <row r="43">
+    <row r="43" customHeight="1" spans="4:4">
       <c r="D43" s="3"/>
     </row>
-    <row r="44">
+    <row r="44" customHeight="1" spans="4:4">
       <c r="D44" s="3"/>
     </row>
-    <row r="45">
+    <row r="45" customHeight="1" spans="4:4">
       <c r="D45" s="3"/>
     </row>
-    <row r="46">
+    <row r="46" customHeight="1" spans="4:4">
       <c r="D46" s="3"/>
     </row>
-    <row r="47">
+    <row r="47" customHeight="1" spans="4:4">
       <c r="D47" s="3"/>
     </row>
-    <row r="48">
+    <row r="48" customHeight="1" spans="4:4">
       <c r="D48" s="3"/>
     </row>
-    <row r="49">
+    <row r="49" customHeight="1" spans="4:4">
       <c r="D49" s="3"/>
     </row>
-    <row r="50">
+    <row r="50" customHeight="1" spans="4:4">
       <c r="D50" s="3"/>
     </row>
-    <row r="51">
+    <row r="51" customHeight="1" spans="4:4">
       <c r="D51" s="3"/>
     </row>
-    <row r="52">
+    <row r="52" customHeight="1" spans="4:4">
       <c r="D52" s="3"/>
     </row>
-    <row r="53">
+    <row r="53" customHeight="1" spans="4:4">
       <c r="D53" s="3"/>
     </row>
-    <row r="54">
+    <row r="54" customHeight="1" spans="4:4">
       <c r="D54" s="3"/>
     </row>
-    <row r="55">
+    <row r="55" customHeight="1" spans="4:4">
       <c r="D55" s="3"/>
     </row>
-    <row r="56">
+    <row r="56" customHeight="1" spans="4:4">
       <c r="D56" s="3"/>
     </row>
-    <row r="57">
+    <row r="57" customHeight="1" spans="4:4">
       <c r="D57" s="3"/>
     </row>
-    <row r="58">
+    <row r="58" customHeight="1" spans="4:4">
       <c r="D58" s="3"/>
     </row>
-    <row r="59">
+    <row r="59" customHeight="1" spans="4:4">
       <c r="D59" s="3"/>
     </row>
-    <row r="60">
+    <row r="60" customHeight="1" spans="4:4">
       <c r="D60" s="3"/>
     </row>
-    <row r="61">
+    <row r="61" customHeight="1" spans="4:4">
       <c r="D61" s="3"/>
     </row>
-    <row r="62">
+    <row r="62" customHeight="1" spans="4:4">
       <c r="D62" s="3"/>
     </row>
-    <row r="63">
+    <row r="63" customHeight="1" spans="4:4">
       <c r="D63" s="3"/>
     </row>
-    <row r="64">
+    <row r="64" customHeight="1" spans="4:4">
       <c r="D64" s="3"/>
     </row>
-    <row r="65">
+    <row r="65" customHeight="1" spans="4:4">
       <c r="D65" s="3"/>
     </row>
-    <row r="66">
+    <row r="66" customHeight="1" spans="4:4">
       <c r="D66" s="3"/>
     </row>
-    <row r="67">
+    <row r="67" customHeight="1" spans="4:4">
       <c r="D67" s="3"/>
     </row>
-    <row r="68">
+    <row r="68" customHeight="1" spans="4:4">
       <c r="D68" s="3"/>
     </row>
-    <row r="69">
+    <row r="69" customHeight="1" spans="4:4">
       <c r="D69" s="3"/>
     </row>
-    <row r="70">
+    <row r="70" customHeight="1" spans="4:4">
       <c r="D70" s="3"/>
     </row>
-    <row r="71">
+    <row r="71" customHeight="1" spans="4:4">
       <c r="D71" s="3"/>
     </row>
-    <row r="72">
+    <row r="72" customHeight="1" spans="4:4">
       <c r="D72" s="3"/>
     </row>
-    <row r="73">
+    <row r="73" customHeight="1" spans="4:4">
       <c r="D73" s="3"/>
     </row>
-    <row r="74">
+    <row r="74" customHeight="1" spans="4:4">
       <c r="D74" s="3"/>
     </row>
-    <row r="75">
+    <row r="75" customHeight="1" spans="4:4">
       <c r="D75" s="3"/>
     </row>
-    <row r="76">
+    <row r="76" customHeight="1" spans="4:4">
       <c r="D76" s="3"/>
     </row>
-    <row r="77">
+    <row r="77" customHeight="1" spans="4:4">
       <c r="D77" s="3"/>
     </row>
-    <row r="78">
+    <row r="78" customHeight="1" spans="4:4">
       <c r="D78" s="3"/>
     </row>
-    <row r="79">
+    <row r="79" customHeight="1" spans="4:4">
       <c r="D79" s="3"/>
     </row>
-    <row r="80">
+    <row r="80" customHeight="1" spans="4:4">
       <c r="D80" s="3"/>
     </row>
-    <row r="81">
+    <row r="81" customHeight="1" spans="4:4">
       <c r="D81" s="3"/>
     </row>
-    <row r="82">
+    <row r="82" customHeight="1" spans="4:4">
       <c r="D82" s="3"/>
     </row>
-    <row r="83">
+    <row r="83" customHeight="1" spans="4:4">
       <c r="D83" s="3"/>
     </row>
-    <row r="84">
+    <row r="84" customHeight="1" spans="4:4">
       <c r="D84" s="3"/>
     </row>
-    <row r="85">
+    <row r="85" customHeight="1" spans="4:4">
       <c r="D85" s="3"/>
     </row>
-    <row r="86">
+    <row r="86" customHeight="1" spans="4:4">
       <c r="D86" s="3"/>
     </row>
-    <row r="87">
+    <row r="87" customHeight="1" spans="4:4">
       <c r="D87" s="3"/>
     </row>
-    <row r="88">
+    <row r="88" customHeight="1" spans="4:4">
       <c r="D88" s="3"/>
     </row>
-    <row r="89">
+    <row r="89" customHeight="1" spans="4:4">
       <c r="D89" s="3"/>
     </row>
-    <row r="90">
+    <row r="90" customHeight="1" spans="4:4">
       <c r="D90" s="3"/>
     </row>
-    <row r="91">
+    <row r="91" customHeight="1" spans="4:4">
       <c r="D91" s="3"/>
     </row>
-    <row r="92">
+    <row r="92" customHeight="1" spans="4:4">
       <c r="D92" s="3"/>
     </row>
-    <row r="93">
+    <row r="93" customHeight="1" spans="4:4">
       <c r="D93" s="3"/>
     </row>
-    <row r="94">
+    <row r="94" customHeight="1" spans="4:4">
       <c r="D94" s="3"/>
     </row>
-    <row r="95">
+    <row r="95" customHeight="1" spans="4:4">
       <c r="D95" s="3"/>
     </row>
-    <row r="96">
+    <row r="96" customHeight="1" spans="4:4">
       <c r="D96" s="3"/>
     </row>
-    <row r="97">
+    <row r="97" customHeight="1" spans="4:4">
       <c r="D97" s="3"/>
     </row>
-    <row r="98">
+    <row r="98" customHeight="1" spans="4:4">
       <c r="D98" s="3"/>
     </row>
-    <row r="99">
+    <row r="99" customHeight="1" spans="4:4">
       <c r="D99" s="3"/>
     </row>
-    <row r="100">
+    <row r="100" customHeight="1" spans="4:4">
       <c r="D100" s="3"/>
     </row>
-    <row r="101">
+    <row r="101" customHeight="1" spans="4:4">
       <c r="D101" s="3"/>
     </row>
-    <row r="102">
+    <row r="102" customHeight="1" spans="4:4">
       <c r="D102" s="3"/>
     </row>
-    <row r="103">
+    <row r="103" customHeight="1" spans="4:4">
       <c r="D103" s="3"/>
     </row>
-    <row r="104">
+    <row r="104" customHeight="1" spans="4:4">
       <c r="D104" s="3"/>
     </row>
-    <row r="105">
+    <row r="105" customHeight="1" spans="4:4">
       <c r="D105" s="3"/>
     </row>
-    <row r="106">
+    <row r="106" customHeight="1" spans="4:4">
       <c r="D106" s="3"/>
     </row>
-    <row r="107">
+    <row r="107" customHeight="1" spans="4:4">
       <c r="D107" s="3"/>
     </row>
-    <row r="108">
+    <row r="108" customHeight="1" spans="4:4">
       <c r="D108" s="3"/>
     </row>
-    <row r="109">
+    <row r="109" customHeight="1" spans="4:4">
       <c r="D109" s="3"/>
     </row>
-    <row r="110">
+    <row r="110" customHeight="1" spans="4:4">
       <c r="D110" s="3"/>
     </row>
-    <row r="111">
+    <row r="111" customHeight="1" spans="4:4">
       <c r="D111" s="3"/>
     </row>
-    <row r="112">
+    <row r="112" customHeight="1" spans="4:4">
       <c r="D112" s="3"/>
     </row>
-    <row r="113">
+    <row r="113" customHeight="1" spans="4:4">
       <c r="D113" s="3"/>
     </row>
-    <row r="114">
+    <row r="114" customHeight="1" spans="4:4">
       <c r="D114" s="3"/>
     </row>
-    <row r="115">
+    <row r="115" customHeight="1" spans="4:4">
       <c r="D115" s="3"/>
     </row>
-    <row r="116">
+    <row r="116" customHeight="1" spans="4:4">
       <c r="D116" s="3"/>
     </row>
-    <row r="117">
+    <row r="117" customHeight="1" spans="4:4">
       <c r="D117" s="3"/>
     </row>
-    <row r="118">
+    <row r="118" customHeight="1" spans="4:4">
       <c r="D118" s="3"/>
     </row>
-    <row r="119">
+    <row r="119" customHeight="1" spans="4:4">
       <c r="D119" s="3"/>
     </row>
-    <row r="120">
+    <row r="120" customHeight="1" spans="4:4">
       <c r="D120" s="3"/>
     </row>
-    <row r="121">
+    <row r="121" customHeight="1" spans="4:4">
       <c r="D121" s="3"/>
     </row>
-    <row r="122">
+    <row r="122" customHeight="1" spans="4:4">
       <c r="D122" s="3"/>
     </row>
-    <row r="123">
+    <row r="123" customHeight="1" spans="4:4">
       <c r="D123" s="3"/>
     </row>
-    <row r="124">
+    <row r="124" customHeight="1" spans="4:4">
       <c r="D124" s="3"/>
     </row>
-    <row r="125">
+    <row r="125" customHeight="1" spans="4:4">
       <c r="D125" s="3"/>
     </row>
-    <row r="126">
+    <row r="126" customHeight="1" spans="4:4">
       <c r="D126" s="3"/>
     </row>
-    <row r="127">
+    <row r="127" customHeight="1" spans="4:4">
       <c r="D127" s="3"/>
     </row>
-    <row r="128">
+    <row r="128" customHeight="1" spans="4:4">
       <c r="D128" s="3"/>
     </row>
-    <row r="129">
+    <row r="129" customHeight="1" spans="4:4">
       <c r="D129" s="3"/>
     </row>
-    <row r="130">
+    <row r="130" customHeight="1" spans="4:4">
       <c r="D130" s="3"/>
     </row>
-    <row r="131">
+    <row r="131" customHeight="1" spans="4:4">
       <c r="D131" s="3"/>
     </row>
-    <row r="132">
+    <row r="132" customHeight="1" spans="4:4">
       <c r="D132" s="3"/>
     </row>
-    <row r="133">
+    <row r="133" customHeight="1" spans="4:4">
       <c r="D133" s="3"/>
     </row>
-    <row r="134">
+    <row r="134" customHeight="1" spans="4:4">
       <c r="D134" s="3"/>
     </row>
-    <row r="135">
+    <row r="135" customHeight="1" spans="4:4">
       <c r="D135" s="3"/>
     </row>
-    <row r="136">
+    <row r="136" customHeight="1" spans="4:4">
       <c r="D136" s="3"/>
     </row>
-    <row r="137">
+    <row r="137" customHeight="1" spans="4:4">
       <c r="D137" s="3"/>
     </row>
-    <row r="138">
+    <row r="138" customHeight="1" spans="4:4">
       <c r="D138" s="3"/>
     </row>
-    <row r="139">
+    <row r="139" customHeight="1" spans="4:4">
       <c r="D139" s="3"/>
     </row>
-    <row r="140">
+    <row r="140" customHeight="1" spans="4:4">
       <c r="D140" s="3"/>
     </row>
-    <row r="141">
+    <row r="141" customHeight="1" spans="4:4">
       <c r="D141" s="3"/>
     </row>
-    <row r="142">
+    <row r="142" customHeight="1" spans="4:4">
       <c r="D142" s="3"/>
     </row>
-    <row r="143">
+    <row r="143" customHeight="1" spans="4:4">
       <c r="D143" s="3"/>
     </row>
-    <row r="144">
+    <row r="144" customHeight="1" spans="4:4">
       <c r="D144" s="3"/>
     </row>
-    <row r="145">
+    <row r="145" customHeight="1" spans="4:4">
       <c r="D145" s="3"/>
     </row>
-    <row r="146">
+    <row r="146" customHeight="1" spans="4:4">
       <c r="D146" s="3"/>
     </row>
-    <row r="147">
+    <row r="147" customHeight="1" spans="4:4">
       <c r="D147" s="3"/>
     </row>
-    <row r="148">
+    <row r="148" customHeight="1" spans="4:4">
       <c r="D148" s="3"/>
     </row>
-    <row r="149">
+    <row r="149" customHeight="1" spans="4:4">
       <c r="D149" s="3"/>
     </row>
-    <row r="150">
+    <row r="150" customHeight="1" spans="4:4">
       <c r="D150" s="3"/>
     </row>
-    <row r="151">
+    <row r="151" customHeight="1" spans="4:4">
       <c r="D151" s="3"/>
     </row>
-    <row r="152">
+    <row r="152" customHeight="1" spans="4:4">
       <c r="D152" s="3"/>
     </row>
-    <row r="153">
+    <row r="153" customHeight="1" spans="4:4">
       <c r="D153" s="3"/>
     </row>
-    <row r="154">
+    <row r="154" customHeight="1" spans="4:4">
       <c r="D154" s="3"/>
     </row>
-    <row r="155">
+    <row r="155" customHeight="1" spans="4:4">
       <c r="D155" s="3"/>
     </row>
-    <row r="156">
+    <row r="156" customHeight="1" spans="4:4">
       <c r="D156" s="3"/>
     </row>
-    <row r="157">
+    <row r="157" customHeight="1" spans="4:4">
       <c r="D157" s="3"/>
     </row>
-    <row r="158">
+    <row r="158" customHeight="1" spans="4:4">
       <c r="D158" s="3"/>
     </row>
-    <row r="159">
+    <row r="159" customHeight="1" spans="4:4">
       <c r="D159" s="3"/>
     </row>
-    <row r="160">
+    <row r="160" customHeight="1" spans="4:4">
       <c r="D160" s="3"/>
     </row>
-    <row r="161">
+    <row r="161" customHeight="1" spans="4:4">
       <c r="D161" s="3"/>
     </row>
-    <row r="162">
+    <row r="162" customHeight="1" spans="4:4">
       <c r="D162" s="3"/>
     </row>
-    <row r="163">
+    <row r="163" customHeight="1" spans="4:4">
       <c r="D163" s="3"/>
     </row>
-    <row r="164">
+    <row r="164" customHeight="1" spans="4:4">
       <c r="D164" s="3"/>
     </row>
-    <row r="165">
+    <row r="165" customHeight="1" spans="4:4">
       <c r="D165" s="3"/>
     </row>
-    <row r="166">
+    <row r="166" customHeight="1" spans="4:4">
       <c r="D166" s="3"/>
     </row>
-    <row r="167">
+    <row r="167" customHeight="1" spans="4:4">
       <c r="D167" s="3"/>
     </row>
-    <row r="168">
+    <row r="168" customHeight="1" spans="4:4">
       <c r="D168" s="3"/>
     </row>
-    <row r="169">
+    <row r="169" customHeight="1" spans="4:4">
       <c r="D169" s="3"/>
     </row>
-    <row r="170">
+    <row r="170" customHeight="1" spans="4:4">
       <c r="D170" s="3"/>
     </row>
-    <row r="171">
+    <row r="171" customHeight="1" spans="4:4">
       <c r="D171" s="3"/>
     </row>
-    <row r="172">
+    <row r="172" customHeight="1" spans="4:4">
       <c r="D172" s="3"/>
     </row>
-    <row r="173">
+    <row r="173" customHeight="1" spans="4:4">
       <c r="D173" s="3"/>
     </row>
-    <row r="174">
+    <row r="174" customHeight="1" spans="4:4">
       <c r="D174" s="3"/>
     </row>
-    <row r="175">
+    <row r="175" customHeight="1" spans="4:4">
       <c r="D175" s="3"/>
     </row>
-    <row r="176">
+    <row r="176" customHeight="1" spans="4:4">
       <c r="D176" s="3"/>
     </row>
-    <row r="177">
+    <row r="177" customHeight="1" spans="4:4">
       <c r="D177" s="3"/>
     </row>
-    <row r="178">
+    <row r="178" customHeight="1" spans="4:4">
       <c r="D178" s="3"/>
     </row>
-    <row r="179">
+    <row r="179" customHeight="1" spans="4:4">
       <c r="D179" s="3"/>
     </row>
-    <row r="180">
+    <row r="180" customHeight="1" spans="4:4">
       <c r="D180" s="3"/>
     </row>
-    <row r="181">
+    <row r="181" customHeight="1" spans="4:4">
       <c r="D181" s="3"/>
     </row>
-    <row r="182">
+    <row r="182" customHeight="1" spans="4:4">
       <c r="D182" s="3"/>
     </row>
-    <row r="183">
+    <row r="183" customHeight="1" spans="4:4">
       <c r="D183" s="3"/>
     </row>
-    <row r="184">
+    <row r="184" customHeight="1" spans="4:4">
       <c r="D184" s="3"/>
     </row>
-    <row r="185">
+    <row r="185" customHeight="1" spans="4:4">
       <c r="D185" s="3"/>
     </row>
-    <row r="186">
+    <row r="186" customHeight="1" spans="4:4">
       <c r="D186" s="3"/>
     </row>
-    <row r="187">
+    <row r="187" customHeight="1" spans="4:4">
       <c r="D187" s="3"/>
     </row>
-    <row r="188">
+    <row r="188" customHeight="1" spans="4:4">
       <c r="D188" s="3"/>
     </row>
-    <row r="189">
+    <row r="189" customHeight="1" spans="4:4">
       <c r="D189" s="3"/>
     </row>
-    <row r="190">
+    <row r="190" customHeight="1" spans="4:4">
       <c r="D190" s="3"/>
     </row>
-    <row r="191">
+    <row r="191" customHeight="1" spans="4:4">
       <c r="D191" s="3"/>
     </row>
-    <row r="192">
+    <row r="192" customHeight="1" spans="4:4">
       <c r="D192" s="3"/>
     </row>
-    <row r="193">
+    <row r="193" customHeight="1" spans="4:4">
       <c r="D193" s="3"/>
     </row>
-    <row r="194">
+    <row r="194" customHeight="1" spans="4:4">
       <c r="D194" s="3"/>
     </row>
-    <row r="195">
+    <row r="195" customHeight="1" spans="4:4">
       <c r="D195" s="3"/>
     </row>
-    <row r="196">
+    <row r="196" customHeight="1" spans="4:4">
       <c r="D196" s="3"/>
     </row>
-    <row r="197">
+    <row r="197" customHeight="1" spans="4:4">
       <c r="D197" s="3"/>
     </row>
-    <row r="198">
+    <row r="198" customHeight="1" spans="4:4">
       <c r="D198" s="3"/>
     </row>
-    <row r="199">
+    <row r="199" customHeight="1" spans="4:4">
       <c r="D199" s="3"/>
     </row>
-    <row r="200">
+    <row r="200" customHeight="1" spans="4:4">
       <c r="D200" s="3"/>
     </row>
-    <row r="201">
+    <row r="201" customHeight="1" spans="4:4">
       <c r="D201" s="3"/>
     </row>
-    <row r="202">
+    <row r="202" customHeight="1" spans="4:4">
       <c r="D202" s="3"/>
     </row>
-    <row r="203">
+    <row r="203" customHeight="1" spans="4:4">
       <c r="D203" s="3"/>
     </row>
-    <row r="204">
+    <row r="204" customHeight="1" spans="4:4">
       <c r="D204" s="3"/>
     </row>
-    <row r="205">
+    <row r="205" customHeight="1" spans="4:4">
       <c r="D205" s="3"/>
     </row>
-    <row r="206">
+    <row r="206" customHeight="1" spans="4:4">
       <c r="D206" s="3"/>
     </row>
-    <row r="207">
+    <row r="207" customHeight="1" spans="4:4">
       <c r="D207" s="3"/>
     </row>
-    <row r="208">
+    <row r="208" customHeight="1" spans="4:4">
       <c r="D208" s="3"/>
     </row>
-    <row r="209">
+    <row r="209" customHeight="1" spans="4:4">
       <c r="D209" s="3"/>
     </row>
-    <row r="210">
+    <row r="210" customHeight="1" spans="4:4">
       <c r="D210" s="3"/>
     </row>
-    <row r="211">
+    <row r="211" customHeight="1" spans="4:4">
       <c r="D211" s="3"/>
     </row>
-    <row r="212">
+    <row r="212" customHeight="1" spans="4:4">
       <c r="D212" s="3"/>
     </row>
-    <row r="213">
+    <row r="213" customHeight="1" spans="4:4">
       <c r="D213" s="3"/>
     </row>
-    <row r="214">
+    <row r="214" customHeight="1" spans="4:4">
       <c r="D214" s="3"/>
     </row>
-    <row r="215">
+    <row r="215" customHeight="1" spans="4:4">
       <c r="D215" s="3"/>
     </row>
-    <row r="216">
+    <row r="216" customHeight="1" spans="4:4">
       <c r="D216" s="3"/>
     </row>
-    <row r="217">
+    <row r="217" customHeight="1" spans="4:4">
       <c r="D217" s="3"/>
     </row>
-    <row r="218">
+    <row r="218" customHeight="1" spans="4:4">
       <c r="D218" s="3"/>
     </row>
-    <row r="219">
+    <row r="219" customHeight="1" spans="4:4">
       <c r="D219" s="3"/>
     </row>
-    <row r="220">
+    <row r="220" customHeight="1" spans="4:4">
       <c r="D220" s="3"/>
     </row>
-    <row r="221">
+    <row r="221" customHeight="1" spans="4:4">
       <c r="D221" s="3"/>
     </row>
-    <row r="222">
+    <row r="222" customHeight="1" spans="4:4">
       <c r="D222" s="3"/>
     </row>
-    <row r="223">
+    <row r="223" customHeight="1" spans="4:4">
       <c r="D223" s="3"/>
     </row>
-    <row r="224">
+    <row r="224" customHeight="1" spans="4:4">
       <c r="D224" s="3"/>
     </row>
-    <row r="225">
+    <row r="225" customHeight="1" spans="4:4">
       <c r="D225" s="3"/>
     </row>
-    <row r="226">
+    <row r="226" customHeight="1" spans="4:4">
       <c r="D226" s="3"/>
     </row>
-    <row r="227">
+    <row r="227" customHeight="1" spans="4:4">
       <c r="D227" s="3"/>
     </row>
-    <row r="228">
+    <row r="228" customHeight="1" spans="4:4">
       <c r="D228" s="3"/>
     </row>
-    <row r="229">
+    <row r="229" customHeight="1" spans="4:4">
       <c r="D229" s="3"/>
     </row>
-    <row r="230">
+    <row r="230" customHeight="1" spans="4:4">
       <c r="D230" s="3"/>
     </row>
-    <row r="231">
+    <row r="231" customHeight="1" spans="4:4">
       <c r="D231" s="3"/>
     </row>
-    <row r="232">
+    <row r="232" customHeight="1" spans="4:4">
       <c r="D232" s="3"/>
     </row>
-    <row r="233">
+    <row r="233" customHeight="1" spans="4:4">
       <c r="D233" s="3"/>
     </row>
-    <row r="234">
+    <row r="234" customHeight="1" spans="4:4">
       <c r="D234" s="3"/>
     </row>
-    <row r="235">
+    <row r="235" customHeight="1" spans="4:4">
       <c r="D235" s="3"/>
     </row>
-    <row r="236">
+    <row r="236" customHeight="1" spans="4:4">
       <c r="D236" s="3"/>
     </row>
-    <row r="237">
+    <row r="237" customHeight="1" spans="4:4">
       <c r="D237" s="3"/>
     </row>
-    <row r="238">
+    <row r="238" customHeight="1" spans="4:4">
       <c r="D238" s="3"/>
     </row>
-    <row r="239">
+    <row r="239" customHeight="1" spans="4:4">
       <c r="D239" s="3"/>
     </row>
-    <row r="240">
+    <row r="240" customHeight="1" spans="4:4">
       <c r="D240" s="3"/>
     </row>
-    <row r="241">
+    <row r="241" customHeight="1" spans="4:4">
       <c r="D241" s="3"/>
     </row>
-    <row r="242">
+    <row r="242" customHeight="1" spans="4:4">
       <c r="D242" s="3"/>
     </row>
-    <row r="243">
+    <row r="243" customHeight="1" spans="4:4">
       <c r="D243" s="3"/>
     </row>
-    <row r="244">
+    <row r="244" customHeight="1" spans="4:4">
       <c r="D244" s="3"/>
     </row>
-    <row r="245">
+    <row r="245" customHeight="1" spans="4:4">
       <c r="D245" s="3"/>
     </row>
-    <row r="246">
+    <row r="246" customHeight="1" spans="4:4">
       <c r="D246" s="3"/>
     </row>
-    <row r="247">
+    <row r="247" customHeight="1" spans="4:4">
       <c r="D247" s="3"/>
     </row>
-    <row r="248">
+    <row r="248" customHeight="1" spans="4:4">
       <c r="D248" s="3"/>
     </row>
-    <row r="249">
+    <row r="249" customHeight="1" spans="4:4">
       <c r="D249" s="3"/>
     </row>
-    <row r="250">
+    <row r="250" customHeight="1" spans="4:4">
       <c r="D250" s="3"/>
     </row>
-    <row r="251">
+    <row r="251" customHeight="1" spans="4:4">
       <c r="D251" s="3"/>
     </row>
-    <row r="252">
+    <row r="252" customHeight="1" spans="4:4">
       <c r="D252" s="3"/>
     </row>
-    <row r="253">
+    <row r="253" customHeight="1" spans="4:4">
       <c r="D253" s="3"/>
     </row>
-    <row r="254">
+    <row r="254" customHeight="1" spans="4:4">
       <c r="D254" s="3"/>
     </row>
-    <row r="255">
+    <row r="255" customHeight="1" spans="4:4">
       <c r="D255" s="3"/>
     </row>
-    <row r="256">
+    <row r="256" customHeight="1" spans="4:4">
       <c r="D256" s="3"/>
     </row>
-    <row r="257">
+    <row r="257" customHeight="1" spans="4:4">
       <c r="D257" s="3"/>
     </row>
-    <row r="258">
+    <row r="258" customHeight="1" spans="4:4">
       <c r="D258" s="3"/>
     </row>
-    <row r="259">
+    <row r="259" customHeight="1" spans="4:4">
       <c r="D259" s="3"/>
     </row>
-    <row r="260">
+    <row r="260" customHeight="1" spans="4:4">
       <c r="D260" s="3"/>
     </row>
-    <row r="261">
+    <row r="261" customHeight="1" spans="4:4">
       <c r="D261" s="3"/>
     </row>
-    <row r="262">
+    <row r="262" customHeight="1" spans="4:4">
       <c r="D262" s="3"/>
     </row>
-    <row r="263">
+    <row r="263" customHeight="1" spans="4:4">
       <c r="D263" s="3"/>
     </row>
-    <row r="264">
+    <row r="264" customHeight="1" spans="4:4">
       <c r="D264" s="3"/>
     </row>
-    <row r="265">
+    <row r="265" customHeight="1" spans="4:4">
       <c r="D265" s="3"/>
     </row>
-    <row r="266">
+    <row r="266" customHeight="1" spans="4:4">
       <c r="D266" s="3"/>
     </row>
-    <row r="267">
+    <row r="267" customHeight="1" spans="4:4">
       <c r="D267" s="3"/>
     </row>
-    <row r="268">
+    <row r="268" customHeight="1" spans="4:4">
       <c r="D268" s="3"/>
     </row>
-    <row r="269">
+    <row r="269" customHeight="1" spans="4:4">
       <c r="D269" s="3"/>
     </row>
-    <row r="270">
+    <row r="270" customHeight="1" spans="4:4">
       <c r="D270" s="3"/>
     </row>
-    <row r="271">
+    <row r="271" customHeight="1" spans="4:4">
       <c r="D271" s="3"/>
     </row>
-    <row r="272">
+    <row r="272" customHeight="1" spans="4:4">
       <c r="D272" s="3"/>
     </row>
-    <row r="273">
+    <row r="273" customHeight="1" spans="4:4">
       <c r="D273" s="3"/>
     </row>
-    <row r="274">
+    <row r="274" customHeight="1" spans="4:4">
       <c r="D274" s="3"/>
     </row>
-    <row r="275">
+    <row r="275" customHeight="1" spans="4:4">
       <c r="D275" s="3"/>
     </row>
-    <row r="276">
+    <row r="276" customHeight="1" spans="4:4">
       <c r="D276" s="3"/>
     </row>
-    <row r="277">
+    <row r="277" customHeight="1" spans="4:4">
       <c r="D277" s="3"/>
     </row>
-    <row r="278">
+    <row r="278" customHeight="1" spans="4:4">
       <c r="D278" s="3"/>
     </row>
-    <row r="279">
+    <row r="279" customHeight="1" spans="4:4">
       <c r="D279" s="3"/>
     </row>
-    <row r="280">
+    <row r="280" customHeight="1" spans="4:4">
       <c r="D280" s="3"/>
     </row>
-    <row r="281">
+    <row r="281" customHeight="1" spans="4:4">
       <c r="D281" s="3"/>
     </row>
-    <row r="282">
+    <row r="282" customHeight="1" spans="4:4">
       <c r="D282" s="3"/>
     </row>
-    <row r="283">
+    <row r="283" customHeight="1" spans="4:4">
       <c r="D283" s="3"/>
     </row>
-    <row r="284">
+    <row r="284" customHeight="1" spans="4:4">
       <c r="D284" s="3"/>
     </row>
-    <row r="285">
+    <row r="285" customHeight="1" spans="4:4">
       <c r="D285" s="3"/>
     </row>
-    <row r="286">
+    <row r="286" customHeight="1" spans="4:4">
       <c r="D286" s="3"/>
     </row>
-    <row r="287">
+    <row r="287" customHeight="1" spans="4:4">
       <c r="D287" s="3"/>
     </row>
-    <row r="288">
+    <row r="288" customHeight="1" spans="4:4">
       <c r="D288" s="3"/>
     </row>
-    <row r="289">
+    <row r="289" customHeight="1" spans="4:4">
       <c r="D289" s="3"/>
     </row>
-    <row r="290">
+    <row r="290" customHeight="1" spans="4:4">
       <c r="D290" s="3"/>
     </row>
-    <row r="291">
+    <row r="291" customHeight="1" spans="4:4">
       <c r="D291" s="3"/>
     </row>
-    <row r="292">
+    <row r="292" customHeight="1" spans="4:4">
       <c r="D292" s="3"/>
     </row>
-    <row r="293">
+    <row r="293" customHeight="1" spans="4:4">
       <c r="D293" s="3"/>
     </row>
-    <row r="294">
+    <row r="294" customHeight="1" spans="4:4">
       <c r="D294" s="3"/>
     </row>
-    <row r="295">
+    <row r="295" customHeight="1" spans="4:4">
       <c r="D295" s="3"/>
     </row>
-    <row r="296">
+    <row r="296" customHeight="1" spans="4:4">
       <c r="D296" s="3"/>
     </row>
-    <row r="297">
+    <row r="297" customHeight="1" spans="4:4">
       <c r="D297" s="3"/>
     </row>
-    <row r="298">
+    <row r="298" customHeight="1" spans="4:4">
       <c r="D298" s="3"/>
     </row>
-    <row r="299">
+    <row r="299" customHeight="1" spans="4:4">
       <c r="D299" s="3"/>
     </row>
-    <row r="300">
+    <row r="300" customHeight="1" spans="4:4">
       <c r="D300" s="3"/>
     </row>
-    <row r="301">
+    <row r="301" customHeight="1" spans="4:4">
       <c r="D301" s="3"/>
     </row>
-    <row r="302">
+    <row r="302" customHeight="1" spans="4:4">
       <c r="D302" s="3"/>
     </row>
-    <row r="303">
+    <row r="303" customHeight="1" spans="4:4">
       <c r="D303" s="3"/>
     </row>
-    <row r="304">
+    <row r="304" customHeight="1" spans="4:4">
       <c r="D304" s="3"/>
     </row>
-    <row r="305">
+    <row r="305" customHeight="1" spans="4:4">
       <c r="D305" s="3"/>
     </row>
-    <row r="306">
+    <row r="306" customHeight="1" spans="4:4">
       <c r="D306" s="3"/>
     </row>
-    <row r="307">
+    <row r="307" customHeight="1" spans="4:4">
       <c r="D307" s="3"/>
     </row>
-    <row r="308">
+    <row r="308" customHeight="1" spans="4:4">
       <c r="D308" s="3"/>
     </row>
-    <row r="309">
+    <row r="309" customHeight="1" spans="4:4">
       <c r="D309" s="3"/>
     </row>
-    <row r="310">
+    <row r="310" customHeight="1" spans="4:4">
       <c r="D310" s="3"/>
     </row>
-    <row r="311">
+    <row r="311" customHeight="1" spans="4:4">
       <c r="D311" s="3"/>
     </row>
-    <row r="312">
+    <row r="312" customHeight="1" spans="4:4">
       <c r="D312" s="3"/>
     </row>
-    <row r="313">
+    <row r="313" customHeight="1" spans="4:4">
       <c r="D313" s="3"/>
     </row>
-    <row r="314">
+    <row r="314" customHeight="1" spans="4:4">
       <c r="D314" s="3"/>
     </row>
-    <row r="315">
+    <row r="315" customHeight="1" spans="4:4">
       <c r="D315" s="3"/>
     </row>
-    <row r="316">
+    <row r="316" customHeight="1" spans="4:4">
       <c r="D316" s="3"/>
     </row>
-    <row r="317">
+    <row r="317" customHeight="1" spans="4:4">
       <c r="D317" s="3"/>
     </row>
-    <row r="318">
+    <row r="318" customHeight="1" spans="4:4">
       <c r="D318" s="3"/>
     </row>
-    <row r="319">
+    <row r="319" customHeight="1" spans="4:4">
       <c r="D319" s="3"/>
     </row>
-    <row r="320">
+    <row r="320" customHeight="1" spans="4:4">
       <c r="D320" s="3"/>
     </row>
-    <row r="321">
+    <row r="321" customHeight="1" spans="4:4">
       <c r="D321" s="3"/>
     </row>
-    <row r="322">
+    <row r="322" customHeight="1" spans="4:4">
       <c r="D322" s="3"/>
     </row>
-    <row r="323">
+    <row r="323" customHeight="1" spans="4:4">
       <c r="D323" s="3"/>
     </row>
-    <row r="324">
+    <row r="324" customHeight="1" spans="4:4">
       <c r="D324" s="3"/>
     </row>
-    <row r="325">
+    <row r="325" customHeight="1" spans="4:4">
       <c r="D325" s="3"/>
     </row>
-    <row r="326">
+    <row r="326" customHeight="1" spans="4:4">
       <c r="D326" s="3"/>
     </row>
-    <row r="327">
+    <row r="327" customHeight="1" spans="4:4">
       <c r="D327" s="3"/>
     </row>
-    <row r="328">
+    <row r="328" customHeight="1" spans="4:4">
       <c r="D328" s="3"/>
     </row>
-    <row r="329">
+    <row r="329" customHeight="1" spans="4:4">
       <c r="D329" s="3"/>
     </row>
-    <row r="330">
+    <row r="330" customHeight="1" spans="4:4">
       <c r="D330" s="3"/>
     </row>
-    <row r="331">
+    <row r="331" customHeight="1" spans="4:4">
       <c r="D331" s="3"/>
     </row>
-    <row r="332">
+    <row r="332" customHeight="1" spans="4:4">
       <c r="D332" s="3"/>
     </row>
-    <row r="333">
+    <row r="333" customHeight="1" spans="4:4">
       <c r="D333" s="3"/>
     </row>
-    <row r="334">
+    <row r="334" customHeight="1" spans="4:4">
       <c r="D334" s="3"/>
     </row>
-    <row r="335">
+    <row r="335" customHeight="1" spans="4:4">
       <c r="D335" s="3"/>
     </row>
-    <row r="336">
+    <row r="336" customHeight="1" spans="4:4">
       <c r="D336" s="3"/>
     </row>
-    <row r="337">
+    <row r="337" customHeight="1" spans="4:4">
       <c r="D337" s="3"/>
     </row>
-    <row r="338">
+    <row r="338" customHeight="1" spans="4:4">
       <c r="D338" s="3"/>
     </row>
-    <row r="339">
+    <row r="339" customHeight="1" spans="4:4">
       <c r="D339" s="3"/>
     </row>
-    <row r="340">
+    <row r="340" customHeight="1" spans="4:4">
       <c r="D340" s="3"/>
     </row>
-    <row r="341">
+    <row r="341" customHeight="1" spans="4:4">
       <c r="D341" s="3"/>
     </row>
-    <row r="342">
+    <row r="342" customHeight="1" spans="4:4">
       <c r="D342" s="3"/>
     </row>
-    <row r="343">
+    <row r="343" customHeight="1" spans="4:4">
       <c r="D343" s="3"/>
     </row>
-    <row r="344">
+    <row r="344" customHeight="1" spans="4:4">
       <c r="D344" s="3"/>
     </row>
-    <row r="345">
+    <row r="345" customHeight="1" spans="4:4">
       <c r="D345" s="3"/>
     </row>
-    <row r="346">
+    <row r="346" customHeight="1" spans="4:4">
       <c r="D346" s="3"/>
     </row>
-    <row r="347">
+    <row r="347" customHeight="1" spans="4:4">
       <c r="D347" s="3"/>
     </row>
-    <row r="348">
+    <row r="348" customHeight="1" spans="4:4">
       <c r="D348" s="3"/>
     </row>
-    <row r="349">
+    <row r="349" customHeight="1" spans="4:4">
       <c r="D349" s="3"/>
     </row>
-    <row r="350">
+    <row r="350" customHeight="1" spans="4:4">
       <c r="D350" s="3"/>
     </row>
-    <row r="351">
+    <row r="351" customHeight="1" spans="4:4">
       <c r="D351" s="3"/>
     </row>
-    <row r="352">
+    <row r="352" customHeight="1" spans="4:4">
       <c r="D352" s="3"/>
     </row>
-    <row r="353">
+    <row r="353" customHeight="1" spans="4:4">
       <c r="D353" s="3"/>
     </row>
-    <row r="354">
+    <row r="354" customHeight="1" spans="4:4">
       <c r="D354" s="3"/>
     </row>
-    <row r="355">
+    <row r="355" customHeight="1" spans="4:4">
       <c r="D355" s="3"/>
     </row>
-    <row r="356">
+    <row r="356" customHeight="1" spans="4:4">
       <c r="D356" s="3"/>
     </row>
-    <row r="357">
+    <row r="357" customHeight="1" spans="4:4">
       <c r="D357" s="3"/>
     </row>
-    <row r="358">
+    <row r="358" customHeight="1" spans="4:4">
       <c r="D358" s="3"/>
     </row>
-    <row r="359">
+    <row r="359" customHeight="1" spans="4:4">
       <c r="D359" s="3"/>
     </row>
-    <row r="360">
+    <row r="360" customHeight="1" spans="4:4">
       <c r="D360" s="3"/>
     </row>
-    <row r="361">
+    <row r="361" customHeight="1" spans="4:4">
       <c r="D361" s="3"/>
     </row>
-    <row r="362">
+    <row r="362" customHeight="1" spans="4:4">
       <c r="D362" s="3"/>
     </row>
-    <row r="363">
+    <row r="363" customHeight="1" spans="4:4">
       <c r="D363" s="3"/>
     </row>
-    <row r="364">
+    <row r="364" customHeight="1" spans="4:4">
       <c r="D364" s="3"/>
     </row>
-    <row r="365">
+    <row r="365" customHeight="1" spans="4:4">
       <c r="D365" s="3"/>
     </row>
-    <row r="366">
+    <row r="366" customHeight="1" spans="4:4">
       <c r="D366" s="3"/>
     </row>
-    <row r="367">
+    <row r="367" customHeight="1" spans="4:4">
       <c r="D367" s="3"/>
     </row>
-    <row r="368">
+    <row r="368" customHeight="1" spans="4:4">
       <c r="D368" s="3"/>
     </row>
-    <row r="369">
+    <row r="369" customHeight="1" spans="4:4">
       <c r="D369" s="3"/>
     </row>
-    <row r="370">
+    <row r="370" customHeight="1" spans="4:4">
       <c r="D370" s="3"/>
     </row>
-    <row r="371">
+    <row r="371" customHeight="1" spans="4:4">
       <c r="D371" s="3"/>
     </row>
-    <row r="372">
+    <row r="372" customHeight="1" spans="4:4">
       <c r="D372" s="3"/>
     </row>
-    <row r="373">
+    <row r="373" customHeight="1" spans="4:4">
       <c r="D373" s="3"/>
     </row>
-    <row r="374">
+    <row r="374" customHeight="1" spans="4:4">
       <c r="D374" s="3"/>
     </row>
-    <row r="375">
+    <row r="375" customHeight="1" spans="4:4">
       <c r="D375" s="3"/>
     </row>
-    <row r="376">
+    <row r="376" customHeight="1" spans="4:4">
       <c r="D376" s="3"/>
     </row>
-    <row r="377">
+    <row r="377" customHeight="1" spans="4:4">
       <c r="D377" s="3"/>
     </row>
-    <row r="378">
+    <row r="378" customHeight="1" spans="4:4">
       <c r="D378" s="3"/>
     </row>
-    <row r="379">
+    <row r="379" customHeight="1" spans="4:4">
       <c r="D379" s="3"/>
     </row>
-    <row r="380">
+    <row r="380" customHeight="1" spans="4:4">
       <c r="D380" s="3"/>
     </row>
-    <row r="381">
+    <row r="381" customHeight="1" spans="4:4">
       <c r="D381" s="3"/>
     </row>
-    <row r="382">
+    <row r="382" customHeight="1" spans="4:4">
       <c r="D382" s="3"/>
     </row>
-    <row r="383">
+    <row r="383" customHeight="1" spans="4:4">
       <c r="D383" s="3"/>
     </row>
-    <row r="384">
+    <row r="384" customHeight="1" spans="4:4">
       <c r="D384" s="3"/>
     </row>
-    <row r="385">
+    <row r="385" customHeight="1" spans="4:4">
       <c r="D385" s="3"/>
     </row>
-    <row r="386">
+    <row r="386" customHeight="1" spans="4:4">
       <c r="D386" s="3"/>
     </row>
-    <row r="387">
+    <row r="387" customHeight="1" spans="4:4">
       <c r="D387" s="3"/>
     </row>
-    <row r="388">
+    <row r="388" customHeight="1" spans="4:4">
       <c r="D388" s="3"/>
     </row>
-    <row r="389">
+    <row r="389" customHeight="1" spans="4:4">
       <c r="D389" s="3"/>
     </row>
-    <row r="390">
+    <row r="390" customHeight="1" spans="4:4">
       <c r="D390" s="3"/>
     </row>
-    <row r="391">
+    <row r="391" customHeight="1" spans="4:4">
       <c r="D391" s="3"/>
     </row>
-    <row r="392">
+    <row r="392" customHeight="1" spans="4:4">
       <c r="D392" s="3"/>
     </row>
-    <row r="393">
+    <row r="393" customHeight="1" spans="4:4">
       <c r="D393" s="3"/>
     </row>
-    <row r="394">
+    <row r="394" customHeight="1" spans="4:4">
       <c r="D394" s="3"/>
     </row>
-    <row r="395">
+    <row r="395" customHeight="1" spans="4:4">
       <c r="D395" s="3"/>
     </row>
-    <row r="396">
+    <row r="396" customHeight="1" spans="4:4">
       <c r="D396" s="3"/>
     </row>
-    <row r="397">
+    <row r="397" customHeight="1" spans="4:4">
       <c r="D397" s="3"/>
     </row>
-    <row r="398">
+    <row r="398" customHeight="1" spans="4:4">
       <c r="D398" s="3"/>
     </row>
-    <row r="399">
+    <row r="399" customHeight="1" spans="4:4">
       <c r="D399" s="3"/>
     </row>
-    <row r="400">
+    <row r="400" customHeight="1" spans="4:4">
       <c r="D400" s="3"/>
     </row>
-    <row r="401">
+    <row r="401" customHeight="1" spans="4:4">
       <c r="D401" s="3"/>
     </row>
-    <row r="402">
+    <row r="402" customHeight="1" spans="4:4">
       <c r="D402" s="3"/>
     </row>
-    <row r="403">
+    <row r="403" customHeight="1" spans="4:4">
       <c r="D403" s="3"/>
     </row>
-    <row r="404">
+    <row r="404" customHeight="1" spans="4:4">
       <c r="D404" s="3"/>
     </row>
-    <row r="405">
+    <row r="405" customHeight="1" spans="4:4">
       <c r="D405" s="3"/>
     </row>
-    <row r="406">
+    <row r="406" customHeight="1" spans="4:4">
       <c r="D406" s="3"/>
     </row>
-    <row r="407">
+    <row r="407" customHeight="1" spans="4:4">
       <c r="D407" s="3"/>
     </row>
-    <row r="408">
+    <row r="408" customHeight="1" spans="4:4">
       <c r="D408" s="3"/>
     </row>
-    <row r="409">
+    <row r="409" customHeight="1" spans="4:4">
       <c r="D409" s="3"/>
     </row>
-    <row r="410">
+    <row r="410" customHeight="1" spans="4:4">
       <c r="D410" s="3"/>
     </row>
-    <row r="411">
+    <row r="411" customHeight="1" spans="4:4">
       <c r="D411" s="3"/>
     </row>
-    <row r="412">
+    <row r="412" customHeight="1" spans="4:4">
       <c r="D412" s="3"/>
     </row>
-    <row r="413">
+    <row r="413" customHeight="1" spans="4:4">
       <c r="D413" s="3"/>
     </row>
-    <row r="414">
+    <row r="414" customHeight="1" spans="4:4">
       <c r="D414" s="3"/>
     </row>
-    <row r="415">
+    <row r="415" customHeight="1" spans="4:4">
       <c r="D415" s="3"/>
     </row>
-    <row r="416">
+    <row r="416" customHeight="1" spans="4:4">
       <c r="D416" s="3"/>
     </row>
-    <row r="417">
+    <row r="417" customHeight="1" spans="4:4">
       <c r="D417" s="3"/>
     </row>
-    <row r="418">
+    <row r="418" customHeight="1" spans="4:4">
       <c r="D418" s="3"/>
     </row>
-    <row r="419">
+    <row r="419" customHeight="1" spans="4:4">
       <c r="D419" s="3"/>
     </row>
-    <row r="420">
+    <row r="420" customHeight="1" spans="4:4">
       <c r="D420" s="3"/>
     </row>
-    <row r="421">
+    <row r="421" customHeight="1" spans="4:4">
       <c r="D421" s="3"/>
     </row>
-    <row r="422">
+    <row r="422" customHeight="1" spans="4:4">
       <c r="D422" s="3"/>
     </row>
-    <row r="423">
+    <row r="423" customHeight="1" spans="4:4">
       <c r="D423" s="3"/>
     </row>
-    <row r="424">
+    <row r="424" customHeight="1" spans="4:4">
       <c r="D424" s="3"/>
     </row>
-    <row r="425">
+    <row r="425" customHeight="1" spans="4:4">
       <c r="D425" s="3"/>
     </row>
-    <row r="426">
+    <row r="426" customHeight="1" spans="4:4">
       <c r="D426" s="3"/>
     </row>
-    <row r="427">
+    <row r="427" customHeight="1" spans="4:4">
       <c r="D427" s="3"/>
     </row>
-    <row r="428">
+    <row r="428" customHeight="1" spans="4:4">
       <c r="D428" s="3"/>
     </row>
-    <row r="429">
+    <row r="429" customHeight="1" spans="4:4">
       <c r="D429" s="3"/>
     </row>
-    <row r="430">
+    <row r="430" customHeight="1" spans="4:4">
       <c r="D430" s="3"/>
     </row>
-    <row r="431">
+    <row r="431" customHeight="1" spans="4:4">
       <c r="D431" s="3"/>
     </row>
-    <row r="432">
+    <row r="432" customHeight="1" spans="4:4">
       <c r="D432" s="3"/>
     </row>
-    <row r="433">
+    <row r="433" customHeight="1" spans="4:4">
       <c r="D433" s="3"/>
     </row>
-    <row r="434">
+    <row r="434" customHeight="1" spans="4:4">
       <c r="D434" s="3"/>
     </row>
-    <row r="435">
+    <row r="435" customHeight="1" spans="4:4">
       <c r="D435" s="3"/>
     </row>
-    <row r="436">
+    <row r="436" customHeight="1" spans="4:4">
       <c r="D436" s="3"/>
     </row>
-    <row r="437">
+    <row r="437" customHeight="1" spans="4:4">
       <c r="D437" s="3"/>
     </row>
-    <row r="438">
+    <row r="438" customHeight="1" spans="4:4">
       <c r="D438" s="3"/>
     </row>
-    <row r="439">
+    <row r="439" customHeight="1" spans="4:4">
       <c r="D439" s="3"/>
     </row>
-    <row r="440">
+    <row r="440" customHeight="1" spans="4:4">
       <c r="D440" s="3"/>
     </row>
-    <row r="441">
+    <row r="441" customHeight="1" spans="4:4">
       <c r="D441" s="3"/>
     </row>
-    <row r="442">
+    <row r="442" customHeight="1" spans="4:4">
       <c r="D442" s="3"/>
     </row>
-    <row r="443">
+    <row r="443" customHeight="1" spans="4:4">
       <c r="D443" s="3"/>
     </row>
-    <row r="444">
+    <row r="444" customHeight="1" spans="4:4">
       <c r="D444" s="3"/>
     </row>
-    <row r="445">
+    <row r="445" customHeight="1" spans="4:4">
       <c r="D445" s="3"/>
     </row>
-    <row r="446">
+    <row r="446" customHeight="1" spans="4:4">
       <c r="D446" s="3"/>
     </row>
-    <row r="447">
+    <row r="447" customHeight="1" spans="4:4">
       <c r="D447" s="3"/>
     </row>
-    <row r="448">
+    <row r="448" customHeight="1" spans="4:4">
       <c r="D448" s="3"/>
     </row>
-    <row r="449">
+    <row r="449" customHeight="1" spans="4:4">
       <c r="D449" s="3"/>
     </row>
-    <row r="450">
+    <row r="450" customHeight="1" spans="4:4">
       <c r="D450" s="3"/>
     </row>
-    <row r="451">
+    <row r="451" customHeight="1" spans="4:4">
       <c r="D451" s="3"/>
     </row>
-    <row r="452">
+    <row r="452" customHeight="1" spans="4:4">
       <c r="D452" s="3"/>
     </row>
-    <row r="453">
+    <row r="453" customHeight="1" spans="4:4">
       <c r="D453" s="3"/>
     </row>
-    <row r="454">
+    <row r="454" customHeight="1" spans="4:4">
       <c r="D454" s="3"/>
     </row>
-    <row r="455">
+    <row r="455" customHeight="1" spans="4:4">
       <c r="D455" s="3"/>
     </row>
-    <row r="456">
+    <row r="456" customHeight="1" spans="4:4">
       <c r="D456" s="3"/>
     </row>
-    <row r="457">
+    <row r="457" customHeight="1" spans="4:4">
       <c r="D457" s="3"/>
     </row>
-    <row r="458">
+    <row r="458" customHeight="1" spans="4:4">
       <c r="D458" s="3"/>
     </row>
-    <row r="459">
+    <row r="459" customHeight="1" spans="4:4">
       <c r="D459" s="3"/>
     </row>
-    <row r="460">
+    <row r="460" customHeight="1" spans="4:4">
       <c r="D460" s="3"/>
     </row>
-    <row r="461">
+    <row r="461" customHeight="1" spans="4:4">
       <c r="D461" s="3"/>
     </row>
-    <row r="462">
+    <row r="462" customHeight="1" spans="4:4">
       <c r="D462" s="3"/>
     </row>
-    <row r="463">
+    <row r="463" customHeight="1" spans="4:4">
       <c r="D463" s="3"/>
     </row>
-    <row r="464">
+    <row r="464" customHeight="1" spans="4:4">
       <c r="D464" s="3"/>
     </row>
-    <row r="465">
+    <row r="465" customHeight="1" spans="4:4">
       <c r="D465" s="3"/>
     </row>
-    <row r="466">
+    <row r="466" customHeight="1" spans="4:4">
       <c r="D466" s="3"/>
     </row>
-    <row r="467">
+    <row r="467" customHeight="1" spans="4:4">
       <c r="D467" s="3"/>
     </row>
-    <row r="468">
+    <row r="468" customHeight="1" spans="4:4">
       <c r="D468" s="3"/>
     </row>
-    <row r="469">
+    <row r="469" customHeight="1" spans="4:4">
       <c r="D469" s="3"/>
     </row>
-    <row r="470">
+    <row r="470" customHeight="1" spans="4:4">
       <c r="D470" s="3"/>
     </row>
-    <row r="471">
+    <row r="471" customHeight="1" spans="4:4">
       <c r="D471" s="3"/>
     </row>
-    <row r="472">
+    <row r="472" customHeight="1" spans="4:4">
       <c r="D472" s="3"/>
     </row>
-    <row r="473">
+    <row r="473" customHeight="1" spans="4:4">
       <c r="D473" s="3"/>
     </row>
-    <row r="474">
+    <row r="474" customHeight="1" spans="4:4">
       <c r="D474" s="3"/>
     </row>
-    <row r="475">
+    <row r="475" customHeight="1" spans="4:4">
       <c r="D475" s="3"/>
     </row>
-    <row r="476">
+    <row r="476" customHeight="1" spans="4:4">
       <c r="D476" s="3"/>
     </row>
-    <row r="477">
+    <row r="477" customHeight="1" spans="4:4">
       <c r="D477" s="3"/>
     </row>
-    <row r="478">
+    <row r="478" customHeight="1" spans="4:4">
       <c r="D478" s="3"/>
     </row>
-    <row r="479">
+    <row r="479" customHeight="1" spans="4:4">
       <c r="D479" s="3"/>
     </row>
-    <row r="480">
+    <row r="480" customHeight="1" spans="4:4">
       <c r="D480" s="3"/>
     </row>
-    <row r="481">
+    <row r="481" customHeight="1" spans="4:4">
       <c r="D481" s="3"/>
     </row>
-    <row r="482">
+    <row r="482" customHeight="1" spans="4:4">
       <c r="D482" s="3"/>
     </row>
-    <row r="483">
+    <row r="483" customHeight="1" spans="4:4">
       <c r="D483" s="3"/>
     </row>
-    <row r="484">
+    <row r="484" customHeight="1" spans="4:4">
       <c r="D484" s="3"/>
     </row>
-    <row r="485">
+    <row r="485" customHeight="1" spans="4:4">
       <c r="D485" s="3"/>
     </row>
-    <row r="486">
+    <row r="486" customHeight="1" spans="4:4">
       <c r="D486" s="3"/>
     </row>
-    <row r="487">
+    <row r="487" customHeight="1" spans="4:4">
       <c r="D487" s="3"/>
     </row>
-    <row r="488">
+    <row r="488" customHeight="1" spans="4:4">
       <c r="D488" s="3"/>
     </row>
-    <row r="489">
+    <row r="489" customHeight="1" spans="4:4">
       <c r="D489" s="3"/>
     </row>
-    <row r="490">
+    <row r="490" customHeight="1" spans="4:4">
       <c r="D490" s="3"/>
     </row>
-    <row r="491">
+    <row r="491" customHeight="1" spans="4:4">
       <c r="D491" s="3"/>
     </row>
-    <row r="492">
+    <row r="492" customHeight="1" spans="4:4">
       <c r="D492" s="3"/>
     </row>
-    <row r="493">
+    <row r="493" customHeight="1" spans="4:4">
       <c r="D493" s="3"/>
     </row>
-    <row r="494">
+    <row r="494" customHeight="1" spans="4:4">
       <c r="D494" s="3"/>
     </row>
-    <row r="495">
+    <row r="495" customHeight="1" spans="4:4">
       <c r="D495" s="3"/>
     </row>
-    <row r="496">
+    <row r="496" customHeight="1" spans="4:4">
       <c r="D496" s="3"/>
     </row>
-    <row r="497">
+    <row r="497" customHeight="1" spans="4:4">
       <c r="D497" s="3"/>
     </row>
-    <row r="498">
+    <row r="498" customHeight="1" spans="4:4">
       <c r="D498" s="3"/>
     </row>
-    <row r="499">
+    <row r="499" customHeight="1" spans="4:4">
       <c r="D499" s="3"/>
     </row>
-    <row r="500">
+    <row r="500" customHeight="1" spans="4:4">
       <c r="D500" s="3"/>
     </row>
-    <row r="501">
+    <row r="501" customHeight="1" spans="4:4">
       <c r="D501" s="3"/>
     </row>
-    <row r="502">
+    <row r="502" customHeight="1" spans="4:4">
       <c r="D502" s="3"/>
     </row>
-    <row r="503">
+    <row r="503" customHeight="1" spans="4:4">
       <c r="D503" s="3"/>
     </row>
-    <row r="504">
+    <row r="504" customHeight="1" spans="4:4">
       <c r="D504" s="3"/>
     </row>
-    <row r="505">
+    <row r="505" customHeight="1" spans="4:4">
       <c r="D505" s="3"/>
     </row>
-    <row r="506">
+    <row r="506" customHeight="1" spans="4:4">
       <c r="D506" s="3"/>
     </row>
-    <row r="507">
+    <row r="507" customHeight="1" spans="4:4">
       <c r="D507" s="3"/>
     </row>
-    <row r="508">
+    <row r="508" customHeight="1" spans="4:4">
       <c r="D508" s="3"/>
     </row>
-    <row r="509">
+    <row r="509" customHeight="1" spans="4:4">
       <c r="D509" s="3"/>
     </row>
-    <row r="510">
+    <row r="510" customHeight="1" spans="4:4">
       <c r="D510" s="3"/>
     </row>
-    <row r="511">
+    <row r="511" customHeight="1" spans="4:4">
       <c r="D511" s="3"/>
     </row>
-    <row r="512">
+    <row r="512" customHeight="1" spans="4:4">
       <c r="D512" s="3"/>
     </row>
-    <row r="513">
+    <row r="513" customHeight="1" spans="4:4">
       <c r="D513" s="3"/>
     </row>
-    <row r="514">
+    <row r="514" customHeight="1" spans="4:4">
       <c r="D514" s="3"/>
     </row>
-    <row r="515">
+    <row r="515" customHeight="1" spans="4:4">
       <c r="D515" s="3"/>
     </row>
-    <row r="516">
+    <row r="516" customHeight="1" spans="4:4">
       <c r="D516" s="3"/>
     </row>
-    <row r="517">
+    <row r="517" customHeight="1" spans="4:4">
       <c r="D517" s="3"/>
     </row>
-    <row r="518">
+    <row r="518" customHeight="1" spans="4:4">
       <c r="D518" s="3"/>
     </row>
-    <row r="519">
+    <row r="519" customHeight="1" spans="4:4">
       <c r="D519" s="3"/>
     </row>
-    <row r="520">
+    <row r="520" customHeight="1" spans="4:4">
       <c r="D520" s="3"/>
     </row>
-    <row r="521">
+    <row r="521" customHeight="1" spans="4:4">
       <c r="D521" s="3"/>
     </row>
-    <row r="522">
+    <row r="522" customHeight="1" spans="4:4">
       <c r="D522" s="3"/>
     </row>
-    <row r="523">
+    <row r="523" customHeight="1" spans="4:4">
       <c r="D523" s="3"/>
     </row>
-    <row r="524">
+    <row r="524" customHeight="1" spans="4:4">
       <c r="D524" s="3"/>
     </row>
-    <row r="525">
+    <row r="525" customHeight="1" spans="4:4">
       <c r="D525" s="3"/>
     </row>
-    <row r="526">
+    <row r="526" customHeight="1" spans="4:4">
       <c r="D526" s="3"/>
     </row>
-    <row r="527">
+    <row r="527" customHeight="1" spans="4:4">
       <c r="D527" s="3"/>
     </row>
-    <row r="528">
+    <row r="528" customHeight="1" spans="4:4">
       <c r="D528" s="3"/>
     </row>
-    <row r="529">
+    <row r="529" customHeight="1" spans="4:4">
       <c r="D529" s="3"/>
     </row>
-    <row r="530">
+    <row r="530" customHeight="1" spans="4:4">
       <c r="D530" s="3"/>
     </row>
-    <row r="531">
+    <row r="531" customHeight="1" spans="4:4">
       <c r="D531" s="3"/>
     </row>
-    <row r="532">
+    <row r="532" customHeight="1" spans="4:4">
       <c r="D532" s="3"/>
     </row>
-    <row r="533">
+    <row r="533" customHeight="1" spans="4:4">
       <c r="D533" s="3"/>
     </row>
-    <row r="534">
+    <row r="534" customHeight="1" spans="4:4">
       <c r="D534" s="3"/>
     </row>
-    <row r="535">
+    <row r="535" customHeight="1" spans="4:4">
       <c r="D535" s="3"/>
     </row>
-    <row r="536">
+    <row r="536" customHeight="1" spans="4:4">
       <c r="D536" s="3"/>
     </row>
-    <row r="537">
+    <row r="537" customHeight="1" spans="4:4">
       <c r="D537" s="3"/>
     </row>
-    <row r="538">
+    <row r="538" customHeight="1" spans="4:4">
       <c r="D538" s="3"/>
     </row>
-    <row r="539">
+    <row r="539" customHeight="1" spans="4:4">
       <c r="D539" s="3"/>
     </row>
-    <row r="540">
+    <row r="540" customHeight="1" spans="4:4">
       <c r="D540" s="3"/>
     </row>
-    <row r="541">
+    <row r="541" customHeight="1" spans="4:4">
       <c r="D541" s="3"/>
     </row>
-    <row r="542">
+    <row r="542" customHeight="1" spans="4:4">
       <c r="D542" s="3"/>
     </row>
-    <row r="543">
+    <row r="543" customHeight="1" spans="4:4">
       <c r="D543" s="3"/>
     </row>
-    <row r="544">
+    <row r="544" customHeight="1" spans="4:4">
       <c r="D544" s="3"/>
     </row>
-    <row r="545">
+    <row r="545" customHeight="1" spans="4:4">
       <c r="D545" s="3"/>
     </row>
-    <row r="546">
+    <row r="546" customHeight="1" spans="4:4">
       <c r="D546" s="3"/>
     </row>
-    <row r="547">
+    <row r="547" customHeight="1" spans="4:4">
       <c r="D547" s="3"/>
     </row>
-    <row r="548">
+    <row r="548" customHeight="1" spans="4:4">
       <c r="D548" s="3"/>
     </row>
-    <row r="549">
+    <row r="549" customHeight="1" spans="4:4">
       <c r="D549" s="3"/>
     </row>
-    <row r="550">
+    <row r="550" customHeight="1" spans="4:4">
       <c r="D550" s="3"/>
     </row>
-    <row r="551">
+    <row r="551" customHeight="1" spans="4:4">
       <c r="D551" s="3"/>
     </row>
-    <row r="552">
+    <row r="552" customHeight="1" spans="4:4">
       <c r="D552" s="3"/>
     </row>
-    <row r="553">
+    <row r="553" customHeight="1" spans="4:4">
       <c r="D553" s="3"/>
     </row>
-    <row r="554">
+    <row r="554" customHeight="1" spans="4:4">
       <c r="D554" s="3"/>
     </row>
-    <row r="555">
+    <row r="555" customHeight="1" spans="4:4">
       <c r="D555" s="3"/>
     </row>
-    <row r="556">
+    <row r="556" customHeight="1" spans="4:4">
       <c r="D556" s="3"/>
     </row>
-    <row r="557">
+    <row r="557" customHeight="1" spans="4:4">
       <c r="D557" s="3"/>
     </row>
-    <row r="558">
+    <row r="558" customHeight="1" spans="4:4">
       <c r="D558" s="3"/>
     </row>
-    <row r="559">
+    <row r="559" customHeight="1" spans="4:4">
       <c r="D559" s="3"/>
     </row>
-    <row r="560">
+    <row r="560" customHeight="1" spans="4:4">
       <c r="D560" s="3"/>
     </row>
-    <row r="561">
+    <row r="561" customHeight="1" spans="4:4">
       <c r="D561" s="3"/>
     </row>
-    <row r="562">
+    <row r="562" customHeight="1" spans="4:4">
       <c r="D562" s="3"/>
     </row>
-    <row r="563">
+    <row r="563" customHeight="1" spans="4:4">
       <c r="D563" s="3"/>
     </row>
-    <row r="564">
+    <row r="564" customHeight="1" spans="4:4">
       <c r="D564" s="3"/>
     </row>
-    <row r="565">
+    <row r="565" customHeight="1" spans="4:4">
       <c r="D565" s="3"/>
     </row>
-    <row r="566">
+    <row r="566" customHeight="1" spans="4:4">
       <c r="D566" s="3"/>
     </row>
-    <row r="567">
+    <row r="567" customHeight="1" spans="4:4">
       <c r="D567" s="3"/>
     </row>
-    <row r="568">
+    <row r="568" customHeight="1" spans="4:4">
       <c r="D568" s="3"/>
     </row>
-    <row r="569">
+    <row r="569" customHeight="1" spans="4:4">
       <c r="D569" s="3"/>
     </row>
-    <row r="570">
+    <row r="570" customHeight="1" spans="4:4">
       <c r="D570" s="3"/>
     </row>
-    <row r="571">
+    <row r="571" customHeight="1" spans="4:4">
       <c r="D571" s="3"/>
     </row>
-    <row r="572">
+    <row r="572" customHeight="1" spans="4:4">
       <c r="D572" s="3"/>
     </row>
-    <row r="573">
+    <row r="573" customHeight="1" spans="4:4">
       <c r="D573" s="3"/>
     </row>
-    <row r="574">
+    <row r="574" customHeight="1" spans="4:4">
       <c r="D574" s="3"/>
     </row>
-    <row r="575">
+    <row r="575" customHeight="1" spans="4:4">
       <c r="D575" s="3"/>
     </row>
-    <row r="576">
+    <row r="576" customHeight="1" spans="4:4">
       <c r="D576" s="3"/>
     </row>
-    <row r="577">
+    <row r="577" customHeight="1" spans="4:4">
       <c r="D577" s="3"/>
     </row>
-    <row r="578">
+    <row r="578" customHeight="1" spans="4:4">
       <c r="D578" s="3"/>
     </row>
-    <row r="579">
+    <row r="579" customHeight="1" spans="4:4">
       <c r="D579" s="3"/>
     </row>
-    <row r="580">
+    <row r="580" customHeight="1" spans="4:4">
       <c r="D580" s="3"/>
     </row>
-    <row r="581">
+    <row r="581" customHeight="1" spans="4:4">
       <c r="D581" s="3"/>
     </row>
-    <row r="582">
+    <row r="582" customHeight="1" spans="4:4">
       <c r="D582" s="3"/>
     </row>
-    <row r="583">
+    <row r="583" customHeight="1" spans="4:4">
       <c r="D583" s="3"/>
     </row>
-    <row r="584">
+    <row r="584" customHeight="1" spans="4:4">
       <c r="D584" s="3"/>
     </row>
-    <row r="585">
+    <row r="585" customHeight="1" spans="4:4">
       <c r="D585" s="3"/>
     </row>
-    <row r="586">
+    <row r="586" customHeight="1" spans="4:4">
       <c r="D586" s="3"/>
     </row>
-    <row r="587">
+    <row r="587" customHeight="1" spans="4:4">
       <c r="D587" s="3"/>
     </row>
-    <row r="588">
+    <row r="588" customHeight="1" spans="4:4">
       <c r="D588" s="3"/>
     </row>
-    <row r="589">
+    <row r="589" customHeight="1" spans="4:4">
       <c r="D589" s="3"/>
     </row>
-    <row r="590">
+    <row r="590" customHeight="1" spans="4:4">
       <c r="D590" s="3"/>
     </row>
-    <row r="591">
+    <row r="591" customHeight="1" spans="4:4">
       <c r="D591" s="3"/>
     </row>
-    <row r="592">
+    <row r="592" customHeight="1" spans="4:4">
       <c r="D592" s="3"/>
     </row>
-    <row r="593">
+    <row r="593" customHeight="1" spans="4:4">
       <c r="D593" s="3"/>
     </row>
-    <row r="594">
+    <row r="594" customHeight="1" spans="4:4">
       <c r="D594" s="3"/>
     </row>
-    <row r="595">
+    <row r="595" customHeight="1" spans="4:4">
       <c r="D595" s="3"/>
     </row>
-    <row r="596">
+    <row r="596" customHeight="1" spans="4:4">
       <c r="D596" s="3"/>
     </row>
-    <row r="597">
+    <row r="597" customHeight="1" spans="4:4">
       <c r="D597" s="3"/>
     </row>
-    <row r="598">
+    <row r="598" customHeight="1" spans="4:4">
       <c r="D598" s="3"/>
     </row>
-    <row r="599">
+    <row r="599" customHeight="1" spans="4:4">
       <c r="D599" s="3"/>
     </row>
-    <row r="600">
+    <row r="600" customHeight="1" spans="4:4">
       <c r="D600" s="3"/>
     </row>
-    <row r="601">
+    <row r="601" customHeight="1" spans="4:4">
       <c r="D601" s="3"/>
     </row>
-    <row r="602">
+    <row r="602" customHeight="1" spans="4:4">
       <c r="D602" s="3"/>
     </row>
-    <row r="603">
+    <row r="603" customHeight="1" spans="4:4">
       <c r="D603" s="3"/>
     </row>
-    <row r="604">
+    <row r="604" customHeight="1" spans="4:4">
       <c r="D604" s="3"/>
     </row>
-    <row r="605">
+    <row r="605" customHeight="1" spans="4:4">
       <c r="D605" s="3"/>
     </row>
-    <row r="606">
+    <row r="606" customHeight="1" spans="4:4">
       <c r="D606" s="3"/>
     </row>
-    <row r="607">
+    <row r="607" customHeight="1" spans="4:4">
       <c r="D607" s="3"/>
     </row>
-    <row r="608">
+    <row r="608" customHeight="1" spans="4:4">
       <c r="D608" s="3"/>
     </row>
-    <row r="609">
+    <row r="609" customHeight="1" spans="4:4">
       <c r="D609" s="3"/>
     </row>
-    <row r="610">
+    <row r="610" customHeight="1" spans="4:4">
       <c r="D610" s="3"/>
     </row>
-    <row r="611">
+    <row r="611" customHeight="1" spans="4:4">
       <c r="D611" s="3"/>
     </row>
-    <row r="612">
+    <row r="612" customHeight="1" spans="4:4">
       <c r="D612" s="3"/>
     </row>
-    <row r="613">
+    <row r="613" customHeight="1" spans="4:4">
       <c r="D613" s="3"/>
     </row>
-    <row r="614">
+    <row r="614" customHeight="1" spans="4:4">
       <c r="D614" s="3"/>
     </row>
-    <row r="615">
+    <row r="615" customHeight="1" spans="4:4">
       <c r="D615" s="3"/>
     </row>
-    <row r="616">
+    <row r="616" customHeight="1" spans="4:4">
       <c r="D616" s="3"/>
     </row>
-    <row r="617">
+    <row r="617" customHeight="1" spans="4:4">
       <c r="D617" s="3"/>
     </row>
-    <row r="618">
+    <row r="618" customHeight="1" spans="4:4">
       <c r="D618" s="3"/>
     </row>
-    <row r="619">
+    <row r="619" customHeight="1" spans="4:4">
       <c r="D619" s="3"/>
     </row>
-    <row r="620">
+    <row r="620" customHeight="1" spans="4:4">
       <c r="D620" s="3"/>
     </row>
-    <row r="621">
+    <row r="621" customHeight="1" spans="4:4">
       <c r="D621" s="3"/>
     </row>
-    <row r="622">
+    <row r="622" customHeight="1" spans="4:4">
       <c r="D622" s="3"/>
     </row>
-    <row r="623">
+    <row r="623" customHeight="1" spans="4:4">
       <c r="D623" s="3"/>
     </row>
-    <row r="624">
+    <row r="624" customHeight="1" spans="4:4">
       <c r="D624" s="3"/>
     </row>
-    <row r="625">
+    <row r="625" customHeight="1" spans="4:4">
       <c r="D625" s="3"/>
     </row>
-    <row r="626">
+    <row r="626" customHeight="1" spans="4:4">
       <c r="D626" s="3"/>
     </row>
-    <row r="627">
+    <row r="627" customHeight="1" spans="4:4">
       <c r="D627" s="3"/>
     </row>
-    <row r="628">
+    <row r="628" customHeight="1" spans="4:4">
       <c r="D628" s="3"/>
     </row>
-    <row r="629">
+    <row r="629" customHeight="1" spans="4:4">
       <c r="D629" s="3"/>
     </row>
-    <row r="630">
+    <row r="630" customHeight="1" spans="4:4">
       <c r="D630" s="3"/>
     </row>
-    <row r="631">
+    <row r="631" customHeight="1" spans="4:4">
       <c r="D631" s="3"/>
     </row>
-    <row r="632">
+    <row r="632" customHeight="1" spans="4:4">
       <c r="D632" s="3"/>
     </row>
-    <row r="633">
+    <row r="633" customHeight="1" spans="4:4">
       <c r="D633" s="3"/>
     </row>
-    <row r="634">
+    <row r="634" customHeight="1" spans="4:4">
       <c r="D634" s="3"/>
     </row>
-    <row r="635">
+    <row r="635" customHeight="1" spans="4:4">
       <c r="D635" s="3"/>
     </row>
-    <row r="636">
+    <row r="636" customHeight="1" spans="4:4">
       <c r="D636" s="3"/>
     </row>
-    <row r="637">
+    <row r="637" customHeight="1" spans="4:4">
       <c r="D637" s="3"/>
     </row>
-    <row r="638">
+    <row r="638" customHeight="1" spans="4:4">
       <c r="D638" s="3"/>
     </row>
-    <row r="639">
+    <row r="639" customHeight="1" spans="4:4">
       <c r="D639" s="3"/>
     </row>
-    <row r="640">
+    <row r="640" customHeight="1" spans="4:4">
       <c r="D640" s="3"/>
     </row>
-    <row r="641">
+    <row r="641" customHeight="1" spans="4:4">
       <c r="D641" s="3"/>
     </row>
-    <row r="642">
+    <row r="642" customHeight="1" spans="4:4">
       <c r="D642" s="3"/>
     </row>
-    <row r="643">
+    <row r="643" customHeight="1" spans="4:4">
       <c r="D643" s="3"/>
     </row>
-    <row r="644">
+    <row r="644" customHeight="1" spans="4:4">
       <c r="D644" s="3"/>
     </row>
-    <row r="645">
+    <row r="645" customHeight="1" spans="4:4">
       <c r="D645" s="3"/>
     </row>
-    <row r="646">
+    <row r="646" customHeight="1" spans="4:4">
       <c r="D646" s="3"/>
     </row>
-    <row r="647">
+    <row r="647" customHeight="1" spans="4:4">
       <c r="D647" s="3"/>
     </row>
-    <row r="648">
+    <row r="648" customHeight="1" spans="4:4">
       <c r="D648" s="3"/>
     </row>
-    <row r="649">
+    <row r="649" customHeight="1" spans="4:4">
       <c r="D649" s="3"/>
     </row>
-    <row r="650">
+    <row r="650" customHeight="1" spans="4:4">
       <c r="D650" s="3"/>
     </row>
-    <row r="651">
+    <row r="651" customHeight="1" spans="4:4">
       <c r="D651" s="3"/>
     </row>
-    <row r="652">
+    <row r="652" customHeight="1" spans="4:4">
       <c r="D652" s="3"/>
     </row>
-    <row r="653">
+    <row r="653" customHeight="1" spans="4:4">
       <c r="D653" s="3"/>
     </row>
-    <row r="654">
+    <row r="654" customHeight="1" spans="4:4">
       <c r="D654" s="3"/>
     </row>
-    <row r="655">
+    <row r="655" customHeight="1" spans="4:4">
       <c r="D655" s="3"/>
     </row>
-    <row r="656">
+    <row r="656" customHeight="1" spans="4:4">
       <c r="D656" s="3"/>
     </row>
-    <row r="657">
+    <row r="657" customHeight="1" spans="4:4">
       <c r="D657" s="3"/>
     </row>
-    <row r="658">
+    <row r="658" customHeight="1" spans="4:4">
       <c r="D658" s="3"/>
     </row>
-    <row r="659">
+    <row r="659" customHeight="1" spans="4:4">
       <c r="D659" s="3"/>
     </row>
-    <row r="660">
+    <row r="660" customHeight="1" spans="4:4">
       <c r="D660" s="3"/>
     </row>
-    <row r="661">
+    <row r="661" customHeight="1" spans="4:4">
       <c r="D661" s="3"/>
     </row>
-    <row r="662">
+    <row r="662" customHeight="1" spans="4:4">
       <c r="D662" s="3"/>
     </row>
-    <row r="663">
+    <row r="663" customHeight="1" spans="4:4">
       <c r="D663" s="3"/>
     </row>
-    <row r="664">
+    <row r="664" customHeight="1" spans="4:4">
       <c r="D664" s="3"/>
     </row>
-    <row r="665">
+    <row r="665" customHeight="1" spans="4:4">
       <c r="D665" s="3"/>
     </row>
-    <row r="666">
+    <row r="666" customHeight="1" spans="4:4">
       <c r="D666" s="3"/>
     </row>
-    <row r="667">
+    <row r="667" customHeight="1" spans="4:4">
       <c r="D667" s="3"/>
     </row>
-    <row r="668">
+    <row r="668" customHeight="1" spans="4:4">
       <c r="D668" s="3"/>
     </row>
-    <row r="669">
+    <row r="669" customHeight="1" spans="4:4">
       <c r="D669" s="3"/>
     </row>
-    <row r="670">
+    <row r="670" customHeight="1" spans="4:4">
       <c r="D670" s="3"/>
     </row>
-    <row r="671">
+    <row r="671" customHeight="1" spans="4:4">
       <c r="D671" s="3"/>
     </row>
-    <row r="672">
+    <row r="672" customHeight="1" spans="4:4">
       <c r="D672" s="3"/>
     </row>
-    <row r="673">
+    <row r="673" customHeight="1" spans="4:4">
       <c r="D673" s="3"/>
     </row>
-    <row r="674">
+    <row r="674" customHeight="1" spans="4:4">
       <c r="D674" s="3"/>
     </row>
-    <row r="675">
+    <row r="675" customHeight="1" spans="4:4">
       <c r="D675" s="3"/>
     </row>
-    <row r="676">
+    <row r="676" customHeight="1" spans="4:4">
       <c r="D676" s="3"/>
     </row>
-    <row r="677">
+    <row r="677" customHeight="1" spans="4:4">
       <c r="D677" s="3"/>
     </row>
-    <row r="678">
+    <row r="678" customHeight="1" spans="4:4">
       <c r="D678" s="3"/>
     </row>
-    <row r="679">
+    <row r="679" customHeight="1" spans="4:4">
       <c r="D679" s="3"/>
     </row>
-    <row r="680">
+    <row r="680" customHeight="1" spans="4:4">
       <c r="D680" s="3"/>
     </row>
-    <row r="681">
+    <row r="681" customHeight="1" spans="4:4">
       <c r="D681" s="3"/>
     </row>
-    <row r="682">
+    <row r="682" customHeight="1" spans="4:4">
       <c r="D682" s="3"/>
     </row>
-    <row r="683">
+    <row r="683" customHeight="1" spans="4:4">
       <c r="D683" s="3"/>
     </row>
-    <row r="684">
+    <row r="684" customHeight="1" spans="4:4">
       <c r="D684" s="3"/>
     </row>
-    <row r="685">
+    <row r="685" customHeight="1" spans="4:4">
       <c r="D685" s="3"/>
     </row>
-    <row r="686">
+    <row r="686" customHeight="1" spans="4:4">
       <c r="D686" s="3"/>
     </row>
-    <row r="687">
+    <row r="687" customHeight="1" spans="4:4">
       <c r="D687" s="3"/>
     </row>
-    <row r="688">
+    <row r="688" customHeight="1" spans="4:4">
       <c r="D688" s="3"/>
     </row>
-    <row r="689">
+    <row r="689" customHeight="1" spans="4:4">
       <c r="D689" s="3"/>
     </row>
-    <row r="690">
+    <row r="690" customHeight="1" spans="4:4">
       <c r="D690" s="3"/>
     </row>
-    <row r="691">
+    <row r="691" customHeight="1" spans="4:4">
       <c r="D691" s="3"/>
     </row>
-    <row r="692">
+    <row r="692" customHeight="1" spans="4:4">
       <c r="D692" s="3"/>
     </row>
-    <row r="693">
+    <row r="693" customHeight="1" spans="4:4">
       <c r="D693" s="3"/>
     </row>
-    <row r="694">
+    <row r="694" customHeight="1" spans="4:4">
       <c r="D694" s="3"/>
     </row>
-    <row r="695">
+    <row r="695" customHeight="1" spans="4:4">
       <c r="D695" s="3"/>
     </row>
-    <row r="696">
+    <row r="696" customHeight="1" spans="4:4">
       <c r="D696" s="3"/>
     </row>
-    <row r="697">
+    <row r="697" customHeight="1" spans="4:4">
       <c r="D697" s="3"/>
     </row>
-    <row r="698">
+    <row r="698" customHeight="1" spans="4:4">
       <c r="D698" s="3"/>
     </row>
-    <row r="699">
+    <row r="699" customHeight="1" spans="4:4">
       <c r="D699" s="3"/>
     </row>
-    <row r="700">
+    <row r="700" customHeight="1" spans="4:4">
       <c r="D700" s="3"/>
     </row>
-    <row r="701">
+    <row r="701" customHeight="1" spans="4:4">
       <c r="D701" s="3"/>
     </row>
-    <row r="702">
+    <row r="702" customHeight="1" spans="4:4">
       <c r="D702" s="3"/>
     </row>
-    <row r="703">
+    <row r="703" customHeight="1" spans="4:4">
       <c r="D703" s="3"/>
     </row>
-    <row r="704">
+    <row r="704" customHeight="1" spans="4:4">
       <c r="D704" s="3"/>
     </row>
-    <row r="705">
+    <row r="705" customHeight="1" spans="4:4">
       <c r="D705" s="3"/>
     </row>
-    <row r="706">
+    <row r="706" customHeight="1" spans="4:4">
       <c r="D706" s="3"/>
     </row>
-    <row r="707">
+    <row r="707" customHeight="1" spans="4:4">
       <c r="D707" s="3"/>
     </row>
-    <row r="708">
+    <row r="708" customHeight="1" spans="4:4">
       <c r="D708" s="3"/>
     </row>
-    <row r="709">
+    <row r="709" customHeight="1" spans="4:4">
       <c r="D709" s="3"/>
     </row>
-    <row r="710">
+    <row r="710" customHeight="1" spans="4:4">
       <c r="D710" s="3"/>
     </row>
-    <row r="711">
+    <row r="711" customHeight="1" spans="4:4">
       <c r="D711" s="3"/>
     </row>
-    <row r="712">
+    <row r="712" customHeight="1" spans="4:4">
       <c r="D712" s="3"/>
     </row>
-    <row r="713">
+    <row r="713" customHeight="1" spans="4:4">
       <c r="D713" s="3"/>
     </row>
-    <row r="714">
+    <row r="714" customHeight="1" spans="4:4">
       <c r="D714" s="3"/>
     </row>
-    <row r="715">
+    <row r="715" customHeight="1" spans="4:4">
       <c r="D715" s="3"/>
     </row>
-    <row r="716">
+    <row r="716" customHeight="1" spans="4:4">
       <c r="D716" s="3"/>
     </row>
-    <row r="717">
+    <row r="717" customHeight="1" spans="4:4">
       <c r="D717" s="3"/>
     </row>
-    <row r="718">
+    <row r="718" customHeight="1" spans="4:4">
       <c r="D718" s="3"/>
     </row>
-    <row r="719">
+    <row r="719" customHeight="1" spans="4:4">
       <c r="D719" s="3"/>
     </row>
-    <row r="720">
+    <row r="720" customHeight="1" spans="4:4">
       <c r="D720" s="3"/>
     </row>
-    <row r="721">
+    <row r="721" customHeight="1" spans="4:4">
       <c r="D721" s="3"/>
     </row>
-    <row r="722">
+    <row r="722" customHeight="1" spans="4:4">
       <c r="D722" s="3"/>
     </row>
-    <row r="723">
+    <row r="723" customHeight="1" spans="4:4">
       <c r="D723" s="3"/>
     </row>
-    <row r="724">
+    <row r="724" customHeight="1" spans="4:4">
       <c r="D724" s="3"/>
     </row>
-    <row r="725">
+    <row r="725" customHeight="1" spans="4:4">
       <c r="D725" s="3"/>
     </row>
-    <row r="726">
+    <row r="726" customHeight="1" spans="4:4">
       <c r="D726" s="3"/>
     </row>
-    <row r="727">
+    <row r="727" customHeight="1" spans="4:4">
       <c r="D727" s="3"/>
     </row>
-    <row r="728">
+    <row r="728" customHeight="1" spans="4:4">
       <c r="D728" s="3"/>
     </row>
-    <row r="729">
+    <row r="729" customHeight="1" spans="4:4">
       <c r="D729" s="3"/>
     </row>
-    <row r="730">
+    <row r="730" customHeight="1" spans="4:4">
       <c r="D730" s="3"/>
     </row>
-    <row r="731">
+    <row r="731" customHeight="1" spans="4:4">
       <c r="D731" s="3"/>
     </row>
-    <row r="732">
+    <row r="732" customHeight="1" spans="4:4">
       <c r="D732" s="3"/>
     </row>
-    <row r="733">
+    <row r="733" customHeight="1" spans="4:4">
       <c r="D733" s="3"/>
     </row>
-    <row r="734">
+    <row r="734" customHeight="1" spans="4:4">
       <c r="D734" s="3"/>
     </row>
-    <row r="735">
+    <row r="735" customHeight="1" spans="4:4">
       <c r="D735" s="3"/>
     </row>
-    <row r="736">
+    <row r="736" customHeight="1" spans="4:4">
       <c r="D736" s="3"/>
     </row>
-    <row r="737">
+    <row r="737" customHeight="1" spans="4:4">
       <c r="D737" s="3"/>
     </row>
-    <row r="738">
+    <row r="738" customHeight="1" spans="4:4">
       <c r="D738" s="3"/>
     </row>
-    <row r="739">
+    <row r="739" customHeight="1" spans="4:4">
       <c r="D739" s="3"/>
     </row>
-    <row r="740">
+    <row r="740" customHeight="1" spans="4:4">
       <c r="D740" s="3"/>
     </row>
-    <row r="741">
+    <row r="741" customHeight="1" spans="4:4">
       <c r="D741" s="3"/>
     </row>
-    <row r="742">
+    <row r="742" customHeight="1" spans="4:4">
       <c r="D742" s="3"/>
     </row>
-    <row r="743">
+    <row r="743" customHeight="1" spans="4:4">
       <c r="D743" s="3"/>
     </row>
-    <row r="744">
+    <row r="744" customHeight="1" spans="4:4">
       <c r="D744" s="3"/>
     </row>
-    <row r="745">
+    <row r="745" customHeight="1" spans="4:4">
       <c r="D745" s="3"/>
     </row>
-    <row r="746">
+    <row r="746" customHeight="1" spans="4:4">
       <c r="D746" s="3"/>
     </row>
-    <row r="747">
+    <row r="747" customHeight="1" spans="4:4">
       <c r="D747" s="3"/>
     </row>
-    <row r="748">
+    <row r="748" customHeight="1" spans="4:4">
       <c r="D748" s="3"/>
     </row>
-    <row r="749">
+    <row r="749" customHeight="1" spans="4:4">
       <c r="D749" s="3"/>
     </row>
-    <row r="750">
+    <row r="750" customHeight="1" spans="4:4">
       <c r="D750" s="3"/>
     </row>
-    <row r="751">
+    <row r="751" customHeight="1" spans="4:4">
       <c r="D751" s="3"/>
     </row>
-    <row r="752">
+    <row r="752" customHeight="1" spans="4:4">
       <c r="D752" s="3"/>
     </row>
-    <row r="753">
+    <row r="753" customHeight="1" spans="4:4">
       <c r="D753" s="3"/>
     </row>
-    <row r="754">
+    <row r="754" customHeight="1" spans="4:4">
       <c r="D754" s="3"/>
     </row>
-    <row r="755">
+    <row r="755" customHeight="1" spans="4:4">
       <c r="D755" s="3"/>
     </row>
-    <row r="756">
+    <row r="756" customHeight="1" spans="4:4">
       <c r="D756" s="3"/>
     </row>
-    <row r="757">
+    <row r="757" customHeight="1" spans="4:4">
       <c r="D757" s="3"/>
     </row>
-    <row r="758">
+    <row r="758" customHeight="1" spans="4:4">
       <c r="D758" s="3"/>
     </row>
-    <row r="759">
+    <row r="759" customHeight="1" spans="4:4">
       <c r="D759" s="3"/>
     </row>
-    <row r="760">
+    <row r="760" customHeight="1" spans="4:4">
       <c r="D760" s="3"/>
     </row>
-    <row r="761">
+    <row r="761" customHeight="1" spans="4:4">
       <c r="D761" s="3"/>
     </row>
-    <row r="762">
+    <row r="762" customHeight="1" spans="4:4">
       <c r="D762" s="3"/>
     </row>
-    <row r="763">
+    <row r="763" customHeight="1" spans="4:4">
       <c r="D763" s="3"/>
     </row>
-    <row r="764">
+    <row r="764" customHeight="1" spans="4:4">
       <c r="D764" s="3"/>
     </row>
-    <row r="765">
+    <row r="765" customHeight="1" spans="4:4">
       <c r="D765" s="3"/>
     </row>
-    <row r="766">
+    <row r="766" customHeight="1" spans="4:4">
       <c r="D766" s="3"/>
     </row>
-    <row r="767">
+    <row r="767" customHeight="1" spans="4:4">
       <c r="D767" s="3"/>
     </row>
-    <row r="768">
+    <row r="768" customHeight="1" spans="4:4">
       <c r="D768" s="3"/>
     </row>
-    <row r="769">
+    <row r="769" customHeight="1" spans="4:4">
       <c r="D769" s="3"/>
     </row>
-    <row r="770">
+    <row r="770" customHeight="1" spans="4:4">
       <c r="D770" s="3"/>
     </row>
-    <row r="771">
+    <row r="771" customHeight="1" spans="4:4">
       <c r="D771" s="3"/>
     </row>
-    <row r="772">
+    <row r="772" customHeight="1" spans="4:4">
       <c r="D772" s="3"/>
     </row>
-    <row r="773">
+    <row r="773" customHeight="1" spans="4:4">
       <c r="D773" s="3"/>
     </row>
-    <row r="774">
+    <row r="774" customHeight="1" spans="4:4">
       <c r="D774" s="3"/>
     </row>
-    <row r="775">
+    <row r="775" customHeight="1" spans="4:4">
       <c r="D775" s="3"/>
     </row>
-    <row r="776">
+    <row r="776" customHeight="1" spans="4:4">
       <c r="D776" s="3"/>
     </row>
-    <row r="777">
+    <row r="777" customHeight="1" spans="4:4">
       <c r="D777" s="3"/>
     </row>
-    <row r="778">
+    <row r="778" customHeight="1" spans="4:4">
       <c r="D778" s="3"/>
     </row>
-    <row r="779">
+    <row r="779" customHeight="1" spans="4:4">
       <c r="D779" s="3"/>
     </row>
-    <row r="780">
+    <row r="780" customHeight="1" spans="4:4">
       <c r="D780" s="3"/>
     </row>
-    <row r="781">
+    <row r="781" customHeight="1" spans="4:4">
       <c r="D781" s="3"/>
     </row>
-    <row r="782">
+    <row r="782" customHeight="1" spans="4:4">
       <c r="D782" s="3"/>
     </row>
-    <row r="783">
+    <row r="783" customHeight="1" spans="4:4">
       <c r="D783" s="3"/>
     </row>
-    <row r="784">
+    <row r="784" customHeight="1" spans="4:4">
       <c r="D784" s="3"/>
     </row>
-    <row r="785">
+    <row r="785" customHeight="1" spans="4:4">
       <c r="D785" s="3"/>
     </row>
-    <row r="786">
+    <row r="786" customHeight="1" spans="4:4">
       <c r="D786" s="3"/>
     </row>
-    <row r="787">
+    <row r="787" customHeight="1" spans="4:4">
       <c r="D787" s="3"/>
     </row>
-    <row r="788">
+    <row r="788" customHeight="1" spans="4:4">
       <c r="D788" s="3"/>
     </row>
-    <row r="789">
+    <row r="789" customHeight="1" spans="4:4">
       <c r="D789" s="3"/>
     </row>
-    <row r="790">
+    <row r="790" customHeight="1" spans="4:4">
       <c r="D790" s="3"/>
     </row>
-    <row r="791">
+    <row r="791" customHeight="1" spans="4:4">
       <c r="D791" s="3"/>
     </row>
-    <row r="792">
+    <row r="792" customHeight="1" spans="4:4">
       <c r="D792" s="3"/>
     </row>
-    <row r="793">
+    <row r="793" customHeight="1" spans="4:4">
       <c r="D793" s="3"/>
     </row>
-    <row r="794">
+    <row r="794" customHeight="1" spans="4:4">
       <c r="D794" s="3"/>
     </row>
-    <row r="795">
+    <row r="795" customHeight="1" spans="4:4">
       <c r="D795" s="3"/>
     </row>
-    <row r="796">
+    <row r="796" customHeight="1" spans="4:4">
       <c r="D796" s="3"/>
     </row>
-    <row r="797">
+    <row r="797" customHeight="1" spans="4:4">
       <c r="D797" s="3"/>
     </row>
-    <row r="798">
+    <row r="798" customHeight="1" spans="4:4">
       <c r="D798" s="3"/>
     </row>
-    <row r="799">
+    <row r="799" customHeight="1" spans="4:4">
       <c r="D799" s="3"/>
     </row>
-    <row r="800">
+    <row r="800" customHeight="1" spans="4:4">
       <c r="D800" s="3"/>
     </row>
-    <row r="801">
+    <row r="801" customHeight="1" spans="4:4">
       <c r="D801" s="3"/>
     </row>
-    <row r="802">
+    <row r="802" customHeight="1" spans="4:4">
       <c r="D802" s="3"/>
     </row>
-    <row r="803">
+    <row r="803" customHeight="1" spans="4:4">
       <c r="D803" s="3"/>
     </row>
-    <row r="804">
+    <row r="804" customHeight="1" spans="4:4">
       <c r="D804" s="3"/>
     </row>
-    <row r="805">
+    <row r="805" customHeight="1" spans="4:4">
       <c r="D805" s="3"/>
     </row>
-    <row r="806">
+    <row r="806" customHeight="1" spans="4:4">
       <c r="D806" s="3"/>
     </row>
-    <row r="807">
+    <row r="807" customHeight="1" spans="4:4">
       <c r="D807" s="3"/>
     </row>
-    <row r="808">
+    <row r="808" customHeight="1" spans="4:4">
       <c r="D808" s="3"/>
     </row>
-    <row r="809">
+    <row r="809" customHeight="1" spans="4:4">
       <c r="D809" s="3"/>
     </row>
-    <row r="810">
+    <row r="810" customHeight="1" spans="4:4">
       <c r="D810" s="3"/>
     </row>
-    <row r="811">
+    <row r="811" customHeight="1" spans="4:4">
       <c r="D811" s="3"/>
     </row>
-    <row r="812">
+    <row r="812" customHeight="1" spans="4:4">
       <c r="D812" s="3"/>
     </row>
-    <row r="813">
+    <row r="813" customHeight="1" spans="4:4">
       <c r="D813" s="3"/>
     </row>
-    <row r="814">
+    <row r="814" customHeight="1" spans="4:4">
       <c r="D814" s="3"/>
     </row>
-    <row r="815">
+    <row r="815" customHeight="1" spans="4:4">
       <c r="D815" s="3"/>
     </row>
-    <row r="816">
+    <row r="816" customHeight="1" spans="4:4">
       <c r="D816" s="3"/>
     </row>
-    <row r="817">
+    <row r="817" customHeight="1" spans="4:4">
       <c r="D817" s="3"/>
     </row>
-    <row r="818">
+    <row r="818" customHeight="1" spans="4:4">
       <c r="D818" s="3"/>
     </row>
-    <row r="819">
+    <row r="819" customHeight="1" spans="4:4">
       <c r="D819" s="3"/>
     </row>
-    <row r="820">
+    <row r="820" customHeight="1" spans="4:4">
       <c r="D820" s="3"/>
     </row>
-    <row r="821">
+    <row r="821" customHeight="1" spans="4:4">
       <c r="D821" s="3"/>
     </row>
-    <row r="822">
+    <row r="822" customHeight="1" spans="4:4">
       <c r="D822" s="3"/>
     </row>
-    <row r="823">
+    <row r="823" customHeight="1" spans="4:4">
       <c r="D823" s="3"/>
     </row>
-    <row r="824">
+    <row r="824" customHeight="1" spans="4:4">
       <c r="D824" s="3"/>
     </row>
-    <row r="825">
+    <row r="825" customHeight="1" spans="4:4">
       <c r="D825" s="3"/>
     </row>
-    <row r="826">
+    <row r="826" customHeight="1" spans="4:4">
       <c r="D826" s="3"/>
     </row>
-    <row r="827">
+    <row r="827" customHeight="1" spans="4:4">
       <c r="D827" s="3"/>
     </row>
-    <row r="828">
+    <row r="828" customHeight="1" spans="4:4">
       <c r="D828" s="3"/>
     </row>
-    <row r="829">
+    <row r="829" customHeight="1" spans="4:4">
       <c r="D829" s="3"/>
     </row>
-    <row r="830">
+    <row r="830" customHeight="1" spans="4:4">
       <c r="D830" s="3"/>
     </row>
-    <row r="831">
+    <row r="831" customHeight="1" spans="4:4">
       <c r="D831" s="3"/>
     </row>
-    <row r="832">
+    <row r="832" customHeight="1" spans="4:4">
       <c r="D832" s="3"/>
     </row>
-    <row r="833">
+    <row r="833" customHeight="1" spans="4:4">
       <c r="D833" s="3"/>
     </row>
-    <row r="834">
+    <row r="834" customHeight="1" spans="4:4">
       <c r="D834" s="3"/>
     </row>
-    <row r="835">
+    <row r="835" customHeight="1" spans="4:4">
       <c r="D835" s="3"/>
     </row>
-    <row r="836">
+    <row r="836" customHeight="1" spans="4:4">
       <c r="D836" s="3"/>
     </row>
-    <row r="837">
+    <row r="837" customHeight="1" spans="4:4">
       <c r="D837" s="3"/>
     </row>
-    <row r="838">
+    <row r="838" customHeight="1" spans="4:4">
       <c r="D838" s="3"/>
     </row>
-    <row r="839">
+    <row r="839" customHeight="1" spans="4:4">
       <c r="D839" s="3"/>
     </row>
-    <row r="840">
+    <row r="840" customHeight="1" spans="4:4">
       <c r="D840" s="3"/>
     </row>
-    <row r="841">
+    <row r="841" customHeight="1" spans="4:4">
       <c r="D841" s="3"/>
     </row>
-    <row r="842">
+    <row r="842" customHeight="1" spans="4:4">
       <c r="D842" s="3"/>
     </row>
-    <row r="843">
+    <row r="843" customHeight="1" spans="4:4">
       <c r="D843" s="3"/>
     </row>
-    <row r="844">
+    <row r="844" customHeight="1" spans="4:4">
       <c r="D844" s="3"/>
     </row>
-    <row r="845">
+    <row r="845" customHeight="1" spans="4:4">
       <c r="D845" s="3"/>
     </row>
-    <row r="846">
+    <row r="846" customHeight="1" spans="4:4">
       <c r="D846" s="3"/>
     </row>
-    <row r="847">
+    <row r="847" customHeight="1" spans="4:4">
       <c r="D847" s="3"/>
     </row>
-    <row r="848">
+    <row r="848" customHeight="1" spans="4:4">
       <c r="D848" s="3"/>
     </row>
-    <row r="849">
+    <row r="849" customHeight="1" spans="4:4">
       <c r="D849" s="3"/>
     </row>
-    <row r="850">
+    <row r="850" customHeight="1" spans="4:4">
       <c r="D850" s="3"/>
     </row>
-    <row r="851">
+    <row r="851" customHeight="1" spans="4:4">
       <c r="D851" s="3"/>
     </row>
-    <row r="852">
+    <row r="852" customHeight="1" spans="4:4">
       <c r="D852" s="3"/>
     </row>
-    <row r="853">
+    <row r="853" customHeight="1" spans="4:4">
       <c r="D853" s="3"/>
     </row>
-    <row r="854">
+    <row r="854" customHeight="1" spans="4:4">
       <c r="D854" s="3"/>
     </row>
-    <row r="855">
+    <row r="855" customHeight="1" spans="4:4">
       <c r="D855" s="3"/>
     </row>
-    <row r="856">
+    <row r="856" customHeight="1" spans="4:4">
       <c r="D856" s="3"/>
     </row>
-    <row r="857">
+    <row r="857" customHeight="1" spans="4:4">
       <c r="D857" s="3"/>
     </row>
-    <row r="858">
+    <row r="858" customHeight="1" spans="4:4">
       <c r="D858" s="3"/>
     </row>
-    <row r="859">
+    <row r="859" customHeight="1" spans="4:4">
       <c r="D859" s="3"/>
     </row>
-    <row r="860">
+    <row r="860" customHeight="1" spans="4:4">
       <c r="D860" s="3"/>
     </row>
-    <row r="861">
+    <row r="861" customHeight="1" spans="4:4">
       <c r="D861" s="3"/>
     </row>
-    <row r="862">
+    <row r="862" customHeight="1" spans="4:4">
       <c r="D862" s="3"/>
     </row>
-    <row r="863">
+    <row r="863" customHeight="1" spans="4:4">
       <c r="D863" s="3"/>
     </row>
-    <row r="864">
+    <row r="864" customHeight="1" spans="4:4">
       <c r="D864" s="3"/>
     </row>
-    <row r="865">
+    <row r="865" customHeight="1" spans="4:4">
       <c r="D865" s="3"/>
     </row>
-    <row r="866">
+    <row r="866" customHeight="1" spans="4:4">
       <c r="D866" s="3"/>
     </row>
-    <row r="867">
+    <row r="867" customHeight="1" spans="4:4">
       <c r="D867" s="3"/>
     </row>
-    <row r="868">
+    <row r="868" customHeight="1" spans="4:4">
       <c r="D868" s="3"/>
     </row>
-    <row r="869">
+    <row r="869" customHeight="1" spans="4:4">
       <c r="D869" s="3"/>
     </row>
-    <row r="870">
+    <row r="870" customHeight="1" spans="4:4">
       <c r="D870" s="3"/>
     </row>
-    <row r="871">
+    <row r="871" customHeight="1" spans="4:4">
       <c r="D871" s="3"/>
     </row>
-    <row r="872">
+    <row r="872" customHeight="1" spans="4:4">
       <c r="D872" s="3"/>
     </row>
-    <row r="873">
+    <row r="873" customHeight="1" spans="4:4">
       <c r="D873" s="3"/>
     </row>
-    <row r="874">
+    <row r="874" customHeight="1" spans="4:4">
       <c r="D874" s="3"/>
     </row>
-    <row r="875">
+    <row r="875" customHeight="1" spans="4:4">
       <c r="D875" s="3"/>
     </row>
-    <row r="876">
+    <row r="876" customHeight="1" spans="4:4">
       <c r="D876" s="3"/>
     </row>
-    <row r="877">
+    <row r="877" customHeight="1" spans="4:4">
       <c r="D877" s="3"/>
     </row>
-    <row r="878">
+    <row r="878" customHeight="1" spans="4:4">
       <c r="D878" s="3"/>
     </row>
-    <row r="879">
+    <row r="879" customHeight="1" spans="4:4">
       <c r="D879" s="3"/>
     </row>
-    <row r="880">
+    <row r="880" customHeight="1" spans="4:4">
       <c r="D880" s="3"/>
     </row>
-    <row r="881">
+    <row r="881" customHeight="1" spans="4:4">
       <c r="D881" s="3"/>
     </row>
-    <row r="882">
+    <row r="882" customHeight="1" spans="4:4">
       <c r="D882" s="3"/>
     </row>
-    <row r="883">
+    <row r="883" customHeight="1" spans="4:4">
       <c r="D883" s="3"/>
     </row>
-    <row r="884">
+    <row r="884" customHeight="1" spans="4:4">
       <c r="D884" s="3"/>
     </row>
-    <row r="885">
+    <row r="885" customHeight="1" spans="4:4">
       <c r="D885" s="3"/>
     </row>
-    <row r="886">
+    <row r="886" customHeight="1" spans="4:4">
       <c r="D886" s="3"/>
     </row>
-    <row r="887">
+    <row r="887" customHeight="1" spans="4:4">
       <c r="D887" s="3"/>
     </row>
-    <row r="888">
+    <row r="888" customHeight="1" spans="4:4">
       <c r="D888" s="3"/>
     </row>
-    <row r="889">
+    <row r="889" customHeight="1" spans="4:4">
       <c r="D889" s="3"/>
     </row>
-    <row r="890">
+    <row r="890" customHeight="1" spans="4:4">
       <c r="D890" s="3"/>
     </row>
-    <row r="891">
+    <row r="891" customHeight="1" spans="4:4">
       <c r="D891" s="3"/>
     </row>
-    <row r="892">
+    <row r="892" customHeight="1" spans="4:4">
       <c r="D892" s="3"/>
     </row>
-    <row r="893">
+    <row r="893" customHeight="1" spans="4:4">
       <c r="D893" s="3"/>
     </row>
-    <row r="894">
+    <row r="894" customHeight="1" spans="4:4">
       <c r="D894" s="3"/>
     </row>
-    <row r="895">
+    <row r="895" customHeight="1" spans="4:4">
       <c r="D895" s="3"/>
     </row>
-    <row r="896">
+    <row r="896" customHeight="1" spans="4:4">
       <c r="D896" s="3"/>
     </row>
-    <row r="897">
+    <row r="897" customHeight="1" spans="4:4">
       <c r="D897" s="3"/>
     </row>
-    <row r="898">
+    <row r="898" customHeight="1" spans="4:4">
       <c r="D898" s="3"/>
     </row>
-    <row r="899">
+    <row r="899" customHeight="1" spans="4:4">
       <c r="D899" s="3"/>
     </row>
-    <row r="900">
+    <row r="900" customHeight="1" spans="4:4">
       <c r="D900" s="3"/>
     </row>
-    <row r="901">
+    <row r="901" customHeight="1" spans="4:4">
       <c r="D901" s="3"/>
     </row>
-    <row r="902">
+    <row r="902" customHeight="1" spans="4:4">
       <c r="D902" s="3"/>
     </row>
-    <row r="903">
+    <row r="903" customHeight="1" spans="4:4">
       <c r="D903" s="3"/>
     </row>
-    <row r="904">
+    <row r="904" customHeight="1" spans="4:4">
       <c r="D904" s="3"/>
     </row>
-    <row r="905">
+    <row r="905" customHeight="1" spans="4:4">
       <c r="D905" s="3"/>
     </row>
-    <row r="906">
+    <row r="906" customHeight="1" spans="4:4">
       <c r="D906" s="3"/>
     </row>
-    <row r="907">
+    <row r="907" customHeight="1" spans="4:4">
       <c r="D907" s="3"/>
     </row>
-    <row r="908">
+    <row r="908" customHeight="1" spans="4:4">
       <c r="D908" s="3"/>
     </row>
-    <row r="909">
+    <row r="909" customHeight="1" spans="4:4">
       <c r="D909" s="3"/>
     </row>
-    <row r="910">
+    <row r="910" customHeight="1" spans="4:4">
       <c r="D910" s="3"/>
     </row>
-    <row r="911">
+    <row r="911" customHeight="1" spans="4:4">
       <c r="D911" s="3"/>
     </row>
-    <row r="912">
+    <row r="912" customHeight="1" spans="4:4">
       <c r="D912" s="3"/>
     </row>
-    <row r="913">
+    <row r="913" customHeight="1" spans="4:4">
       <c r="D913" s="3"/>
     </row>
-    <row r="914">
+    <row r="914" customHeight="1" spans="4:4">
       <c r="D914" s="3"/>
     </row>
-    <row r="915">
+    <row r="915" customHeight="1" spans="4:4">
       <c r="D915" s="3"/>
     </row>
-    <row r="916">
+    <row r="916" customHeight="1" spans="4:4">
       <c r="D916" s="3"/>
     </row>
-    <row r="917">
+    <row r="917" customHeight="1" spans="4:4">
       <c r="D917" s="3"/>
     </row>
-    <row r="918">
+    <row r="918" customHeight="1" spans="4:4">
       <c r="D918" s="3"/>
     </row>
-    <row r="919">
+    <row r="919" customHeight="1" spans="4:4">
       <c r="D919" s="3"/>
     </row>
-    <row r="920">
+    <row r="920" customHeight="1" spans="4:4">
       <c r="D920" s="3"/>
     </row>
-    <row r="921">
+    <row r="921" customHeight="1" spans="4:4">
       <c r="D921" s="3"/>
     </row>
-    <row r="922">
+    <row r="922" customHeight="1" spans="4:4">
       <c r="D922" s="3"/>
     </row>
-    <row r="923">
+    <row r="923" customHeight="1" spans="4:4">
       <c r="D923" s="3"/>
     </row>
-    <row r="924">
+    <row r="924" customHeight="1" spans="4:4">
       <c r="D924" s="3"/>
     </row>
-    <row r="925">
+    <row r="925" customHeight="1" spans="4:4">
       <c r="D925" s="3"/>
     </row>
-    <row r="926">
+    <row r="926" customHeight="1" spans="4:4">
       <c r="D926" s="3"/>
     </row>
-    <row r="927">
+    <row r="927" customHeight="1" spans="4:4">
       <c r="D927" s="3"/>
     </row>
-    <row r="928">
+    <row r="928" customHeight="1" spans="4:4">
       <c r="D928" s="3"/>
     </row>
-    <row r="929">
+    <row r="929" customHeight="1" spans="4:4">
       <c r="D929" s="3"/>
     </row>
-    <row r="930">
+    <row r="930" customHeight="1" spans="4:4">
       <c r="D930" s="3"/>
     </row>
-    <row r="931">
+    <row r="931" customHeight="1" spans="4:4">
       <c r="D931" s="3"/>
     </row>
-    <row r="932">
+    <row r="932" customHeight="1" spans="4:4">
       <c r="D932" s="3"/>
     </row>
-    <row r="933">
+    <row r="933" customHeight="1" spans="4:4">
       <c r="D933" s="3"/>
     </row>
-    <row r="934">
+    <row r="934" customHeight="1" spans="4:4">
       <c r="D934" s="3"/>
     </row>
-    <row r="935">
+    <row r="935" customHeight="1" spans="4:4">
       <c r="D935" s="3"/>
     </row>
-    <row r="936">
+    <row r="936" customHeight="1" spans="4:4">
       <c r="D936" s="3"/>
     </row>
-    <row r="937">
+    <row r="937" customHeight="1" spans="4:4">
       <c r="D937" s="3"/>
     </row>
-    <row r="938">
+    <row r="938" customHeight="1" spans="4:4">
       <c r="D938" s="3"/>
     </row>
-    <row r="939">
+    <row r="939" customHeight="1" spans="4:4">
       <c r="D939" s="3"/>
     </row>
-    <row r="940">
+    <row r="940" customHeight="1" spans="4:4">
       <c r="D940" s="3"/>
     </row>
-    <row r="941">
+    <row r="941" customHeight="1" spans="4:4">
       <c r="D941" s="3"/>
     </row>
-    <row r="942">
+    <row r="942" customHeight="1" spans="4:4">
       <c r="D942" s="3"/>
     </row>
-    <row r="943">
+    <row r="943" customHeight="1" spans="4:4">
       <c r="D943" s="3"/>
     </row>
-    <row r="944">
+    <row r="944" customHeight="1" spans="4:4">
       <c r="D944" s="3"/>
     </row>
-    <row r="945">
+    <row r="945" customHeight="1" spans="4:4">
       <c r="D945" s="3"/>
     </row>
-    <row r="946">
+    <row r="946" customHeight="1" spans="4:4">
       <c r="D946" s="3"/>
     </row>
-    <row r="947">
+    <row r="947" customHeight="1" spans="4:4">
       <c r="D947" s="3"/>
     </row>
-    <row r="948">
+    <row r="948" customHeight="1" spans="4:4">
       <c r="D948" s="3"/>
     </row>
-    <row r="949">
+    <row r="949" customHeight="1" spans="4:4">
       <c r="D949" s="3"/>
     </row>
-    <row r="950">
+    <row r="950" customHeight="1" spans="4:4">
       <c r="D950" s="3"/>
     </row>
-    <row r="951">
+    <row r="951" customHeight="1" spans="4:4">
       <c r="D951" s="3"/>
     </row>
-    <row r="952">
+    <row r="952" customHeight="1" spans="4:4">
       <c r="D952" s="3"/>
     </row>
-    <row r="953">
+    <row r="953" customHeight="1" spans="4:4">
       <c r="D953" s="3"/>
     </row>
-    <row r="954">
+    <row r="954" customHeight="1" spans="4:4">
       <c r="D954" s="3"/>
     </row>
-    <row r="955">
+    <row r="955" customHeight="1" spans="4:4">
       <c r="D955" s="3"/>
     </row>
-    <row r="956">
+    <row r="956" customHeight="1" spans="4:4">
       <c r="D956" s="3"/>
     </row>
-    <row r="957">
+    <row r="957" customHeight="1" spans="4:4">
       <c r="D957" s="3"/>
     </row>
-    <row r="958">
+    <row r="958" customHeight="1" spans="4:4">
       <c r="D958" s="3"/>
     </row>
-    <row r="959">
+    <row r="959" customHeight="1" spans="4:4">
       <c r="D959" s="3"/>
     </row>
-    <row r="960">
+    <row r="960" customHeight="1" spans="4:4">
       <c r="D960" s="3"/>
     </row>
-    <row r="961">
+    <row r="961" customHeight="1" spans="4:4">
       <c r="D961" s="3"/>
     </row>
-    <row r="962">
+    <row r="962" customHeight="1" spans="4:4">
       <c r="D962" s="3"/>
     </row>
-    <row r="963">
+    <row r="963" customHeight="1" spans="4:4">
       <c r="D963" s="3"/>
     </row>
-    <row r="964">
+    <row r="964" customHeight="1" spans="4:4">
       <c r="D964" s="3"/>
     </row>
-    <row r="965">
+    <row r="965" customHeight="1" spans="4:4">
       <c r="D965" s="3"/>
     </row>
-    <row r="966">
+    <row r="966" customHeight="1" spans="4:4">
       <c r="D966" s="3"/>
     </row>
-    <row r="967">
+    <row r="967" customHeight="1" spans="4:4">
       <c r="D967" s="3"/>
     </row>
-    <row r="968">
+    <row r="968" customHeight="1" spans="4:4">
       <c r="D968" s="3"/>
     </row>
-    <row r="969">
+    <row r="969" customHeight="1" spans="4:4">
       <c r="D969" s="3"/>
     </row>
-    <row r="970">
+    <row r="970" customHeight="1" spans="4:4">
       <c r="D970" s="3"/>
     </row>
-    <row r="971">
+    <row r="971" customHeight="1" spans="4:4">
       <c r="D971" s="3"/>
     </row>
-    <row r="972">
+    <row r="972" customHeight="1" spans="4:4">
       <c r="D972" s="3"/>
     </row>
-    <row r="973">
+    <row r="973" customHeight="1" spans="4:4">
       <c r="D973" s="3"/>
     </row>
-    <row r="974">
+    <row r="974" customHeight="1" spans="4:4">
       <c r="D974" s="3"/>
     </row>
-    <row r="975">
+    <row r="975" customHeight="1" spans="4:4">
       <c r="D975" s="3"/>
     </row>
-    <row r="976">
+    <row r="976" customHeight="1" spans="4:4">
       <c r="D976" s="3"/>
     </row>
-    <row r="977">
+    <row r="977" customHeight="1" spans="4:4">
       <c r="D977" s="3"/>
     </row>
-    <row r="978">
+    <row r="978" customHeight="1" spans="4:4">
       <c r="D978" s="3"/>
     </row>
-    <row r="979">
+    <row r="979" customHeight="1" spans="4:4">
       <c r="D979" s="3"/>
     </row>
-    <row r="980">
+    <row r="980" customHeight="1" spans="4:4">
       <c r="D980" s="3"/>
     </row>
-    <row r="981">
+    <row r="981" customHeight="1" spans="4:4">
       <c r="D981" s="3"/>
     </row>
-    <row r="982">
+    <row r="982" customHeight="1" spans="4:4">
       <c r="D982" s="3"/>
     </row>
-    <row r="983">
+    <row r="983" customHeight="1" spans="4:4">
       <c r="D983" s="3"/>
     </row>
-    <row r="984">
+    <row r="984" customHeight="1" spans="4:4">
       <c r="D984" s="3"/>
     </row>
-    <row r="985">
+    <row r="985" customHeight="1" spans="4:4">
       <c r="D985" s="3"/>
     </row>
-    <row r="986">
+    <row r="986" customHeight="1" spans="4:4">
       <c r="D986" s="3"/>
     </row>
-    <row r="987">
+    <row r="987" customHeight="1" spans="4:4">
       <c r="D987" s="3"/>
     </row>
-    <row r="988">
+    <row r="988" customHeight="1" spans="4:4">
       <c r="D988" s="3"/>
     </row>
-    <row r="989">
+    <row r="989" customHeight="1" spans="4:4">
       <c r="D989" s="3"/>
     </row>
-    <row r="990">
+    <row r="990" customHeight="1" spans="4:4">
       <c r="D990" s="3"/>
     </row>
-    <row r="991">
+    <row r="991" customHeight="1" spans="4:4">
       <c r="D991" s="3"/>
     </row>
-    <row r="992">
+    <row r="992" customHeight="1" spans="4:4">
       <c r="D992" s="3"/>
     </row>
-    <row r="993">
+    <row r="993" customHeight="1" spans="4:4">
       <c r="D993" s="3"/>
     </row>
-    <row r="994">
+    <row r="994" customHeight="1" spans="4:4">
       <c r="D994" s="3"/>
     </row>
-    <row r="995">
+    <row r="995" customHeight="1" spans="4:4">
       <c r="D995" s="3"/>
     </row>
-    <row r="996">
+    <row r="996" customHeight="1" spans="4:4">
       <c r="D996" s="3"/>
     </row>
-    <row r="997">
+    <row r="997" customHeight="1" spans="4:4">
       <c r="D997" s="3"/>
     </row>
-    <row r="998">
+    <row r="998" customHeight="1" spans="4:4">
       <c r="D998" s="3"/>
     </row>
-    <row r="999">
+    <row r="999" customHeight="1" spans="4:4">
       <c r="D999" s="3"/>
     </row>
-    <row r="1000">
+    <row r="1000" customHeight="1" spans="4:4">
       <c r="D1000" s="3"/>
     </row>
-    <row r="1001">
+    <row r="1001" customHeight="1" spans="4:4">
       <c r="D1001" s="3"/>
     </row>
   </sheetData>
@@ -3797,6 +4659,7 @@
       <formula>LEN(TRIM(D1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/SoundData.xlsx
+++ b/JsonConverter/ExcelFiles/SoundData.xlsx
@@ -1,12 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="시트1" sheetId="1" r:id="rId5"/>
+    <sheet name="시트1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -49,7 +65,7 @@
     <t>Sound_BGM_01</t>
   </si>
   <si>
-    <t>BGM_01</t>
+    <t>PlayTheme</t>
   </si>
   <si>
     <t>true</t>
@@ -205,71 +221,915 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
-    <border/>
+  <borders count="9">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="18">
     <dxf>
-      <font/>
       <fill>
         <patternFill patternType="none"/>
       </fill>
-      <border/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
     </dxf>
   </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="totalRow" dxfId="5"/>
+      <tableStyleElement type="firstColumn" dxfId="4"/>
+      <tableStyleElement type="lastColumn" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="totalRow" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
+      <tableStyleElement type="pageFieldValues" dxfId="8"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -459,28 +1319,30 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:D1001"/>
+  <sheetFormatPr defaultColWidth="12.6296296296296" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="3"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.75"/>
-    <col customWidth="1" min="2" max="2" width="14.5"/>
-    <col customWidth="1" min="3" max="3" width="13.5"/>
-    <col customWidth="1" min="4" max="4" width="12.75"/>
-    <col customWidth="1" min="5" max="5" width="16.5"/>
-    <col customWidth="1" min="6" max="6" width="16.25"/>
-    <col customWidth="1" min="7" max="7" width="23.75"/>
-    <col customWidth="1" min="8" max="8" width="29.63"/>
-    <col customWidth="1" min="9" max="9" width="17.25"/>
+    <col min="1" max="1" width="14.75" customWidth="1"/>
+    <col min="2" max="2" width="14.5" customWidth="1"/>
+    <col min="3" max="3" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="12.75" customWidth="1"/>
+    <col min="5" max="5" width="16.5" customWidth="1"/>
+    <col min="6" max="6" width="16.25" customWidth="1"/>
+    <col min="7" max="7" width="23.75" customWidth="1"/>
+    <col min="8" max="8" width="29.6296296296296" customWidth="1"/>
+    <col min="9" max="9" width="17.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -494,7 +1356,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" customHeight="1" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -508,7 +1370,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" customHeight="1" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -522,7 +1384,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" customHeight="1" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -530,13 +1392,13 @@
         <v>12</v>
       </c>
       <c r="C4" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" customHeight="1" spans="1:4">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -544,13 +1406,13 @@
         <v>15</v>
       </c>
       <c r="C5" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" customHeight="1" spans="1:4">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -558,13 +1420,13 @@
         <v>17</v>
       </c>
       <c r="C6" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" customHeight="1" spans="1:4">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -572,13 +1434,13 @@
         <v>20</v>
       </c>
       <c r="C7" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" customHeight="1" spans="1:4">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -586,13 +1448,13 @@
         <v>22</v>
       </c>
       <c r="C8" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" customHeight="1" spans="1:4">
       <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
@@ -600,13 +1462,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" customHeight="1" spans="1:4">
       <c r="A10" s="1" t="s">
         <v>25</v>
       </c>
@@ -614,13 +1476,13 @@
         <v>26</v>
       </c>
       <c r="C10" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" customHeight="1" spans="1:4">
       <c r="A11" s="1" t="s">
         <v>27</v>
       </c>
@@ -628,13 +1490,13 @@
         <v>28</v>
       </c>
       <c r="C11" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" customHeight="1" spans="1:4">
       <c r="A12" s="1" t="s">
         <v>29</v>
       </c>
@@ -642,13 +1504,13 @@
         <v>30</v>
       </c>
       <c r="C12" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" customHeight="1" spans="1:4">
       <c r="A13" s="1" t="s">
         <v>31</v>
       </c>
@@ -656,13 +1518,13 @@
         <v>32</v>
       </c>
       <c r="C13" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" customHeight="1" spans="1:4">
       <c r="A14" s="1" t="s">
         <v>33</v>
       </c>
@@ -670,13 +1532,13 @@
         <v>34</v>
       </c>
       <c r="C14" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" customHeight="1" spans="1:4">
       <c r="A15" s="1" t="s">
         <v>35</v>
       </c>
@@ -684,13 +1546,13 @@
         <v>36</v>
       </c>
       <c r="C15" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" customHeight="1" spans="1:4">
       <c r="A16" s="1" t="s">
         <v>37</v>
       </c>
@@ -698,13 +1560,13 @@
         <v>38</v>
       </c>
       <c r="C16" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" customHeight="1" spans="1:4">
       <c r="A17" s="1" t="s">
         <v>39</v>
       </c>
@@ -712,13 +1574,13 @@
         <v>40</v>
       </c>
       <c r="C17" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" customHeight="1" spans="1:4">
       <c r="A18" s="1" t="s">
         <v>41</v>
       </c>
@@ -726,13 +1588,13 @@
         <v>42</v>
       </c>
       <c r="C18" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" customHeight="1" spans="1:4">
       <c r="A19" s="1" t="s">
         <v>43</v>
       </c>
@@ -740,13 +1602,13 @@
         <v>44</v>
       </c>
       <c r="C19" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" customHeight="1" spans="1:4">
       <c r="A20" s="1" t="s">
         <v>45</v>
       </c>
@@ -754,13 +1616,13 @@
         <v>46</v>
       </c>
       <c r="C20" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" customHeight="1" spans="1:4">
       <c r="A21" s="1" t="s">
         <v>47</v>
       </c>
@@ -768,13 +1630,13 @@
         <v>48</v>
       </c>
       <c r="C21" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" customHeight="1" spans="1:4">
       <c r="A22" s="1" t="s">
         <v>49</v>
       </c>
@@ -782,13 +1644,13 @@
         <v>50</v>
       </c>
       <c r="C22" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" customHeight="1" spans="1:4">
       <c r="A23" s="1" t="s">
         <v>51</v>
       </c>
@@ -796,13 +1658,13 @@
         <v>52</v>
       </c>
       <c r="C23" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" customHeight="1" spans="1:4">
       <c r="A24" s="1" t="s">
         <v>53</v>
       </c>
@@ -810,13 +1672,13 @@
         <v>54</v>
       </c>
       <c r="C24" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" customHeight="1" spans="1:4">
       <c r="A25" s="1" t="s">
         <v>55</v>
       </c>
@@ -824,13 +1686,13 @@
         <v>56</v>
       </c>
       <c r="C25" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" customHeight="1" spans="1:4">
       <c r="A26" s="1" t="s">
         <v>57</v>
       </c>
@@ -838,13 +1700,13 @@
         <v>58</v>
       </c>
       <c r="C26" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" customHeight="1" spans="1:4">
       <c r="A27" s="1" t="s">
         <v>59</v>
       </c>
@@ -852,13 +1714,13 @@
         <v>60</v>
       </c>
       <c r="C27" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" customHeight="1" spans="1:4">
       <c r="A28" s="1" t="s">
         <v>61</v>
       </c>
@@ -866,2929 +1728,2929 @@
         <v>62</v>
       </c>
       <c r="C28" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" customHeight="1" spans="1:4">
       <c r="D29" s="3"/>
     </row>
-    <row r="30">
+    <row r="30" customHeight="1" spans="1:4">
       <c r="D30" s="3"/>
     </row>
-    <row r="31">
+    <row r="31" customHeight="1" spans="1:4">
       <c r="D31" s="3"/>
     </row>
-    <row r="32">
+    <row r="32" customHeight="1" spans="1:4">
       <c r="D32" s="3"/>
     </row>
-    <row r="33">
+    <row r="33" customHeight="1" spans="4:4">
       <c r="D33" s="3"/>
     </row>
-    <row r="34">
+    <row r="34" customHeight="1" spans="4:4">
       <c r="D34" s="3"/>
     </row>
-    <row r="35">
+    <row r="35" customHeight="1" spans="4:4">
       <c r="D35" s="3"/>
     </row>
-    <row r="36">
+    <row r="36" customHeight="1" spans="4:4">
       <c r="D36" s="3"/>
     </row>
-    <row r="37">
+    <row r="37" customHeight="1" spans="4:4">
       <c r="D37" s="3"/>
     </row>
-    <row r="38">
+    <row r="38" customHeight="1" spans="4:4">
       <c r="D38" s="3"/>
     </row>
-    <row r="39">
+    <row r="39" customHeight="1" spans="4:4">
       <c r="D39" s="3"/>
     </row>
-    <row r="40">
+    <row r="40" customHeight="1" spans="4:4">
       <c r="D40" s="3"/>
     </row>
-    <row r="41">
+    <row r="41" customHeight="1" spans="4:4">
       <c r="D41" s="3"/>
     </row>
-    <row r="42">
+    <row r="42" customHeight="1" spans="4:4">
       <c r="D42" s="3"/>
     </row>
-    <row r="43">
+    <row r="43" customHeight="1" spans="4:4">
       <c r="D43" s="3"/>
     </row>
-    <row r="44">
+    <row r="44" customHeight="1" spans="4:4">
       <c r="D44" s="3"/>
     </row>
-    <row r="45">
+    <row r="45" customHeight="1" spans="4:4">
       <c r="D45" s="3"/>
     </row>
-    <row r="46">
+    <row r="46" customHeight="1" spans="4:4">
       <c r="D46" s="3"/>
     </row>
-    <row r="47">
+    <row r="47" customHeight="1" spans="4:4">
       <c r="D47" s="3"/>
     </row>
-    <row r="48">
+    <row r="48" customHeight="1" spans="4:4">
       <c r="D48" s="3"/>
     </row>
-    <row r="49">
+    <row r="49" customHeight="1" spans="4:4">
       <c r="D49" s="3"/>
     </row>
-    <row r="50">
+    <row r="50" customHeight="1" spans="4:4">
       <c r="D50" s="3"/>
     </row>
-    <row r="51">
+    <row r="51" customHeight="1" spans="4:4">
       <c r="D51" s="3"/>
     </row>
-    <row r="52">
+    <row r="52" customHeight="1" spans="4:4">
       <c r="D52" s="3"/>
     </row>
-    <row r="53">
+    <row r="53" customHeight="1" spans="4:4">
       <c r="D53" s="3"/>
     </row>
-    <row r="54">
+    <row r="54" customHeight="1" spans="4:4">
       <c r="D54" s="3"/>
     </row>
-    <row r="55">
+    <row r="55" customHeight="1" spans="4:4">
       <c r="D55" s="3"/>
     </row>
-    <row r="56">
+    <row r="56" customHeight="1" spans="4:4">
       <c r="D56" s="3"/>
     </row>
-    <row r="57">
+    <row r="57" customHeight="1" spans="4:4">
       <c r="D57" s="3"/>
     </row>
-    <row r="58">
+    <row r="58" customHeight="1" spans="4:4">
       <c r="D58" s="3"/>
     </row>
-    <row r="59">
+    <row r="59" customHeight="1" spans="4:4">
       <c r="D59" s="3"/>
     </row>
-    <row r="60">
+    <row r="60" customHeight="1" spans="4:4">
       <c r="D60" s="3"/>
     </row>
-    <row r="61">
+    <row r="61" customHeight="1" spans="4:4">
       <c r="D61" s="3"/>
     </row>
-    <row r="62">
+    <row r="62" customHeight="1" spans="4:4">
       <c r="D62" s="3"/>
     </row>
-    <row r="63">
+    <row r="63" customHeight="1" spans="4:4">
       <c r="D63" s="3"/>
     </row>
-    <row r="64">
+    <row r="64" customHeight="1" spans="4:4">
       <c r="D64" s="3"/>
     </row>
-    <row r="65">
+    <row r="65" customHeight="1" spans="4:4">
       <c r="D65" s="3"/>
     </row>
-    <row r="66">
+    <row r="66" customHeight="1" spans="4:4">
       <c r="D66" s="3"/>
     </row>
-    <row r="67">
+    <row r="67" customHeight="1" spans="4:4">
       <c r="D67" s="3"/>
     </row>
-    <row r="68">
+    <row r="68" customHeight="1" spans="4:4">
       <c r="D68" s="3"/>
     </row>
-    <row r="69">
+    <row r="69" customHeight="1" spans="4:4">
       <c r="D69" s="3"/>
     </row>
-    <row r="70">
+    <row r="70" customHeight="1" spans="4:4">
       <c r="D70" s="3"/>
     </row>
-    <row r="71">
+    <row r="71" customHeight="1" spans="4:4">
       <c r="D71" s="3"/>
     </row>
-    <row r="72">
+    <row r="72" customHeight="1" spans="4:4">
       <c r="D72" s="3"/>
     </row>
-    <row r="73">
+    <row r="73" customHeight="1" spans="4:4">
       <c r="D73" s="3"/>
     </row>
-    <row r="74">
+    <row r="74" customHeight="1" spans="4:4">
       <c r="D74" s="3"/>
     </row>
-    <row r="75">
+    <row r="75" customHeight="1" spans="4:4">
       <c r="D75" s="3"/>
     </row>
-    <row r="76">
+    <row r="76" customHeight="1" spans="4:4">
       <c r="D76" s="3"/>
     </row>
-    <row r="77">
+    <row r="77" customHeight="1" spans="4:4">
       <c r="D77" s="3"/>
     </row>
-    <row r="78">
+    <row r="78" customHeight="1" spans="4:4">
       <c r="D78" s="3"/>
     </row>
-    <row r="79">
+    <row r="79" customHeight="1" spans="4:4">
       <c r="D79" s="3"/>
     </row>
-    <row r="80">
+    <row r="80" customHeight="1" spans="4:4">
       <c r="D80" s="3"/>
     </row>
-    <row r="81">
+    <row r="81" customHeight="1" spans="4:4">
       <c r="D81" s="3"/>
     </row>
-    <row r="82">
+    <row r="82" customHeight="1" spans="4:4">
       <c r="D82" s="3"/>
     </row>
-    <row r="83">
+    <row r="83" customHeight="1" spans="4:4">
       <c r="D83" s="3"/>
     </row>
-    <row r="84">
+    <row r="84" customHeight="1" spans="4:4">
       <c r="D84" s="3"/>
     </row>
-    <row r="85">
+    <row r="85" customHeight="1" spans="4:4">
       <c r="D85" s="3"/>
     </row>
-    <row r="86">
+    <row r="86" customHeight="1" spans="4:4">
       <c r="D86" s="3"/>
     </row>
-    <row r="87">
+    <row r="87" customHeight="1" spans="4:4">
       <c r="D87" s="3"/>
     </row>
-    <row r="88">
+    <row r="88" customHeight="1" spans="4:4">
       <c r="D88" s="3"/>
     </row>
-    <row r="89">
+    <row r="89" customHeight="1" spans="4:4">
       <c r="D89" s="3"/>
     </row>
-    <row r="90">
+    <row r="90" customHeight="1" spans="4:4">
       <c r="D90" s="3"/>
     </row>
-    <row r="91">
+    <row r="91" customHeight="1" spans="4:4">
       <c r="D91" s="3"/>
     </row>
-    <row r="92">
+    <row r="92" customHeight="1" spans="4:4">
       <c r="D92" s="3"/>
     </row>
-    <row r="93">
+    <row r="93" customHeight="1" spans="4:4">
       <c r="D93" s="3"/>
     </row>
-    <row r="94">
+    <row r="94" customHeight="1" spans="4:4">
       <c r="D94" s="3"/>
     </row>
-    <row r="95">
+    <row r="95" customHeight="1" spans="4:4">
       <c r="D95" s="3"/>
     </row>
-    <row r="96">
+    <row r="96" customHeight="1" spans="4:4">
       <c r="D96" s="3"/>
     </row>
-    <row r="97">
+    <row r="97" customHeight="1" spans="4:4">
       <c r="D97" s="3"/>
     </row>
-    <row r="98">
+    <row r="98" customHeight="1" spans="4:4">
       <c r="D98" s="3"/>
     </row>
-    <row r="99">
+    <row r="99" customHeight="1" spans="4:4">
       <c r="D99" s="3"/>
     </row>
-    <row r="100">
+    <row r="100" customHeight="1" spans="4:4">
       <c r="D100" s="3"/>
     </row>
-    <row r="101">
+    <row r="101" customHeight="1" spans="4:4">
       <c r="D101" s="3"/>
     </row>
-    <row r="102">
+    <row r="102" customHeight="1" spans="4:4">
       <c r="D102" s="3"/>
     </row>
-    <row r="103">
+    <row r="103" customHeight="1" spans="4:4">
       <c r="D103" s="3"/>
     </row>
-    <row r="104">
+    <row r="104" customHeight="1" spans="4:4">
       <c r="D104" s="3"/>
     </row>
-    <row r="105">
+    <row r="105" customHeight="1" spans="4:4">
       <c r="D105" s="3"/>
     </row>
-    <row r="106">
+    <row r="106" customHeight="1" spans="4:4">
       <c r="D106" s="3"/>
     </row>
-    <row r="107">
+    <row r="107" customHeight="1" spans="4:4">
       <c r="D107" s="3"/>
     </row>
-    <row r="108">
+    <row r="108" customHeight="1" spans="4:4">
       <c r="D108" s="3"/>
     </row>
-    <row r="109">
+    <row r="109" customHeight="1" spans="4:4">
       <c r="D109" s="3"/>
     </row>
-    <row r="110">
+    <row r="110" customHeight="1" spans="4:4">
       <c r="D110" s="3"/>
     </row>
-    <row r="111">
+    <row r="111" customHeight="1" spans="4:4">
       <c r="D111" s="3"/>
     </row>
-    <row r="112">
+    <row r="112" customHeight="1" spans="4:4">
       <c r="D112" s="3"/>
     </row>
-    <row r="113">
+    <row r="113" customHeight="1" spans="4:4">
       <c r="D113" s="3"/>
     </row>
-    <row r="114">
+    <row r="114" customHeight="1" spans="4:4">
       <c r="D114" s="3"/>
     </row>
-    <row r="115">
+    <row r="115" customHeight="1" spans="4:4">
       <c r="D115" s="3"/>
     </row>
-    <row r="116">
+    <row r="116" customHeight="1" spans="4:4">
       <c r="D116" s="3"/>
     </row>
-    <row r="117">
+    <row r="117" customHeight="1" spans="4:4">
       <c r="D117" s="3"/>
     </row>
-    <row r="118">
+    <row r="118" customHeight="1" spans="4:4">
       <c r="D118" s="3"/>
     </row>
-    <row r="119">
+    <row r="119" customHeight="1" spans="4:4">
       <c r="D119" s="3"/>
     </row>
-    <row r="120">
+    <row r="120" customHeight="1" spans="4:4">
       <c r="D120" s="3"/>
     </row>
-    <row r="121">
+    <row r="121" customHeight="1" spans="4:4">
       <c r="D121" s="3"/>
     </row>
-    <row r="122">
+    <row r="122" customHeight="1" spans="4:4">
       <c r="D122" s="3"/>
     </row>
-    <row r="123">
+    <row r="123" customHeight="1" spans="4:4">
       <c r="D123" s="3"/>
     </row>
-    <row r="124">
+    <row r="124" customHeight="1" spans="4:4">
       <c r="D124" s="3"/>
     </row>
-    <row r="125">
+    <row r="125" customHeight="1" spans="4:4">
       <c r="D125" s="3"/>
     </row>
-    <row r="126">
+    <row r="126" customHeight="1" spans="4:4">
       <c r="D126" s="3"/>
     </row>
-    <row r="127">
+    <row r="127" customHeight="1" spans="4:4">
       <c r="D127" s="3"/>
     </row>
-    <row r="128">
+    <row r="128" customHeight="1" spans="4:4">
       <c r="D128" s="3"/>
     </row>
-    <row r="129">
+    <row r="129" customHeight="1" spans="4:4">
       <c r="D129" s="3"/>
     </row>
-    <row r="130">
+    <row r="130" customHeight="1" spans="4:4">
       <c r="D130" s="3"/>
     </row>
-    <row r="131">
+    <row r="131" customHeight="1" spans="4:4">
       <c r="D131" s="3"/>
     </row>
-    <row r="132">
+    <row r="132" customHeight="1" spans="4:4">
       <c r="D132" s="3"/>
     </row>
-    <row r="133">
+    <row r="133" customHeight="1" spans="4:4">
       <c r="D133" s="3"/>
     </row>
-    <row r="134">
+    <row r="134" customHeight="1" spans="4:4">
       <c r="D134" s="3"/>
     </row>
-    <row r="135">
+    <row r="135" customHeight="1" spans="4:4">
       <c r="D135" s="3"/>
     </row>
-    <row r="136">
+    <row r="136" customHeight="1" spans="4:4">
       <c r="D136" s="3"/>
     </row>
-    <row r="137">
+    <row r="137" customHeight="1" spans="4:4">
       <c r="D137" s="3"/>
     </row>
-    <row r="138">
+    <row r="138" customHeight="1" spans="4:4">
       <c r="D138" s="3"/>
     </row>
-    <row r="139">
+    <row r="139" customHeight="1" spans="4:4">
       <c r="D139" s="3"/>
     </row>
-    <row r="140">
+    <row r="140" customHeight="1" spans="4:4">
       <c r="D140" s="3"/>
     </row>
-    <row r="141">
+    <row r="141" customHeight="1" spans="4:4">
       <c r="D141" s="3"/>
     </row>
-    <row r="142">
+    <row r="142" customHeight="1" spans="4:4">
       <c r="D142" s="3"/>
     </row>
-    <row r="143">
+    <row r="143" customHeight="1" spans="4:4">
       <c r="D143" s="3"/>
     </row>
-    <row r="144">
+    <row r="144" customHeight="1" spans="4:4">
       <c r="D144" s="3"/>
     </row>
-    <row r="145">
+    <row r="145" customHeight="1" spans="4:4">
       <c r="D145" s="3"/>
     </row>
-    <row r="146">
+    <row r="146" customHeight="1" spans="4:4">
       <c r="D146" s="3"/>
     </row>
-    <row r="147">
+    <row r="147" customHeight="1" spans="4:4">
       <c r="D147" s="3"/>
     </row>
-    <row r="148">
+    <row r="148" customHeight="1" spans="4:4">
       <c r="D148" s="3"/>
     </row>
-    <row r="149">
+    <row r="149" customHeight="1" spans="4:4">
       <c r="D149" s="3"/>
     </row>
-    <row r="150">
+    <row r="150" customHeight="1" spans="4:4">
       <c r="D150" s="3"/>
     </row>
-    <row r="151">
+    <row r="151" customHeight="1" spans="4:4">
       <c r="D151" s="3"/>
     </row>
-    <row r="152">
+    <row r="152" customHeight="1" spans="4:4">
       <c r="D152" s="3"/>
     </row>
-    <row r="153">
+    <row r="153" customHeight="1" spans="4:4">
       <c r="D153" s="3"/>
     </row>
-    <row r="154">
+    <row r="154" customHeight="1" spans="4:4">
       <c r="D154" s="3"/>
     </row>
-    <row r="155">
+    <row r="155" customHeight="1" spans="4:4">
       <c r="D155" s="3"/>
     </row>
-    <row r="156">
+    <row r="156" customHeight="1" spans="4:4">
       <c r="D156" s="3"/>
     </row>
-    <row r="157">
+    <row r="157" customHeight="1" spans="4:4">
       <c r="D157" s="3"/>
     </row>
-    <row r="158">
+    <row r="158" customHeight="1" spans="4:4">
       <c r="D158" s="3"/>
     </row>
-    <row r="159">
+    <row r="159" customHeight="1" spans="4:4">
       <c r="D159" s="3"/>
     </row>
-    <row r="160">
+    <row r="160" customHeight="1" spans="4:4">
       <c r="D160" s="3"/>
     </row>
-    <row r="161">
+    <row r="161" customHeight="1" spans="4:4">
       <c r="D161" s="3"/>
     </row>
-    <row r="162">
+    <row r="162" customHeight="1" spans="4:4">
       <c r="D162" s="3"/>
     </row>
-    <row r="163">
+    <row r="163" customHeight="1" spans="4:4">
       <c r="D163" s="3"/>
     </row>
-    <row r="164">
+    <row r="164" customHeight="1" spans="4:4">
       <c r="D164" s="3"/>
     </row>
-    <row r="165">
+    <row r="165" customHeight="1" spans="4:4">
       <c r="D165" s="3"/>
     </row>
-    <row r="166">
+    <row r="166" customHeight="1" spans="4:4">
       <c r="D166" s="3"/>
     </row>
-    <row r="167">
+    <row r="167" customHeight="1" spans="4:4">
       <c r="D167" s="3"/>
     </row>
-    <row r="168">
+    <row r="168" customHeight="1" spans="4:4">
       <c r="D168" s="3"/>
     </row>
-    <row r="169">
+    <row r="169" customHeight="1" spans="4:4">
       <c r="D169" s="3"/>
     </row>
-    <row r="170">
+    <row r="170" customHeight="1" spans="4:4">
       <c r="D170" s="3"/>
     </row>
-    <row r="171">
+    <row r="171" customHeight="1" spans="4:4">
       <c r="D171" s="3"/>
     </row>
-    <row r="172">
+    <row r="172" customHeight="1" spans="4:4">
       <c r="D172" s="3"/>
     </row>
-    <row r="173">
+    <row r="173" customHeight="1" spans="4:4">
       <c r="D173" s="3"/>
     </row>
-    <row r="174">
+    <row r="174" customHeight="1" spans="4:4">
       <c r="D174" s="3"/>
     </row>
-    <row r="175">
+    <row r="175" customHeight="1" spans="4:4">
       <c r="D175" s="3"/>
     </row>
-    <row r="176">
+    <row r="176" customHeight="1" spans="4:4">
       <c r="D176" s="3"/>
     </row>
-    <row r="177">
+    <row r="177" customHeight="1" spans="4:4">
       <c r="D177" s="3"/>
     </row>
-    <row r="178">
+    <row r="178" customHeight="1" spans="4:4">
       <c r="D178" s="3"/>
     </row>
-    <row r="179">
+    <row r="179" customHeight="1" spans="4:4">
       <c r="D179" s="3"/>
     </row>
-    <row r="180">
+    <row r="180" customHeight="1" spans="4:4">
       <c r="D180" s="3"/>
     </row>
-    <row r="181">
+    <row r="181" customHeight="1" spans="4:4">
       <c r="D181" s="3"/>
     </row>
-    <row r="182">
+    <row r="182" customHeight="1" spans="4:4">
       <c r="D182" s="3"/>
     </row>
-    <row r="183">
+    <row r="183" customHeight="1" spans="4:4">
       <c r="D183" s="3"/>
     </row>
-    <row r="184">
+    <row r="184" customHeight="1" spans="4:4">
       <c r="D184" s="3"/>
     </row>
-    <row r="185">
+    <row r="185" customHeight="1" spans="4:4">
       <c r="D185" s="3"/>
     </row>
-    <row r="186">
+    <row r="186" customHeight="1" spans="4:4">
       <c r="D186" s="3"/>
     </row>
-    <row r="187">
+    <row r="187" customHeight="1" spans="4:4">
       <c r="D187" s="3"/>
     </row>
-    <row r="188">
+    <row r="188" customHeight="1" spans="4:4">
       <c r="D188" s="3"/>
     </row>
-    <row r="189">
+    <row r="189" customHeight="1" spans="4:4">
       <c r="D189" s="3"/>
     </row>
-    <row r="190">
+    <row r="190" customHeight="1" spans="4:4">
       <c r="D190" s="3"/>
     </row>
-    <row r="191">
+    <row r="191" customHeight="1" spans="4:4">
       <c r="D191" s="3"/>
     </row>
-    <row r="192">
+    <row r="192" customHeight="1" spans="4:4">
       <c r="D192" s="3"/>
     </row>
-    <row r="193">
+    <row r="193" customHeight="1" spans="4:4">
       <c r="D193" s="3"/>
     </row>
-    <row r="194">
+    <row r="194" customHeight="1" spans="4:4">
       <c r="D194" s="3"/>
     </row>
-    <row r="195">
+    <row r="195" customHeight="1" spans="4:4">
       <c r="D195" s="3"/>
     </row>
-    <row r="196">
+    <row r="196" customHeight="1" spans="4:4">
       <c r="D196" s="3"/>
     </row>
-    <row r="197">
+    <row r="197" customHeight="1" spans="4:4">
       <c r="D197" s="3"/>
     </row>
-    <row r="198">
+    <row r="198" customHeight="1" spans="4:4">
       <c r="D198" s="3"/>
     </row>
-    <row r="199">
+    <row r="199" customHeight="1" spans="4:4">
       <c r="D199" s="3"/>
     </row>
-    <row r="200">
+    <row r="200" customHeight="1" spans="4:4">
       <c r="D200" s="3"/>
     </row>
-    <row r="201">
+    <row r="201" customHeight="1" spans="4:4">
       <c r="D201" s="3"/>
     </row>
-    <row r="202">
+    <row r="202" customHeight="1" spans="4:4">
       <c r="D202" s="3"/>
     </row>
-    <row r="203">
+    <row r="203" customHeight="1" spans="4:4">
       <c r="D203" s="3"/>
     </row>
-    <row r="204">
+    <row r="204" customHeight="1" spans="4:4">
       <c r="D204" s="3"/>
     </row>
-    <row r="205">
+    <row r="205" customHeight="1" spans="4:4">
       <c r="D205" s="3"/>
     </row>
-    <row r="206">
+    <row r="206" customHeight="1" spans="4:4">
       <c r="D206" s="3"/>
     </row>
-    <row r="207">
+    <row r="207" customHeight="1" spans="4:4">
       <c r="D207" s="3"/>
     </row>
-    <row r="208">
+    <row r="208" customHeight="1" spans="4:4">
       <c r="D208" s="3"/>
     </row>
-    <row r="209">
+    <row r="209" customHeight="1" spans="4:4">
       <c r="D209" s="3"/>
     </row>
-    <row r="210">
+    <row r="210" customHeight="1" spans="4:4">
       <c r="D210" s="3"/>
     </row>
-    <row r="211">
+    <row r="211" customHeight="1" spans="4:4">
       <c r="D211" s="3"/>
     </row>
-    <row r="212">
+    <row r="212" customHeight="1" spans="4:4">
       <c r="D212" s="3"/>
     </row>
-    <row r="213">
+    <row r="213" customHeight="1" spans="4:4">
       <c r="D213" s="3"/>
     </row>
-    <row r="214">
+    <row r="214" customHeight="1" spans="4:4">
       <c r="D214" s="3"/>
     </row>
-    <row r="215">
+    <row r="215" customHeight="1" spans="4:4">
       <c r="D215" s="3"/>
     </row>
-    <row r="216">
+    <row r="216" customHeight="1" spans="4:4">
       <c r="D216" s="3"/>
     </row>
-    <row r="217">
+    <row r="217" customHeight="1" spans="4:4">
       <c r="D217" s="3"/>
     </row>
-    <row r="218">
+    <row r="218" customHeight="1" spans="4:4">
       <c r="D218" s="3"/>
     </row>
-    <row r="219">
+    <row r="219" customHeight="1" spans="4:4">
       <c r="D219" s="3"/>
     </row>
-    <row r="220">
+    <row r="220" customHeight="1" spans="4:4">
       <c r="D220" s="3"/>
     </row>
-    <row r="221">
+    <row r="221" customHeight="1" spans="4:4">
       <c r="D221" s="3"/>
     </row>
-    <row r="222">
+    <row r="222" customHeight="1" spans="4:4">
       <c r="D222" s="3"/>
     </row>
-    <row r="223">
+    <row r="223" customHeight="1" spans="4:4">
       <c r="D223" s="3"/>
     </row>
-    <row r="224">
+    <row r="224" customHeight="1" spans="4:4">
       <c r="D224" s="3"/>
     </row>
-    <row r="225">
+    <row r="225" customHeight="1" spans="4:4">
       <c r="D225" s="3"/>
     </row>
-    <row r="226">
+    <row r="226" customHeight="1" spans="4:4">
       <c r="D226" s="3"/>
     </row>
-    <row r="227">
+    <row r="227" customHeight="1" spans="4:4">
       <c r="D227" s="3"/>
     </row>
-    <row r="228">
+    <row r="228" customHeight="1" spans="4:4">
       <c r="D228" s="3"/>
     </row>
-    <row r="229">
+    <row r="229" customHeight="1" spans="4:4">
       <c r="D229" s="3"/>
     </row>
-    <row r="230">
+    <row r="230" customHeight="1" spans="4:4">
       <c r="D230" s="3"/>
     </row>
-    <row r="231">
+    <row r="231" customHeight="1" spans="4:4">
       <c r="D231" s="3"/>
     </row>
-    <row r="232">
+    <row r="232" customHeight="1" spans="4:4">
       <c r="D232" s="3"/>
     </row>
-    <row r="233">
+    <row r="233" customHeight="1" spans="4:4">
       <c r="D233" s="3"/>
     </row>
-    <row r="234">
+    <row r="234" customHeight="1" spans="4:4">
       <c r="D234" s="3"/>
     </row>
-    <row r="235">
+    <row r="235" customHeight="1" spans="4:4">
       <c r="D235" s="3"/>
     </row>
-    <row r="236">
+    <row r="236" customHeight="1" spans="4:4">
       <c r="D236" s="3"/>
     </row>
-    <row r="237">
+    <row r="237" customHeight="1" spans="4:4">
       <c r="D237" s="3"/>
     </row>
-    <row r="238">
+    <row r="238" customHeight="1" spans="4:4">
       <c r="D238" s="3"/>
     </row>
-    <row r="239">
+    <row r="239" customHeight="1" spans="4:4">
       <c r="D239" s="3"/>
     </row>
-    <row r="240">
+    <row r="240" customHeight="1" spans="4:4">
       <c r="D240" s="3"/>
     </row>
-    <row r="241">
+    <row r="241" customHeight="1" spans="4:4">
       <c r="D241" s="3"/>
     </row>
-    <row r="242">
+    <row r="242" customHeight="1" spans="4:4">
       <c r="D242" s="3"/>
     </row>
-    <row r="243">
+    <row r="243" customHeight="1" spans="4:4">
       <c r="D243" s="3"/>
     </row>
-    <row r="244">
+    <row r="244" customHeight="1" spans="4:4">
       <c r="D244" s="3"/>
     </row>
-    <row r="245">
+    <row r="245" customHeight="1" spans="4:4">
       <c r="D245" s="3"/>
     </row>
-    <row r="246">
+    <row r="246" customHeight="1" spans="4:4">
       <c r="D246" s="3"/>
     </row>
-    <row r="247">
+    <row r="247" customHeight="1" spans="4:4">
       <c r="D247" s="3"/>
     </row>
-    <row r="248">
+    <row r="248" customHeight="1" spans="4:4">
       <c r="D248" s="3"/>
     </row>
-    <row r="249">
+    <row r="249" customHeight="1" spans="4:4">
       <c r="D249" s="3"/>
     </row>
-    <row r="250">
+    <row r="250" customHeight="1" spans="4:4">
       <c r="D250" s="3"/>
     </row>
-    <row r="251">
+    <row r="251" customHeight="1" spans="4:4">
       <c r="D251" s="3"/>
     </row>
-    <row r="252">
+    <row r="252" customHeight="1" spans="4:4">
       <c r="D252" s="3"/>
     </row>
-    <row r="253">
+    <row r="253" customHeight="1" spans="4:4">
       <c r="D253" s="3"/>
     </row>
-    <row r="254">
+    <row r="254" customHeight="1" spans="4:4">
       <c r="D254" s="3"/>
     </row>
-    <row r="255">
+    <row r="255" customHeight="1" spans="4:4">
       <c r="D255" s="3"/>
     </row>
-    <row r="256">
+    <row r="256" customHeight="1" spans="4:4">
       <c r="D256" s="3"/>
     </row>
-    <row r="257">
+    <row r="257" customHeight="1" spans="4:4">
       <c r="D257" s="3"/>
     </row>
-    <row r="258">
+    <row r="258" customHeight="1" spans="4:4">
       <c r="D258" s="3"/>
     </row>
-    <row r="259">
+    <row r="259" customHeight="1" spans="4:4">
       <c r="D259" s="3"/>
     </row>
-    <row r="260">
+    <row r="260" customHeight="1" spans="4:4">
       <c r="D260" s="3"/>
     </row>
-    <row r="261">
+    <row r="261" customHeight="1" spans="4:4">
       <c r="D261" s="3"/>
     </row>
-    <row r="262">
+    <row r="262" customHeight="1" spans="4:4">
       <c r="D262" s="3"/>
     </row>
-    <row r="263">
+    <row r="263" customHeight="1" spans="4:4">
       <c r="D263" s="3"/>
     </row>
-    <row r="264">
+    <row r="264" customHeight="1" spans="4:4">
       <c r="D264" s="3"/>
     </row>
-    <row r="265">
+    <row r="265" customHeight="1" spans="4:4">
       <c r="D265" s="3"/>
     </row>
-    <row r="266">
+    <row r="266" customHeight="1" spans="4:4">
       <c r="D266" s="3"/>
     </row>
-    <row r="267">
+    <row r="267" customHeight="1" spans="4:4">
       <c r="D267" s="3"/>
     </row>
-    <row r="268">
+    <row r="268" customHeight="1" spans="4:4">
       <c r="D268" s="3"/>
     </row>
-    <row r="269">
+    <row r="269" customHeight="1" spans="4:4">
       <c r="D269" s="3"/>
     </row>
-    <row r="270">
+    <row r="270" customHeight="1" spans="4:4">
       <c r="D270" s="3"/>
     </row>
-    <row r="271">
+    <row r="271" customHeight="1" spans="4:4">
       <c r="D271" s="3"/>
     </row>
-    <row r="272">
+    <row r="272" customHeight="1" spans="4:4">
       <c r="D272" s="3"/>
     </row>
-    <row r="273">
+    <row r="273" customHeight="1" spans="4:4">
       <c r="D273" s="3"/>
     </row>
-    <row r="274">
+    <row r="274" customHeight="1" spans="4:4">
       <c r="D274" s="3"/>
     </row>
-    <row r="275">
+    <row r="275" customHeight="1" spans="4:4">
       <c r="D275" s="3"/>
     </row>
-    <row r="276">
+    <row r="276" customHeight="1" spans="4:4">
       <c r="D276" s="3"/>
     </row>
-    <row r="277">
+    <row r="277" customHeight="1" spans="4:4">
       <c r="D277" s="3"/>
     </row>
-    <row r="278">
+    <row r="278" customHeight="1" spans="4:4">
       <c r="D278" s="3"/>
     </row>
-    <row r="279">
+    <row r="279" customHeight="1" spans="4:4">
       <c r="D279" s="3"/>
     </row>
-    <row r="280">
+    <row r="280" customHeight="1" spans="4:4">
       <c r="D280" s="3"/>
     </row>
-    <row r="281">
+    <row r="281" customHeight="1" spans="4:4">
       <c r="D281" s="3"/>
     </row>
-    <row r="282">
+    <row r="282" customHeight="1" spans="4:4">
       <c r="D282" s="3"/>
     </row>
-    <row r="283">
+    <row r="283" customHeight="1" spans="4:4">
       <c r="D283" s="3"/>
     </row>
-    <row r="284">
+    <row r="284" customHeight="1" spans="4:4">
       <c r="D284" s="3"/>
     </row>
-    <row r="285">
+    <row r="285" customHeight="1" spans="4:4">
       <c r="D285" s="3"/>
     </row>
-    <row r="286">
+    <row r="286" customHeight="1" spans="4:4">
       <c r="D286" s="3"/>
     </row>
-    <row r="287">
+    <row r="287" customHeight="1" spans="4:4">
       <c r="D287" s="3"/>
     </row>
-    <row r="288">
+    <row r="288" customHeight="1" spans="4:4">
       <c r="D288" s="3"/>
     </row>
-    <row r="289">
+    <row r="289" customHeight="1" spans="4:4">
       <c r="D289" s="3"/>
     </row>
-    <row r="290">
+    <row r="290" customHeight="1" spans="4:4">
       <c r="D290" s="3"/>
     </row>
-    <row r="291">
+    <row r="291" customHeight="1" spans="4:4">
       <c r="D291" s="3"/>
     </row>
-    <row r="292">
+    <row r="292" customHeight="1" spans="4:4">
       <c r="D292" s="3"/>
     </row>
-    <row r="293">
+    <row r="293" customHeight="1" spans="4:4">
       <c r="D293" s="3"/>
     </row>
-    <row r="294">
+    <row r="294" customHeight="1" spans="4:4">
       <c r="D294" s="3"/>
     </row>
-    <row r="295">
+    <row r="295" customHeight="1" spans="4:4">
       <c r="D295" s="3"/>
     </row>
-    <row r="296">
+    <row r="296" customHeight="1" spans="4:4">
       <c r="D296" s="3"/>
     </row>
-    <row r="297">
+    <row r="297" customHeight="1" spans="4:4">
       <c r="D297" s="3"/>
     </row>
-    <row r="298">
+    <row r="298" customHeight="1" spans="4:4">
       <c r="D298" s="3"/>
     </row>
-    <row r="299">
+    <row r="299" customHeight="1" spans="4:4">
       <c r="D299" s="3"/>
     </row>
-    <row r="300">
+    <row r="300" customHeight="1" spans="4:4">
       <c r="D300" s="3"/>
     </row>
-    <row r="301">
+    <row r="301" customHeight="1" spans="4:4">
       <c r="D301" s="3"/>
     </row>
-    <row r="302">
+    <row r="302" customHeight="1" spans="4:4">
       <c r="D302" s="3"/>
     </row>
-    <row r="303">
+    <row r="303" customHeight="1" spans="4:4">
       <c r="D303" s="3"/>
     </row>
-    <row r="304">
+    <row r="304" customHeight="1" spans="4:4">
       <c r="D304" s="3"/>
     </row>
-    <row r="305">
+    <row r="305" customHeight="1" spans="4:4">
       <c r="D305" s="3"/>
     </row>
-    <row r="306">
+    <row r="306" customHeight="1" spans="4:4">
       <c r="D306" s="3"/>
     </row>
-    <row r="307">
+    <row r="307" customHeight="1" spans="4:4">
       <c r="D307" s="3"/>
     </row>
-    <row r="308">
+    <row r="308" customHeight="1" spans="4:4">
       <c r="D308" s="3"/>
     </row>
-    <row r="309">
+    <row r="309" customHeight="1" spans="4:4">
       <c r="D309" s="3"/>
     </row>
-    <row r="310">
+    <row r="310" customHeight="1" spans="4:4">
       <c r="D310" s="3"/>
     </row>
-    <row r="311">
+    <row r="311" customHeight="1" spans="4:4">
       <c r="D311" s="3"/>
     </row>
-    <row r="312">
+    <row r="312" customHeight="1" spans="4:4">
       <c r="D312" s="3"/>
     </row>
-    <row r="313">
+    <row r="313" customHeight="1" spans="4:4">
       <c r="D313" s="3"/>
     </row>
-    <row r="314">
+    <row r="314" customHeight="1" spans="4:4">
       <c r="D314" s="3"/>
     </row>
-    <row r="315">
+    <row r="315" customHeight="1" spans="4:4">
       <c r="D315" s="3"/>
     </row>
-    <row r="316">
+    <row r="316" customHeight="1" spans="4:4">
       <c r="D316" s="3"/>
     </row>
-    <row r="317">
+    <row r="317" customHeight="1" spans="4:4">
       <c r="D317" s="3"/>
     </row>
-    <row r="318">
+    <row r="318" customHeight="1" spans="4:4">
       <c r="D318" s="3"/>
     </row>
-    <row r="319">
+    <row r="319" customHeight="1" spans="4:4">
       <c r="D319" s="3"/>
     </row>
-    <row r="320">
+    <row r="320" customHeight="1" spans="4:4">
       <c r="D320" s="3"/>
     </row>
-    <row r="321">
+    <row r="321" customHeight="1" spans="4:4">
       <c r="D321" s="3"/>
     </row>
-    <row r="322">
+    <row r="322" customHeight="1" spans="4:4">
       <c r="D322" s="3"/>
     </row>
-    <row r="323">
+    <row r="323" customHeight="1" spans="4:4">
       <c r="D323" s="3"/>
     </row>
-    <row r="324">
+    <row r="324" customHeight="1" spans="4:4">
       <c r="D324" s="3"/>
     </row>
-    <row r="325">
+    <row r="325" customHeight="1" spans="4:4">
       <c r="D325" s="3"/>
     </row>
-    <row r="326">
+    <row r="326" customHeight="1" spans="4:4">
       <c r="D326" s="3"/>
     </row>
-    <row r="327">
+    <row r="327" customHeight="1" spans="4:4">
       <c r="D327" s="3"/>
     </row>
-    <row r="328">
+    <row r="328" customHeight="1" spans="4:4">
       <c r="D328" s="3"/>
     </row>
-    <row r="329">
+    <row r="329" customHeight="1" spans="4:4">
       <c r="D329" s="3"/>
     </row>
-    <row r="330">
+    <row r="330" customHeight="1" spans="4:4">
       <c r="D330" s="3"/>
     </row>
-    <row r="331">
+    <row r="331" customHeight="1" spans="4:4">
       <c r="D331" s="3"/>
     </row>
-    <row r="332">
+    <row r="332" customHeight="1" spans="4:4">
       <c r="D332" s="3"/>
     </row>
-    <row r="333">
+    <row r="333" customHeight="1" spans="4:4">
       <c r="D333" s="3"/>
     </row>
-    <row r="334">
+    <row r="334" customHeight="1" spans="4:4">
       <c r="D334" s="3"/>
     </row>
-    <row r="335">
+    <row r="335" customHeight="1" spans="4:4">
       <c r="D335" s="3"/>
     </row>
-    <row r="336">
+    <row r="336" customHeight="1" spans="4:4">
       <c r="D336" s="3"/>
     </row>
-    <row r="337">
+    <row r="337" customHeight="1" spans="4:4">
       <c r="D337" s="3"/>
     </row>
-    <row r="338">
+    <row r="338" customHeight="1" spans="4:4">
       <c r="D338" s="3"/>
     </row>
-    <row r="339">
+    <row r="339" customHeight="1" spans="4:4">
       <c r="D339" s="3"/>
     </row>
-    <row r="340">
+    <row r="340" customHeight="1" spans="4:4">
       <c r="D340" s="3"/>
     </row>
-    <row r="341">
+    <row r="341" customHeight="1" spans="4:4">
       <c r="D341" s="3"/>
     </row>
-    <row r="342">
+    <row r="342" customHeight="1" spans="4:4">
       <c r="D342" s="3"/>
     </row>
-    <row r="343">
+    <row r="343" customHeight="1" spans="4:4">
       <c r="D343" s="3"/>
     </row>
-    <row r="344">
+    <row r="344" customHeight="1" spans="4:4">
       <c r="D344" s="3"/>
     </row>
-    <row r="345">
+    <row r="345" customHeight="1" spans="4:4">
       <c r="D345" s="3"/>
     </row>
-    <row r="346">
+    <row r="346" customHeight="1" spans="4:4">
       <c r="D346" s="3"/>
     </row>
-    <row r="347">
+    <row r="347" customHeight="1" spans="4:4">
       <c r="D347" s="3"/>
     </row>
-    <row r="348">
+    <row r="348" customHeight="1" spans="4:4">
       <c r="D348" s="3"/>
     </row>
-    <row r="349">
+    <row r="349" customHeight="1" spans="4:4">
       <c r="D349" s="3"/>
     </row>
-    <row r="350">
+    <row r="350" customHeight="1" spans="4:4">
       <c r="D350" s="3"/>
     </row>
-    <row r="351">
+    <row r="351" customHeight="1" spans="4:4">
       <c r="D351" s="3"/>
     </row>
-    <row r="352">
+    <row r="352" customHeight="1" spans="4:4">
       <c r="D352" s="3"/>
     </row>
-    <row r="353">
+    <row r="353" customHeight="1" spans="4:4">
       <c r="D353" s="3"/>
     </row>
-    <row r="354">
+    <row r="354" customHeight="1" spans="4:4">
       <c r="D354" s="3"/>
     </row>
-    <row r="355">
+    <row r="355" customHeight="1" spans="4:4">
       <c r="D355" s="3"/>
     </row>
-    <row r="356">
+    <row r="356" customHeight="1" spans="4:4">
       <c r="D356" s="3"/>
     </row>
-    <row r="357">
+    <row r="357" customHeight="1" spans="4:4">
       <c r="D357" s="3"/>
     </row>
-    <row r="358">
+    <row r="358" customHeight="1" spans="4:4">
       <c r="D358" s="3"/>
     </row>
-    <row r="359">
+    <row r="359" customHeight="1" spans="4:4">
       <c r="D359" s="3"/>
     </row>
-    <row r="360">
+    <row r="360" customHeight="1" spans="4:4">
       <c r="D360" s="3"/>
     </row>
-    <row r="361">
+    <row r="361" customHeight="1" spans="4:4">
       <c r="D361" s="3"/>
     </row>
-    <row r="362">
+    <row r="362" customHeight="1" spans="4:4">
       <c r="D362" s="3"/>
     </row>
-    <row r="363">
+    <row r="363" customHeight="1" spans="4:4">
       <c r="D363" s="3"/>
     </row>
-    <row r="364">
+    <row r="364" customHeight="1" spans="4:4">
       <c r="D364" s="3"/>
     </row>
-    <row r="365">
+    <row r="365" customHeight="1" spans="4:4">
       <c r="D365" s="3"/>
     </row>
-    <row r="366">
+    <row r="366" customHeight="1" spans="4:4">
       <c r="D366" s="3"/>
     </row>
-    <row r="367">
+    <row r="367" customHeight="1" spans="4:4">
       <c r="D367" s="3"/>
     </row>
-    <row r="368">
+    <row r="368" customHeight="1" spans="4:4">
       <c r="D368" s="3"/>
     </row>
-    <row r="369">
+    <row r="369" customHeight="1" spans="4:4">
       <c r="D369" s="3"/>
     </row>
-    <row r="370">
+    <row r="370" customHeight="1" spans="4:4">
       <c r="D370" s="3"/>
     </row>
-    <row r="371">
+    <row r="371" customHeight="1" spans="4:4">
       <c r="D371" s="3"/>
     </row>
-    <row r="372">
+    <row r="372" customHeight="1" spans="4:4">
       <c r="D372" s="3"/>
     </row>
-    <row r="373">
+    <row r="373" customHeight="1" spans="4:4">
       <c r="D373" s="3"/>
     </row>
-    <row r="374">
+    <row r="374" customHeight="1" spans="4:4">
       <c r="D374" s="3"/>
     </row>
-    <row r="375">
+    <row r="375" customHeight="1" spans="4:4">
       <c r="D375" s="3"/>
     </row>
-    <row r="376">
+    <row r="376" customHeight="1" spans="4:4">
       <c r="D376" s="3"/>
     </row>
-    <row r="377">
+    <row r="377" customHeight="1" spans="4:4">
       <c r="D377" s="3"/>
     </row>
-    <row r="378">
+    <row r="378" customHeight="1" spans="4:4">
       <c r="D378" s="3"/>
     </row>
-    <row r="379">
+    <row r="379" customHeight="1" spans="4:4">
       <c r="D379" s="3"/>
     </row>
-    <row r="380">
+    <row r="380" customHeight="1" spans="4:4">
       <c r="D380" s="3"/>
     </row>
-    <row r="381">
+    <row r="381" customHeight="1" spans="4:4">
       <c r="D381" s="3"/>
     </row>
-    <row r="382">
+    <row r="382" customHeight="1" spans="4:4">
       <c r="D382" s="3"/>
     </row>
-    <row r="383">
+    <row r="383" customHeight="1" spans="4:4">
       <c r="D383" s="3"/>
     </row>
-    <row r="384">
+    <row r="384" customHeight="1" spans="4:4">
       <c r="D384" s="3"/>
     </row>
-    <row r="385">
+    <row r="385" customHeight="1" spans="4:4">
       <c r="D385" s="3"/>
     </row>
-    <row r="386">
+    <row r="386" customHeight="1" spans="4:4">
       <c r="D386" s="3"/>
     </row>
-    <row r="387">
+    <row r="387" customHeight="1" spans="4:4">
       <c r="D387" s="3"/>
     </row>
-    <row r="388">
+    <row r="388" customHeight="1" spans="4:4">
       <c r="D388" s="3"/>
     </row>
-    <row r="389">
+    <row r="389" customHeight="1" spans="4:4">
       <c r="D389" s="3"/>
     </row>
-    <row r="390">
+    <row r="390" customHeight="1" spans="4:4">
       <c r="D390" s="3"/>
     </row>
-    <row r="391">
+    <row r="391" customHeight="1" spans="4:4">
       <c r="D391" s="3"/>
     </row>
-    <row r="392">
+    <row r="392" customHeight="1" spans="4:4">
       <c r="D392" s="3"/>
     </row>
-    <row r="393">
+    <row r="393" customHeight="1" spans="4:4">
       <c r="D393" s="3"/>
     </row>
-    <row r="394">
+    <row r="394" customHeight="1" spans="4:4">
       <c r="D394" s="3"/>
     </row>
-    <row r="395">
+    <row r="395" customHeight="1" spans="4:4">
       <c r="D395" s="3"/>
     </row>
-    <row r="396">
+    <row r="396" customHeight="1" spans="4:4">
       <c r="D396" s="3"/>
     </row>
-    <row r="397">
+    <row r="397" customHeight="1" spans="4:4">
       <c r="D397" s="3"/>
     </row>
-    <row r="398">
+    <row r="398" customHeight="1" spans="4:4">
       <c r="D398" s="3"/>
     </row>
-    <row r="399">
+    <row r="399" customHeight="1" spans="4:4">
       <c r="D399" s="3"/>
     </row>
-    <row r="400">
+    <row r="400" customHeight="1" spans="4:4">
       <c r="D400" s="3"/>
     </row>
-    <row r="401">
+    <row r="401" customHeight="1" spans="4:4">
       <c r="D401" s="3"/>
     </row>
-    <row r="402">
+    <row r="402" customHeight="1" spans="4:4">
       <c r="D402" s="3"/>
     </row>
-    <row r="403">
+    <row r="403" customHeight="1" spans="4:4">
       <c r="D403" s="3"/>
     </row>
-    <row r="404">
+    <row r="404" customHeight="1" spans="4:4">
       <c r="D404" s="3"/>
     </row>
-    <row r="405">
+    <row r="405" customHeight="1" spans="4:4">
       <c r="D405" s="3"/>
     </row>
-    <row r="406">
+    <row r="406" customHeight="1" spans="4:4">
       <c r="D406" s="3"/>
     </row>
-    <row r="407">
+    <row r="407" customHeight="1" spans="4:4">
       <c r="D407" s="3"/>
     </row>
-    <row r="408">
+    <row r="408" customHeight="1" spans="4:4">
       <c r="D408" s="3"/>
     </row>
-    <row r="409">
+    <row r="409" customHeight="1" spans="4:4">
       <c r="D409" s="3"/>
     </row>
-    <row r="410">
+    <row r="410" customHeight="1" spans="4:4">
       <c r="D410" s="3"/>
     </row>
-    <row r="411">
+    <row r="411" customHeight="1" spans="4:4">
       <c r="D411" s="3"/>
     </row>
-    <row r="412">
+    <row r="412" customHeight="1" spans="4:4">
       <c r="D412" s="3"/>
     </row>
-    <row r="413">
+    <row r="413" customHeight="1" spans="4:4">
       <c r="D413" s="3"/>
     </row>
-    <row r="414">
+    <row r="414" customHeight="1" spans="4:4">
       <c r="D414" s="3"/>
     </row>
-    <row r="415">
+    <row r="415" customHeight="1" spans="4:4">
       <c r="D415" s="3"/>
     </row>
-    <row r="416">
+    <row r="416" customHeight="1" spans="4:4">
       <c r="D416" s="3"/>
     </row>
-    <row r="417">
+    <row r="417" customHeight="1" spans="4:4">
       <c r="D417" s="3"/>
     </row>
-    <row r="418">
+    <row r="418" customHeight="1" spans="4:4">
       <c r="D418" s="3"/>
     </row>
-    <row r="419">
+    <row r="419" customHeight="1" spans="4:4">
       <c r="D419" s="3"/>
     </row>
-    <row r="420">
+    <row r="420" customHeight="1" spans="4:4">
       <c r="D420" s="3"/>
     </row>
-    <row r="421">
+    <row r="421" customHeight="1" spans="4:4">
       <c r="D421" s="3"/>
     </row>
-    <row r="422">
+    <row r="422" customHeight="1" spans="4:4">
       <c r="D422" s="3"/>
     </row>
-    <row r="423">
+    <row r="423" customHeight="1" spans="4:4">
       <c r="D423" s="3"/>
     </row>
-    <row r="424">
+    <row r="424" customHeight="1" spans="4:4">
       <c r="D424" s="3"/>
     </row>
-    <row r="425">
+    <row r="425" customHeight="1" spans="4:4">
       <c r="D425" s="3"/>
     </row>
-    <row r="426">
+    <row r="426" customHeight="1" spans="4:4">
       <c r="D426" s="3"/>
     </row>
-    <row r="427">
+    <row r="427" customHeight="1" spans="4:4">
       <c r="D427" s="3"/>
     </row>
-    <row r="428">
+    <row r="428" customHeight="1" spans="4:4">
       <c r="D428" s="3"/>
     </row>
-    <row r="429">
+    <row r="429" customHeight="1" spans="4:4">
       <c r="D429" s="3"/>
     </row>
-    <row r="430">
+    <row r="430" customHeight="1" spans="4:4">
       <c r="D430" s="3"/>
     </row>
-    <row r="431">
+    <row r="431" customHeight="1" spans="4:4">
       <c r="D431" s="3"/>
     </row>
-    <row r="432">
+    <row r="432" customHeight="1" spans="4:4">
       <c r="D432" s="3"/>
     </row>
-    <row r="433">
+    <row r="433" customHeight="1" spans="4:4">
       <c r="D433" s="3"/>
     </row>
-    <row r="434">
+    <row r="434" customHeight="1" spans="4:4">
       <c r="D434" s="3"/>
     </row>
-    <row r="435">
+    <row r="435" customHeight="1" spans="4:4">
       <c r="D435" s="3"/>
     </row>
-    <row r="436">
+    <row r="436" customHeight="1" spans="4:4">
       <c r="D436" s="3"/>
     </row>
-    <row r="437">
+    <row r="437" customHeight="1" spans="4:4">
       <c r="D437" s="3"/>
     </row>
-    <row r="438">
+    <row r="438" customHeight="1" spans="4:4">
       <c r="D438" s="3"/>
     </row>
-    <row r="439">
+    <row r="439" customHeight="1" spans="4:4">
       <c r="D439" s="3"/>
     </row>
-    <row r="440">
+    <row r="440" customHeight="1" spans="4:4">
       <c r="D440" s="3"/>
     </row>
-    <row r="441">
+    <row r="441" customHeight="1" spans="4:4">
       <c r="D441" s="3"/>
     </row>
-    <row r="442">
+    <row r="442" customHeight="1" spans="4:4">
       <c r="D442" s="3"/>
     </row>
-    <row r="443">
+    <row r="443" customHeight="1" spans="4:4">
       <c r="D443" s="3"/>
     </row>
-    <row r="444">
+    <row r="444" customHeight="1" spans="4:4">
       <c r="D444" s="3"/>
     </row>
-    <row r="445">
+    <row r="445" customHeight="1" spans="4:4">
       <c r="D445" s="3"/>
     </row>
-    <row r="446">
+    <row r="446" customHeight="1" spans="4:4">
       <c r="D446" s="3"/>
     </row>
-    <row r="447">
+    <row r="447" customHeight="1" spans="4:4">
       <c r="D447" s="3"/>
     </row>
-    <row r="448">
+    <row r="448" customHeight="1" spans="4:4">
       <c r="D448" s="3"/>
     </row>
-    <row r="449">
+    <row r="449" customHeight="1" spans="4:4">
       <c r="D449" s="3"/>
     </row>
-    <row r="450">
+    <row r="450" customHeight="1" spans="4:4">
       <c r="D450" s="3"/>
     </row>
-    <row r="451">
+    <row r="451" customHeight="1" spans="4:4">
       <c r="D451" s="3"/>
     </row>
-    <row r="452">
+    <row r="452" customHeight="1" spans="4:4">
       <c r="D452" s="3"/>
     </row>
-    <row r="453">
+    <row r="453" customHeight="1" spans="4:4">
       <c r="D453" s="3"/>
     </row>
-    <row r="454">
+    <row r="454" customHeight="1" spans="4:4">
       <c r="D454" s="3"/>
     </row>
-    <row r="455">
+    <row r="455" customHeight="1" spans="4:4">
       <c r="D455" s="3"/>
     </row>
-    <row r="456">
+    <row r="456" customHeight="1" spans="4:4">
       <c r="D456" s="3"/>
     </row>
-    <row r="457">
+    <row r="457" customHeight="1" spans="4:4">
       <c r="D457" s="3"/>
     </row>
-    <row r="458">
+    <row r="458" customHeight="1" spans="4:4">
       <c r="D458" s="3"/>
     </row>
-    <row r="459">
+    <row r="459" customHeight="1" spans="4:4">
       <c r="D459" s="3"/>
     </row>
-    <row r="460">
+    <row r="460" customHeight="1" spans="4:4">
       <c r="D460" s="3"/>
     </row>
-    <row r="461">
+    <row r="461" customHeight="1" spans="4:4">
       <c r="D461" s="3"/>
     </row>
-    <row r="462">
+    <row r="462" customHeight="1" spans="4:4">
       <c r="D462" s="3"/>
     </row>
-    <row r="463">
+    <row r="463" customHeight="1" spans="4:4">
       <c r="D463" s="3"/>
     </row>
-    <row r="464">
+    <row r="464" customHeight="1" spans="4:4">
       <c r="D464" s="3"/>
     </row>
-    <row r="465">
+    <row r="465" customHeight="1" spans="4:4">
       <c r="D465" s="3"/>
     </row>
-    <row r="466">
+    <row r="466" customHeight="1" spans="4:4">
       <c r="D466" s="3"/>
     </row>
-    <row r="467">
+    <row r="467" customHeight="1" spans="4:4">
       <c r="D467" s="3"/>
     </row>
-    <row r="468">
+    <row r="468" customHeight="1" spans="4:4">
       <c r="D468" s="3"/>
     </row>
-    <row r="469">
+    <row r="469" customHeight="1" spans="4:4">
       <c r="D469" s="3"/>
     </row>
-    <row r="470">
+    <row r="470" customHeight="1" spans="4:4">
       <c r="D470" s="3"/>
     </row>
-    <row r="471">
+    <row r="471" customHeight="1" spans="4:4">
       <c r="D471" s="3"/>
     </row>
-    <row r="472">
+    <row r="472" customHeight="1" spans="4:4">
       <c r="D472" s="3"/>
     </row>
-    <row r="473">
+    <row r="473" customHeight="1" spans="4:4">
       <c r="D473" s="3"/>
     </row>
-    <row r="474">
+    <row r="474" customHeight="1" spans="4:4">
       <c r="D474" s="3"/>
     </row>
-    <row r="475">
+    <row r="475" customHeight="1" spans="4:4">
       <c r="D475" s="3"/>
     </row>
-    <row r="476">
+    <row r="476" customHeight="1" spans="4:4">
       <c r="D476" s="3"/>
     </row>
-    <row r="477">
+    <row r="477" customHeight="1" spans="4:4">
       <c r="D477" s="3"/>
     </row>
-    <row r="478">
+    <row r="478" customHeight="1" spans="4:4">
       <c r="D478" s="3"/>
     </row>
-    <row r="479">
+    <row r="479" customHeight="1" spans="4:4">
       <c r="D479" s="3"/>
     </row>
-    <row r="480">
+    <row r="480" customHeight="1" spans="4:4">
       <c r="D480" s="3"/>
     </row>
-    <row r="481">
+    <row r="481" customHeight="1" spans="4:4">
       <c r="D481" s="3"/>
     </row>
-    <row r="482">
+    <row r="482" customHeight="1" spans="4:4">
       <c r="D482" s="3"/>
     </row>
-    <row r="483">
+    <row r="483" customHeight="1" spans="4:4">
       <c r="D483" s="3"/>
     </row>
-    <row r="484">
+    <row r="484" customHeight="1" spans="4:4">
       <c r="D484" s="3"/>
     </row>
-    <row r="485">
+    <row r="485" customHeight="1" spans="4:4">
       <c r="D485" s="3"/>
     </row>
-    <row r="486">
+    <row r="486" customHeight="1" spans="4:4">
       <c r="D486" s="3"/>
     </row>
-    <row r="487">
+    <row r="487" customHeight="1" spans="4:4">
       <c r="D487" s="3"/>
     </row>
-    <row r="488">
+    <row r="488" customHeight="1" spans="4:4">
       <c r="D488" s="3"/>
     </row>
-    <row r="489">
+    <row r="489" customHeight="1" spans="4:4">
       <c r="D489" s="3"/>
     </row>
-    <row r="490">
+    <row r="490" customHeight="1" spans="4:4">
       <c r="D490" s="3"/>
     </row>
-    <row r="491">
+    <row r="491" customHeight="1" spans="4:4">
       <c r="D491" s="3"/>
     </row>
-    <row r="492">
+    <row r="492" customHeight="1" spans="4:4">
       <c r="D492" s="3"/>
     </row>
-    <row r="493">
+    <row r="493" customHeight="1" spans="4:4">
       <c r="D493" s="3"/>
     </row>
-    <row r="494">
+    <row r="494" customHeight="1" spans="4:4">
       <c r="D494" s="3"/>
     </row>
-    <row r="495">
+    <row r="495" customHeight="1" spans="4:4">
       <c r="D495" s="3"/>
     </row>
-    <row r="496">
+    <row r="496" customHeight="1" spans="4:4">
       <c r="D496" s="3"/>
     </row>
-    <row r="497">
+    <row r="497" customHeight="1" spans="4:4">
       <c r="D497" s="3"/>
     </row>
-    <row r="498">
+    <row r="498" customHeight="1" spans="4:4">
       <c r="D498" s="3"/>
     </row>
-    <row r="499">
+    <row r="499" customHeight="1" spans="4:4">
       <c r="D499" s="3"/>
     </row>
-    <row r="500">
+    <row r="500" customHeight="1" spans="4:4">
       <c r="D500" s="3"/>
     </row>
-    <row r="501">
+    <row r="501" customHeight="1" spans="4:4">
       <c r="D501" s="3"/>
     </row>
-    <row r="502">
+    <row r="502" customHeight="1" spans="4:4">
       <c r="D502" s="3"/>
     </row>
-    <row r="503">
+    <row r="503" customHeight="1" spans="4:4">
       <c r="D503" s="3"/>
     </row>
-    <row r="504">
+    <row r="504" customHeight="1" spans="4:4">
       <c r="D504" s="3"/>
     </row>
-    <row r="505">
+    <row r="505" customHeight="1" spans="4:4">
       <c r="D505" s="3"/>
     </row>
-    <row r="506">
+    <row r="506" customHeight="1" spans="4:4">
       <c r="D506" s="3"/>
     </row>
-    <row r="507">
+    <row r="507" customHeight="1" spans="4:4">
       <c r="D507" s="3"/>
     </row>
-    <row r="508">
+    <row r="508" customHeight="1" spans="4:4">
       <c r="D508" s="3"/>
     </row>
-    <row r="509">
+    <row r="509" customHeight="1" spans="4:4">
       <c r="D509" s="3"/>
     </row>
-    <row r="510">
+    <row r="510" customHeight="1" spans="4:4">
       <c r="D510" s="3"/>
     </row>
-    <row r="511">
+    <row r="511" customHeight="1" spans="4:4">
       <c r="D511" s="3"/>
     </row>
-    <row r="512">
+    <row r="512" customHeight="1" spans="4:4">
       <c r="D512" s="3"/>
     </row>
-    <row r="513">
+    <row r="513" customHeight="1" spans="4:4">
       <c r="D513" s="3"/>
     </row>
-    <row r="514">
+    <row r="514" customHeight="1" spans="4:4">
       <c r="D514" s="3"/>
     </row>
-    <row r="515">
+    <row r="515" customHeight="1" spans="4:4">
       <c r="D515" s="3"/>
     </row>
-    <row r="516">
+    <row r="516" customHeight="1" spans="4:4">
       <c r="D516" s="3"/>
     </row>
-    <row r="517">
+    <row r="517" customHeight="1" spans="4:4">
       <c r="D517" s="3"/>
     </row>
-    <row r="518">
+    <row r="518" customHeight="1" spans="4:4">
       <c r="D518" s="3"/>
     </row>
-    <row r="519">
+    <row r="519" customHeight="1" spans="4:4">
       <c r="D519" s="3"/>
     </row>
-    <row r="520">
+    <row r="520" customHeight="1" spans="4:4">
       <c r="D520" s="3"/>
     </row>
-    <row r="521">
+    <row r="521" customHeight="1" spans="4:4">
       <c r="D521" s="3"/>
     </row>
-    <row r="522">
+    <row r="522" customHeight="1" spans="4:4">
       <c r="D522" s="3"/>
     </row>
-    <row r="523">
+    <row r="523" customHeight="1" spans="4:4">
       <c r="D523" s="3"/>
     </row>
-    <row r="524">
+    <row r="524" customHeight="1" spans="4:4">
       <c r="D524" s="3"/>
     </row>
-    <row r="525">
+    <row r="525" customHeight="1" spans="4:4">
       <c r="D525" s="3"/>
     </row>
-    <row r="526">
+    <row r="526" customHeight="1" spans="4:4">
       <c r="D526" s="3"/>
     </row>
-    <row r="527">
+    <row r="527" customHeight="1" spans="4:4">
       <c r="D527" s="3"/>
     </row>
-    <row r="528">
+    <row r="528" customHeight="1" spans="4:4">
       <c r="D528" s="3"/>
     </row>
-    <row r="529">
+    <row r="529" customHeight="1" spans="4:4">
       <c r="D529" s="3"/>
     </row>
-    <row r="530">
+    <row r="530" customHeight="1" spans="4:4">
       <c r="D530" s="3"/>
     </row>
-    <row r="531">
+    <row r="531" customHeight="1" spans="4:4">
       <c r="D531" s="3"/>
     </row>
-    <row r="532">
+    <row r="532" customHeight="1" spans="4:4">
       <c r="D532" s="3"/>
     </row>
-    <row r="533">
+    <row r="533" customHeight="1" spans="4:4">
       <c r="D533" s="3"/>
     </row>
-    <row r="534">
+    <row r="534" customHeight="1" spans="4:4">
       <c r="D534" s="3"/>
     </row>
-    <row r="535">
+    <row r="535" customHeight="1" spans="4:4">
       <c r="D535" s="3"/>
     </row>
-    <row r="536">
+    <row r="536" customHeight="1" spans="4:4">
       <c r="D536" s="3"/>
     </row>
-    <row r="537">
+    <row r="537" customHeight="1" spans="4:4">
       <c r="D537" s="3"/>
     </row>
-    <row r="538">
+    <row r="538" customHeight="1" spans="4:4">
       <c r="D538" s="3"/>
     </row>
-    <row r="539">
+    <row r="539" customHeight="1" spans="4:4">
       <c r="D539" s="3"/>
     </row>
-    <row r="540">
+    <row r="540" customHeight="1" spans="4:4">
       <c r="D540" s="3"/>
     </row>
-    <row r="541">
+    <row r="541" customHeight="1" spans="4:4">
       <c r="D541" s="3"/>
     </row>
-    <row r="542">
+    <row r="542" customHeight="1" spans="4:4">
       <c r="D542" s="3"/>
     </row>
-    <row r="543">
+    <row r="543" customHeight="1" spans="4:4">
       <c r="D543" s="3"/>
     </row>
-    <row r="544">
+    <row r="544" customHeight="1" spans="4:4">
       <c r="D544" s="3"/>
     </row>
-    <row r="545">
+    <row r="545" customHeight="1" spans="4:4">
       <c r="D545" s="3"/>
     </row>
-    <row r="546">
+    <row r="546" customHeight="1" spans="4:4">
       <c r="D546" s="3"/>
     </row>
-    <row r="547">
+    <row r="547" customHeight="1" spans="4:4">
       <c r="D547" s="3"/>
     </row>
-    <row r="548">
+    <row r="548" customHeight="1" spans="4:4">
       <c r="D548" s="3"/>
     </row>
-    <row r="549">
+    <row r="549" customHeight="1" spans="4:4">
       <c r="D549" s="3"/>
     </row>
-    <row r="550">
+    <row r="550" customHeight="1" spans="4:4">
       <c r="D550" s="3"/>
     </row>
-    <row r="551">
+    <row r="551" customHeight="1" spans="4:4">
       <c r="D551" s="3"/>
     </row>
-    <row r="552">
+    <row r="552" customHeight="1" spans="4:4">
       <c r="D552" s="3"/>
     </row>
-    <row r="553">
+    <row r="553" customHeight="1" spans="4:4">
       <c r="D553" s="3"/>
     </row>
-    <row r="554">
+    <row r="554" customHeight="1" spans="4:4">
       <c r="D554" s="3"/>
     </row>
-    <row r="555">
+    <row r="555" customHeight="1" spans="4:4">
       <c r="D555" s="3"/>
     </row>
-    <row r="556">
+    <row r="556" customHeight="1" spans="4:4">
       <c r="D556" s="3"/>
     </row>
-    <row r="557">
+    <row r="557" customHeight="1" spans="4:4">
       <c r="D557" s="3"/>
     </row>
-    <row r="558">
+    <row r="558" customHeight="1" spans="4:4">
       <c r="D558" s="3"/>
     </row>
-    <row r="559">
+    <row r="559" customHeight="1" spans="4:4">
       <c r="D559" s="3"/>
     </row>
-    <row r="560">
+    <row r="560" customHeight="1" spans="4:4">
       <c r="D560" s="3"/>
     </row>
-    <row r="561">
+    <row r="561" customHeight="1" spans="4:4">
       <c r="D561" s="3"/>
     </row>
-    <row r="562">
+    <row r="562" customHeight="1" spans="4:4">
       <c r="D562" s="3"/>
     </row>
-    <row r="563">
+    <row r="563" customHeight="1" spans="4:4">
       <c r="D563" s="3"/>
     </row>
-    <row r="564">
+    <row r="564" customHeight="1" spans="4:4">
       <c r="D564" s="3"/>
     </row>
-    <row r="565">
+    <row r="565" customHeight="1" spans="4:4">
       <c r="D565" s="3"/>
     </row>
-    <row r="566">
+    <row r="566" customHeight="1" spans="4:4">
       <c r="D566" s="3"/>
     </row>
-    <row r="567">
+    <row r="567" customHeight="1" spans="4:4">
       <c r="D567" s="3"/>
     </row>
-    <row r="568">
+    <row r="568" customHeight="1" spans="4:4">
       <c r="D568" s="3"/>
     </row>
-    <row r="569">
+    <row r="569" customHeight="1" spans="4:4">
       <c r="D569" s="3"/>
     </row>
-    <row r="570">
+    <row r="570" customHeight="1" spans="4:4">
       <c r="D570" s="3"/>
     </row>
-    <row r="571">
+    <row r="571" customHeight="1" spans="4:4">
       <c r="D571" s="3"/>
     </row>
-    <row r="572">
+    <row r="572" customHeight="1" spans="4:4">
       <c r="D572" s="3"/>
     </row>
-    <row r="573">
+    <row r="573" customHeight="1" spans="4:4">
       <c r="D573" s="3"/>
     </row>
-    <row r="574">
+    <row r="574" customHeight="1" spans="4:4">
       <c r="D574" s="3"/>
     </row>
-    <row r="575">
+    <row r="575" customHeight="1" spans="4:4">
       <c r="D575" s="3"/>
     </row>
-    <row r="576">
+    <row r="576" customHeight="1" spans="4:4">
       <c r="D576" s="3"/>
     </row>
-    <row r="577">
+    <row r="577" customHeight="1" spans="4:4">
       <c r="D577" s="3"/>
     </row>
-    <row r="578">
+    <row r="578" customHeight="1" spans="4:4">
       <c r="D578" s="3"/>
     </row>
-    <row r="579">
+    <row r="579" customHeight="1" spans="4:4">
       <c r="D579" s="3"/>
     </row>
-    <row r="580">
+    <row r="580" customHeight="1" spans="4:4">
       <c r="D580" s="3"/>
     </row>
-    <row r="581">
+    <row r="581" customHeight="1" spans="4:4">
       <c r="D581" s="3"/>
     </row>
-    <row r="582">
+    <row r="582" customHeight="1" spans="4:4">
       <c r="D582" s="3"/>
     </row>
-    <row r="583">
+    <row r="583" customHeight="1" spans="4:4">
       <c r="D583" s="3"/>
     </row>
-    <row r="584">
+    <row r="584" customHeight="1" spans="4:4">
       <c r="D584" s="3"/>
     </row>
-    <row r="585">
+    <row r="585" customHeight="1" spans="4:4">
       <c r="D585" s="3"/>
     </row>
-    <row r="586">
+    <row r="586" customHeight="1" spans="4:4">
       <c r="D586" s="3"/>
     </row>
-    <row r="587">
+    <row r="587" customHeight="1" spans="4:4">
       <c r="D587" s="3"/>
     </row>
-    <row r="588">
+    <row r="588" customHeight="1" spans="4:4">
       <c r="D588" s="3"/>
     </row>
-    <row r="589">
+    <row r="589" customHeight="1" spans="4:4">
       <c r="D589" s="3"/>
     </row>
-    <row r="590">
+    <row r="590" customHeight="1" spans="4:4">
       <c r="D590" s="3"/>
     </row>
-    <row r="591">
+    <row r="591" customHeight="1" spans="4:4">
       <c r="D591" s="3"/>
     </row>
-    <row r="592">
+    <row r="592" customHeight="1" spans="4:4">
       <c r="D592" s="3"/>
     </row>
-    <row r="593">
+    <row r="593" customHeight="1" spans="4:4">
       <c r="D593" s="3"/>
     </row>
-    <row r="594">
+    <row r="594" customHeight="1" spans="4:4">
       <c r="D594" s="3"/>
     </row>
-    <row r="595">
+    <row r="595" customHeight="1" spans="4:4">
       <c r="D595" s="3"/>
     </row>
-    <row r="596">
+    <row r="596" customHeight="1" spans="4:4">
       <c r="D596" s="3"/>
     </row>
-    <row r="597">
+    <row r="597" customHeight="1" spans="4:4">
       <c r="D597" s="3"/>
     </row>
-    <row r="598">
+    <row r="598" customHeight="1" spans="4:4">
       <c r="D598" s="3"/>
     </row>
-    <row r="599">
+    <row r="599" customHeight="1" spans="4:4">
       <c r="D599" s="3"/>
     </row>
-    <row r="600">
+    <row r="600" customHeight="1" spans="4:4">
       <c r="D600" s="3"/>
     </row>
-    <row r="601">
+    <row r="601" customHeight="1" spans="4:4">
       <c r="D601" s="3"/>
     </row>
-    <row r="602">
+    <row r="602" customHeight="1" spans="4:4">
       <c r="D602" s="3"/>
     </row>
-    <row r="603">
+    <row r="603" customHeight="1" spans="4:4">
       <c r="D603" s="3"/>
     </row>
-    <row r="604">
+    <row r="604" customHeight="1" spans="4:4">
       <c r="D604" s="3"/>
     </row>
-    <row r="605">
+    <row r="605" customHeight="1" spans="4:4">
       <c r="D605" s="3"/>
     </row>
-    <row r="606">
+    <row r="606" customHeight="1" spans="4:4">
       <c r="D606" s="3"/>
     </row>
-    <row r="607">
+    <row r="607" customHeight="1" spans="4:4">
       <c r="D607" s="3"/>
     </row>
-    <row r="608">
+    <row r="608" customHeight="1" spans="4:4">
       <c r="D608" s="3"/>
     </row>
-    <row r="609">
+    <row r="609" customHeight="1" spans="4:4">
       <c r="D609" s="3"/>
     </row>
-    <row r="610">
+    <row r="610" customHeight="1" spans="4:4">
       <c r="D610" s="3"/>
     </row>
-    <row r="611">
+    <row r="611" customHeight="1" spans="4:4">
       <c r="D611" s="3"/>
     </row>
-    <row r="612">
+    <row r="612" customHeight="1" spans="4:4">
       <c r="D612" s="3"/>
     </row>
-    <row r="613">
+    <row r="613" customHeight="1" spans="4:4">
       <c r="D613" s="3"/>
     </row>
-    <row r="614">
+    <row r="614" customHeight="1" spans="4:4">
       <c r="D614" s="3"/>
     </row>
-    <row r="615">
+    <row r="615" customHeight="1" spans="4:4">
       <c r="D615" s="3"/>
     </row>
-    <row r="616">
+    <row r="616" customHeight="1" spans="4:4">
       <c r="D616" s="3"/>
     </row>
-    <row r="617">
+    <row r="617" customHeight="1" spans="4:4">
       <c r="D617" s="3"/>
     </row>
-    <row r="618">
+    <row r="618" customHeight="1" spans="4:4">
       <c r="D618" s="3"/>
     </row>
-    <row r="619">
+    <row r="619" customHeight="1" spans="4:4">
       <c r="D619" s="3"/>
     </row>
-    <row r="620">
+    <row r="620" customHeight="1" spans="4:4">
       <c r="D620" s="3"/>
     </row>
-    <row r="621">
+    <row r="621" customHeight="1" spans="4:4">
       <c r="D621" s="3"/>
     </row>
-    <row r="622">
+    <row r="622" customHeight="1" spans="4:4">
       <c r="D622" s="3"/>
     </row>
-    <row r="623">
+    <row r="623" customHeight="1" spans="4:4">
       <c r="D623" s="3"/>
     </row>
-    <row r="624">
+    <row r="624" customHeight="1" spans="4:4">
       <c r="D624" s="3"/>
     </row>
-    <row r="625">
+    <row r="625" customHeight="1" spans="4:4">
       <c r="D625" s="3"/>
     </row>
-    <row r="626">
+    <row r="626" customHeight="1" spans="4:4">
       <c r="D626" s="3"/>
     </row>
-    <row r="627">
+    <row r="627" customHeight="1" spans="4:4">
       <c r="D627" s="3"/>
     </row>
-    <row r="628">
+    <row r="628" customHeight="1" spans="4:4">
       <c r="D628" s="3"/>
     </row>
-    <row r="629">
+    <row r="629" customHeight="1" spans="4:4">
       <c r="D629" s="3"/>
     </row>
-    <row r="630">
+    <row r="630" customHeight="1" spans="4:4">
       <c r="D630" s="3"/>
     </row>
-    <row r="631">
+    <row r="631" customHeight="1" spans="4:4">
       <c r="D631" s="3"/>
     </row>
-    <row r="632">
+    <row r="632" customHeight="1" spans="4:4">
       <c r="D632" s="3"/>
     </row>
-    <row r="633">
+    <row r="633" customHeight="1" spans="4:4">
       <c r="D633" s="3"/>
     </row>
-    <row r="634">
+    <row r="634" customHeight="1" spans="4:4">
       <c r="D634" s="3"/>
     </row>
-    <row r="635">
+    <row r="635" customHeight="1" spans="4:4">
       <c r="D635" s="3"/>
     </row>
-    <row r="636">
+    <row r="636" customHeight="1" spans="4:4">
       <c r="D636" s="3"/>
     </row>
-    <row r="637">
+    <row r="637" customHeight="1" spans="4:4">
       <c r="D637" s="3"/>
     </row>
-    <row r="638">
+    <row r="638" customHeight="1" spans="4:4">
       <c r="D638" s="3"/>
     </row>
-    <row r="639">
+    <row r="639" customHeight="1" spans="4:4">
       <c r="D639" s="3"/>
     </row>
-    <row r="640">
+    <row r="640" customHeight="1" spans="4:4">
       <c r="D640" s="3"/>
     </row>
-    <row r="641">
+    <row r="641" customHeight="1" spans="4:4">
       <c r="D641" s="3"/>
     </row>
-    <row r="642">
+    <row r="642" customHeight="1" spans="4:4">
       <c r="D642" s="3"/>
     </row>
-    <row r="643">
+    <row r="643" customHeight="1" spans="4:4">
       <c r="D643" s="3"/>
     </row>
-    <row r="644">
+    <row r="644" customHeight="1" spans="4:4">
       <c r="D644" s="3"/>
     </row>
-    <row r="645">
+    <row r="645" customHeight="1" spans="4:4">
       <c r="D645" s="3"/>
     </row>
-    <row r="646">
+    <row r="646" customHeight="1" spans="4:4">
       <c r="D646" s="3"/>
     </row>
-    <row r="647">
+    <row r="647" customHeight="1" spans="4:4">
       <c r="D647" s="3"/>
     </row>
-    <row r="648">
+    <row r="648" customHeight="1" spans="4:4">
       <c r="D648" s="3"/>
     </row>
-    <row r="649">
+    <row r="649" customHeight="1" spans="4:4">
       <c r="D649" s="3"/>
     </row>
-    <row r="650">
+    <row r="650" customHeight="1" spans="4:4">
       <c r="D650" s="3"/>
     </row>
-    <row r="651">
+    <row r="651" customHeight="1" spans="4:4">
       <c r="D651" s="3"/>
     </row>
-    <row r="652">
+    <row r="652" customHeight="1" spans="4:4">
       <c r="D652" s="3"/>
     </row>
-    <row r="653">
+    <row r="653" customHeight="1" spans="4:4">
       <c r="D653" s="3"/>
     </row>
-    <row r="654">
+    <row r="654" customHeight="1" spans="4:4">
       <c r="D654" s="3"/>
     </row>
-    <row r="655">
+    <row r="655" customHeight="1" spans="4:4">
       <c r="D655" s="3"/>
     </row>
-    <row r="656">
+    <row r="656" customHeight="1" spans="4:4">
       <c r="D656" s="3"/>
     </row>
-    <row r="657">
+    <row r="657" customHeight="1" spans="4:4">
       <c r="D657" s="3"/>
     </row>
-    <row r="658">
+    <row r="658" customHeight="1" spans="4:4">
       <c r="D658" s="3"/>
     </row>
-    <row r="659">
+    <row r="659" customHeight="1" spans="4:4">
       <c r="D659" s="3"/>
     </row>
-    <row r="660">
+    <row r="660" customHeight="1" spans="4:4">
       <c r="D660" s="3"/>
     </row>
-    <row r="661">
+    <row r="661" customHeight="1" spans="4:4">
       <c r="D661" s="3"/>
     </row>
-    <row r="662">
+    <row r="662" customHeight="1" spans="4:4">
       <c r="D662" s="3"/>
     </row>
-    <row r="663">
+    <row r="663" customHeight="1" spans="4:4">
       <c r="D663" s="3"/>
     </row>
-    <row r="664">
+    <row r="664" customHeight="1" spans="4:4">
       <c r="D664" s="3"/>
     </row>
-    <row r="665">
+    <row r="665" customHeight="1" spans="4:4">
       <c r="D665" s="3"/>
     </row>
-    <row r="666">
+    <row r="666" customHeight="1" spans="4:4">
       <c r="D666" s="3"/>
     </row>
-    <row r="667">
+    <row r="667" customHeight="1" spans="4:4">
       <c r="D667" s="3"/>
     </row>
-    <row r="668">
+    <row r="668" customHeight="1" spans="4:4">
       <c r="D668" s="3"/>
     </row>
-    <row r="669">
+    <row r="669" customHeight="1" spans="4:4">
       <c r="D669" s="3"/>
     </row>
-    <row r="670">
+    <row r="670" customHeight="1" spans="4:4">
       <c r="D670" s="3"/>
     </row>
-    <row r="671">
+    <row r="671" customHeight="1" spans="4:4">
       <c r="D671" s="3"/>
     </row>
-    <row r="672">
+    <row r="672" customHeight="1" spans="4:4">
       <c r="D672" s="3"/>
     </row>
-    <row r="673">
+    <row r="673" customHeight="1" spans="4:4">
       <c r="D673" s="3"/>
     </row>
-    <row r="674">
+    <row r="674" customHeight="1" spans="4:4">
       <c r="D674" s="3"/>
     </row>
-    <row r="675">
+    <row r="675" customHeight="1" spans="4:4">
       <c r="D675" s="3"/>
     </row>
-    <row r="676">
+    <row r="676" customHeight="1" spans="4:4">
       <c r="D676" s="3"/>
     </row>
-    <row r="677">
+    <row r="677" customHeight="1" spans="4:4">
       <c r="D677" s="3"/>
     </row>
-    <row r="678">
+    <row r="678" customHeight="1" spans="4:4">
       <c r="D678" s="3"/>
     </row>
-    <row r="679">
+    <row r="679" customHeight="1" spans="4:4">
       <c r="D679" s="3"/>
     </row>
-    <row r="680">
+    <row r="680" customHeight="1" spans="4:4">
       <c r="D680" s="3"/>
     </row>
-    <row r="681">
+    <row r="681" customHeight="1" spans="4:4">
       <c r="D681" s="3"/>
     </row>
-    <row r="682">
+    <row r="682" customHeight="1" spans="4:4">
       <c r="D682" s="3"/>
     </row>
-    <row r="683">
+    <row r="683" customHeight="1" spans="4:4">
       <c r="D683" s="3"/>
     </row>
-    <row r="684">
+    <row r="684" customHeight="1" spans="4:4">
       <c r="D684" s="3"/>
     </row>
-    <row r="685">
+    <row r="685" customHeight="1" spans="4:4">
       <c r="D685" s="3"/>
     </row>
-    <row r="686">
+    <row r="686" customHeight="1" spans="4:4">
       <c r="D686" s="3"/>
     </row>
-    <row r="687">
+    <row r="687" customHeight="1" spans="4:4">
       <c r="D687" s="3"/>
     </row>
-    <row r="688">
+    <row r="688" customHeight="1" spans="4:4">
       <c r="D688" s="3"/>
     </row>
-    <row r="689">
+    <row r="689" customHeight="1" spans="4:4">
       <c r="D689" s="3"/>
     </row>
-    <row r="690">
+    <row r="690" customHeight="1" spans="4:4">
       <c r="D690" s="3"/>
     </row>
-    <row r="691">
+    <row r="691" customHeight="1" spans="4:4">
       <c r="D691" s="3"/>
     </row>
-    <row r="692">
+    <row r="692" customHeight="1" spans="4:4">
       <c r="D692" s="3"/>
     </row>
-    <row r="693">
+    <row r="693" customHeight="1" spans="4:4">
       <c r="D693" s="3"/>
     </row>
-    <row r="694">
+    <row r="694" customHeight="1" spans="4:4">
       <c r="D694" s="3"/>
     </row>
-    <row r="695">
+    <row r="695" customHeight="1" spans="4:4">
       <c r="D695" s="3"/>
     </row>
-    <row r="696">
+    <row r="696" customHeight="1" spans="4:4">
       <c r="D696" s="3"/>
     </row>
-    <row r="697">
+    <row r="697" customHeight="1" spans="4:4">
       <c r="D697" s="3"/>
     </row>
-    <row r="698">
+    <row r="698" customHeight="1" spans="4:4">
       <c r="D698" s="3"/>
     </row>
-    <row r="699">
+    <row r="699" customHeight="1" spans="4:4">
       <c r="D699" s="3"/>
     </row>
-    <row r="700">
+    <row r="700" customHeight="1" spans="4:4">
       <c r="D700" s="3"/>
     </row>
-    <row r="701">
+    <row r="701" customHeight="1" spans="4:4">
       <c r="D701" s="3"/>
     </row>
-    <row r="702">
+    <row r="702" customHeight="1" spans="4:4">
       <c r="D702" s="3"/>
     </row>
-    <row r="703">
+    <row r="703" customHeight="1" spans="4:4">
       <c r="D703" s="3"/>
     </row>
-    <row r="704">
+    <row r="704" customHeight="1" spans="4:4">
       <c r="D704" s="3"/>
     </row>
-    <row r="705">
+    <row r="705" customHeight="1" spans="4:4">
       <c r="D705" s="3"/>
     </row>
-    <row r="706">
+    <row r="706" customHeight="1" spans="4:4">
       <c r="D706" s="3"/>
     </row>
-    <row r="707">
+    <row r="707" customHeight="1" spans="4:4">
       <c r="D707" s="3"/>
     </row>
-    <row r="708">
+    <row r="708" customHeight="1" spans="4:4">
       <c r="D708" s="3"/>
     </row>
-    <row r="709">
+    <row r="709" customHeight="1" spans="4:4">
       <c r="D709" s="3"/>
     </row>
-    <row r="710">
+    <row r="710" customHeight="1" spans="4:4">
       <c r="D710" s="3"/>
     </row>
-    <row r="711">
+    <row r="711" customHeight="1" spans="4:4">
       <c r="D711" s="3"/>
     </row>
-    <row r="712">
+    <row r="712" customHeight="1" spans="4:4">
       <c r="D712" s="3"/>
     </row>
-    <row r="713">
+    <row r="713" customHeight="1" spans="4:4">
       <c r="D713" s="3"/>
     </row>
-    <row r="714">
+    <row r="714" customHeight="1" spans="4:4">
       <c r="D714" s="3"/>
     </row>
-    <row r="715">
+    <row r="715" customHeight="1" spans="4:4">
       <c r="D715" s="3"/>
     </row>
-    <row r="716">
+    <row r="716" customHeight="1" spans="4:4">
       <c r="D716" s="3"/>
     </row>
-    <row r="717">
+    <row r="717" customHeight="1" spans="4:4">
       <c r="D717" s="3"/>
     </row>
-    <row r="718">
+    <row r="718" customHeight="1" spans="4:4">
       <c r="D718" s="3"/>
     </row>
-    <row r="719">
+    <row r="719" customHeight="1" spans="4:4">
       <c r="D719" s="3"/>
     </row>
-    <row r="720">
+    <row r="720" customHeight="1" spans="4:4">
       <c r="D720" s="3"/>
     </row>
-    <row r="721">
+    <row r="721" customHeight="1" spans="4:4">
       <c r="D721" s="3"/>
     </row>
-    <row r="722">
+    <row r="722" customHeight="1" spans="4:4">
       <c r="D722" s="3"/>
     </row>
-    <row r="723">
+    <row r="723" customHeight="1" spans="4:4">
       <c r="D723" s="3"/>
     </row>
-    <row r="724">
+    <row r="724" customHeight="1" spans="4:4">
       <c r="D724" s="3"/>
     </row>
-    <row r="725">
+    <row r="725" customHeight="1" spans="4:4">
       <c r="D725" s="3"/>
     </row>
-    <row r="726">
+    <row r="726" customHeight="1" spans="4:4">
       <c r="D726" s="3"/>
     </row>
-    <row r="727">
+    <row r="727" customHeight="1" spans="4:4">
       <c r="D727" s="3"/>
     </row>
-    <row r="728">
+    <row r="728" customHeight="1" spans="4:4">
       <c r="D728" s="3"/>
     </row>
-    <row r="729">
+    <row r="729" customHeight="1" spans="4:4">
       <c r="D729" s="3"/>
     </row>
-    <row r="730">
+    <row r="730" customHeight="1" spans="4:4">
       <c r="D730" s="3"/>
     </row>
-    <row r="731">
+    <row r="731" customHeight="1" spans="4:4">
       <c r="D731" s="3"/>
     </row>
-    <row r="732">
+    <row r="732" customHeight="1" spans="4:4">
       <c r="D732" s="3"/>
     </row>
-    <row r="733">
+    <row r="733" customHeight="1" spans="4:4">
       <c r="D733" s="3"/>
     </row>
-    <row r="734">
+    <row r="734" customHeight="1" spans="4:4">
       <c r="D734" s="3"/>
     </row>
-    <row r="735">
+    <row r="735" customHeight="1" spans="4:4">
       <c r="D735" s="3"/>
     </row>
-    <row r="736">
+    <row r="736" customHeight="1" spans="4:4">
       <c r="D736" s="3"/>
     </row>
-    <row r="737">
+    <row r="737" customHeight="1" spans="4:4">
       <c r="D737" s="3"/>
     </row>
-    <row r="738">
+    <row r="738" customHeight="1" spans="4:4">
       <c r="D738" s="3"/>
     </row>
-    <row r="739">
+    <row r="739" customHeight="1" spans="4:4">
       <c r="D739" s="3"/>
     </row>
-    <row r="740">
+    <row r="740" customHeight="1" spans="4:4">
       <c r="D740" s="3"/>
     </row>
-    <row r="741">
+    <row r="741" customHeight="1" spans="4:4">
       <c r="D741" s="3"/>
     </row>
-    <row r="742">
+    <row r="742" customHeight="1" spans="4:4">
       <c r="D742" s="3"/>
     </row>
-    <row r="743">
+    <row r="743" customHeight="1" spans="4:4">
       <c r="D743" s="3"/>
     </row>
-    <row r="744">
+    <row r="744" customHeight="1" spans="4:4">
       <c r="D744" s="3"/>
     </row>
-    <row r="745">
+    <row r="745" customHeight="1" spans="4:4">
       <c r="D745" s="3"/>
     </row>
-    <row r="746">
+    <row r="746" customHeight="1" spans="4:4">
       <c r="D746" s="3"/>
     </row>
-    <row r="747">
+    <row r="747" customHeight="1" spans="4:4">
       <c r="D747" s="3"/>
     </row>
-    <row r="748">
+    <row r="748" customHeight="1" spans="4:4">
       <c r="D748" s="3"/>
     </row>
-    <row r="749">
+    <row r="749" customHeight="1" spans="4:4">
       <c r="D749" s="3"/>
     </row>
-    <row r="750">
+    <row r="750" customHeight="1" spans="4:4">
       <c r="D750" s="3"/>
     </row>
-    <row r="751">
+    <row r="751" customHeight="1" spans="4:4">
       <c r="D751" s="3"/>
     </row>
-    <row r="752">
+    <row r="752" customHeight="1" spans="4:4">
       <c r="D752" s="3"/>
     </row>
-    <row r="753">
+    <row r="753" customHeight="1" spans="4:4">
       <c r="D753" s="3"/>
     </row>
-    <row r="754">
+    <row r="754" customHeight="1" spans="4:4">
       <c r="D754" s="3"/>
     </row>
-    <row r="755">
+    <row r="755" customHeight="1" spans="4:4">
       <c r="D755" s="3"/>
     </row>
-    <row r="756">
+    <row r="756" customHeight="1" spans="4:4">
       <c r="D756" s="3"/>
     </row>
-    <row r="757">
+    <row r="757" customHeight="1" spans="4:4">
       <c r="D757" s="3"/>
     </row>
-    <row r="758">
+    <row r="758" customHeight="1" spans="4:4">
       <c r="D758" s="3"/>
     </row>
-    <row r="759">
+    <row r="759" customHeight="1" spans="4:4">
       <c r="D759" s="3"/>
     </row>
-    <row r="760">
+    <row r="760" customHeight="1" spans="4:4">
       <c r="D760" s="3"/>
     </row>
-    <row r="761">
+    <row r="761" customHeight="1" spans="4:4">
       <c r="D761" s="3"/>
     </row>
-    <row r="762">
+    <row r="762" customHeight="1" spans="4:4">
       <c r="D762" s="3"/>
     </row>
-    <row r="763">
+    <row r="763" customHeight="1" spans="4:4">
       <c r="D763" s="3"/>
     </row>
-    <row r="764">
+    <row r="764" customHeight="1" spans="4:4">
       <c r="D764" s="3"/>
     </row>
-    <row r="765">
+    <row r="765" customHeight="1" spans="4:4">
       <c r="D765" s="3"/>
     </row>
-    <row r="766">
+    <row r="766" customHeight="1" spans="4:4">
       <c r="D766" s="3"/>
     </row>
-    <row r="767">
+    <row r="767" customHeight="1" spans="4:4">
       <c r="D767" s="3"/>
     </row>
-    <row r="768">
+    <row r="768" customHeight="1" spans="4:4">
       <c r="D768" s="3"/>
     </row>
-    <row r="769">
+    <row r="769" customHeight="1" spans="4:4">
       <c r="D769" s="3"/>
     </row>
-    <row r="770">
+    <row r="770" customHeight="1" spans="4:4">
       <c r="D770" s="3"/>
     </row>
-    <row r="771">
+    <row r="771" customHeight="1" spans="4:4">
       <c r="D771" s="3"/>
     </row>
-    <row r="772">
+    <row r="772" customHeight="1" spans="4:4">
       <c r="D772" s="3"/>
     </row>
-    <row r="773">
+    <row r="773" customHeight="1" spans="4:4">
       <c r="D773" s="3"/>
     </row>
-    <row r="774">
+    <row r="774" customHeight="1" spans="4:4">
       <c r="D774" s="3"/>
     </row>
-    <row r="775">
+    <row r="775" customHeight="1" spans="4:4">
       <c r="D775" s="3"/>
     </row>
-    <row r="776">
+    <row r="776" customHeight="1" spans="4:4">
       <c r="D776" s="3"/>
     </row>
-    <row r="777">
+    <row r="777" customHeight="1" spans="4:4">
       <c r="D777" s="3"/>
     </row>
-    <row r="778">
+    <row r="778" customHeight="1" spans="4:4">
       <c r="D778" s="3"/>
     </row>
-    <row r="779">
+    <row r="779" customHeight="1" spans="4:4">
       <c r="D779" s="3"/>
     </row>
-    <row r="780">
+    <row r="780" customHeight="1" spans="4:4">
       <c r="D780" s="3"/>
     </row>
-    <row r="781">
+    <row r="781" customHeight="1" spans="4:4">
       <c r="D781" s="3"/>
     </row>
-    <row r="782">
+    <row r="782" customHeight="1" spans="4:4">
       <c r="D782" s="3"/>
     </row>
-    <row r="783">
+    <row r="783" customHeight="1" spans="4:4">
       <c r="D783" s="3"/>
     </row>
-    <row r="784">
+    <row r="784" customHeight="1" spans="4:4">
       <c r="D784" s="3"/>
     </row>
-    <row r="785">
+    <row r="785" customHeight="1" spans="4:4">
       <c r="D785" s="3"/>
     </row>
-    <row r="786">
+    <row r="786" customHeight="1" spans="4:4">
       <c r="D786" s="3"/>
     </row>
-    <row r="787">
+    <row r="787" customHeight="1" spans="4:4">
       <c r="D787" s="3"/>
     </row>
-    <row r="788">
+    <row r="788" customHeight="1" spans="4:4">
       <c r="D788" s="3"/>
     </row>
-    <row r="789">
+    <row r="789" customHeight="1" spans="4:4">
       <c r="D789" s="3"/>
     </row>
-    <row r="790">
+    <row r="790" customHeight="1" spans="4:4">
       <c r="D790" s="3"/>
     </row>
-    <row r="791">
+    <row r="791" customHeight="1" spans="4:4">
       <c r="D791" s="3"/>
     </row>
-    <row r="792">
+    <row r="792" customHeight="1" spans="4:4">
       <c r="D792" s="3"/>
     </row>
-    <row r="793">
+    <row r="793" customHeight="1" spans="4:4">
       <c r="D793" s="3"/>
     </row>
-    <row r="794">
+    <row r="794" customHeight="1" spans="4:4">
       <c r="D794" s="3"/>
     </row>
-    <row r="795">
+    <row r="795" customHeight="1" spans="4:4">
       <c r="D795" s="3"/>
     </row>
-    <row r="796">
+    <row r="796" customHeight="1" spans="4:4">
       <c r="D796" s="3"/>
     </row>
-    <row r="797">
+    <row r="797" customHeight="1" spans="4:4">
       <c r="D797" s="3"/>
     </row>
-    <row r="798">
+    <row r="798" customHeight="1" spans="4:4">
       <c r="D798" s="3"/>
     </row>
-    <row r="799">
+    <row r="799" customHeight="1" spans="4:4">
       <c r="D799" s="3"/>
     </row>
-    <row r="800">
+    <row r="800" customHeight="1" spans="4:4">
       <c r="D800" s="3"/>
     </row>
-    <row r="801">
+    <row r="801" customHeight="1" spans="4:4">
       <c r="D801" s="3"/>
     </row>
-    <row r="802">
+    <row r="802" customHeight="1" spans="4:4">
       <c r="D802" s="3"/>
     </row>
-    <row r="803">
+    <row r="803" customHeight="1" spans="4:4">
       <c r="D803" s="3"/>
     </row>
-    <row r="804">
+    <row r="804" customHeight="1" spans="4:4">
       <c r="D804" s="3"/>
     </row>
-    <row r="805">
+    <row r="805" customHeight="1" spans="4:4">
       <c r="D805" s="3"/>
     </row>
-    <row r="806">
+    <row r="806" customHeight="1" spans="4:4">
       <c r="D806" s="3"/>
     </row>
-    <row r="807">
+    <row r="807" customHeight="1" spans="4:4">
       <c r="D807" s="3"/>
     </row>
-    <row r="808">
+    <row r="808" customHeight="1" spans="4:4">
       <c r="D808" s="3"/>
     </row>
-    <row r="809">
+    <row r="809" customHeight="1" spans="4:4">
       <c r="D809" s="3"/>
     </row>
-    <row r="810">
+    <row r="810" customHeight="1" spans="4:4">
       <c r="D810" s="3"/>
     </row>
-    <row r="811">
+    <row r="811" customHeight="1" spans="4:4">
       <c r="D811" s="3"/>
     </row>
-    <row r="812">
+    <row r="812" customHeight="1" spans="4:4">
       <c r="D812" s="3"/>
     </row>
-    <row r="813">
+    <row r="813" customHeight="1" spans="4:4">
       <c r="D813" s="3"/>
     </row>
-    <row r="814">
+    <row r="814" customHeight="1" spans="4:4">
       <c r="D814" s="3"/>
     </row>
-    <row r="815">
+    <row r="815" customHeight="1" spans="4:4">
       <c r="D815" s="3"/>
     </row>
-    <row r="816">
+    <row r="816" customHeight="1" spans="4:4">
       <c r="D816" s="3"/>
     </row>
-    <row r="817">
+    <row r="817" customHeight="1" spans="4:4">
       <c r="D817" s="3"/>
     </row>
-    <row r="818">
+    <row r="818" customHeight="1" spans="4:4">
       <c r="D818" s="3"/>
     </row>
-    <row r="819">
+    <row r="819" customHeight="1" spans="4:4">
       <c r="D819" s="3"/>
     </row>
-    <row r="820">
+    <row r="820" customHeight="1" spans="4:4">
       <c r="D820" s="3"/>
     </row>
-    <row r="821">
+    <row r="821" customHeight="1" spans="4:4">
       <c r="D821" s="3"/>
     </row>
-    <row r="822">
+    <row r="822" customHeight="1" spans="4:4">
       <c r="D822" s="3"/>
     </row>
-    <row r="823">
+    <row r="823" customHeight="1" spans="4:4">
       <c r="D823" s="3"/>
     </row>
-    <row r="824">
+    <row r="824" customHeight="1" spans="4:4">
       <c r="D824" s="3"/>
     </row>
-    <row r="825">
+    <row r="825" customHeight="1" spans="4:4">
       <c r="D825" s="3"/>
     </row>
-    <row r="826">
+    <row r="826" customHeight="1" spans="4:4">
       <c r="D826" s="3"/>
     </row>
-    <row r="827">
+    <row r="827" customHeight="1" spans="4:4">
       <c r="D827" s="3"/>
     </row>
-    <row r="828">
+    <row r="828" customHeight="1" spans="4:4">
       <c r="D828" s="3"/>
     </row>
-    <row r="829">
+    <row r="829" customHeight="1" spans="4:4">
       <c r="D829" s="3"/>
     </row>
-    <row r="830">
+    <row r="830" customHeight="1" spans="4:4">
       <c r="D830" s="3"/>
     </row>
-    <row r="831">
+    <row r="831" customHeight="1" spans="4:4">
       <c r="D831" s="3"/>
     </row>
-    <row r="832">
+    <row r="832" customHeight="1" spans="4:4">
       <c r="D832" s="3"/>
     </row>
-    <row r="833">
+    <row r="833" customHeight="1" spans="4:4">
       <c r="D833" s="3"/>
     </row>
-    <row r="834">
+    <row r="834" customHeight="1" spans="4:4">
       <c r="D834" s="3"/>
     </row>
-    <row r="835">
+    <row r="835" customHeight="1" spans="4:4">
       <c r="D835" s="3"/>
     </row>
-    <row r="836">
+    <row r="836" customHeight="1" spans="4:4">
       <c r="D836" s="3"/>
     </row>
-    <row r="837">
+    <row r="837" customHeight="1" spans="4:4">
       <c r="D837" s="3"/>
     </row>
-    <row r="838">
+    <row r="838" customHeight="1" spans="4:4">
       <c r="D838" s="3"/>
     </row>
-    <row r="839">
+    <row r="839" customHeight="1" spans="4:4">
       <c r="D839" s="3"/>
     </row>
-    <row r="840">
+    <row r="840" customHeight="1" spans="4:4">
       <c r="D840" s="3"/>
     </row>
-    <row r="841">
+    <row r="841" customHeight="1" spans="4:4">
       <c r="D841" s="3"/>
     </row>
-    <row r="842">
+    <row r="842" customHeight="1" spans="4:4">
       <c r="D842" s="3"/>
     </row>
-    <row r="843">
+    <row r="843" customHeight="1" spans="4:4">
       <c r="D843" s="3"/>
     </row>
-    <row r="844">
+    <row r="844" customHeight="1" spans="4:4">
       <c r="D844" s="3"/>
     </row>
-    <row r="845">
+    <row r="845" customHeight="1" spans="4:4">
       <c r="D845" s="3"/>
     </row>
-    <row r="846">
+    <row r="846" customHeight="1" spans="4:4">
       <c r="D846" s="3"/>
     </row>
-    <row r="847">
+    <row r="847" customHeight="1" spans="4:4">
       <c r="D847" s="3"/>
     </row>
-    <row r="848">
+    <row r="848" customHeight="1" spans="4:4">
       <c r="D848" s="3"/>
     </row>
-    <row r="849">
+    <row r="849" customHeight="1" spans="4:4">
       <c r="D849" s="3"/>
     </row>
-    <row r="850">
+    <row r="850" customHeight="1" spans="4:4">
       <c r="D850" s="3"/>
     </row>
-    <row r="851">
+    <row r="851" customHeight="1" spans="4:4">
       <c r="D851" s="3"/>
     </row>
-    <row r="852">
+    <row r="852" customHeight="1" spans="4:4">
       <c r="D852" s="3"/>
     </row>
-    <row r="853">
+    <row r="853" customHeight="1" spans="4:4">
       <c r="D853" s="3"/>
     </row>
-    <row r="854">
+    <row r="854" customHeight="1" spans="4:4">
       <c r="D854" s="3"/>
     </row>
-    <row r="855">
+    <row r="855" customHeight="1" spans="4:4">
       <c r="D855" s="3"/>
     </row>
-    <row r="856">
+    <row r="856" customHeight="1" spans="4:4">
       <c r="D856" s="3"/>
     </row>
-    <row r="857">
+    <row r="857" customHeight="1" spans="4:4">
       <c r="D857" s="3"/>
     </row>
-    <row r="858">
+    <row r="858" customHeight="1" spans="4:4">
       <c r="D858" s="3"/>
     </row>
-    <row r="859">
+    <row r="859" customHeight="1" spans="4:4">
       <c r="D859" s="3"/>
     </row>
-    <row r="860">
+    <row r="860" customHeight="1" spans="4:4">
       <c r="D860" s="3"/>
     </row>
-    <row r="861">
+    <row r="861" customHeight="1" spans="4:4">
       <c r="D861" s="3"/>
     </row>
-    <row r="862">
+    <row r="862" customHeight="1" spans="4:4">
       <c r="D862" s="3"/>
     </row>
-    <row r="863">
+    <row r="863" customHeight="1" spans="4:4">
       <c r="D863" s="3"/>
     </row>
-    <row r="864">
+    <row r="864" customHeight="1" spans="4:4">
       <c r="D864" s="3"/>
     </row>
-    <row r="865">
+    <row r="865" customHeight="1" spans="4:4">
       <c r="D865" s="3"/>
     </row>
-    <row r="866">
+    <row r="866" customHeight="1" spans="4:4">
       <c r="D866" s="3"/>
     </row>
-    <row r="867">
+    <row r="867" customHeight="1" spans="4:4">
       <c r="D867" s="3"/>
     </row>
-    <row r="868">
+    <row r="868" customHeight="1" spans="4:4">
       <c r="D868" s="3"/>
     </row>
-    <row r="869">
+    <row r="869" customHeight="1" spans="4:4">
       <c r="D869" s="3"/>
     </row>
-    <row r="870">
+    <row r="870" customHeight="1" spans="4:4">
       <c r="D870" s="3"/>
     </row>
-    <row r="871">
+    <row r="871" customHeight="1" spans="4:4">
       <c r="D871" s="3"/>
     </row>
-    <row r="872">
+    <row r="872" customHeight="1" spans="4:4">
       <c r="D872" s="3"/>
     </row>
-    <row r="873">
+    <row r="873" customHeight="1" spans="4:4">
       <c r="D873" s="3"/>
     </row>
-    <row r="874">
+    <row r="874" customHeight="1" spans="4:4">
       <c r="D874" s="3"/>
     </row>
-    <row r="875">
+    <row r="875" customHeight="1" spans="4:4">
       <c r="D875" s="3"/>
     </row>
-    <row r="876">
+    <row r="876" customHeight="1" spans="4:4">
       <c r="D876" s="3"/>
     </row>
-    <row r="877">
+    <row r="877" customHeight="1" spans="4:4">
       <c r="D877" s="3"/>
     </row>
-    <row r="878">
+    <row r="878" customHeight="1" spans="4:4">
       <c r="D878" s="3"/>
     </row>
-    <row r="879">
+    <row r="879" customHeight="1" spans="4:4">
       <c r="D879" s="3"/>
     </row>
-    <row r="880">
+    <row r="880" customHeight="1" spans="4:4">
       <c r="D880" s="3"/>
     </row>
-    <row r="881">
+    <row r="881" customHeight="1" spans="4:4">
       <c r="D881" s="3"/>
     </row>
-    <row r="882">
+    <row r="882" customHeight="1" spans="4:4">
       <c r="D882" s="3"/>
     </row>
-    <row r="883">
+    <row r="883" customHeight="1" spans="4:4">
       <c r="D883" s="3"/>
     </row>
-    <row r="884">
+    <row r="884" customHeight="1" spans="4:4">
       <c r="D884" s="3"/>
     </row>
-    <row r="885">
+    <row r="885" customHeight="1" spans="4:4">
       <c r="D885" s="3"/>
     </row>
-    <row r="886">
+    <row r="886" customHeight="1" spans="4:4">
       <c r="D886" s="3"/>
     </row>
-    <row r="887">
+    <row r="887" customHeight="1" spans="4:4">
       <c r="D887" s="3"/>
     </row>
-    <row r="888">
+    <row r="888" customHeight="1" spans="4:4">
       <c r="D888" s="3"/>
     </row>
-    <row r="889">
+    <row r="889" customHeight="1" spans="4:4">
       <c r="D889" s="3"/>
     </row>
-    <row r="890">
+    <row r="890" customHeight="1" spans="4:4">
       <c r="D890" s="3"/>
     </row>
-    <row r="891">
+    <row r="891" customHeight="1" spans="4:4">
       <c r="D891" s="3"/>
     </row>
-    <row r="892">
+    <row r="892" customHeight="1" spans="4:4">
       <c r="D892" s="3"/>
     </row>
-    <row r="893">
+    <row r="893" customHeight="1" spans="4:4">
       <c r="D893" s="3"/>
     </row>
-    <row r="894">
+    <row r="894" customHeight="1" spans="4:4">
       <c r="D894" s="3"/>
     </row>
-    <row r="895">
+    <row r="895" customHeight="1" spans="4:4">
       <c r="D895" s="3"/>
     </row>
-    <row r="896">
+    <row r="896" customHeight="1" spans="4:4">
       <c r="D896" s="3"/>
     </row>
-    <row r="897">
+    <row r="897" customHeight="1" spans="4:4">
       <c r="D897" s="3"/>
     </row>
-    <row r="898">
+    <row r="898" customHeight="1" spans="4:4">
       <c r="D898" s="3"/>
     </row>
-    <row r="899">
+    <row r="899" customHeight="1" spans="4:4">
       <c r="D899" s="3"/>
     </row>
-    <row r="900">
+    <row r="900" customHeight="1" spans="4:4">
       <c r="D900" s="3"/>
     </row>
-    <row r="901">
+    <row r="901" customHeight="1" spans="4:4">
       <c r="D901" s="3"/>
     </row>
-    <row r="902">
+    <row r="902" customHeight="1" spans="4:4">
       <c r="D902" s="3"/>
     </row>
-    <row r="903">
+    <row r="903" customHeight="1" spans="4:4">
       <c r="D903" s="3"/>
     </row>
-    <row r="904">
+    <row r="904" customHeight="1" spans="4:4">
       <c r="D904" s="3"/>
     </row>
-    <row r="905">
+    <row r="905" customHeight="1" spans="4:4">
       <c r="D905" s="3"/>
     </row>
-    <row r="906">
+    <row r="906" customHeight="1" spans="4:4">
       <c r="D906" s="3"/>
     </row>
-    <row r="907">
+    <row r="907" customHeight="1" spans="4:4">
       <c r="D907" s="3"/>
     </row>
-    <row r="908">
+    <row r="908" customHeight="1" spans="4:4">
       <c r="D908" s="3"/>
     </row>
-    <row r="909">
+    <row r="909" customHeight="1" spans="4:4">
       <c r="D909" s="3"/>
     </row>
-    <row r="910">
+    <row r="910" customHeight="1" spans="4:4">
       <c r="D910" s="3"/>
     </row>
-    <row r="911">
+    <row r="911" customHeight="1" spans="4:4">
       <c r="D911" s="3"/>
     </row>
-    <row r="912">
+    <row r="912" customHeight="1" spans="4:4">
       <c r="D912" s="3"/>
     </row>
-    <row r="913">
+    <row r="913" customHeight="1" spans="4:4">
       <c r="D913" s="3"/>
     </row>
-    <row r="914">
+    <row r="914" customHeight="1" spans="4:4">
       <c r="D914" s="3"/>
     </row>
-    <row r="915">
+    <row r="915" customHeight="1" spans="4:4">
       <c r="D915" s="3"/>
     </row>
-    <row r="916">
+    <row r="916" customHeight="1" spans="4:4">
       <c r="D916" s="3"/>
     </row>
-    <row r="917">
+    <row r="917" customHeight="1" spans="4:4">
       <c r="D917" s="3"/>
     </row>
-    <row r="918">
+    <row r="918" customHeight="1" spans="4:4">
       <c r="D918" s="3"/>
     </row>
-    <row r="919">
+    <row r="919" customHeight="1" spans="4:4">
       <c r="D919" s="3"/>
     </row>
-    <row r="920">
+    <row r="920" customHeight="1" spans="4:4">
       <c r="D920" s="3"/>
     </row>
-    <row r="921">
+    <row r="921" customHeight="1" spans="4:4">
       <c r="D921" s="3"/>
     </row>
-    <row r="922">
+    <row r="922" customHeight="1" spans="4:4">
       <c r="D922" s="3"/>
     </row>
-    <row r="923">
+    <row r="923" customHeight="1" spans="4:4">
       <c r="D923" s="3"/>
     </row>
-    <row r="924">
+    <row r="924" customHeight="1" spans="4:4">
       <c r="D924" s="3"/>
     </row>
-    <row r="925">
+    <row r="925" customHeight="1" spans="4:4">
       <c r="D925" s="3"/>
     </row>
-    <row r="926">
+    <row r="926" customHeight="1" spans="4:4">
       <c r="D926" s="3"/>
     </row>
-    <row r="927">
+    <row r="927" customHeight="1" spans="4:4">
       <c r="D927" s="3"/>
     </row>
-    <row r="928">
+    <row r="928" customHeight="1" spans="4:4">
       <c r="D928" s="3"/>
     </row>
-    <row r="929">
+    <row r="929" customHeight="1" spans="4:4">
       <c r="D929" s="3"/>
     </row>
-    <row r="930">
+    <row r="930" customHeight="1" spans="4:4">
       <c r="D930" s="3"/>
     </row>
-    <row r="931">
+    <row r="931" customHeight="1" spans="4:4">
       <c r="D931" s="3"/>
     </row>
-    <row r="932">
+    <row r="932" customHeight="1" spans="4:4">
       <c r="D932" s="3"/>
     </row>
-    <row r="933">
+    <row r="933" customHeight="1" spans="4:4">
       <c r="D933" s="3"/>
     </row>
-    <row r="934">
+    <row r="934" customHeight="1" spans="4:4">
       <c r="D934" s="3"/>
     </row>
-    <row r="935">
+    <row r="935" customHeight="1" spans="4:4">
       <c r="D935" s="3"/>
     </row>
-    <row r="936">
+    <row r="936" customHeight="1" spans="4:4">
       <c r="D936" s="3"/>
     </row>
-    <row r="937">
+    <row r="937" customHeight="1" spans="4:4">
       <c r="D937" s="3"/>
     </row>
-    <row r="938">
+    <row r="938" customHeight="1" spans="4:4">
       <c r="D938" s="3"/>
     </row>
-    <row r="939">
+    <row r="939" customHeight="1" spans="4:4">
       <c r="D939" s="3"/>
     </row>
-    <row r="940">
+    <row r="940" customHeight="1" spans="4:4">
       <c r="D940" s="3"/>
     </row>
-    <row r="941">
+    <row r="941" customHeight="1" spans="4:4">
       <c r="D941" s="3"/>
     </row>
-    <row r="942">
+    <row r="942" customHeight="1" spans="4:4">
       <c r="D942" s="3"/>
     </row>
-    <row r="943">
+    <row r="943" customHeight="1" spans="4:4">
       <c r="D943" s="3"/>
     </row>
-    <row r="944">
+    <row r="944" customHeight="1" spans="4:4">
       <c r="D944" s="3"/>
     </row>
-    <row r="945">
+    <row r="945" customHeight="1" spans="4:4">
       <c r="D945" s="3"/>
     </row>
-    <row r="946">
+    <row r="946" customHeight="1" spans="4:4">
       <c r="D946" s="3"/>
     </row>
-    <row r="947">
+    <row r="947" customHeight="1" spans="4:4">
       <c r="D947" s="3"/>
     </row>
-    <row r="948">
+    <row r="948" customHeight="1" spans="4:4">
       <c r="D948" s="3"/>
     </row>
-    <row r="949">
+    <row r="949" customHeight="1" spans="4:4">
       <c r="D949" s="3"/>
     </row>
-    <row r="950">
+    <row r="950" customHeight="1" spans="4:4">
       <c r="D950" s="3"/>
     </row>
-    <row r="951">
+    <row r="951" customHeight="1" spans="4:4">
       <c r="D951" s="3"/>
     </row>
-    <row r="952">
+    <row r="952" customHeight="1" spans="4:4">
       <c r="D952" s="3"/>
     </row>
-    <row r="953">
+    <row r="953" customHeight="1" spans="4:4">
       <c r="D953" s="3"/>
     </row>
-    <row r="954">
+    <row r="954" customHeight="1" spans="4:4">
       <c r="D954" s="3"/>
     </row>
-    <row r="955">
+    <row r="955" customHeight="1" spans="4:4">
       <c r="D955" s="3"/>
     </row>
-    <row r="956">
+    <row r="956" customHeight="1" spans="4:4">
       <c r="D956" s="3"/>
     </row>
-    <row r="957">
+    <row r="957" customHeight="1" spans="4:4">
       <c r="D957" s="3"/>
     </row>
-    <row r="958">
+    <row r="958" customHeight="1" spans="4:4">
       <c r="D958" s="3"/>
     </row>
-    <row r="959">
+    <row r="959" customHeight="1" spans="4:4">
       <c r="D959" s="3"/>
     </row>
-    <row r="960">
+    <row r="960" customHeight="1" spans="4:4">
       <c r="D960" s="3"/>
     </row>
-    <row r="961">
+    <row r="961" customHeight="1" spans="4:4">
       <c r="D961" s="3"/>
     </row>
-    <row r="962">
+    <row r="962" customHeight="1" spans="4:4">
       <c r="D962" s="3"/>
     </row>
-    <row r="963">
+    <row r="963" customHeight="1" spans="4:4">
       <c r="D963" s="3"/>
     </row>
-    <row r="964">
+    <row r="964" customHeight="1" spans="4:4">
       <c r="D964" s="3"/>
     </row>
-    <row r="965">
+    <row r="965" customHeight="1" spans="4:4">
       <c r="D965" s="3"/>
     </row>
-    <row r="966">
+    <row r="966" customHeight="1" spans="4:4">
       <c r="D966" s="3"/>
     </row>
-    <row r="967">
+    <row r="967" customHeight="1" spans="4:4">
       <c r="D967" s="3"/>
     </row>
-    <row r="968">
+    <row r="968" customHeight="1" spans="4:4">
       <c r="D968" s="3"/>
     </row>
-    <row r="969">
+    <row r="969" customHeight="1" spans="4:4">
       <c r="D969" s="3"/>
     </row>
-    <row r="970">
+    <row r="970" customHeight="1" spans="4:4">
       <c r="D970" s="3"/>
     </row>
-    <row r="971">
+    <row r="971" customHeight="1" spans="4:4">
       <c r="D971" s="3"/>
     </row>
-    <row r="972">
+    <row r="972" customHeight="1" spans="4:4">
       <c r="D972" s="3"/>
     </row>
-    <row r="973">
+    <row r="973" customHeight="1" spans="4:4">
       <c r="D973" s="3"/>
     </row>
-    <row r="974">
+    <row r="974" customHeight="1" spans="4:4">
       <c r="D974" s="3"/>
     </row>
-    <row r="975">
+    <row r="975" customHeight="1" spans="4:4">
       <c r="D975" s="3"/>
     </row>
-    <row r="976">
+    <row r="976" customHeight="1" spans="4:4">
       <c r="D976" s="3"/>
     </row>
-    <row r="977">
+    <row r="977" customHeight="1" spans="4:4">
       <c r="D977" s="3"/>
     </row>
-    <row r="978">
+    <row r="978" customHeight="1" spans="4:4">
       <c r="D978" s="3"/>
     </row>
-    <row r="979">
+    <row r="979" customHeight="1" spans="4:4">
       <c r="D979" s="3"/>
     </row>
-    <row r="980">
+    <row r="980" customHeight="1" spans="4:4">
       <c r="D980" s="3"/>
     </row>
-    <row r="981">
+    <row r="981" customHeight="1" spans="4:4">
       <c r="D981" s="3"/>
     </row>
-    <row r="982">
+    <row r="982" customHeight="1" spans="4:4">
       <c r="D982" s="3"/>
     </row>
-    <row r="983">
+    <row r="983" customHeight="1" spans="4:4">
       <c r="D983" s="3"/>
     </row>
-    <row r="984">
+    <row r="984" customHeight="1" spans="4:4">
       <c r="D984" s="3"/>
     </row>
-    <row r="985">
+    <row r="985" customHeight="1" spans="4:4">
       <c r="D985" s="3"/>
     </row>
-    <row r="986">
+    <row r="986" customHeight="1" spans="4:4">
       <c r="D986" s="3"/>
     </row>
-    <row r="987">
+    <row r="987" customHeight="1" spans="4:4">
       <c r="D987" s="3"/>
     </row>
-    <row r="988">
+    <row r="988" customHeight="1" spans="4:4">
       <c r="D988" s="3"/>
     </row>
-    <row r="989">
+    <row r="989" customHeight="1" spans="4:4">
       <c r="D989" s="3"/>
     </row>
-    <row r="990">
+    <row r="990" customHeight="1" spans="4:4">
       <c r="D990" s="3"/>
     </row>
-    <row r="991">
+    <row r="991" customHeight="1" spans="4:4">
       <c r="D991" s="3"/>
     </row>
-    <row r="992">
+    <row r="992" customHeight="1" spans="4:4">
       <c r="D992" s="3"/>
     </row>
-    <row r="993">
+    <row r="993" customHeight="1" spans="4:4">
       <c r="D993" s="3"/>
     </row>
-    <row r="994">
+    <row r="994" customHeight="1" spans="4:4">
       <c r="D994" s="3"/>
     </row>
-    <row r="995">
+    <row r="995" customHeight="1" spans="4:4">
       <c r="D995" s="3"/>
     </row>
-    <row r="996">
+    <row r="996" customHeight="1" spans="4:4">
       <c r="D996" s="3"/>
     </row>
-    <row r="997">
+    <row r="997" customHeight="1" spans="4:4">
       <c r="D997" s="3"/>
     </row>
-    <row r="998">
+    <row r="998" customHeight="1" spans="4:4">
       <c r="D998" s="3"/>
     </row>
-    <row r="999">
+    <row r="999" customHeight="1" spans="4:4">
       <c r="D999" s="3"/>
     </row>
-    <row r="1000">
+    <row r="1000" customHeight="1" spans="4:4">
       <c r="D1000" s="3"/>
     </row>
-    <row r="1001">
+    <row r="1001" customHeight="1" spans="4:4">
       <c r="D1001" s="3"/>
     </row>
   </sheetData>
@@ -3797,6 +4659,7 @@
       <formula>LEN(TRIM(D1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/SoundData.xlsx
+++ b/JsonConverter/ExcelFiles/SoundData.xlsx
@@ -1,12 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="시트1" sheetId="1" r:id="rId5"/>
+    <sheet name="시트1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -223,81 +239,927 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
-    <border/>
+  <borders count="9">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="18">
     <dxf>
-      <font/>
       <fill>
         <patternFill patternType="none"/>
       </fill>
-      <border/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
     </dxf>
   </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="totalRow" dxfId="5"/>
+      <tableStyleElement type="firstColumn" dxfId="4"/>
+      <tableStyleElement type="lastColumn" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="totalRow" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
+      <tableStyleElement type="pageFieldValues" dxfId="8"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -487,28 +1349,30 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:D1001"/>
+  <sheetFormatPr defaultColWidth="12.6296296296296" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="3"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.75"/>
-    <col customWidth="1" min="2" max="2" width="14.5"/>
-    <col customWidth="1" min="3" max="3" width="13.5"/>
-    <col customWidth="1" min="4" max="4" width="12.75"/>
-    <col customWidth="1" min="5" max="5" width="16.5"/>
-    <col customWidth="1" min="6" max="6" width="16.25"/>
-    <col customWidth="1" min="7" max="7" width="23.75"/>
-    <col customWidth="1" min="8" max="8" width="29.63"/>
-    <col customWidth="1" min="9" max="9" width="17.25"/>
+    <col min="1" max="1" width="14.75" customWidth="1"/>
+    <col min="2" max="2" width="14.5" customWidth="1"/>
+    <col min="3" max="3" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="12.75" customWidth="1"/>
+    <col min="5" max="5" width="16.5" customWidth="1"/>
+    <col min="6" max="6" width="16.25" customWidth="1"/>
+    <col min="7" max="7" width="23.75" customWidth="1"/>
+    <col min="8" max="8" width="29.6296296296296" customWidth="1"/>
+    <col min="9" max="9" width="17.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -522,7 +1386,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" customHeight="1" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -536,7 +1400,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" customHeight="1" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -550,7 +1414,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" customHeight="1" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -558,13 +1422,13 @@
         <v>12</v>
       </c>
       <c r="C4" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" customHeight="1" spans="1:4">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -572,13 +1436,13 @@
         <v>15</v>
       </c>
       <c r="C5" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" customHeight="1" spans="1:4">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -586,13 +1450,13 @@
         <v>17</v>
       </c>
       <c r="C6" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" customHeight="1" spans="1:4">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -600,13 +1464,13 @@
         <v>20</v>
       </c>
       <c r="C7" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" customHeight="1" spans="1:4">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -614,13 +1478,13 @@
         <v>22</v>
       </c>
       <c r="C8" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" customHeight="1" spans="1:4">
       <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
@@ -628,13 +1492,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" customHeight="1" spans="1:4">
       <c r="A10" s="1" t="s">
         <v>25</v>
       </c>
@@ -642,13 +1506,13 @@
         <v>26</v>
       </c>
       <c r="C10" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" customHeight="1" spans="1:4">
       <c r="A11" s="1" t="s">
         <v>27</v>
       </c>
@@ -656,13 +1520,13 @@
         <v>28</v>
       </c>
       <c r="C11" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" customHeight="1" spans="1:4">
       <c r="A12" s="1" t="s">
         <v>29</v>
       </c>
@@ -670,13 +1534,13 @@
         <v>30</v>
       </c>
       <c r="C12" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" customHeight="1" spans="1:4">
       <c r="A13" s="1" t="s">
         <v>31</v>
       </c>
@@ -684,13 +1548,13 @@
         <v>32</v>
       </c>
       <c r="C13" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" customHeight="1" spans="1:4">
       <c r="A14" s="1" t="s">
         <v>33</v>
       </c>
@@ -698,13 +1562,13 @@
         <v>34</v>
       </c>
       <c r="C14" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" customHeight="1" spans="1:4">
       <c r="A15" s="1" t="s">
         <v>35</v>
       </c>
@@ -712,13 +1576,13 @@
         <v>36</v>
       </c>
       <c r="C15" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" customHeight="1" spans="1:4">
       <c r="A16" s="1" t="s">
         <v>37</v>
       </c>
@@ -726,13 +1590,13 @@
         <v>38</v>
       </c>
       <c r="C16" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" customHeight="1" spans="1:4">
       <c r="A17" s="1" t="s">
         <v>39</v>
       </c>
@@ -740,13 +1604,13 @@
         <v>40</v>
       </c>
       <c r="C17" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" customHeight="1" spans="1:4">
       <c r="A18" s="1" t="s">
         <v>41</v>
       </c>
@@ -754,13 +1618,13 @@
         <v>42</v>
       </c>
       <c r="C18" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" customHeight="1" spans="1:4">
       <c r="A19" s="1" t="s">
         <v>43</v>
       </c>
@@ -768,13 +1632,13 @@
         <v>44</v>
       </c>
       <c r="C19" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" customHeight="1" spans="1:4">
       <c r="A20" s="1" t="s">
         <v>45</v>
       </c>
@@ -782,13 +1646,13 @@
         <v>46</v>
       </c>
       <c r="C20" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" customHeight="1" spans="1:4">
       <c r="A21" s="1" t="s">
         <v>47</v>
       </c>
@@ -796,13 +1660,13 @@
         <v>48</v>
       </c>
       <c r="C21" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" customHeight="1" spans="1:4">
       <c r="A22" s="1" t="s">
         <v>49</v>
       </c>
@@ -810,13 +1674,13 @@
         <v>50</v>
       </c>
       <c r="C22" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" customHeight="1" spans="1:4">
       <c r="A23" s="1" t="s">
         <v>51</v>
       </c>
@@ -824,13 +1688,13 @@
         <v>52</v>
       </c>
       <c r="C23" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" customHeight="1" spans="1:4">
       <c r="A24" s="1" t="s">
         <v>53</v>
       </c>
@@ -838,13 +1702,13 @@
         <v>54</v>
       </c>
       <c r="C24" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" customHeight="1" spans="1:4">
       <c r="A25" s="1" t="s">
         <v>55</v>
       </c>
@@ -852,13 +1716,13 @@
         <v>56</v>
       </c>
       <c r="C25" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" customHeight="1" spans="1:4">
       <c r="A26" s="1" t="s">
         <v>57</v>
       </c>
@@ -866,13 +1730,13 @@
         <v>58</v>
       </c>
       <c r="C26" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" customHeight="1" spans="1:4">
       <c r="A27" s="1" t="s">
         <v>59</v>
       </c>
@@ -880,13 +1744,13 @@
         <v>60</v>
       </c>
       <c r="C27" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" customHeight="1" spans="1:4">
       <c r="A28" s="1" t="s">
         <v>61</v>
       </c>
@@ -894,13 +1758,13 @@
         <v>62</v>
       </c>
       <c r="C28" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" customHeight="1" spans="1:4">
       <c r="A29" s="3" t="s">
         <v>63</v>
       </c>
@@ -908,13 +1772,13 @@
         <v>64</v>
       </c>
       <c r="C29" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" customHeight="1" spans="1:4">
       <c r="A30" s="3" t="s">
         <v>65</v>
       </c>
@@ -922,13 +1786,13 @@
         <v>66</v>
       </c>
       <c r="C30" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" customHeight="1" spans="1:4">
       <c r="A31" s="3" t="s">
         <v>67</v>
       </c>
@@ -936,2920 +1800,2920 @@
         <v>68</v>
       </c>
       <c r="C31" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" customHeight="1" spans="1:4">
       <c r="D32" s="5"/>
     </row>
-    <row r="33">
+    <row r="33" customHeight="1" spans="4:4">
       <c r="D33" s="5"/>
     </row>
-    <row r="34">
+    <row r="34" customHeight="1" spans="4:4">
       <c r="D34" s="5"/>
     </row>
-    <row r="35">
+    <row r="35" customHeight="1" spans="4:4">
       <c r="D35" s="5"/>
     </row>
-    <row r="36">
+    <row r="36" customHeight="1" spans="4:4">
       <c r="D36" s="5"/>
     </row>
-    <row r="37">
+    <row r="37" customHeight="1" spans="4:4">
       <c r="D37" s="5"/>
     </row>
-    <row r="38">
+    <row r="38" customHeight="1" spans="4:4">
       <c r="D38" s="5"/>
     </row>
-    <row r="39">
+    <row r="39" customHeight="1" spans="4:4">
       <c r="D39" s="5"/>
     </row>
-    <row r="40">
+    <row r="40" customHeight="1" spans="4:4">
       <c r="D40" s="5"/>
     </row>
-    <row r="41">
+    <row r="41" customHeight="1" spans="4:4">
       <c r="D41" s="5"/>
     </row>
-    <row r="42">
+    <row r="42" customHeight="1" spans="4:4">
       <c r="D42" s="5"/>
     </row>
-    <row r="43">
+    <row r="43" customHeight="1" spans="4:4">
       <c r="D43" s="5"/>
     </row>
-    <row r="44">
+    <row r="44" customHeight="1" spans="4:4">
       <c r="D44" s="5"/>
     </row>
-    <row r="45">
+    <row r="45" customHeight="1" spans="4:4">
       <c r="D45" s="5"/>
     </row>
-    <row r="46">
+    <row r="46" customHeight="1" spans="4:4">
       <c r="D46" s="5"/>
     </row>
-    <row r="47">
+    <row r="47" customHeight="1" spans="4:4">
       <c r="D47" s="5"/>
     </row>
-    <row r="48">
+    <row r="48" customHeight="1" spans="4:4">
       <c r="D48" s="5"/>
     </row>
-    <row r="49">
+    <row r="49" customHeight="1" spans="4:4">
       <c r="D49" s="5"/>
     </row>
-    <row r="50">
+    <row r="50" customHeight="1" spans="4:4">
       <c r="D50" s="5"/>
     </row>
-    <row r="51">
+    <row r="51" customHeight="1" spans="4:4">
       <c r="D51" s="5"/>
     </row>
-    <row r="52">
+    <row r="52" customHeight="1" spans="4:4">
       <c r="D52" s="5"/>
     </row>
-    <row r="53">
+    <row r="53" customHeight="1" spans="4:4">
       <c r="D53" s="5"/>
     </row>
-    <row r="54">
+    <row r="54" customHeight="1" spans="4:4">
       <c r="D54" s="5"/>
     </row>
-    <row r="55">
+    <row r="55" customHeight="1" spans="4:4">
       <c r="D55" s="5"/>
     </row>
-    <row r="56">
+    <row r="56" customHeight="1" spans="4:4">
       <c r="D56" s="5"/>
     </row>
-    <row r="57">
+    <row r="57" customHeight="1" spans="4:4">
       <c r="D57" s="5"/>
     </row>
-    <row r="58">
+    <row r="58" customHeight="1" spans="4:4">
       <c r="D58" s="5"/>
     </row>
-    <row r="59">
+    <row r="59" customHeight="1" spans="4:4">
       <c r="D59" s="5"/>
     </row>
-    <row r="60">
+    <row r="60" customHeight="1" spans="4:4">
       <c r="D60" s="5"/>
     </row>
-    <row r="61">
+    <row r="61" customHeight="1" spans="4:4">
       <c r="D61" s="5"/>
     </row>
-    <row r="62">
+    <row r="62" customHeight="1" spans="4:4">
       <c r="D62" s="5"/>
     </row>
-    <row r="63">
+    <row r="63" customHeight="1" spans="4:4">
       <c r="D63" s="5"/>
     </row>
-    <row r="64">
+    <row r="64" customHeight="1" spans="4:4">
       <c r="D64" s="5"/>
     </row>
-    <row r="65">
+    <row r="65" customHeight="1" spans="4:4">
       <c r="D65" s="5"/>
     </row>
-    <row r="66">
+    <row r="66" customHeight="1" spans="4:4">
       <c r="D66" s="5"/>
     </row>
-    <row r="67">
+    <row r="67" customHeight="1" spans="4:4">
       <c r="D67" s="5"/>
     </row>
-    <row r="68">
+    <row r="68" customHeight="1" spans="4:4">
       <c r="D68" s="5"/>
     </row>
-    <row r="69">
+    <row r="69" customHeight="1" spans="4:4">
       <c r="D69" s="5"/>
     </row>
-    <row r="70">
+    <row r="70" customHeight="1" spans="4:4">
       <c r="D70" s="5"/>
     </row>
-    <row r="71">
+    <row r="71" customHeight="1" spans="4:4">
       <c r="D71" s="5"/>
     </row>
-    <row r="72">
+    <row r="72" customHeight="1" spans="4:4">
       <c r="D72" s="5"/>
     </row>
-    <row r="73">
+    <row r="73" customHeight="1" spans="4:4">
       <c r="D73" s="5"/>
     </row>
-    <row r="74">
+    <row r="74" customHeight="1" spans="4:4">
       <c r="D74" s="5"/>
     </row>
-    <row r="75">
+    <row r="75" customHeight="1" spans="4:4">
       <c r="D75" s="5"/>
     </row>
-    <row r="76">
+    <row r="76" customHeight="1" spans="4:4">
       <c r="D76" s="5"/>
     </row>
-    <row r="77">
+    <row r="77" customHeight="1" spans="4:4">
       <c r="D77" s="5"/>
     </row>
-    <row r="78">
+    <row r="78" customHeight="1" spans="4:4">
       <c r="D78" s="5"/>
     </row>
-    <row r="79">
+    <row r="79" customHeight="1" spans="4:4">
       <c r="D79" s="5"/>
     </row>
-    <row r="80">
+    <row r="80" customHeight="1" spans="4:4">
       <c r="D80" s="5"/>
     </row>
-    <row r="81">
+    <row r="81" customHeight="1" spans="4:4">
       <c r="D81" s="5"/>
     </row>
-    <row r="82">
+    <row r="82" customHeight="1" spans="4:4">
       <c r="D82" s="5"/>
     </row>
-    <row r="83">
+    <row r="83" customHeight="1" spans="4:4">
       <c r="D83" s="5"/>
     </row>
-    <row r="84">
+    <row r="84" customHeight="1" spans="4:4">
       <c r="D84" s="5"/>
     </row>
-    <row r="85">
+    <row r="85" customHeight="1" spans="4:4">
       <c r="D85" s="5"/>
     </row>
-    <row r="86">
+    <row r="86" customHeight="1" spans="4:4">
       <c r="D86" s="5"/>
     </row>
-    <row r="87">
+    <row r="87" customHeight="1" spans="4:4">
       <c r="D87" s="5"/>
     </row>
-    <row r="88">
+    <row r="88" customHeight="1" spans="4:4">
       <c r="D88" s="5"/>
     </row>
-    <row r="89">
+    <row r="89" customHeight="1" spans="4:4">
       <c r="D89" s="5"/>
     </row>
-    <row r="90">
+    <row r="90" customHeight="1" spans="4:4">
       <c r="D90" s="5"/>
     </row>
-    <row r="91">
+    <row r="91" customHeight="1" spans="4:4">
       <c r="D91" s="5"/>
     </row>
-    <row r="92">
+    <row r="92" customHeight="1" spans="4:4">
       <c r="D92" s="5"/>
     </row>
-    <row r="93">
+    <row r="93" customHeight="1" spans="4:4">
       <c r="D93" s="5"/>
     </row>
-    <row r="94">
+    <row r="94" customHeight="1" spans="4:4">
       <c r="D94" s="5"/>
     </row>
-    <row r="95">
+    <row r="95" customHeight="1" spans="4:4">
       <c r="D95" s="5"/>
     </row>
-    <row r="96">
+    <row r="96" customHeight="1" spans="4:4">
       <c r="D96" s="5"/>
     </row>
-    <row r="97">
+    <row r="97" customHeight="1" spans="4:4">
       <c r="D97" s="5"/>
     </row>
-    <row r="98">
+    <row r="98" customHeight="1" spans="4:4">
       <c r="D98" s="5"/>
     </row>
-    <row r="99">
+    <row r="99" customHeight="1" spans="4:4">
       <c r="D99" s="5"/>
     </row>
-    <row r="100">
+    <row r="100" customHeight="1" spans="4:4">
       <c r="D100" s="5"/>
     </row>
-    <row r="101">
+    <row r="101" customHeight="1" spans="4:4">
       <c r="D101" s="5"/>
     </row>
-    <row r="102">
+    <row r="102" customHeight="1" spans="4:4">
       <c r="D102" s="5"/>
     </row>
-    <row r="103">
+    <row r="103" customHeight="1" spans="4:4">
       <c r="D103" s="5"/>
     </row>
-    <row r="104">
+    <row r="104" customHeight="1" spans="4:4">
       <c r="D104" s="5"/>
     </row>
-    <row r="105">
+    <row r="105" customHeight="1" spans="4:4">
       <c r="D105" s="5"/>
     </row>
-    <row r="106">
+    <row r="106" customHeight="1" spans="4:4">
       <c r="D106" s="5"/>
     </row>
-    <row r="107">
+    <row r="107" customHeight="1" spans="4:4">
       <c r="D107" s="5"/>
     </row>
-    <row r="108">
+    <row r="108" customHeight="1" spans="4:4">
       <c r="D108" s="5"/>
     </row>
-    <row r="109">
+    <row r="109" customHeight="1" spans="4:4">
       <c r="D109" s="5"/>
     </row>
-    <row r="110">
+    <row r="110" customHeight="1" spans="4:4">
       <c r="D110" s="5"/>
     </row>
-    <row r="111">
+    <row r="111" customHeight="1" spans="4:4">
       <c r="D111" s="5"/>
     </row>
-    <row r="112">
+    <row r="112" customHeight="1" spans="4:4">
       <c r="D112" s="5"/>
     </row>
-    <row r="113">
+    <row r="113" customHeight="1" spans="4:4">
       <c r="D113" s="5"/>
     </row>
-    <row r="114">
+    <row r="114" customHeight="1" spans="4:4">
       <c r="D114" s="5"/>
     </row>
-    <row r="115">
+    <row r="115" customHeight="1" spans="4:4">
       <c r="D115" s="5"/>
     </row>
-    <row r="116">
+    <row r="116" customHeight="1" spans="4:4">
       <c r="D116" s="5"/>
     </row>
-    <row r="117">
+    <row r="117" customHeight="1" spans="4:4">
       <c r="D117" s="5"/>
     </row>
-    <row r="118">
+    <row r="118" customHeight="1" spans="4:4">
       <c r="D118" s="5"/>
     </row>
-    <row r="119">
+    <row r="119" customHeight="1" spans="4:4">
       <c r="D119" s="5"/>
     </row>
-    <row r="120">
+    <row r="120" customHeight="1" spans="4:4">
       <c r="D120" s="5"/>
     </row>
-    <row r="121">
+    <row r="121" customHeight="1" spans="4:4">
       <c r="D121" s="5"/>
     </row>
-    <row r="122">
+    <row r="122" customHeight="1" spans="4:4">
       <c r="D122" s="5"/>
     </row>
-    <row r="123">
+    <row r="123" customHeight="1" spans="4:4">
       <c r="D123" s="5"/>
     </row>
-    <row r="124">
+    <row r="124" customHeight="1" spans="4:4">
       <c r="D124" s="5"/>
     </row>
-    <row r="125">
+    <row r="125" customHeight="1" spans="4:4">
       <c r="D125" s="5"/>
     </row>
-    <row r="126">
+    <row r="126" customHeight="1" spans="4:4">
       <c r="D126" s="5"/>
     </row>
-    <row r="127">
+    <row r="127" customHeight="1" spans="4:4">
       <c r="D127" s="5"/>
     </row>
-    <row r="128">
+    <row r="128" customHeight="1" spans="4:4">
       <c r="D128" s="5"/>
     </row>
-    <row r="129">
+    <row r="129" customHeight="1" spans="4:4">
       <c r="D129" s="5"/>
     </row>
-    <row r="130">
+    <row r="130" customHeight="1" spans="4:4">
       <c r="D130" s="5"/>
     </row>
-    <row r="131">
+    <row r="131" customHeight="1" spans="4:4">
       <c r="D131" s="5"/>
     </row>
-    <row r="132">
+    <row r="132" customHeight="1" spans="4:4">
       <c r="D132" s="5"/>
     </row>
-    <row r="133">
+    <row r="133" customHeight="1" spans="4:4">
       <c r="D133" s="5"/>
     </row>
-    <row r="134">
+    <row r="134" customHeight="1" spans="4:4">
       <c r="D134" s="5"/>
     </row>
-    <row r="135">
+    <row r="135" customHeight="1" spans="4:4">
       <c r="D135" s="5"/>
     </row>
-    <row r="136">
+    <row r="136" customHeight="1" spans="4:4">
       <c r="D136" s="5"/>
     </row>
-    <row r="137">
+    <row r="137" customHeight="1" spans="4:4">
       <c r="D137" s="5"/>
     </row>
-    <row r="138">
+    <row r="138" customHeight="1" spans="4:4">
       <c r="D138" s="5"/>
     </row>
-    <row r="139">
+    <row r="139" customHeight="1" spans="4:4">
       <c r="D139" s="5"/>
     </row>
-    <row r="140">
+    <row r="140" customHeight="1" spans="4:4">
       <c r="D140" s="5"/>
     </row>
-    <row r="141">
+    <row r="141" customHeight="1" spans="4:4">
       <c r="D141" s="5"/>
     </row>
-    <row r="142">
+    <row r="142" customHeight="1" spans="4:4">
       <c r="D142" s="5"/>
     </row>
-    <row r="143">
+    <row r="143" customHeight="1" spans="4:4">
       <c r="D143" s="5"/>
     </row>
-    <row r="144">
+    <row r="144" customHeight="1" spans="4:4">
       <c r="D144" s="5"/>
     </row>
-    <row r="145">
+    <row r="145" customHeight="1" spans="4:4">
       <c r="D145" s="5"/>
     </row>
-    <row r="146">
+    <row r="146" customHeight="1" spans="4:4">
       <c r="D146" s="5"/>
     </row>
-    <row r="147">
+    <row r="147" customHeight="1" spans="4:4">
       <c r="D147" s="5"/>
     </row>
-    <row r="148">
+    <row r="148" customHeight="1" spans="4:4">
       <c r="D148" s="5"/>
     </row>
-    <row r="149">
+    <row r="149" customHeight="1" spans="4:4">
       <c r="D149" s="5"/>
     </row>
-    <row r="150">
+    <row r="150" customHeight="1" spans="4:4">
       <c r="D150" s="5"/>
     </row>
-    <row r="151">
+    <row r="151" customHeight="1" spans="4:4">
       <c r="D151" s="5"/>
     </row>
-    <row r="152">
+    <row r="152" customHeight="1" spans="4:4">
       <c r="D152" s="5"/>
     </row>
-    <row r="153">
+    <row r="153" customHeight="1" spans="4:4">
       <c r="D153" s="5"/>
     </row>
-    <row r="154">
+    <row r="154" customHeight="1" spans="4:4">
       <c r="D154" s="5"/>
     </row>
-    <row r="155">
+    <row r="155" customHeight="1" spans="4:4">
       <c r="D155" s="5"/>
     </row>
-    <row r="156">
+    <row r="156" customHeight="1" spans="4:4">
       <c r="D156" s="5"/>
     </row>
-    <row r="157">
+    <row r="157" customHeight="1" spans="4:4">
       <c r="D157" s="5"/>
     </row>
-    <row r="158">
+    <row r="158" customHeight="1" spans="4:4">
       <c r="D158" s="5"/>
     </row>
-    <row r="159">
+    <row r="159" customHeight="1" spans="4:4">
       <c r="D159" s="5"/>
     </row>
-    <row r="160">
+    <row r="160" customHeight="1" spans="4:4">
       <c r="D160" s="5"/>
     </row>
-    <row r="161">
+    <row r="161" customHeight="1" spans="4:4">
       <c r="D161" s="5"/>
     </row>
-    <row r="162">
+    <row r="162" customHeight="1" spans="4:4">
       <c r="D162" s="5"/>
     </row>
-    <row r="163">
+    <row r="163" customHeight="1" spans="4:4">
       <c r="D163" s="5"/>
     </row>
-    <row r="164">
+    <row r="164" customHeight="1" spans="4:4">
       <c r="D164" s="5"/>
     </row>
-    <row r="165">
+    <row r="165" customHeight="1" spans="4:4">
       <c r="D165" s="5"/>
     </row>
-    <row r="166">
+    <row r="166" customHeight="1" spans="4:4">
       <c r="D166" s="5"/>
     </row>
-    <row r="167">
+    <row r="167" customHeight="1" spans="4:4">
       <c r="D167" s="5"/>
     </row>
-    <row r="168">
+    <row r="168" customHeight="1" spans="4:4">
       <c r="D168" s="5"/>
     </row>
-    <row r="169">
+    <row r="169" customHeight="1" spans="4:4">
       <c r="D169" s="5"/>
     </row>
-    <row r="170">
+    <row r="170" customHeight="1" spans="4:4">
       <c r="D170" s="5"/>
     </row>
-    <row r="171">
+    <row r="171" customHeight="1" spans="4:4">
       <c r="D171" s="5"/>
     </row>
-    <row r="172">
+    <row r="172" customHeight="1" spans="4:4">
       <c r="D172" s="5"/>
     </row>
-    <row r="173">
+    <row r="173" customHeight="1" spans="4:4">
       <c r="D173" s="5"/>
     </row>
-    <row r="174">
+    <row r="174" customHeight="1" spans="4:4">
       <c r="D174" s="5"/>
     </row>
-    <row r="175">
+    <row r="175" customHeight="1" spans="4:4">
       <c r="D175" s="5"/>
     </row>
-    <row r="176">
+    <row r="176" customHeight="1" spans="4:4">
       <c r="D176" s="5"/>
     </row>
-    <row r="177">
+    <row r="177" customHeight="1" spans="4:4">
       <c r="D177" s="5"/>
     </row>
-    <row r="178">
+    <row r="178" customHeight="1" spans="4:4">
       <c r="D178" s="5"/>
     </row>
-    <row r="179">
+    <row r="179" customHeight="1" spans="4:4">
       <c r="D179" s="5"/>
     </row>
-    <row r="180">
+    <row r="180" customHeight="1" spans="4:4">
       <c r="D180" s="5"/>
     </row>
-    <row r="181">
+    <row r="181" customHeight="1" spans="4:4">
       <c r="D181" s="5"/>
     </row>
-    <row r="182">
+    <row r="182" customHeight="1" spans="4:4">
       <c r="D182" s="5"/>
     </row>
-    <row r="183">
+    <row r="183" customHeight="1" spans="4:4">
       <c r="D183" s="5"/>
     </row>
-    <row r="184">
+    <row r="184" customHeight="1" spans="4:4">
       <c r="D184" s="5"/>
     </row>
-    <row r="185">
+    <row r="185" customHeight="1" spans="4:4">
       <c r="D185" s="5"/>
     </row>
-    <row r="186">
+    <row r="186" customHeight="1" spans="4:4">
       <c r="D186" s="5"/>
     </row>
-    <row r="187">
+    <row r="187" customHeight="1" spans="4:4">
       <c r="D187" s="5"/>
     </row>
-    <row r="188">
+    <row r="188" customHeight="1" spans="4:4">
       <c r="D188" s="5"/>
     </row>
-    <row r="189">
+    <row r="189" customHeight="1" spans="4:4">
       <c r="D189" s="5"/>
     </row>
-    <row r="190">
+    <row r="190" customHeight="1" spans="4:4">
       <c r="D190" s="5"/>
     </row>
-    <row r="191">
+    <row r="191" customHeight="1" spans="4:4">
       <c r="D191" s="5"/>
     </row>
-    <row r="192">
+    <row r="192" customHeight="1" spans="4:4">
       <c r="D192" s="5"/>
     </row>
-    <row r="193">
+    <row r="193" customHeight="1" spans="4:4">
       <c r="D193" s="5"/>
     </row>
-    <row r="194">
+    <row r="194" customHeight="1" spans="4:4">
       <c r="D194" s="5"/>
     </row>
-    <row r="195">
+    <row r="195" customHeight="1" spans="4:4">
       <c r="D195" s="5"/>
     </row>
-    <row r="196">
+    <row r="196" customHeight="1" spans="4:4">
       <c r="D196" s="5"/>
     </row>
-    <row r="197">
+    <row r="197" customHeight="1" spans="4:4">
       <c r="D197" s="5"/>
     </row>
-    <row r="198">
+    <row r="198" customHeight="1" spans="4:4">
       <c r="D198" s="5"/>
     </row>
-    <row r="199">
+    <row r="199" customHeight="1" spans="4:4">
       <c r="D199" s="5"/>
     </row>
-    <row r="200">
+    <row r="200" customHeight="1" spans="4:4">
       <c r="D200" s="5"/>
     </row>
-    <row r="201">
+    <row r="201" customHeight="1" spans="4:4">
       <c r="D201" s="5"/>
     </row>
-    <row r="202">
+    <row r="202" customHeight="1" spans="4:4">
       <c r="D202" s="5"/>
     </row>
-    <row r="203">
+    <row r="203" customHeight="1" spans="4:4">
       <c r="D203" s="5"/>
     </row>
-    <row r="204">
+    <row r="204" customHeight="1" spans="4:4">
       <c r="D204" s="5"/>
     </row>
-    <row r="205">
+    <row r="205" customHeight="1" spans="4:4">
       <c r="D205" s="5"/>
     </row>
-    <row r="206">
+    <row r="206" customHeight="1" spans="4:4">
       <c r="D206" s="5"/>
     </row>
-    <row r="207">
+    <row r="207" customHeight="1" spans="4:4">
       <c r="D207" s="5"/>
     </row>
-    <row r="208">
+    <row r="208" customHeight="1" spans="4:4">
       <c r="D208" s="5"/>
     </row>
-    <row r="209">
+    <row r="209" customHeight="1" spans="4:4">
       <c r="D209" s="5"/>
     </row>
-    <row r="210">
+    <row r="210" customHeight="1" spans="4:4">
       <c r="D210" s="5"/>
     </row>
-    <row r="211">
+    <row r="211" customHeight="1" spans="4:4">
       <c r="D211" s="5"/>
     </row>
-    <row r="212">
+    <row r="212" customHeight="1" spans="4:4">
       <c r="D212" s="5"/>
     </row>
-    <row r="213">
+    <row r="213" customHeight="1" spans="4:4">
       <c r="D213" s="5"/>
     </row>
-    <row r="214">
+    <row r="214" customHeight="1" spans="4:4">
       <c r="D214" s="5"/>
     </row>
-    <row r="215">
+    <row r="215" customHeight="1" spans="4:4">
       <c r="D215" s="5"/>
     </row>
-    <row r="216">
+    <row r="216" customHeight="1" spans="4:4">
       <c r="D216" s="5"/>
     </row>
-    <row r="217">
+    <row r="217" customHeight="1" spans="4:4">
       <c r="D217" s="5"/>
     </row>
-    <row r="218">
+    <row r="218" customHeight="1" spans="4:4">
       <c r="D218" s="5"/>
     </row>
-    <row r="219">
+    <row r="219" customHeight="1" spans="4:4">
       <c r="D219" s="5"/>
     </row>
-    <row r="220">
+    <row r="220" customHeight="1" spans="4:4">
       <c r="D220" s="5"/>
     </row>
-    <row r="221">
+    <row r="221" customHeight="1" spans="4:4">
       <c r="D221" s="5"/>
     </row>
-    <row r="222">
+    <row r="222" customHeight="1" spans="4:4">
       <c r="D222" s="5"/>
     </row>
-    <row r="223">
+    <row r="223" customHeight="1" spans="4:4">
       <c r="D223" s="5"/>
     </row>
-    <row r="224">
+    <row r="224" customHeight="1" spans="4:4">
       <c r="D224" s="5"/>
     </row>
-    <row r="225">
+    <row r="225" customHeight="1" spans="4:4">
       <c r="D225" s="5"/>
     </row>
-    <row r="226">
+    <row r="226" customHeight="1" spans="4:4">
       <c r="D226" s="5"/>
     </row>
-    <row r="227">
+    <row r="227" customHeight="1" spans="4:4">
       <c r="D227" s="5"/>
     </row>
-    <row r="228">
+    <row r="228" customHeight="1" spans="4:4">
       <c r="D228" s="5"/>
     </row>
-    <row r="229">
+    <row r="229" customHeight="1" spans="4:4">
       <c r="D229" s="5"/>
     </row>
-    <row r="230">
+    <row r="230" customHeight="1" spans="4:4">
       <c r="D230" s="5"/>
     </row>
-    <row r="231">
+    <row r="231" customHeight="1" spans="4:4">
       <c r="D231" s="5"/>
     </row>
-    <row r="232">
+    <row r="232" customHeight="1" spans="4:4">
       <c r="D232" s="5"/>
     </row>
-    <row r="233">
+    <row r="233" customHeight="1" spans="4:4">
       <c r="D233" s="5"/>
     </row>
-    <row r="234">
+    <row r="234" customHeight="1" spans="4:4">
       <c r="D234" s="5"/>
     </row>
-    <row r="235">
+    <row r="235" customHeight="1" spans="4:4">
       <c r="D235" s="5"/>
     </row>
-    <row r="236">
+    <row r="236" customHeight="1" spans="4:4">
       <c r="D236" s="5"/>
     </row>
-    <row r="237">
+    <row r="237" customHeight="1" spans="4:4">
       <c r="D237" s="5"/>
     </row>
-    <row r="238">
+    <row r="238" customHeight="1" spans="4:4">
       <c r="D238" s="5"/>
     </row>
-    <row r="239">
+    <row r="239" customHeight="1" spans="4:4">
       <c r="D239" s="5"/>
     </row>
-    <row r="240">
+    <row r="240" customHeight="1" spans="4:4">
       <c r="D240" s="5"/>
     </row>
-    <row r="241">
+    <row r="241" customHeight="1" spans="4:4">
       <c r="D241" s="5"/>
     </row>
-    <row r="242">
+    <row r="242" customHeight="1" spans="4:4">
       <c r="D242" s="5"/>
     </row>
-    <row r="243">
+    <row r="243" customHeight="1" spans="4:4">
       <c r="D243" s="5"/>
     </row>
-    <row r="244">
+    <row r="244" customHeight="1" spans="4:4">
       <c r="D244" s="5"/>
     </row>
-    <row r="245">
+    <row r="245" customHeight="1" spans="4:4">
       <c r="D245" s="5"/>
     </row>
-    <row r="246">
+    <row r="246" customHeight="1" spans="4:4">
       <c r="D246" s="5"/>
     </row>
-    <row r="247">
+    <row r="247" customHeight="1" spans="4:4">
       <c r="D247" s="5"/>
     </row>
-    <row r="248">
+    <row r="248" customHeight="1" spans="4:4">
       <c r="D248" s="5"/>
     </row>
-    <row r="249">
+    <row r="249" customHeight="1" spans="4:4">
       <c r="D249" s="5"/>
     </row>
-    <row r="250">
+    <row r="250" customHeight="1" spans="4:4">
       <c r="D250" s="5"/>
     </row>
-    <row r="251">
+    <row r="251" customHeight="1" spans="4:4">
       <c r="D251" s="5"/>
     </row>
-    <row r="252">
+    <row r="252" customHeight="1" spans="4:4">
       <c r="D252" s="5"/>
     </row>
-    <row r="253">
+    <row r="253" customHeight="1" spans="4:4">
       <c r="D253" s="5"/>
     </row>
-    <row r="254">
+    <row r="254" customHeight="1" spans="4:4">
       <c r="D254" s="5"/>
     </row>
-    <row r="255">
+    <row r="255" customHeight="1" spans="4:4">
       <c r="D255" s="5"/>
     </row>
-    <row r="256">
+    <row r="256" customHeight="1" spans="4:4">
       <c r="D256" s="5"/>
     </row>
-    <row r="257">
+    <row r="257" customHeight="1" spans="4:4">
       <c r="D257" s="5"/>
     </row>
-    <row r="258">
+    <row r="258" customHeight="1" spans="4:4">
       <c r="D258" s="5"/>
     </row>
-    <row r="259">
+    <row r="259" customHeight="1" spans="4:4">
       <c r="D259" s="5"/>
     </row>
-    <row r="260">
+    <row r="260" customHeight="1" spans="4:4">
       <c r="D260" s="5"/>
     </row>
-    <row r="261">
+    <row r="261" customHeight="1" spans="4:4">
       <c r="D261" s="5"/>
     </row>
-    <row r="262">
+    <row r="262" customHeight="1" spans="4:4">
       <c r="D262" s="5"/>
     </row>
-    <row r="263">
+    <row r="263" customHeight="1" spans="4:4">
       <c r="D263" s="5"/>
     </row>
-    <row r="264">
+    <row r="264" customHeight="1" spans="4:4">
       <c r="D264" s="5"/>
     </row>
-    <row r="265">
+    <row r="265" customHeight="1" spans="4:4">
       <c r="D265" s="5"/>
     </row>
-    <row r="266">
+    <row r="266" customHeight="1" spans="4:4">
       <c r="D266" s="5"/>
     </row>
-    <row r="267">
+    <row r="267" customHeight="1" spans="4:4">
       <c r="D267" s="5"/>
     </row>
-    <row r="268">
+    <row r="268" customHeight="1" spans="4:4">
       <c r="D268" s="5"/>
     </row>
-    <row r="269">
+    <row r="269" customHeight="1" spans="4:4">
       <c r="D269" s="5"/>
     </row>
-    <row r="270">
+    <row r="270" customHeight="1" spans="4:4">
       <c r="D270" s="5"/>
     </row>
-    <row r="271">
+    <row r="271" customHeight="1" spans="4:4">
       <c r="D271" s="5"/>
     </row>
-    <row r="272">
+    <row r="272" customHeight="1" spans="4:4">
       <c r="D272" s="5"/>
     </row>
-    <row r="273">
+    <row r="273" customHeight="1" spans="4:4">
       <c r="D273" s="5"/>
     </row>
-    <row r="274">
+    <row r="274" customHeight="1" spans="4:4">
       <c r="D274" s="5"/>
     </row>
-    <row r="275">
+    <row r="275" customHeight="1" spans="4:4">
       <c r="D275" s="5"/>
     </row>
-    <row r="276">
+    <row r="276" customHeight="1" spans="4:4">
       <c r="D276" s="5"/>
     </row>
-    <row r="277">
+    <row r="277" customHeight="1" spans="4:4">
       <c r="D277" s="5"/>
     </row>
-    <row r="278">
+    <row r="278" customHeight="1" spans="4:4">
       <c r="D278" s="5"/>
     </row>
-    <row r="279">
+    <row r="279" customHeight="1" spans="4:4">
       <c r="D279" s="5"/>
     </row>
-    <row r="280">
+    <row r="280" customHeight="1" spans="4:4">
       <c r="D280" s="5"/>
     </row>
-    <row r="281">
+    <row r="281" customHeight="1" spans="4:4">
       <c r="D281" s="5"/>
     </row>
-    <row r="282">
+    <row r="282" customHeight="1" spans="4:4">
       <c r="D282" s="5"/>
     </row>
-    <row r="283">
+    <row r="283" customHeight="1" spans="4:4">
       <c r="D283" s="5"/>
     </row>
-    <row r="284">
+    <row r="284" customHeight="1" spans="4:4">
       <c r="D284" s="5"/>
     </row>
-    <row r="285">
+    <row r="285" customHeight="1" spans="4:4">
       <c r="D285" s="5"/>
     </row>
-    <row r="286">
+    <row r="286" customHeight="1" spans="4:4">
       <c r="D286" s="5"/>
     </row>
-    <row r="287">
+    <row r="287" customHeight="1" spans="4:4">
       <c r="D287" s="5"/>
     </row>
-    <row r="288">
+    <row r="288" customHeight="1" spans="4:4">
       <c r="D288" s="5"/>
     </row>
-    <row r="289">
+    <row r="289" customHeight="1" spans="4:4">
       <c r="D289" s="5"/>
     </row>
-    <row r="290">
+    <row r="290" customHeight="1" spans="4:4">
       <c r="D290" s="5"/>
     </row>
-    <row r="291">
+    <row r="291" customHeight="1" spans="4:4">
       <c r="D291" s="5"/>
     </row>
-    <row r="292">
+    <row r="292" customHeight="1" spans="4:4">
       <c r="D292" s="5"/>
     </row>
-    <row r="293">
+    <row r="293" customHeight="1" spans="4:4">
       <c r="D293" s="5"/>
     </row>
-    <row r="294">
+    <row r="294" customHeight="1" spans="4:4">
       <c r="D294" s="5"/>
     </row>
-    <row r="295">
+    <row r="295" customHeight="1" spans="4:4">
       <c r="D295" s="5"/>
     </row>
-    <row r="296">
+    <row r="296" customHeight="1" spans="4:4">
       <c r="D296" s="5"/>
     </row>
-    <row r="297">
+    <row r="297" customHeight="1" spans="4:4">
       <c r="D297" s="5"/>
     </row>
-    <row r="298">
+    <row r="298" customHeight="1" spans="4:4">
       <c r="D298" s="5"/>
     </row>
-    <row r="299">
+    <row r="299" customHeight="1" spans="4:4">
       <c r="D299" s="5"/>
     </row>
-    <row r="300">
+    <row r="300" customHeight="1" spans="4:4">
       <c r="D300" s="5"/>
     </row>
-    <row r="301">
+    <row r="301" customHeight="1" spans="4:4">
       <c r="D301" s="5"/>
     </row>
-    <row r="302">
+    <row r="302" customHeight="1" spans="4:4">
       <c r="D302" s="5"/>
     </row>
-    <row r="303">
+    <row r="303" customHeight="1" spans="4:4">
       <c r="D303" s="5"/>
     </row>
-    <row r="304">
+    <row r="304" customHeight="1" spans="4:4">
       <c r="D304" s="5"/>
     </row>
-    <row r="305">
+    <row r="305" customHeight="1" spans="4:4">
       <c r="D305" s="5"/>
     </row>
-    <row r="306">
+    <row r="306" customHeight="1" spans="4:4">
       <c r="D306" s="5"/>
     </row>
-    <row r="307">
+    <row r="307" customHeight="1" spans="4:4">
       <c r="D307" s="5"/>
     </row>
-    <row r="308">
+    <row r="308" customHeight="1" spans="4:4">
       <c r="D308" s="5"/>
     </row>
-    <row r="309">
+    <row r="309" customHeight="1" spans="4:4">
       <c r="D309" s="5"/>
     </row>
-    <row r="310">
+    <row r="310" customHeight="1" spans="4:4">
       <c r="D310" s="5"/>
     </row>
-    <row r="311">
+    <row r="311" customHeight="1" spans="4:4">
       <c r="D311" s="5"/>
     </row>
-    <row r="312">
+    <row r="312" customHeight="1" spans="4:4">
       <c r="D312" s="5"/>
     </row>
-    <row r="313">
+    <row r="313" customHeight="1" spans="4:4">
       <c r="D313" s="5"/>
     </row>
-    <row r="314">
+    <row r="314" customHeight="1" spans="4:4">
       <c r="D314" s="5"/>
     </row>
-    <row r="315">
+    <row r="315" customHeight="1" spans="4:4">
       <c r="D315" s="5"/>
     </row>
-    <row r="316">
+    <row r="316" customHeight="1" spans="4:4">
       <c r="D316" s="5"/>
     </row>
-    <row r="317">
+    <row r="317" customHeight="1" spans="4:4">
       <c r="D317" s="5"/>
     </row>
-    <row r="318">
+    <row r="318" customHeight="1" spans="4:4">
       <c r="D318" s="5"/>
     </row>
-    <row r="319">
+    <row r="319" customHeight="1" spans="4:4">
       <c r="D319" s="5"/>
     </row>
-    <row r="320">
+    <row r="320" customHeight="1" spans="4:4">
       <c r="D320" s="5"/>
     </row>
-    <row r="321">
+    <row r="321" customHeight="1" spans="4:4">
       <c r="D321" s="5"/>
     </row>
-    <row r="322">
+    <row r="322" customHeight="1" spans="4:4">
       <c r="D322" s="5"/>
     </row>
-    <row r="323">
+    <row r="323" customHeight="1" spans="4:4">
       <c r="D323" s="5"/>
     </row>
-    <row r="324">
+    <row r="324" customHeight="1" spans="4:4">
       <c r="D324" s="5"/>
     </row>
-    <row r="325">
+    <row r="325" customHeight="1" spans="4:4">
       <c r="D325" s="5"/>
     </row>
-    <row r="326">
+    <row r="326" customHeight="1" spans="4:4">
       <c r="D326" s="5"/>
     </row>
-    <row r="327">
+    <row r="327" customHeight="1" spans="4:4">
       <c r="D327" s="5"/>
     </row>
-    <row r="328">
+    <row r="328" customHeight="1" spans="4:4">
       <c r="D328" s="5"/>
     </row>
-    <row r="329">
+    <row r="329" customHeight="1" spans="4:4">
       <c r="D329" s="5"/>
     </row>
-    <row r="330">
+    <row r="330" customHeight="1" spans="4:4">
       <c r="D330" s="5"/>
     </row>
-    <row r="331">
+    <row r="331" customHeight="1" spans="4:4">
       <c r="D331" s="5"/>
     </row>
-    <row r="332">
+    <row r="332" customHeight="1" spans="4:4">
       <c r="D332" s="5"/>
     </row>
-    <row r="333">
+    <row r="333" customHeight="1" spans="4:4">
       <c r="D333" s="5"/>
     </row>
-    <row r="334">
+    <row r="334" customHeight="1" spans="4:4">
       <c r="D334" s="5"/>
     </row>
-    <row r="335">
+    <row r="335" customHeight="1" spans="4:4">
       <c r="D335" s="5"/>
     </row>
-    <row r="336">
+    <row r="336" customHeight="1" spans="4:4">
       <c r="D336" s="5"/>
     </row>
-    <row r="337">
+    <row r="337" customHeight="1" spans="4:4">
       <c r="D337" s="5"/>
     </row>
-    <row r="338">
+    <row r="338" customHeight="1" spans="4:4">
       <c r="D338" s="5"/>
     </row>
-    <row r="339">
+    <row r="339" customHeight="1" spans="4:4">
       <c r="D339" s="5"/>
     </row>
-    <row r="340">
+    <row r="340" customHeight="1" spans="4:4">
       <c r="D340" s="5"/>
     </row>
-    <row r="341">
+    <row r="341" customHeight="1" spans="4:4">
       <c r="D341" s="5"/>
     </row>
-    <row r="342">
+    <row r="342" customHeight="1" spans="4:4">
       <c r="D342" s="5"/>
     </row>
-    <row r="343">
+    <row r="343" customHeight="1" spans="4:4">
       <c r="D343" s="5"/>
     </row>
-    <row r="344">
+    <row r="344" customHeight="1" spans="4:4">
       <c r="D344" s="5"/>
     </row>
-    <row r="345">
+    <row r="345" customHeight="1" spans="4:4">
       <c r="D345" s="5"/>
     </row>
-    <row r="346">
+    <row r="346" customHeight="1" spans="4:4">
       <c r="D346" s="5"/>
     </row>
-    <row r="347">
+    <row r="347" customHeight="1" spans="4:4">
       <c r="D347" s="5"/>
     </row>
-    <row r="348">
+    <row r="348" customHeight="1" spans="4:4">
       <c r="D348" s="5"/>
     </row>
-    <row r="349">
+    <row r="349" customHeight="1" spans="4:4">
       <c r="D349" s="5"/>
     </row>
-    <row r="350">
+    <row r="350" customHeight="1" spans="4:4">
       <c r="D350" s="5"/>
     </row>
-    <row r="351">
+    <row r="351" customHeight="1" spans="4:4">
       <c r="D351" s="5"/>
     </row>
-    <row r="352">
+    <row r="352" customHeight="1" spans="4:4">
       <c r="D352" s="5"/>
     </row>
-    <row r="353">
+    <row r="353" customHeight="1" spans="4:4">
       <c r="D353" s="5"/>
     </row>
-    <row r="354">
+    <row r="354" customHeight="1" spans="4:4">
       <c r="D354" s="5"/>
     </row>
-    <row r="355">
+    <row r="355" customHeight="1" spans="4:4">
       <c r="D355" s="5"/>
     </row>
-    <row r="356">
+    <row r="356" customHeight="1" spans="4:4">
       <c r="D356" s="5"/>
     </row>
-    <row r="357">
+    <row r="357" customHeight="1" spans="4:4">
       <c r="D357" s="5"/>
     </row>
-    <row r="358">
+    <row r="358" customHeight="1" spans="4:4">
       <c r="D358" s="5"/>
     </row>
-    <row r="359">
+    <row r="359" customHeight="1" spans="4:4">
       <c r="D359" s="5"/>
     </row>
-    <row r="360">
+    <row r="360" customHeight="1" spans="4:4">
       <c r="D360" s="5"/>
     </row>
-    <row r="361">
+    <row r="361" customHeight="1" spans="4:4">
       <c r="D361" s="5"/>
     </row>
-    <row r="362">
+    <row r="362" customHeight="1" spans="4:4">
       <c r="D362" s="5"/>
     </row>
-    <row r="363">
+    <row r="363" customHeight="1" spans="4:4">
       <c r="D363" s="5"/>
     </row>
-    <row r="364">
+    <row r="364" customHeight="1" spans="4:4">
       <c r="D364" s="5"/>
     </row>
-    <row r="365">
+    <row r="365" customHeight="1" spans="4:4">
       <c r="D365" s="5"/>
     </row>
-    <row r="366">
+    <row r="366" customHeight="1" spans="4:4">
       <c r="D366" s="5"/>
     </row>
-    <row r="367">
+    <row r="367" customHeight="1" spans="4:4">
       <c r="D367" s="5"/>
     </row>
-    <row r="368">
+    <row r="368" customHeight="1" spans="4:4">
       <c r="D368" s="5"/>
     </row>
-    <row r="369">
+    <row r="369" customHeight="1" spans="4:4">
       <c r="D369" s="5"/>
     </row>
-    <row r="370">
+    <row r="370" customHeight="1" spans="4:4">
       <c r="D370" s="5"/>
     </row>
-    <row r="371">
+    <row r="371" customHeight="1" spans="4:4">
       <c r="D371" s="5"/>
     </row>
-    <row r="372">
+    <row r="372" customHeight="1" spans="4:4">
       <c r="D372" s="5"/>
     </row>
-    <row r="373">
+    <row r="373" customHeight="1" spans="4:4">
       <c r="D373" s="5"/>
     </row>
-    <row r="374">
+    <row r="374" customHeight="1" spans="4:4">
       <c r="D374" s="5"/>
     </row>
-    <row r="375">
+    <row r="375" customHeight="1" spans="4:4">
       <c r="D375" s="5"/>
     </row>
-    <row r="376">
+    <row r="376" customHeight="1" spans="4:4">
       <c r="D376" s="5"/>
     </row>
-    <row r="377">
+    <row r="377" customHeight="1" spans="4:4">
       <c r="D377" s="5"/>
     </row>
-    <row r="378">
+    <row r="378" customHeight="1" spans="4:4">
       <c r="D378" s="5"/>
     </row>
-    <row r="379">
+    <row r="379" customHeight="1" spans="4:4">
       <c r="D379" s="5"/>
     </row>
-    <row r="380">
+    <row r="380" customHeight="1" spans="4:4">
       <c r="D380" s="5"/>
     </row>
-    <row r="381">
+    <row r="381" customHeight="1" spans="4:4">
       <c r="D381" s="5"/>
     </row>
-    <row r="382">
+    <row r="382" customHeight="1" spans="4:4">
       <c r="D382" s="5"/>
     </row>
-    <row r="383">
+    <row r="383" customHeight="1" spans="4:4">
       <c r="D383" s="5"/>
     </row>
-    <row r="384">
+    <row r="384" customHeight="1" spans="4:4">
       <c r="D384" s="5"/>
     </row>
-    <row r="385">
+    <row r="385" customHeight="1" spans="4:4">
       <c r="D385" s="5"/>
     </row>
-    <row r="386">
+    <row r="386" customHeight="1" spans="4:4">
       <c r="D386" s="5"/>
     </row>
-    <row r="387">
+    <row r="387" customHeight="1" spans="4:4">
       <c r="D387" s="5"/>
     </row>
-    <row r="388">
+    <row r="388" customHeight="1" spans="4:4">
       <c r="D388" s="5"/>
     </row>
-    <row r="389">
+    <row r="389" customHeight="1" spans="4:4">
       <c r="D389" s="5"/>
     </row>
-    <row r="390">
+    <row r="390" customHeight="1" spans="4:4">
       <c r="D390" s="5"/>
     </row>
-    <row r="391">
+    <row r="391" customHeight="1" spans="4:4">
       <c r="D391" s="5"/>
     </row>
-    <row r="392">
+    <row r="392" customHeight="1" spans="4:4">
       <c r="D392" s="5"/>
     </row>
-    <row r="393">
+    <row r="393" customHeight="1" spans="4:4">
       <c r="D393" s="5"/>
     </row>
-    <row r="394">
+    <row r="394" customHeight="1" spans="4:4">
       <c r="D394" s="5"/>
     </row>
-    <row r="395">
+    <row r="395" customHeight="1" spans="4:4">
       <c r="D395" s="5"/>
     </row>
-    <row r="396">
+    <row r="396" customHeight="1" spans="4:4">
       <c r="D396" s="5"/>
     </row>
-    <row r="397">
+    <row r="397" customHeight="1" spans="4:4">
       <c r="D397" s="5"/>
     </row>
-    <row r="398">
+    <row r="398" customHeight="1" spans="4:4">
       <c r="D398" s="5"/>
     </row>
-    <row r="399">
+    <row r="399" customHeight="1" spans="4:4">
       <c r="D399" s="5"/>
     </row>
-    <row r="400">
+    <row r="400" customHeight="1" spans="4:4">
       <c r="D400" s="5"/>
     </row>
-    <row r="401">
+    <row r="401" customHeight="1" spans="4:4">
       <c r="D401" s="5"/>
     </row>
-    <row r="402">
+    <row r="402" customHeight="1" spans="4:4">
       <c r="D402" s="5"/>
     </row>
-    <row r="403">
+    <row r="403" customHeight="1" spans="4:4">
       <c r="D403" s="5"/>
     </row>
-    <row r="404">
+    <row r="404" customHeight="1" spans="4:4">
       <c r="D404" s="5"/>
     </row>
-    <row r="405">
+    <row r="405" customHeight="1" spans="4:4">
       <c r="D405" s="5"/>
     </row>
-    <row r="406">
+    <row r="406" customHeight="1" spans="4:4">
       <c r="D406" s="5"/>
     </row>
-    <row r="407">
+    <row r="407" customHeight="1" spans="4:4">
       <c r="D407" s="5"/>
     </row>
-    <row r="408">
+    <row r="408" customHeight="1" spans="4:4">
       <c r="D408" s="5"/>
     </row>
-    <row r="409">
+    <row r="409" customHeight="1" spans="4:4">
       <c r="D409" s="5"/>
     </row>
-    <row r="410">
+    <row r="410" customHeight="1" spans="4:4">
       <c r="D410" s="5"/>
     </row>
-    <row r="411">
+    <row r="411" customHeight="1" spans="4:4">
       <c r="D411" s="5"/>
     </row>
-    <row r="412">
+    <row r="412" customHeight="1" spans="4:4">
       <c r="D412" s="5"/>
     </row>
-    <row r="413">
+    <row r="413" customHeight="1" spans="4:4">
       <c r="D413" s="5"/>
     </row>
-    <row r="414">
+    <row r="414" customHeight="1" spans="4:4">
       <c r="D414" s="5"/>
     </row>
-    <row r="415">
+    <row r="415" customHeight="1" spans="4:4">
       <c r="D415" s="5"/>
     </row>
-    <row r="416">
+    <row r="416" customHeight="1" spans="4:4">
       <c r="D416" s="5"/>
     </row>
-    <row r="417">
+    <row r="417" customHeight="1" spans="4:4">
       <c r="D417" s="5"/>
     </row>
-    <row r="418">
+    <row r="418" customHeight="1" spans="4:4">
       <c r="D418" s="5"/>
     </row>
-    <row r="419">
+    <row r="419" customHeight="1" spans="4:4">
       <c r="D419" s="5"/>
     </row>
-    <row r="420">
+    <row r="420" customHeight="1" spans="4:4">
       <c r="D420" s="5"/>
     </row>
-    <row r="421">
+    <row r="421" customHeight="1" spans="4:4">
       <c r="D421" s="5"/>
     </row>
-    <row r="422">
+    <row r="422" customHeight="1" spans="4:4">
       <c r="D422" s="5"/>
     </row>
-    <row r="423">
+    <row r="423" customHeight="1" spans="4:4">
       <c r="D423" s="5"/>
     </row>
-    <row r="424">
+    <row r="424" customHeight="1" spans="4:4">
       <c r="D424" s="5"/>
     </row>
-    <row r="425">
+    <row r="425" customHeight="1" spans="4:4">
       <c r="D425" s="5"/>
     </row>
-    <row r="426">
+    <row r="426" customHeight="1" spans="4:4">
       <c r="D426" s="5"/>
     </row>
-    <row r="427">
+    <row r="427" customHeight="1" spans="4:4">
       <c r="D427" s="5"/>
     </row>
-    <row r="428">
+    <row r="428" customHeight="1" spans="4:4">
       <c r="D428" s="5"/>
     </row>
-    <row r="429">
+    <row r="429" customHeight="1" spans="4:4">
       <c r="D429" s="5"/>
     </row>
-    <row r="430">
+    <row r="430" customHeight="1" spans="4:4">
       <c r="D430" s="5"/>
     </row>
-    <row r="431">
+    <row r="431" customHeight="1" spans="4:4">
       <c r="D431" s="5"/>
     </row>
-    <row r="432">
+    <row r="432" customHeight="1" spans="4:4">
       <c r="D432" s="5"/>
     </row>
-    <row r="433">
+    <row r="433" customHeight="1" spans="4:4">
       <c r="D433" s="5"/>
     </row>
-    <row r="434">
+    <row r="434" customHeight="1" spans="4:4">
       <c r="D434" s="5"/>
     </row>
-    <row r="435">
+    <row r="435" customHeight="1" spans="4:4">
       <c r="D435" s="5"/>
     </row>
-    <row r="436">
+    <row r="436" customHeight="1" spans="4:4">
       <c r="D436" s="5"/>
     </row>
-    <row r="437">
+    <row r="437" customHeight="1" spans="4:4">
       <c r="D437" s="5"/>
     </row>
-    <row r="438">
+    <row r="438" customHeight="1" spans="4:4">
       <c r="D438" s="5"/>
     </row>
-    <row r="439">
+    <row r="439" customHeight="1" spans="4:4">
       <c r="D439" s="5"/>
     </row>
-    <row r="440">
+    <row r="440" customHeight="1" spans="4:4">
       <c r="D440" s="5"/>
     </row>
-    <row r="441">
+    <row r="441" customHeight="1" spans="4:4">
       <c r="D441" s="5"/>
     </row>
-    <row r="442">
+    <row r="442" customHeight="1" spans="4:4">
       <c r="D442" s="5"/>
     </row>
-    <row r="443">
+    <row r="443" customHeight="1" spans="4:4">
       <c r="D443" s="5"/>
     </row>
-    <row r="444">
+    <row r="444" customHeight="1" spans="4:4">
       <c r="D444" s="5"/>
     </row>
-    <row r="445">
+    <row r="445" customHeight="1" spans="4:4">
       <c r="D445" s="5"/>
     </row>
-    <row r="446">
+    <row r="446" customHeight="1" spans="4:4">
       <c r="D446" s="5"/>
     </row>
-    <row r="447">
+    <row r="447" customHeight="1" spans="4:4">
       <c r="D447" s="5"/>
     </row>
-    <row r="448">
+    <row r="448" customHeight="1" spans="4:4">
       <c r="D448" s="5"/>
     </row>
-    <row r="449">
+    <row r="449" customHeight="1" spans="4:4">
       <c r="D449" s="5"/>
     </row>
-    <row r="450">
+    <row r="450" customHeight="1" spans="4:4">
       <c r="D450" s="5"/>
     </row>
-    <row r="451">
+    <row r="451" customHeight="1" spans="4:4">
       <c r="D451" s="5"/>
     </row>
-    <row r="452">
+    <row r="452" customHeight="1" spans="4:4">
       <c r="D452" s="5"/>
     </row>
-    <row r="453">
+    <row r="453" customHeight="1" spans="4:4">
       <c r="D453" s="5"/>
     </row>
-    <row r="454">
+    <row r="454" customHeight="1" spans="4:4">
       <c r="D454" s="5"/>
     </row>
-    <row r="455">
+    <row r="455" customHeight="1" spans="4:4">
       <c r="D455" s="5"/>
     </row>
-    <row r="456">
+    <row r="456" customHeight="1" spans="4:4">
       <c r="D456" s="5"/>
     </row>
-    <row r="457">
+    <row r="457" customHeight="1" spans="4:4">
       <c r="D457" s="5"/>
     </row>
-    <row r="458">
+    <row r="458" customHeight="1" spans="4:4">
       <c r="D458" s="5"/>
     </row>
-    <row r="459">
+    <row r="459" customHeight="1" spans="4:4">
       <c r="D459" s="5"/>
     </row>
-    <row r="460">
+    <row r="460" customHeight="1" spans="4:4">
       <c r="D460" s="5"/>
     </row>
-    <row r="461">
+    <row r="461" customHeight="1" spans="4:4">
       <c r="D461" s="5"/>
     </row>
-    <row r="462">
+    <row r="462" customHeight="1" spans="4:4">
       <c r="D462" s="5"/>
     </row>
-    <row r="463">
+    <row r="463" customHeight="1" spans="4:4">
       <c r="D463" s="5"/>
     </row>
-    <row r="464">
+    <row r="464" customHeight="1" spans="4:4">
       <c r="D464" s="5"/>
     </row>
-    <row r="465">
+    <row r="465" customHeight="1" spans="4:4">
       <c r="D465" s="5"/>
     </row>
-    <row r="466">
+    <row r="466" customHeight="1" spans="4:4">
       <c r="D466" s="5"/>
     </row>
-    <row r="467">
+    <row r="467" customHeight="1" spans="4:4">
       <c r="D467" s="5"/>
     </row>
-    <row r="468">
+    <row r="468" customHeight="1" spans="4:4">
       <c r="D468" s="5"/>
     </row>
-    <row r="469">
+    <row r="469" customHeight="1" spans="4:4">
       <c r="D469" s="5"/>
     </row>
-    <row r="470">
+    <row r="470" customHeight="1" spans="4:4">
       <c r="D470" s="5"/>
     </row>
-    <row r="471">
+    <row r="471" customHeight="1" spans="4:4">
       <c r="D471" s="5"/>
     </row>
-    <row r="472">
+    <row r="472" customHeight="1" spans="4:4">
       <c r="D472" s="5"/>
     </row>
-    <row r="473">
+    <row r="473" customHeight="1" spans="4:4">
       <c r="D473" s="5"/>
     </row>
-    <row r="474">
+    <row r="474" customHeight="1" spans="4:4">
       <c r="D474" s="5"/>
     </row>
-    <row r="475">
+    <row r="475" customHeight="1" spans="4:4">
       <c r="D475" s="5"/>
     </row>
-    <row r="476">
+    <row r="476" customHeight="1" spans="4:4">
       <c r="D476" s="5"/>
     </row>
-    <row r="477">
+    <row r="477" customHeight="1" spans="4:4">
       <c r="D477" s="5"/>
     </row>
-    <row r="478">
+    <row r="478" customHeight="1" spans="4:4">
       <c r="D478" s="5"/>
     </row>
-    <row r="479">
+    <row r="479" customHeight="1" spans="4:4">
       <c r="D479" s="5"/>
     </row>
-    <row r="480">
+    <row r="480" customHeight="1" spans="4:4">
       <c r="D480" s="5"/>
     </row>
-    <row r="481">
+    <row r="481" customHeight="1" spans="4:4">
       <c r="D481" s="5"/>
     </row>
-    <row r="482">
+    <row r="482" customHeight="1" spans="4:4">
       <c r="D482" s="5"/>
     </row>
-    <row r="483">
+    <row r="483" customHeight="1" spans="4:4">
       <c r="D483" s="5"/>
     </row>
-    <row r="484">
+    <row r="484" customHeight="1" spans="4:4">
       <c r="D484" s="5"/>
     </row>
-    <row r="485">
+    <row r="485" customHeight="1" spans="4:4">
       <c r="D485" s="5"/>
     </row>
-    <row r="486">
+    <row r="486" customHeight="1" spans="4:4">
       <c r="D486" s="5"/>
     </row>
-    <row r="487">
+    <row r="487" customHeight="1" spans="4:4">
       <c r="D487" s="5"/>
     </row>
-    <row r="488">
+    <row r="488" customHeight="1" spans="4:4">
       <c r="D488" s="5"/>
     </row>
-    <row r="489">
+    <row r="489" customHeight="1" spans="4:4">
       <c r="D489" s="5"/>
     </row>
-    <row r="490">
+    <row r="490" customHeight="1" spans="4:4">
       <c r="D490" s="5"/>
     </row>
-    <row r="491">
+    <row r="491" customHeight="1" spans="4:4">
       <c r="D491" s="5"/>
     </row>
-    <row r="492">
+    <row r="492" customHeight="1" spans="4:4">
       <c r="D492" s="5"/>
     </row>
-    <row r="493">
+    <row r="493" customHeight="1" spans="4:4">
       <c r="D493" s="5"/>
     </row>
-    <row r="494">
+    <row r="494" customHeight="1" spans="4:4">
       <c r="D494" s="5"/>
     </row>
-    <row r="495">
+    <row r="495" customHeight="1" spans="4:4">
       <c r="D495" s="5"/>
     </row>
-    <row r="496">
+    <row r="496" customHeight="1" spans="4:4">
       <c r="D496" s="5"/>
     </row>
-    <row r="497">
+    <row r="497" customHeight="1" spans="4:4">
       <c r="D497" s="5"/>
     </row>
-    <row r="498">
+    <row r="498" customHeight="1" spans="4:4">
       <c r="D498" s="5"/>
     </row>
-    <row r="499">
+    <row r="499" customHeight="1" spans="4:4">
       <c r="D499" s="5"/>
     </row>
-    <row r="500">
+    <row r="500" customHeight="1" spans="4:4">
       <c r="D500" s="5"/>
     </row>
-    <row r="501">
+    <row r="501" customHeight="1" spans="4:4">
       <c r="D501" s="5"/>
     </row>
-    <row r="502">
+    <row r="502" customHeight="1" spans="4:4">
       <c r="D502" s="5"/>
     </row>
-    <row r="503">
+    <row r="503" customHeight="1" spans="4:4">
       <c r="D503" s="5"/>
     </row>
-    <row r="504">
+    <row r="504" customHeight="1" spans="4:4">
       <c r="D504" s="5"/>
     </row>
-    <row r="505">
+    <row r="505" customHeight="1" spans="4:4">
       <c r="D505" s="5"/>
     </row>
-    <row r="506">
+    <row r="506" customHeight="1" spans="4:4">
       <c r="D506" s="5"/>
     </row>
-    <row r="507">
+    <row r="507" customHeight="1" spans="4:4">
       <c r="D507" s="5"/>
     </row>
-    <row r="508">
+    <row r="508" customHeight="1" spans="4:4">
       <c r="D508" s="5"/>
     </row>
-    <row r="509">
+    <row r="509" customHeight="1" spans="4:4">
       <c r="D509" s="5"/>
     </row>
-    <row r="510">
+    <row r="510" customHeight="1" spans="4:4">
       <c r="D510" s="5"/>
     </row>
-    <row r="511">
+    <row r="511" customHeight="1" spans="4:4">
       <c r="D511" s="5"/>
     </row>
-    <row r="512">
+    <row r="512" customHeight="1" spans="4:4">
       <c r="D512" s="5"/>
     </row>
-    <row r="513">
+    <row r="513" customHeight="1" spans="4:4">
       <c r="D513" s="5"/>
     </row>
-    <row r="514">
+    <row r="514" customHeight="1" spans="4:4">
       <c r="D514" s="5"/>
     </row>
-    <row r="515">
+    <row r="515" customHeight="1" spans="4:4">
       <c r="D515" s="5"/>
     </row>
-    <row r="516">
+    <row r="516" customHeight="1" spans="4:4">
       <c r="D516" s="5"/>
     </row>
-    <row r="517">
+    <row r="517" customHeight="1" spans="4:4">
       <c r="D517" s="5"/>
     </row>
-    <row r="518">
+    <row r="518" customHeight="1" spans="4:4">
       <c r="D518" s="5"/>
     </row>
-    <row r="519">
+    <row r="519" customHeight="1" spans="4:4">
       <c r="D519" s="5"/>
     </row>
-    <row r="520">
+    <row r="520" customHeight="1" spans="4:4">
       <c r="D520" s="5"/>
     </row>
-    <row r="521">
+    <row r="521" customHeight="1" spans="4:4">
       <c r="D521" s="5"/>
     </row>
-    <row r="522">
+    <row r="522" customHeight="1" spans="4:4">
       <c r="D522" s="5"/>
     </row>
-    <row r="523">
+    <row r="523" customHeight="1" spans="4:4">
       <c r="D523" s="5"/>
     </row>
-    <row r="524">
+    <row r="524" customHeight="1" spans="4:4">
       <c r="D524" s="5"/>
     </row>
-    <row r="525">
+    <row r="525" customHeight="1" spans="4:4">
       <c r="D525" s="5"/>
     </row>
-    <row r="526">
+    <row r="526" customHeight="1" spans="4:4">
       <c r="D526" s="5"/>
     </row>
-    <row r="527">
+    <row r="527" customHeight="1" spans="4:4">
       <c r="D527" s="5"/>
     </row>
-    <row r="528">
+    <row r="528" customHeight="1" spans="4:4">
       <c r="D528" s="5"/>
     </row>
-    <row r="529">
+    <row r="529" customHeight="1" spans="4:4">
       <c r="D529" s="5"/>
     </row>
-    <row r="530">
+    <row r="530" customHeight="1" spans="4:4">
       <c r="D530" s="5"/>
     </row>
-    <row r="531">
+    <row r="531" customHeight="1" spans="4:4">
       <c r="D531" s="5"/>
     </row>
-    <row r="532">
+    <row r="532" customHeight="1" spans="4:4">
       <c r="D532" s="5"/>
     </row>
-    <row r="533">
+    <row r="533" customHeight="1" spans="4:4">
       <c r="D533" s="5"/>
     </row>
-    <row r="534">
+    <row r="534" customHeight="1" spans="4:4">
       <c r="D534" s="5"/>
     </row>
-    <row r="535">
+    <row r="535" customHeight="1" spans="4:4">
       <c r="D535" s="5"/>
     </row>
-    <row r="536">
+    <row r="536" customHeight="1" spans="4:4">
       <c r="D536" s="5"/>
     </row>
-    <row r="537">
+    <row r="537" customHeight="1" spans="4:4">
       <c r="D537" s="5"/>
     </row>
-    <row r="538">
+    <row r="538" customHeight="1" spans="4:4">
       <c r="D538" s="5"/>
     </row>
-    <row r="539">
+    <row r="539" customHeight="1" spans="4:4">
       <c r="D539" s="5"/>
     </row>
-    <row r="540">
+    <row r="540" customHeight="1" spans="4:4">
       <c r="D540" s="5"/>
     </row>
-    <row r="541">
+    <row r="541" customHeight="1" spans="4:4">
       <c r="D541" s="5"/>
     </row>
-    <row r="542">
+    <row r="542" customHeight="1" spans="4:4">
       <c r="D542" s="5"/>
     </row>
-    <row r="543">
+    <row r="543" customHeight="1" spans="4:4">
       <c r="D543" s="5"/>
     </row>
-    <row r="544">
+    <row r="544" customHeight="1" spans="4:4">
       <c r="D544" s="5"/>
     </row>
-    <row r="545">
+    <row r="545" customHeight="1" spans="4:4">
       <c r="D545" s="5"/>
     </row>
-    <row r="546">
+    <row r="546" customHeight="1" spans="4:4">
       <c r="D546" s="5"/>
     </row>
-    <row r="547">
+    <row r="547" customHeight="1" spans="4:4">
       <c r="D547" s="5"/>
     </row>
-    <row r="548">
+    <row r="548" customHeight="1" spans="4:4">
       <c r="D548" s="5"/>
     </row>
-    <row r="549">
+    <row r="549" customHeight="1" spans="4:4">
       <c r="D549" s="5"/>
     </row>
-    <row r="550">
+    <row r="550" customHeight="1" spans="4:4">
       <c r="D550" s="5"/>
     </row>
-    <row r="551">
+    <row r="551" customHeight="1" spans="4:4">
       <c r="D551" s="5"/>
     </row>
-    <row r="552">
+    <row r="552" customHeight="1" spans="4:4">
       <c r="D552" s="5"/>
     </row>
-    <row r="553">
+    <row r="553" customHeight="1" spans="4:4">
       <c r="D553" s="5"/>
     </row>
-    <row r="554">
+    <row r="554" customHeight="1" spans="4:4">
       <c r="D554" s="5"/>
     </row>
-    <row r="555">
+    <row r="555" customHeight="1" spans="4:4">
       <c r="D555" s="5"/>
     </row>
-    <row r="556">
+    <row r="556" customHeight="1" spans="4:4">
       <c r="D556" s="5"/>
     </row>
-    <row r="557">
+    <row r="557" customHeight="1" spans="4:4">
       <c r="D557" s="5"/>
     </row>
-    <row r="558">
+    <row r="558" customHeight="1" spans="4:4">
       <c r="D558" s="5"/>
     </row>
-    <row r="559">
+    <row r="559" customHeight="1" spans="4:4">
       <c r="D559" s="5"/>
     </row>
-    <row r="560">
+    <row r="560" customHeight="1" spans="4:4">
       <c r="D560" s="5"/>
     </row>
-    <row r="561">
+    <row r="561" customHeight="1" spans="4:4">
       <c r="D561" s="5"/>
     </row>
-    <row r="562">
+    <row r="562" customHeight="1" spans="4:4">
       <c r="D562" s="5"/>
     </row>
-    <row r="563">
+    <row r="563" customHeight="1" spans="4:4">
       <c r="D563" s="5"/>
     </row>
-    <row r="564">
+    <row r="564" customHeight="1" spans="4:4">
       <c r="D564" s="5"/>
     </row>
-    <row r="565">
+    <row r="565" customHeight="1" spans="4:4">
       <c r="D565" s="5"/>
     </row>
-    <row r="566">
+    <row r="566" customHeight="1" spans="4:4">
       <c r="D566" s="5"/>
     </row>
-    <row r="567">
+    <row r="567" customHeight="1" spans="4:4">
       <c r="D567" s="5"/>
     </row>
-    <row r="568">
+    <row r="568" customHeight="1" spans="4:4">
       <c r="D568" s="5"/>
     </row>
-    <row r="569">
+    <row r="569" customHeight="1" spans="4:4">
       <c r="D569" s="5"/>
     </row>
-    <row r="570">
+    <row r="570" customHeight="1" spans="4:4">
       <c r="D570" s="5"/>
     </row>
-    <row r="571">
+    <row r="571" customHeight="1" spans="4:4">
       <c r="D571" s="5"/>
     </row>
-    <row r="572">
+    <row r="572" customHeight="1" spans="4:4">
       <c r="D572" s="5"/>
     </row>
-    <row r="573">
+    <row r="573" customHeight="1" spans="4:4">
       <c r="D573" s="5"/>
     </row>
-    <row r="574">
+    <row r="574" customHeight="1" spans="4:4">
       <c r="D574" s="5"/>
     </row>
-    <row r="575">
+    <row r="575" customHeight="1" spans="4:4">
       <c r="D575" s="5"/>
     </row>
-    <row r="576">
+    <row r="576" customHeight="1" spans="4:4">
       <c r="D576" s="5"/>
     </row>
-    <row r="577">
+    <row r="577" customHeight="1" spans="4:4">
       <c r="D577" s="5"/>
     </row>
-    <row r="578">
+    <row r="578" customHeight="1" spans="4:4">
       <c r="D578" s="5"/>
     </row>
-    <row r="579">
+    <row r="579" customHeight="1" spans="4:4">
       <c r="D579" s="5"/>
     </row>
-    <row r="580">
+    <row r="580" customHeight="1" spans="4:4">
       <c r="D580" s="5"/>
     </row>
-    <row r="581">
+    <row r="581" customHeight="1" spans="4:4">
       <c r="D581" s="5"/>
     </row>
-    <row r="582">
+    <row r="582" customHeight="1" spans="4:4">
       <c r="D582" s="5"/>
     </row>
-    <row r="583">
+    <row r="583" customHeight="1" spans="4:4">
       <c r="D583" s="5"/>
     </row>
-    <row r="584">
+    <row r="584" customHeight="1" spans="4:4">
       <c r="D584" s="5"/>
     </row>
-    <row r="585">
+    <row r="585" customHeight="1" spans="4:4">
       <c r="D585" s="5"/>
     </row>
-    <row r="586">
+    <row r="586" customHeight="1" spans="4:4">
       <c r="D586" s="5"/>
     </row>
-    <row r="587">
+    <row r="587" customHeight="1" spans="4:4">
       <c r="D587" s="5"/>
     </row>
-    <row r="588">
+    <row r="588" customHeight="1" spans="4:4">
       <c r="D588" s="5"/>
     </row>
-    <row r="589">
+    <row r="589" customHeight="1" spans="4:4">
       <c r="D589" s="5"/>
     </row>
-    <row r="590">
+    <row r="590" customHeight="1" spans="4:4">
       <c r="D590" s="5"/>
     </row>
-    <row r="591">
+    <row r="591" customHeight="1" spans="4:4">
       <c r="D591" s="5"/>
     </row>
-    <row r="592">
+    <row r="592" customHeight="1" spans="4:4">
       <c r="D592" s="5"/>
     </row>
-    <row r="593">
+    <row r="593" customHeight="1" spans="4:4">
       <c r="D593" s="5"/>
     </row>
-    <row r="594">
+    <row r="594" customHeight="1" spans="4:4">
       <c r="D594" s="5"/>
     </row>
-    <row r="595">
+    <row r="595" customHeight="1" spans="4:4">
       <c r="D595" s="5"/>
     </row>
-    <row r="596">
+    <row r="596" customHeight="1" spans="4:4">
       <c r="D596" s="5"/>
     </row>
-    <row r="597">
+    <row r="597" customHeight="1" spans="4:4">
       <c r="D597" s="5"/>
     </row>
-    <row r="598">
+    <row r="598" customHeight="1" spans="4:4">
       <c r="D598" s="5"/>
     </row>
-    <row r="599">
+    <row r="599" customHeight="1" spans="4:4">
       <c r="D599" s="5"/>
     </row>
-    <row r="600">
+    <row r="600" customHeight="1" spans="4:4">
       <c r="D600" s="5"/>
     </row>
-    <row r="601">
+    <row r="601" customHeight="1" spans="4:4">
       <c r="D601" s="5"/>
     </row>
-    <row r="602">
+    <row r="602" customHeight="1" spans="4:4">
       <c r="D602" s="5"/>
     </row>
-    <row r="603">
+    <row r="603" customHeight="1" spans="4:4">
       <c r="D603" s="5"/>
     </row>
-    <row r="604">
+    <row r="604" customHeight="1" spans="4:4">
       <c r="D604" s="5"/>
     </row>
-    <row r="605">
+    <row r="605" customHeight="1" spans="4:4">
       <c r="D605" s="5"/>
     </row>
-    <row r="606">
+    <row r="606" customHeight="1" spans="4:4">
       <c r="D606" s="5"/>
     </row>
-    <row r="607">
+    <row r="607" customHeight="1" spans="4:4">
       <c r="D607" s="5"/>
     </row>
-    <row r="608">
+    <row r="608" customHeight="1" spans="4:4">
       <c r="D608" s="5"/>
     </row>
-    <row r="609">
+    <row r="609" customHeight="1" spans="4:4">
       <c r="D609" s="5"/>
     </row>
-    <row r="610">
+    <row r="610" customHeight="1" spans="4:4">
       <c r="D610" s="5"/>
     </row>
-    <row r="611">
+    <row r="611" customHeight="1" spans="4:4">
       <c r="D611" s="5"/>
     </row>
-    <row r="612">
+    <row r="612" customHeight="1" spans="4:4">
       <c r="D612" s="5"/>
     </row>
-    <row r="613">
+    <row r="613" customHeight="1" spans="4:4">
       <c r="D613" s="5"/>
     </row>
-    <row r="614">
+    <row r="614" customHeight="1" spans="4:4">
       <c r="D614" s="5"/>
     </row>
-    <row r="615">
+    <row r="615" customHeight="1" spans="4:4">
       <c r="D615" s="5"/>
     </row>
-    <row r="616">
+    <row r="616" customHeight="1" spans="4:4">
       <c r="D616" s="5"/>
     </row>
-    <row r="617">
+    <row r="617" customHeight="1" spans="4:4">
       <c r="D617" s="5"/>
     </row>
-    <row r="618">
+    <row r="618" customHeight="1" spans="4:4">
       <c r="D618" s="5"/>
     </row>
-    <row r="619">
+    <row r="619" customHeight="1" spans="4:4">
       <c r="D619" s="5"/>
     </row>
-    <row r="620">
+    <row r="620" customHeight="1" spans="4:4">
       <c r="D620" s="5"/>
     </row>
-    <row r="621">
+    <row r="621" customHeight="1" spans="4:4">
       <c r="D621" s="5"/>
     </row>
-    <row r="622">
+    <row r="622" customHeight="1" spans="4:4">
       <c r="D622" s="5"/>
     </row>
-    <row r="623">
+    <row r="623" customHeight="1" spans="4:4">
       <c r="D623" s="5"/>
     </row>
-    <row r="624">
+    <row r="624" customHeight="1" spans="4:4">
       <c r="D624" s="5"/>
     </row>
-    <row r="625">
+    <row r="625" customHeight="1" spans="4:4">
       <c r="D625" s="5"/>
     </row>
-    <row r="626">
+    <row r="626" customHeight="1" spans="4:4">
       <c r="D626" s="5"/>
     </row>
-    <row r="627">
+    <row r="627" customHeight="1" spans="4:4">
       <c r="D627" s="5"/>
     </row>
-    <row r="628">
+    <row r="628" customHeight="1" spans="4:4">
       <c r="D628" s="5"/>
     </row>
-    <row r="629">
+    <row r="629" customHeight="1" spans="4:4">
       <c r="D629" s="5"/>
     </row>
-    <row r="630">
+    <row r="630" customHeight="1" spans="4:4">
       <c r="D630" s="5"/>
     </row>
-    <row r="631">
+    <row r="631" customHeight="1" spans="4:4">
       <c r="D631" s="5"/>
     </row>
-    <row r="632">
+    <row r="632" customHeight="1" spans="4:4">
       <c r="D632" s="5"/>
     </row>
-    <row r="633">
+    <row r="633" customHeight="1" spans="4:4">
       <c r="D633" s="5"/>
     </row>
-    <row r="634">
+    <row r="634" customHeight="1" spans="4:4">
       <c r="D634" s="5"/>
     </row>
-    <row r="635">
+    <row r="635" customHeight="1" spans="4:4">
       <c r="D635" s="5"/>
     </row>
-    <row r="636">
+    <row r="636" customHeight="1" spans="4:4">
       <c r="D636" s="5"/>
     </row>
-    <row r="637">
+    <row r="637" customHeight="1" spans="4:4">
       <c r="D637" s="5"/>
     </row>
-    <row r="638">
+    <row r="638" customHeight="1" spans="4:4">
       <c r="D638" s="5"/>
     </row>
-    <row r="639">
+    <row r="639" customHeight="1" spans="4:4">
       <c r="D639" s="5"/>
     </row>
-    <row r="640">
+    <row r="640" customHeight="1" spans="4:4">
       <c r="D640" s="5"/>
     </row>
-    <row r="641">
+    <row r="641" customHeight="1" spans="4:4">
       <c r="D641" s="5"/>
     </row>
-    <row r="642">
+    <row r="642" customHeight="1" spans="4:4">
       <c r="D642" s="5"/>
     </row>
-    <row r="643">
+    <row r="643" customHeight="1" spans="4:4">
       <c r="D643" s="5"/>
     </row>
-    <row r="644">
+    <row r="644" customHeight="1" spans="4:4">
       <c r="D644" s="5"/>
     </row>
-    <row r="645">
+    <row r="645" customHeight="1" spans="4:4">
       <c r="D645" s="5"/>
     </row>
-    <row r="646">
+    <row r="646" customHeight="1" spans="4:4">
       <c r="D646" s="5"/>
     </row>
-    <row r="647">
+    <row r="647" customHeight="1" spans="4:4">
       <c r="D647" s="5"/>
     </row>
-    <row r="648">
+    <row r="648" customHeight="1" spans="4:4">
       <c r="D648" s="5"/>
     </row>
-    <row r="649">
+    <row r="649" customHeight="1" spans="4:4">
       <c r="D649" s="5"/>
     </row>
-    <row r="650">
+    <row r="650" customHeight="1" spans="4:4">
       <c r="D650" s="5"/>
     </row>
-    <row r="651">
+    <row r="651" customHeight="1" spans="4:4">
       <c r="D651" s="5"/>
     </row>
-    <row r="652">
+    <row r="652" customHeight="1" spans="4:4">
       <c r="D652" s="5"/>
     </row>
-    <row r="653">
+    <row r="653" customHeight="1" spans="4:4">
       <c r="D653" s="5"/>
     </row>
-    <row r="654">
+    <row r="654" customHeight="1" spans="4:4">
       <c r="D654" s="5"/>
     </row>
-    <row r="655">
+    <row r="655" customHeight="1" spans="4:4">
       <c r="D655" s="5"/>
     </row>
-    <row r="656">
+    <row r="656" customHeight="1" spans="4:4">
       <c r="D656" s="5"/>
     </row>
-    <row r="657">
+    <row r="657" customHeight="1" spans="4:4">
       <c r="D657" s="5"/>
     </row>
-    <row r="658">
+    <row r="658" customHeight="1" spans="4:4">
       <c r="D658" s="5"/>
     </row>
-    <row r="659">
+    <row r="659" customHeight="1" spans="4:4">
       <c r="D659" s="5"/>
     </row>
-    <row r="660">
+    <row r="660" customHeight="1" spans="4:4">
       <c r="D660" s="5"/>
     </row>
-    <row r="661">
+    <row r="661" customHeight="1" spans="4:4">
       <c r="D661" s="5"/>
     </row>
-    <row r="662">
+    <row r="662" customHeight="1" spans="4:4">
       <c r="D662" s="5"/>
     </row>
-    <row r="663">
+    <row r="663" customHeight="1" spans="4:4">
       <c r="D663" s="5"/>
     </row>
-    <row r="664">
+    <row r="664" customHeight="1" spans="4:4">
       <c r="D664" s="5"/>
     </row>
-    <row r="665">
+    <row r="665" customHeight="1" spans="4:4">
       <c r="D665" s="5"/>
     </row>
-    <row r="666">
+    <row r="666" customHeight="1" spans="4:4">
       <c r="D666" s="5"/>
     </row>
-    <row r="667">
+    <row r="667" customHeight="1" spans="4:4">
       <c r="D667" s="5"/>
     </row>
-    <row r="668">
+    <row r="668" customHeight="1" spans="4:4">
       <c r="D668" s="5"/>
     </row>
-    <row r="669">
+    <row r="669" customHeight="1" spans="4:4">
       <c r="D669" s="5"/>
     </row>
-    <row r="670">
+    <row r="670" customHeight="1" spans="4:4">
       <c r="D670" s="5"/>
     </row>
-    <row r="671">
+    <row r="671" customHeight="1" spans="4:4">
       <c r="D671" s="5"/>
     </row>
-    <row r="672">
+    <row r="672" customHeight="1" spans="4:4">
       <c r="D672" s="5"/>
     </row>
-    <row r="673">
+    <row r="673" customHeight="1" spans="4:4">
       <c r="D673" s="5"/>
     </row>
-    <row r="674">
+    <row r="674" customHeight="1" spans="4:4">
       <c r="D674" s="5"/>
     </row>
-    <row r="675">
+    <row r="675" customHeight="1" spans="4:4">
       <c r="D675" s="5"/>
     </row>
-    <row r="676">
+    <row r="676" customHeight="1" spans="4:4">
       <c r="D676" s="5"/>
     </row>
-    <row r="677">
+    <row r="677" customHeight="1" spans="4:4">
       <c r="D677" s="5"/>
     </row>
-    <row r="678">
+    <row r="678" customHeight="1" spans="4:4">
       <c r="D678" s="5"/>
     </row>
-    <row r="679">
+    <row r="679" customHeight="1" spans="4:4">
       <c r="D679" s="5"/>
     </row>
-    <row r="680">
+    <row r="680" customHeight="1" spans="4:4">
       <c r="D680" s="5"/>
     </row>
-    <row r="681">
+    <row r="681" customHeight="1" spans="4:4">
       <c r="D681" s="5"/>
     </row>
-    <row r="682">
+    <row r="682" customHeight="1" spans="4:4">
       <c r="D682" s="5"/>
     </row>
-    <row r="683">
+    <row r="683" customHeight="1" spans="4:4">
       <c r="D683" s="5"/>
     </row>
-    <row r="684">
+    <row r="684" customHeight="1" spans="4:4">
       <c r="D684" s="5"/>
     </row>
-    <row r="685">
+    <row r="685" customHeight="1" spans="4:4">
       <c r="D685" s="5"/>
     </row>
-    <row r="686">
+    <row r="686" customHeight="1" spans="4:4">
       <c r="D686" s="5"/>
     </row>
-    <row r="687">
+    <row r="687" customHeight="1" spans="4:4">
       <c r="D687" s="5"/>
     </row>
-    <row r="688">
+    <row r="688" customHeight="1" spans="4:4">
       <c r="D688" s="5"/>
     </row>
-    <row r="689">
+    <row r="689" customHeight="1" spans="4:4">
       <c r="D689" s="5"/>
     </row>
-    <row r="690">
+    <row r="690" customHeight="1" spans="4:4">
       <c r="D690" s="5"/>
     </row>
-    <row r="691">
+    <row r="691" customHeight="1" spans="4:4">
       <c r="D691" s="5"/>
     </row>
-    <row r="692">
+    <row r="692" customHeight="1" spans="4:4">
       <c r="D692" s="5"/>
     </row>
-    <row r="693">
+    <row r="693" customHeight="1" spans="4:4">
       <c r="D693" s="5"/>
     </row>
-    <row r="694">
+    <row r="694" customHeight="1" spans="4:4">
       <c r="D694" s="5"/>
     </row>
-    <row r="695">
+    <row r="695" customHeight="1" spans="4:4">
       <c r="D695" s="5"/>
     </row>
-    <row r="696">
+    <row r="696" customHeight="1" spans="4:4">
       <c r="D696" s="5"/>
     </row>
-    <row r="697">
+    <row r="697" customHeight="1" spans="4:4">
       <c r="D697" s="5"/>
     </row>
-    <row r="698">
+    <row r="698" customHeight="1" spans="4:4">
       <c r="D698" s="5"/>
     </row>
-    <row r="699">
+    <row r="699" customHeight="1" spans="4:4">
       <c r="D699" s="5"/>
     </row>
-    <row r="700">
+    <row r="700" customHeight="1" spans="4:4">
       <c r="D700" s="5"/>
     </row>
-    <row r="701">
+    <row r="701" customHeight="1" spans="4:4">
       <c r="D701" s="5"/>
     </row>
-    <row r="702">
+    <row r="702" customHeight="1" spans="4:4">
       <c r="D702" s="5"/>
     </row>
-    <row r="703">
+    <row r="703" customHeight="1" spans="4:4">
       <c r="D703" s="5"/>
     </row>
-    <row r="704">
+    <row r="704" customHeight="1" spans="4:4">
       <c r="D704" s="5"/>
     </row>
-    <row r="705">
+    <row r="705" customHeight="1" spans="4:4">
       <c r="D705" s="5"/>
     </row>
-    <row r="706">
+    <row r="706" customHeight="1" spans="4:4">
       <c r="D706" s="5"/>
     </row>
-    <row r="707">
+    <row r="707" customHeight="1" spans="4:4">
       <c r="D707" s="5"/>
     </row>
-    <row r="708">
+    <row r="708" customHeight="1" spans="4:4">
       <c r="D708" s="5"/>
     </row>
-    <row r="709">
+    <row r="709" customHeight="1" spans="4:4">
       <c r="D709" s="5"/>
     </row>
-    <row r="710">
+    <row r="710" customHeight="1" spans="4:4">
       <c r="D710" s="5"/>
     </row>
-    <row r="711">
+    <row r="711" customHeight="1" spans="4:4">
       <c r="D711" s="5"/>
     </row>
-    <row r="712">
+    <row r="712" customHeight="1" spans="4:4">
       <c r="D712" s="5"/>
     </row>
-    <row r="713">
+    <row r="713" customHeight="1" spans="4:4">
       <c r="D713" s="5"/>
     </row>
-    <row r="714">
+    <row r="714" customHeight="1" spans="4:4">
       <c r="D714" s="5"/>
     </row>
-    <row r="715">
+    <row r="715" customHeight="1" spans="4:4">
       <c r="D715" s="5"/>
     </row>
-    <row r="716">
+    <row r="716" customHeight="1" spans="4:4">
       <c r="D716" s="5"/>
     </row>
-    <row r="717">
+    <row r="717" customHeight="1" spans="4:4">
       <c r="D717" s="5"/>
     </row>
-    <row r="718">
+    <row r="718" customHeight="1" spans="4:4">
       <c r="D718" s="5"/>
     </row>
-    <row r="719">
+    <row r="719" customHeight="1" spans="4:4">
       <c r="D719" s="5"/>
     </row>
-    <row r="720">
+    <row r="720" customHeight="1" spans="4:4">
       <c r="D720" s="5"/>
     </row>
-    <row r="721">
+    <row r="721" customHeight="1" spans="4:4">
       <c r="D721" s="5"/>
     </row>
-    <row r="722">
+    <row r="722" customHeight="1" spans="4:4">
       <c r="D722" s="5"/>
     </row>
-    <row r="723">
+    <row r="723" customHeight="1" spans="4:4">
       <c r="D723" s="5"/>
     </row>
-    <row r="724">
+    <row r="724" customHeight="1" spans="4:4">
       <c r="D724" s="5"/>
     </row>
-    <row r="725">
+    <row r="725" customHeight="1" spans="4:4">
       <c r="D725" s="5"/>
     </row>
-    <row r="726">
+    <row r="726" customHeight="1" spans="4:4">
       <c r="D726" s="5"/>
     </row>
-    <row r="727">
+    <row r="727" customHeight="1" spans="4:4">
       <c r="D727" s="5"/>
     </row>
-    <row r="728">
+    <row r="728" customHeight="1" spans="4:4">
       <c r="D728" s="5"/>
     </row>
-    <row r="729">
+    <row r="729" customHeight="1" spans="4:4">
       <c r="D729" s="5"/>
     </row>
-    <row r="730">
+    <row r="730" customHeight="1" spans="4:4">
       <c r="D730" s="5"/>
     </row>
-    <row r="731">
+    <row r="731" customHeight="1" spans="4:4">
       <c r="D731" s="5"/>
     </row>
-    <row r="732">
+    <row r="732" customHeight="1" spans="4:4">
       <c r="D732" s="5"/>
     </row>
-    <row r="733">
+    <row r="733" customHeight="1" spans="4:4">
       <c r="D733" s="5"/>
     </row>
-    <row r="734">
+    <row r="734" customHeight="1" spans="4:4">
       <c r="D734" s="5"/>
     </row>
-    <row r="735">
+    <row r="735" customHeight="1" spans="4:4">
       <c r="D735" s="5"/>
     </row>
-    <row r="736">
+    <row r="736" customHeight="1" spans="4:4">
       <c r="D736" s="5"/>
     </row>
-    <row r="737">
+    <row r="737" customHeight="1" spans="4:4">
       <c r="D737" s="5"/>
     </row>
-    <row r="738">
+    <row r="738" customHeight="1" spans="4:4">
       <c r="D738" s="5"/>
     </row>
-    <row r="739">
+    <row r="739" customHeight="1" spans="4:4">
       <c r="D739" s="5"/>
     </row>
-    <row r="740">
+    <row r="740" customHeight="1" spans="4:4">
       <c r="D740" s="5"/>
     </row>
-    <row r="741">
+    <row r="741" customHeight="1" spans="4:4">
       <c r="D741" s="5"/>
     </row>
-    <row r="742">
+    <row r="742" customHeight="1" spans="4:4">
       <c r="D742" s="5"/>
     </row>
-    <row r="743">
+    <row r="743" customHeight="1" spans="4:4">
       <c r="D743" s="5"/>
     </row>
-    <row r="744">
+    <row r="744" customHeight="1" spans="4:4">
       <c r="D744" s="5"/>
     </row>
-    <row r="745">
+    <row r="745" customHeight="1" spans="4:4">
       <c r="D745" s="5"/>
     </row>
-    <row r="746">
+    <row r="746" customHeight="1" spans="4:4">
       <c r="D746" s="5"/>
     </row>
-    <row r="747">
+    <row r="747" customHeight="1" spans="4:4">
       <c r="D747" s="5"/>
     </row>
-    <row r="748">
+    <row r="748" customHeight="1" spans="4:4">
       <c r="D748" s="5"/>
     </row>
-    <row r="749">
+    <row r="749" customHeight="1" spans="4:4">
       <c r="D749" s="5"/>
     </row>
-    <row r="750">
+    <row r="750" customHeight="1" spans="4:4">
       <c r="D750" s="5"/>
     </row>
-    <row r="751">
+    <row r="751" customHeight="1" spans="4:4">
       <c r="D751" s="5"/>
     </row>
-    <row r="752">
+    <row r="752" customHeight="1" spans="4:4">
       <c r="D752" s="5"/>
     </row>
-    <row r="753">
+    <row r="753" customHeight="1" spans="4:4">
       <c r="D753" s="5"/>
     </row>
-    <row r="754">
+    <row r="754" customHeight="1" spans="4:4">
       <c r="D754" s="5"/>
     </row>
-    <row r="755">
+    <row r="755" customHeight="1" spans="4:4">
       <c r="D755" s="5"/>
     </row>
-    <row r="756">
+    <row r="756" customHeight="1" spans="4:4">
       <c r="D756" s="5"/>
     </row>
-    <row r="757">
+    <row r="757" customHeight="1" spans="4:4">
       <c r="D757" s="5"/>
     </row>
-    <row r="758">
+    <row r="758" customHeight="1" spans="4:4">
       <c r="D758" s="5"/>
     </row>
-    <row r="759">
+    <row r="759" customHeight="1" spans="4:4">
       <c r="D759" s="5"/>
     </row>
-    <row r="760">
+    <row r="760" customHeight="1" spans="4:4">
       <c r="D760" s="5"/>
     </row>
-    <row r="761">
+    <row r="761" customHeight="1" spans="4:4">
       <c r="D761" s="5"/>
     </row>
-    <row r="762">
+    <row r="762" customHeight="1" spans="4:4">
       <c r="D762" s="5"/>
     </row>
-    <row r="763">
+    <row r="763" customHeight="1" spans="4:4">
       <c r="D763" s="5"/>
     </row>
-    <row r="764">
+    <row r="764" customHeight="1" spans="4:4">
       <c r="D764" s="5"/>
     </row>
-    <row r="765">
+    <row r="765" customHeight="1" spans="4:4">
       <c r="D765" s="5"/>
     </row>
-    <row r="766">
+    <row r="766" customHeight="1" spans="4:4">
       <c r="D766" s="5"/>
     </row>
-    <row r="767">
+    <row r="767" customHeight="1" spans="4:4">
       <c r="D767" s="5"/>
     </row>
-    <row r="768">
+    <row r="768" customHeight="1" spans="4:4">
       <c r="D768" s="5"/>
     </row>
-    <row r="769">
+    <row r="769" customHeight="1" spans="4:4">
       <c r="D769" s="5"/>
     </row>
-    <row r="770">
+    <row r="770" customHeight="1" spans="4:4">
       <c r="D770" s="5"/>
     </row>
-    <row r="771">
+    <row r="771" customHeight="1" spans="4:4">
       <c r="D771" s="5"/>
     </row>
-    <row r="772">
+    <row r="772" customHeight="1" spans="4:4">
       <c r="D772" s="5"/>
     </row>
-    <row r="773">
+    <row r="773" customHeight="1" spans="4:4">
       <c r="D773" s="5"/>
     </row>
-    <row r="774">
+    <row r="774" customHeight="1" spans="4:4">
       <c r="D774" s="5"/>
     </row>
-    <row r="775">
+    <row r="775" customHeight="1" spans="4:4">
       <c r="D775" s="5"/>
     </row>
-    <row r="776">
+    <row r="776" customHeight="1" spans="4:4">
       <c r="D776" s="5"/>
     </row>
-    <row r="777">
+    <row r="777" customHeight="1" spans="4:4">
       <c r="D777" s="5"/>
     </row>
-    <row r="778">
+    <row r="778" customHeight="1" spans="4:4">
       <c r="D778" s="5"/>
     </row>
-    <row r="779">
+    <row r="779" customHeight="1" spans="4:4">
       <c r="D779" s="5"/>
     </row>
-    <row r="780">
+    <row r="780" customHeight="1" spans="4:4">
       <c r="D780" s="5"/>
     </row>
-    <row r="781">
+    <row r="781" customHeight="1" spans="4:4">
       <c r="D781" s="5"/>
     </row>
-    <row r="782">
+    <row r="782" customHeight="1" spans="4:4">
       <c r="D782" s="5"/>
     </row>
-    <row r="783">
+    <row r="783" customHeight="1" spans="4:4">
       <c r="D783" s="5"/>
     </row>
-    <row r="784">
+    <row r="784" customHeight="1" spans="4:4">
       <c r="D784" s="5"/>
     </row>
-    <row r="785">
+    <row r="785" customHeight="1" spans="4:4">
       <c r="D785" s="5"/>
     </row>
-    <row r="786">
+    <row r="786" customHeight="1" spans="4:4">
       <c r="D786" s="5"/>
     </row>
-    <row r="787">
+    <row r="787" customHeight="1" spans="4:4">
       <c r="D787" s="5"/>
     </row>
-    <row r="788">
+    <row r="788" customHeight="1" spans="4:4">
       <c r="D788" s="5"/>
     </row>
-    <row r="789">
+    <row r="789" customHeight="1" spans="4:4">
       <c r="D789" s="5"/>
     </row>
-    <row r="790">
+    <row r="790" customHeight="1" spans="4:4">
       <c r="D790" s="5"/>
     </row>
-    <row r="791">
+    <row r="791" customHeight="1" spans="4:4">
       <c r="D791" s="5"/>
     </row>
-    <row r="792">
+    <row r="792" customHeight="1" spans="4:4">
       <c r="D792" s="5"/>
     </row>
-    <row r="793">
+    <row r="793" customHeight="1" spans="4:4">
       <c r="D793" s="5"/>
     </row>
-    <row r="794">
+    <row r="794" customHeight="1" spans="4:4">
       <c r="D794" s="5"/>
     </row>
-    <row r="795">
+    <row r="795" customHeight="1" spans="4:4">
       <c r="D795" s="5"/>
     </row>
-    <row r="796">
+    <row r="796" customHeight="1" spans="4:4">
       <c r="D796" s="5"/>
     </row>
-    <row r="797">
+    <row r="797" customHeight="1" spans="4:4">
       <c r="D797" s="5"/>
     </row>
-    <row r="798">
+    <row r="798" customHeight="1" spans="4:4">
       <c r="D798" s="5"/>
     </row>
-    <row r="799">
+    <row r="799" customHeight="1" spans="4:4">
       <c r="D799" s="5"/>
     </row>
-    <row r="800">
+    <row r="800" customHeight="1" spans="4:4">
       <c r="D800" s="5"/>
     </row>
-    <row r="801">
+    <row r="801" customHeight="1" spans="4:4">
       <c r="D801" s="5"/>
     </row>
-    <row r="802">
+    <row r="802" customHeight="1" spans="4:4">
       <c r="D802" s="5"/>
     </row>
-    <row r="803">
+    <row r="803" customHeight="1" spans="4:4">
       <c r="D803" s="5"/>
     </row>
-    <row r="804">
+    <row r="804" customHeight="1" spans="4:4">
       <c r="D804" s="5"/>
     </row>
-    <row r="805">
+    <row r="805" customHeight="1" spans="4:4">
       <c r="D805" s="5"/>
     </row>
-    <row r="806">
+    <row r="806" customHeight="1" spans="4:4">
       <c r="D806" s="5"/>
     </row>
-    <row r="807">
+    <row r="807" customHeight="1" spans="4:4">
       <c r="D807" s="5"/>
     </row>
-    <row r="808">
+    <row r="808" customHeight="1" spans="4:4">
       <c r="D808" s="5"/>
     </row>
-    <row r="809">
+    <row r="809" customHeight="1" spans="4:4">
       <c r="D809" s="5"/>
     </row>
-    <row r="810">
+    <row r="810" customHeight="1" spans="4:4">
       <c r="D810" s="5"/>
     </row>
-    <row r="811">
+    <row r="811" customHeight="1" spans="4:4">
       <c r="D811" s="5"/>
     </row>
-    <row r="812">
+    <row r="812" customHeight="1" spans="4:4">
       <c r="D812" s="5"/>
     </row>
-    <row r="813">
+    <row r="813" customHeight="1" spans="4:4">
       <c r="D813" s="5"/>
     </row>
-    <row r="814">
+    <row r="814" customHeight="1" spans="4:4">
       <c r="D814" s="5"/>
     </row>
-    <row r="815">
+    <row r="815" customHeight="1" spans="4:4">
       <c r="D815" s="5"/>
     </row>
-    <row r="816">
+    <row r="816" customHeight="1" spans="4:4">
       <c r="D816" s="5"/>
     </row>
-    <row r="817">
+    <row r="817" customHeight="1" spans="4:4">
       <c r="D817" s="5"/>
     </row>
-    <row r="818">
+    <row r="818" customHeight="1" spans="4:4">
       <c r="D818" s="5"/>
     </row>
-    <row r="819">
+    <row r="819" customHeight="1" spans="4:4">
       <c r="D819" s="5"/>
     </row>
-    <row r="820">
+    <row r="820" customHeight="1" spans="4:4">
       <c r="D820" s="5"/>
     </row>
-    <row r="821">
+    <row r="821" customHeight="1" spans="4:4">
       <c r="D821" s="5"/>
     </row>
-    <row r="822">
+    <row r="822" customHeight="1" spans="4:4">
       <c r="D822" s="5"/>
     </row>
-    <row r="823">
+    <row r="823" customHeight="1" spans="4:4">
       <c r="D823" s="5"/>
     </row>
-    <row r="824">
+    <row r="824" customHeight="1" spans="4:4">
       <c r="D824" s="5"/>
     </row>
-    <row r="825">
+    <row r="825" customHeight="1" spans="4:4">
       <c r="D825" s="5"/>
     </row>
-    <row r="826">
+    <row r="826" customHeight="1" spans="4:4">
       <c r="D826" s="5"/>
     </row>
-    <row r="827">
+    <row r="827" customHeight="1" spans="4:4">
       <c r="D827" s="5"/>
     </row>
-    <row r="828">
+    <row r="828" customHeight="1" spans="4:4">
       <c r="D828" s="5"/>
     </row>
-    <row r="829">
+    <row r="829" customHeight="1" spans="4:4">
       <c r="D829" s="5"/>
     </row>
-    <row r="830">
+    <row r="830" customHeight="1" spans="4:4">
       <c r="D830" s="5"/>
     </row>
-    <row r="831">
+    <row r="831" customHeight="1" spans="4:4">
       <c r="D831" s="5"/>
     </row>
-    <row r="832">
+    <row r="832" customHeight="1" spans="4:4">
       <c r="D832" s="5"/>
     </row>
-    <row r="833">
+    <row r="833" customHeight="1" spans="4:4">
       <c r="D833" s="5"/>
     </row>
-    <row r="834">
+    <row r="834" customHeight="1" spans="4:4">
       <c r="D834" s="5"/>
     </row>
-    <row r="835">
+    <row r="835" customHeight="1" spans="4:4">
       <c r="D835" s="5"/>
     </row>
-    <row r="836">
+    <row r="836" customHeight="1" spans="4:4">
       <c r="D836" s="5"/>
     </row>
-    <row r="837">
+    <row r="837" customHeight="1" spans="4:4">
       <c r="D837" s="5"/>
     </row>
-    <row r="838">
+    <row r="838" customHeight="1" spans="4:4">
       <c r="D838" s="5"/>
     </row>
-    <row r="839">
+    <row r="839" customHeight="1" spans="4:4">
       <c r="D839" s="5"/>
     </row>
-    <row r="840">
+    <row r="840" customHeight="1" spans="4:4">
       <c r="D840" s="5"/>
     </row>
-    <row r="841">
+    <row r="841" customHeight="1" spans="4:4">
       <c r="D841" s="5"/>
     </row>
-    <row r="842">
+    <row r="842" customHeight="1" spans="4:4">
       <c r="D842" s="5"/>
     </row>
-    <row r="843">
+    <row r="843" customHeight="1" spans="4:4">
       <c r="D843" s="5"/>
     </row>
-    <row r="844">
+    <row r="844" customHeight="1" spans="4:4">
       <c r="D844" s="5"/>
     </row>
-    <row r="845">
+    <row r="845" customHeight="1" spans="4:4">
       <c r="D845" s="5"/>
     </row>
-    <row r="846">
+    <row r="846" customHeight="1" spans="4:4">
       <c r="D846" s="5"/>
     </row>
-    <row r="847">
+    <row r="847" customHeight="1" spans="4:4">
       <c r="D847" s="5"/>
     </row>
-    <row r="848">
+    <row r="848" customHeight="1" spans="4:4">
       <c r="D848" s="5"/>
     </row>
-    <row r="849">
+    <row r="849" customHeight="1" spans="4:4">
       <c r="D849" s="5"/>
     </row>
-    <row r="850">
+    <row r="850" customHeight="1" spans="4:4">
       <c r="D850" s="5"/>
     </row>
-    <row r="851">
+    <row r="851" customHeight="1" spans="4:4">
       <c r="D851" s="5"/>
     </row>
-    <row r="852">
+    <row r="852" customHeight="1" spans="4:4">
       <c r="D852" s="5"/>
     </row>
-    <row r="853">
+    <row r="853" customHeight="1" spans="4:4">
       <c r="D853" s="5"/>
     </row>
-    <row r="854">
+    <row r="854" customHeight="1" spans="4:4">
       <c r="D854" s="5"/>
     </row>
-    <row r="855">
+    <row r="855" customHeight="1" spans="4:4">
       <c r="D855" s="5"/>
     </row>
-    <row r="856">
+    <row r="856" customHeight="1" spans="4:4">
       <c r="D856" s="5"/>
     </row>
-    <row r="857">
+    <row r="857" customHeight="1" spans="4:4">
       <c r="D857" s="5"/>
     </row>
-    <row r="858">
+    <row r="858" customHeight="1" spans="4:4">
       <c r="D858" s="5"/>
     </row>
-    <row r="859">
+    <row r="859" customHeight="1" spans="4:4">
       <c r="D859" s="5"/>
     </row>
-    <row r="860">
+    <row r="860" customHeight="1" spans="4:4">
       <c r="D860" s="5"/>
     </row>
-    <row r="861">
+    <row r="861" customHeight="1" spans="4:4">
       <c r="D861" s="5"/>
     </row>
-    <row r="862">
+    <row r="862" customHeight="1" spans="4:4">
       <c r="D862" s="5"/>
     </row>
-    <row r="863">
+    <row r="863" customHeight="1" spans="4:4">
       <c r="D863" s="5"/>
     </row>
-    <row r="864">
+    <row r="864" customHeight="1" spans="4:4">
       <c r="D864" s="5"/>
     </row>
-    <row r="865">
+    <row r="865" customHeight="1" spans="4:4">
       <c r="D865" s="5"/>
     </row>
-    <row r="866">
+    <row r="866" customHeight="1" spans="4:4">
       <c r="D866" s="5"/>
     </row>
-    <row r="867">
+    <row r="867" customHeight="1" spans="4:4">
       <c r="D867" s="5"/>
     </row>
-    <row r="868">
+    <row r="868" customHeight="1" spans="4:4">
       <c r="D868" s="5"/>
     </row>
-    <row r="869">
+    <row r="869" customHeight="1" spans="4:4">
       <c r="D869" s="5"/>
     </row>
-    <row r="870">
+    <row r="870" customHeight="1" spans="4:4">
       <c r="D870" s="5"/>
     </row>
-    <row r="871">
+    <row r="871" customHeight="1" spans="4:4">
       <c r="D871" s="5"/>
     </row>
-    <row r="872">
+    <row r="872" customHeight="1" spans="4:4">
       <c r="D872" s="5"/>
     </row>
-    <row r="873">
+    <row r="873" customHeight="1" spans="4:4">
       <c r="D873" s="5"/>
     </row>
-    <row r="874">
+    <row r="874" customHeight="1" spans="4:4">
       <c r="D874" s="5"/>
     </row>
-    <row r="875">
+    <row r="875" customHeight="1" spans="4:4">
       <c r="D875" s="5"/>
     </row>
-    <row r="876">
+    <row r="876" customHeight="1" spans="4:4">
       <c r="D876" s="5"/>
     </row>
-    <row r="877">
+    <row r="877" customHeight="1" spans="4:4">
       <c r="D877" s="5"/>
     </row>
-    <row r="878">
+    <row r="878" customHeight="1" spans="4:4">
       <c r="D878" s="5"/>
     </row>
-    <row r="879">
+    <row r="879" customHeight="1" spans="4:4">
       <c r="D879" s="5"/>
     </row>
-    <row r="880">
+    <row r="880" customHeight="1" spans="4:4">
       <c r="D880" s="5"/>
     </row>
-    <row r="881">
+    <row r="881" customHeight="1" spans="4:4">
       <c r="D881" s="5"/>
     </row>
-    <row r="882">
+    <row r="882" customHeight="1" spans="4:4">
       <c r="D882" s="5"/>
     </row>
-    <row r="883">
+    <row r="883" customHeight="1" spans="4:4">
       <c r="D883" s="5"/>
     </row>
-    <row r="884">
+    <row r="884" customHeight="1" spans="4:4">
       <c r="D884" s="5"/>
     </row>
-    <row r="885">
+    <row r="885" customHeight="1" spans="4:4">
       <c r="D885" s="5"/>
     </row>
-    <row r="886">
+    <row r="886" customHeight="1" spans="4:4">
       <c r="D886" s="5"/>
     </row>
-    <row r="887">
+    <row r="887" customHeight="1" spans="4:4">
       <c r="D887" s="5"/>
     </row>
-    <row r="888">
+    <row r="888" customHeight="1" spans="4:4">
       <c r="D888" s="5"/>
     </row>
-    <row r="889">
+    <row r="889" customHeight="1" spans="4:4">
       <c r="D889" s="5"/>
     </row>
-    <row r="890">
+    <row r="890" customHeight="1" spans="4:4">
       <c r="D890" s="5"/>
     </row>
-    <row r="891">
+    <row r="891" customHeight="1" spans="4:4">
       <c r="D891" s="5"/>
     </row>
-    <row r="892">
+    <row r="892" customHeight="1" spans="4:4">
       <c r="D892" s="5"/>
     </row>
-    <row r="893">
+    <row r="893" customHeight="1" spans="4:4">
       <c r="D893" s="5"/>
     </row>
-    <row r="894">
+    <row r="894" customHeight="1" spans="4:4">
       <c r="D894" s="5"/>
     </row>
-    <row r="895">
+    <row r="895" customHeight="1" spans="4:4">
       <c r="D895" s="5"/>
     </row>
-    <row r="896">
+    <row r="896" customHeight="1" spans="4:4">
       <c r="D896" s="5"/>
     </row>
-    <row r="897">
+    <row r="897" customHeight="1" spans="4:4">
       <c r="D897" s="5"/>
     </row>
-    <row r="898">
+    <row r="898" customHeight="1" spans="4:4">
       <c r="D898" s="5"/>
     </row>
-    <row r="899">
+    <row r="899" customHeight="1" spans="4:4">
       <c r="D899" s="5"/>
     </row>
-    <row r="900">
+    <row r="900" customHeight="1" spans="4:4">
       <c r="D900" s="5"/>
     </row>
-    <row r="901">
+    <row r="901" customHeight="1" spans="4:4">
       <c r="D901" s="5"/>
     </row>
-    <row r="902">
+    <row r="902" customHeight="1" spans="4:4">
       <c r="D902" s="5"/>
     </row>
-    <row r="903">
+    <row r="903" customHeight="1" spans="4:4">
       <c r="D903" s="5"/>
     </row>
-    <row r="904">
+    <row r="904" customHeight="1" spans="4:4">
       <c r="D904" s="5"/>
     </row>
-    <row r="905">
+    <row r="905" customHeight="1" spans="4:4">
       <c r="D905" s="5"/>
     </row>
-    <row r="906">
+    <row r="906" customHeight="1" spans="4:4">
       <c r="D906" s="5"/>
     </row>
-    <row r="907">
+    <row r="907" customHeight="1" spans="4:4">
       <c r="D907" s="5"/>
     </row>
-    <row r="908">
+    <row r="908" customHeight="1" spans="4:4">
       <c r="D908" s="5"/>
     </row>
-    <row r="909">
+    <row r="909" customHeight="1" spans="4:4">
       <c r="D909" s="5"/>
     </row>
-    <row r="910">
+    <row r="910" customHeight="1" spans="4:4">
       <c r="D910" s="5"/>
     </row>
-    <row r="911">
+    <row r="911" customHeight="1" spans="4:4">
       <c r="D911" s="5"/>
     </row>
-    <row r="912">
+    <row r="912" customHeight="1" spans="4:4">
       <c r="D912" s="5"/>
     </row>
-    <row r="913">
+    <row r="913" customHeight="1" spans="4:4">
       <c r="D913" s="5"/>
     </row>
-    <row r="914">
+    <row r="914" customHeight="1" spans="4:4">
       <c r="D914" s="5"/>
     </row>
-    <row r="915">
+    <row r="915" customHeight="1" spans="4:4">
       <c r="D915" s="5"/>
     </row>
-    <row r="916">
+    <row r="916" customHeight="1" spans="4:4">
       <c r="D916" s="5"/>
     </row>
-    <row r="917">
+    <row r="917" customHeight="1" spans="4:4">
       <c r="D917" s="5"/>
     </row>
-    <row r="918">
+    <row r="918" customHeight="1" spans="4:4">
       <c r="D918" s="5"/>
     </row>
-    <row r="919">
+    <row r="919" customHeight="1" spans="4:4">
       <c r="D919" s="5"/>
     </row>
-    <row r="920">
+    <row r="920" customHeight="1" spans="4:4">
       <c r="D920" s="5"/>
     </row>
-    <row r="921">
+    <row r="921" customHeight="1" spans="4:4">
       <c r="D921" s="5"/>
     </row>
-    <row r="922">
+    <row r="922" customHeight="1" spans="4:4">
       <c r="D922" s="5"/>
     </row>
-    <row r="923">
+    <row r="923" customHeight="1" spans="4:4">
       <c r="D923" s="5"/>
     </row>
-    <row r="924">
+    <row r="924" customHeight="1" spans="4:4">
       <c r="D924" s="5"/>
     </row>
-    <row r="925">
+    <row r="925" customHeight="1" spans="4:4">
       <c r="D925" s="5"/>
     </row>
-    <row r="926">
+    <row r="926" customHeight="1" spans="4:4">
       <c r="D926" s="5"/>
     </row>
-    <row r="927">
+    <row r="927" customHeight="1" spans="4:4">
       <c r="D927" s="5"/>
     </row>
-    <row r="928">
+    <row r="928" customHeight="1" spans="4:4">
       <c r="D928" s="5"/>
     </row>
-    <row r="929">
+    <row r="929" customHeight="1" spans="4:4">
       <c r="D929" s="5"/>
     </row>
-    <row r="930">
+    <row r="930" customHeight="1" spans="4:4">
       <c r="D930" s="5"/>
     </row>
-    <row r="931">
+    <row r="931" customHeight="1" spans="4:4">
       <c r="D931" s="5"/>
     </row>
-    <row r="932">
+    <row r="932" customHeight="1" spans="4:4">
       <c r="D932" s="5"/>
     </row>
-    <row r="933">
+    <row r="933" customHeight="1" spans="4:4">
       <c r="D933" s="5"/>
     </row>
-    <row r="934">
+    <row r="934" customHeight="1" spans="4:4">
       <c r="D934" s="5"/>
     </row>
-    <row r="935">
+    <row r="935" customHeight="1" spans="4:4">
       <c r="D935" s="5"/>
     </row>
-    <row r="936">
+    <row r="936" customHeight="1" spans="4:4">
       <c r="D936" s="5"/>
     </row>
-    <row r="937">
+    <row r="937" customHeight="1" spans="4:4">
       <c r="D937" s="5"/>
     </row>
-    <row r="938">
+    <row r="938" customHeight="1" spans="4:4">
       <c r="D938" s="5"/>
     </row>
-    <row r="939">
+    <row r="939" customHeight="1" spans="4:4">
       <c r="D939" s="5"/>
     </row>
-    <row r="940">
+    <row r="940" customHeight="1" spans="4:4">
       <c r="D940" s="5"/>
     </row>
-    <row r="941">
+    <row r="941" customHeight="1" spans="4:4">
       <c r="D941" s="5"/>
     </row>
-    <row r="942">
+    <row r="942" customHeight="1" spans="4:4">
       <c r="D942" s="5"/>
     </row>
-    <row r="943">
+    <row r="943" customHeight="1" spans="4:4">
       <c r="D943" s="5"/>
     </row>
-    <row r="944">
+    <row r="944" customHeight="1" spans="4:4">
       <c r="D944" s="5"/>
     </row>
-    <row r="945">
+    <row r="945" customHeight="1" spans="4:4">
       <c r="D945" s="5"/>
     </row>
-    <row r="946">
+    <row r="946" customHeight="1" spans="4:4">
       <c r="D946" s="5"/>
     </row>
-    <row r="947">
+    <row r="947" customHeight="1" spans="4:4">
       <c r="D947" s="5"/>
     </row>
-    <row r="948">
+    <row r="948" customHeight="1" spans="4:4">
       <c r="D948" s="5"/>
     </row>
-    <row r="949">
+    <row r="949" customHeight="1" spans="4:4">
       <c r="D949" s="5"/>
     </row>
-    <row r="950">
+    <row r="950" customHeight="1" spans="4:4">
       <c r="D950" s="5"/>
     </row>
-    <row r="951">
+    <row r="951" customHeight="1" spans="4:4">
       <c r="D951" s="5"/>
     </row>
-    <row r="952">
+    <row r="952" customHeight="1" spans="4:4">
       <c r="D952" s="5"/>
     </row>
-    <row r="953">
+    <row r="953" customHeight="1" spans="4:4">
       <c r="D953" s="5"/>
     </row>
-    <row r="954">
+    <row r="954" customHeight="1" spans="4:4">
       <c r="D954" s="5"/>
     </row>
-    <row r="955">
+    <row r="955" customHeight="1" spans="4:4">
       <c r="D955" s="5"/>
     </row>
-    <row r="956">
+    <row r="956" customHeight="1" spans="4:4">
       <c r="D956" s="5"/>
     </row>
-    <row r="957">
+    <row r="957" customHeight="1" spans="4:4">
       <c r="D957" s="5"/>
     </row>
-    <row r="958">
+    <row r="958" customHeight="1" spans="4:4">
       <c r="D958" s="5"/>
     </row>
-    <row r="959">
+    <row r="959" customHeight="1" spans="4:4">
       <c r="D959" s="5"/>
     </row>
-    <row r="960">
+    <row r="960" customHeight="1" spans="4:4">
       <c r="D960" s="5"/>
     </row>
-    <row r="961">
+    <row r="961" customHeight="1" spans="4:4">
       <c r="D961" s="5"/>
     </row>
-    <row r="962">
+    <row r="962" customHeight="1" spans="4:4">
       <c r="D962" s="5"/>
     </row>
-    <row r="963">
+    <row r="963" customHeight="1" spans="4:4">
       <c r="D963" s="5"/>
     </row>
-    <row r="964">
+    <row r="964" customHeight="1" spans="4:4">
       <c r="D964" s="5"/>
     </row>
-    <row r="965">
+    <row r="965" customHeight="1" spans="4:4">
       <c r="D965" s="5"/>
     </row>
-    <row r="966">
+    <row r="966" customHeight="1" spans="4:4">
       <c r="D966" s="5"/>
     </row>
-    <row r="967">
+    <row r="967" customHeight="1" spans="4:4">
       <c r="D967" s="5"/>
     </row>
-    <row r="968">
+    <row r="968" customHeight="1" spans="4:4">
       <c r="D968" s="5"/>
     </row>
-    <row r="969">
+    <row r="969" customHeight="1" spans="4:4">
       <c r="D969" s="5"/>
     </row>
-    <row r="970">
+    <row r="970" customHeight="1" spans="4:4">
       <c r="D970" s="5"/>
     </row>
-    <row r="971">
+    <row r="971" customHeight="1" spans="4:4">
       <c r="D971" s="5"/>
     </row>
-    <row r="972">
+    <row r="972" customHeight="1" spans="4:4">
       <c r="D972" s="5"/>
     </row>
-    <row r="973">
+    <row r="973" customHeight="1" spans="4:4">
       <c r="D973" s="5"/>
     </row>
-    <row r="974">
+    <row r="974" customHeight="1" spans="4:4">
       <c r="D974" s="5"/>
     </row>
-    <row r="975">
+    <row r="975" customHeight="1" spans="4:4">
       <c r="D975" s="5"/>
     </row>
-    <row r="976">
+    <row r="976" customHeight="1" spans="4:4">
       <c r="D976" s="5"/>
     </row>
-    <row r="977">
+    <row r="977" customHeight="1" spans="4:4">
       <c r="D977" s="5"/>
     </row>
-    <row r="978">
+    <row r="978" customHeight="1" spans="4:4">
       <c r="D978" s="5"/>
     </row>
-    <row r="979">
+    <row r="979" customHeight="1" spans="4:4">
       <c r="D979" s="5"/>
     </row>
-    <row r="980">
+    <row r="980" customHeight="1" spans="4:4">
       <c r="D980" s="5"/>
     </row>
-    <row r="981">
+    <row r="981" customHeight="1" spans="4:4">
       <c r="D981" s="5"/>
     </row>
-    <row r="982">
+    <row r="982" customHeight="1" spans="4:4">
       <c r="D982" s="5"/>
     </row>
-    <row r="983">
+    <row r="983" customHeight="1" spans="4:4">
       <c r="D983" s="5"/>
     </row>
-    <row r="984">
+    <row r="984" customHeight="1" spans="4:4">
       <c r="D984" s="5"/>
     </row>
-    <row r="985">
+    <row r="985" customHeight="1" spans="4:4">
       <c r="D985" s="5"/>
     </row>
-    <row r="986">
+    <row r="986" customHeight="1" spans="4:4">
       <c r="D986" s="5"/>
     </row>
-    <row r="987">
+    <row r="987" customHeight="1" spans="4:4">
       <c r="D987" s="5"/>
     </row>
-    <row r="988">
+    <row r="988" customHeight="1" spans="4:4">
       <c r="D988" s="5"/>
     </row>
-    <row r="989">
+    <row r="989" customHeight="1" spans="4:4">
       <c r="D989" s="5"/>
     </row>
-    <row r="990">
+    <row r="990" customHeight="1" spans="4:4">
       <c r="D990" s="5"/>
     </row>
-    <row r="991">
+    <row r="991" customHeight="1" spans="4:4">
       <c r="D991" s="5"/>
     </row>
-    <row r="992">
+    <row r="992" customHeight="1" spans="4:4">
       <c r="D992" s="5"/>
     </row>
-    <row r="993">
+    <row r="993" customHeight="1" spans="4:4">
       <c r="D993" s="5"/>
     </row>
-    <row r="994">
+    <row r="994" customHeight="1" spans="4:4">
       <c r="D994" s="5"/>
     </row>
-    <row r="995">
+    <row r="995" customHeight="1" spans="4:4">
       <c r="D995" s="5"/>
     </row>
-    <row r="996">
+    <row r="996" customHeight="1" spans="4:4">
       <c r="D996" s="5"/>
     </row>
-    <row r="997">
+    <row r="997" customHeight="1" spans="4:4">
       <c r="D997" s="5"/>
     </row>
-    <row r="998">
+    <row r="998" customHeight="1" spans="4:4">
       <c r="D998" s="5"/>
     </row>
-    <row r="999">
+    <row r="999" customHeight="1" spans="4:4">
       <c r="D999" s="5"/>
     </row>
-    <row r="1000">
+    <row r="1000" customHeight="1" spans="4:4">
       <c r="D1000" s="5"/>
     </row>
-    <row r="1001">
+    <row r="1001" customHeight="1" spans="4:4">
       <c r="D1001" s="5"/>
     </row>
   </sheetData>
@@ -3858,6 +4722,7 @@
       <formula>LEN(TRIM(D1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/SoundData.xlsx
+++ b/JsonConverter/ExcelFiles/SoundData.xlsx
@@ -149,7 +149,7 @@
     <t>Sound_SFX_012</t>
   </si>
   <si>
-    <t>GunTrap_Fire</t>
+    <t>GunTrap_01</t>
   </si>
   <si>
     <t>Sound_SFX_013</t>

--- a/JsonConverter/ExcelFiles/SoundData.xlsx
+++ b/JsonConverter/ExcelFiles/SoundData.xlsx
@@ -1,28 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
-  </bookViews>
   <sheets>
-    <sheet name="시트1" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="시트1" sheetId="1" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
@@ -239,927 +223,81 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="3">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
+      <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="9">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
+  <borders count="1">
+    <border/>
   </borders>
-  <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+  <cellStyleXfs count="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="1">
     <dxf>
+      <font/>
       <fill>
         <patternFill patternType="none"/>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="double">
-          <color theme="4"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-        <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
+      <border/>
     </dxf>
   </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="7"/>
-      <tableStyleElement type="headerRow" dxfId="6"/>
-      <tableStyleElement type="totalRow" dxfId="5"/>
-      <tableStyleElement type="firstColumn" dxfId="4"/>
-      <tableStyleElement type="lastColumn" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="17"/>
-      <tableStyleElement type="totalRow" dxfId="16"/>
-      <tableStyleElement type="firstRowStripe" dxfId="15"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
-      <tableStyleElement type="pageFieldValues" dxfId="8"/>
-    </tableStyle>
-  </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1349,30 +487,28 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D1001"/>
-  <sheetFormatPr defaultColWidth="12.6296296296296" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="3"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="14.75" customWidth="1"/>
-    <col min="2" max="2" width="14.5" customWidth="1"/>
-    <col min="3" max="3" width="13.5" customWidth="1"/>
-    <col min="4" max="4" width="12.75" customWidth="1"/>
-    <col min="5" max="5" width="16.5" customWidth="1"/>
-    <col min="6" max="6" width="16.25" customWidth="1"/>
-    <col min="7" max="7" width="23.75" customWidth="1"/>
-    <col min="8" max="8" width="29.6296296296296" customWidth="1"/>
-    <col min="9" max="9" width="17.25" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="14.75"/>
+    <col customWidth="1" min="2" max="2" width="14.5"/>
+    <col customWidth="1" min="3" max="3" width="13.5"/>
+    <col customWidth="1" min="4" max="4" width="12.75"/>
+    <col customWidth="1" min="5" max="5" width="16.5"/>
+    <col customWidth="1" min="6" max="6" width="16.25"/>
+    <col customWidth="1" min="7" max="7" width="23.75"/>
+    <col customWidth="1" min="8" max="8" width="29.63"/>
+    <col customWidth="1" min="9" max="9" width="17.25"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:4">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1386,7 +522,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:4">
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1400,7 +536,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:4">
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1414,7 +550,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:4">
+    <row r="4">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -1422,13 +558,13 @@
         <v>12</v>
       </c>
       <c r="C4" s="1">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:4">
+    <row r="5">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -1436,13 +572,13 @@
         <v>15</v>
       </c>
       <c r="C5" s="1">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:4">
+    <row r="6">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -1450,13 +586,13 @@
         <v>17</v>
       </c>
       <c r="C6" s="1">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:4">
+    <row r="7">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -1464,13 +600,13 @@
         <v>20</v>
       </c>
       <c r="C7" s="1">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:4">
+    <row r="8">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -1478,13 +614,13 @@
         <v>22</v>
       </c>
       <c r="C8" s="1">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:4">
+    <row r="9">
       <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
@@ -1492,13 +628,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="1">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:4">
+    <row r="10">
       <c r="A10" s="1" t="s">
         <v>25</v>
       </c>
@@ -1506,13 +642,13 @@
         <v>26</v>
       </c>
       <c r="C10" s="1">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:4">
+    <row r="11">
       <c r="A11" s="1" t="s">
         <v>27</v>
       </c>
@@ -1520,13 +656,13 @@
         <v>28</v>
       </c>
       <c r="C11" s="1">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:4">
+    <row r="12">
       <c r="A12" s="1" t="s">
         <v>29</v>
       </c>
@@ -1534,13 +670,13 @@
         <v>30</v>
       </c>
       <c r="C12" s="1">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:4">
+    <row r="13">
       <c r="A13" s="1" t="s">
         <v>31</v>
       </c>
@@ -1548,13 +684,13 @@
         <v>32</v>
       </c>
       <c r="C13" s="1">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:4">
+    <row r="14">
       <c r="A14" s="1" t="s">
         <v>33</v>
       </c>
@@ -1562,13 +698,13 @@
         <v>34</v>
       </c>
       <c r="C14" s="1">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:4">
+    <row r="15">
       <c r="A15" s="1" t="s">
         <v>35</v>
       </c>
@@ -1576,13 +712,13 @@
         <v>36</v>
       </c>
       <c r="C15" s="1">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:4">
+    <row r="16">
       <c r="A16" s="1" t="s">
         <v>37</v>
       </c>
@@ -1590,13 +726,13 @@
         <v>38</v>
       </c>
       <c r="C16" s="1">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:4">
+    <row r="17">
       <c r="A17" s="1" t="s">
         <v>39</v>
       </c>
@@ -1604,13 +740,13 @@
         <v>40</v>
       </c>
       <c r="C17" s="1">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="1:4">
+    <row r="18">
       <c r="A18" s="1" t="s">
         <v>41</v>
       </c>
@@ -1618,13 +754,13 @@
         <v>42</v>
       </c>
       <c r="C18" s="1">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:4">
+    <row r="19">
       <c r="A19" s="1" t="s">
         <v>43</v>
       </c>
@@ -1632,13 +768,13 @@
         <v>44</v>
       </c>
       <c r="C19" s="1">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="1:4">
+    <row r="20">
       <c r="A20" s="1" t="s">
         <v>45</v>
       </c>
@@ -1646,13 +782,13 @@
         <v>46</v>
       </c>
       <c r="C20" s="1">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="1:4">
+    <row r="21">
       <c r="A21" s="1" t="s">
         <v>47</v>
       </c>
@@ -1660,13 +796,13 @@
         <v>48</v>
       </c>
       <c r="C21" s="1">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="1:4">
+    <row r="22">
       <c r="A22" s="1" t="s">
         <v>49</v>
       </c>
@@ -1674,13 +810,13 @@
         <v>50</v>
       </c>
       <c r="C22" s="1">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="1:4">
+    <row r="23">
       <c r="A23" s="1" t="s">
         <v>51</v>
       </c>
@@ -1688,13 +824,13 @@
         <v>52</v>
       </c>
       <c r="C23" s="1">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="1:4">
+    <row r="24">
       <c r="A24" s="1" t="s">
         <v>53</v>
       </c>
@@ -1702,13 +838,13 @@
         <v>54</v>
       </c>
       <c r="C24" s="1">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="1:4">
+    <row r="25">
       <c r="A25" s="1" t="s">
         <v>55</v>
       </c>
@@ -1716,13 +852,13 @@
         <v>56</v>
       </c>
       <c r="C25" s="1">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="1:4">
+    <row r="26">
       <c r="A26" s="1" t="s">
         <v>57</v>
       </c>
@@ -1730,13 +866,13 @@
         <v>58</v>
       </c>
       <c r="C26" s="1">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="1:4">
+    <row r="27">
       <c r="A27" s="1" t="s">
         <v>59</v>
       </c>
@@ -1744,13 +880,13 @@
         <v>60</v>
       </c>
       <c r="C27" s="1">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="1:4">
+    <row r="28">
       <c r="A28" s="1" t="s">
         <v>61</v>
       </c>
@@ -1758,13 +894,13 @@
         <v>62</v>
       </c>
       <c r="C28" s="1">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="1:4">
+    <row r="29">
       <c r="A29" s="3" t="s">
         <v>63</v>
       </c>
@@ -1772,13 +908,13 @@
         <v>64</v>
       </c>
       <c r="C29" s="1">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="1:4">
+    <row r="30">
       <c r="A30" s="3" t="s">
         <v>65</v>
       </c>
@@ -1786,13 +922,13 @@
         <v>66</v>
       </c>
       <c r="C30" s="1">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="1:4">
+    <row r="31">
       <c r="A31" s="3" t="s">
         <v>67</v>
       </c>
@@ -1800,2920 +936,2920 @@
         <v>68</v>
       </c>
       <c r="C31" s="1">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="1:4">
+    <row r="32">
       <c r="D32" s="5"/>
     </row>
-    <row r="33" customHeight="1" spans="4:4">
+    <row r="33">
       <c r="D33" s="5"/>
     </row>
-    <row r="34" customHeight="1" spans="4:4">
+    <row r="34">
       <c r="D34" s="5"/>
     </row>
-    <row r="35" customHeight="1" spans="4:4">
+    <row r="35">
       <c r="D35" s="5"/>
     </row>
-    <row r="36" customHeight="1" spans="4:4">
+    <row r="36">
       <c r="D36" s="5"/>
     </row>
-    <row r="37" customHeight="1" spans="4:4">
+    <row r="37">
       <c r="D37" s="5"/>
     </row>
-    <row r="38" customHeight="1" spans="4:4">
+    <row r="38">
       <c r="D38" s="5"/>
     </row>
-    <row r="39" customHeight="1" spans="4:4">
+    <row r="39">
       <c r="D39" s="5"/>
     </row>
-    <row r="40" customHeight="1" spans="4:4">
+    <row r="40">
       <c r="D40" s="5"/>
     </row>
-    <row r="41" customHeight="1" spans="4:4">
+    <row r="41">
       <c r="D41" s="5"/>
     </row>
-    <row r="42" customHeight="1" spans="4:4">
+    <row r="42">
       <c r="D42" s="5"/>
     </row>
-    <row r="43" customHeight="1" spans="4:4">
+    <row r="43">
       <c r="D43" s="5"/>
     </row>
-    <row r="44" customHeight="1" spans="4:4">
+    <row r="44">
       <c r="D44" s="5"/>
     </row>
-    <row r="45" customHeight="1" spans="4:4">
+    <row r="45">
       <c r="D45" s="5"/>
     </row>
-    <row r="46" customHeight="1" spans="4:4">
+    <row r="46">
       <c r="D46" s="5"/>
     </row>
-    <row r="47" customHeight="1" spans="4:4">
+    <row r="47">
       <c r="D47" s="5"/>
     </row>
-    <row r="48" customHeight="1" spans="4:4">
+    <row r="48">
       <c r="D48" s="5"/>
     </row>
-    <row r="49" customHeight="1" spans="4:4">
+    <row r="49">
       <c r="D49" s="5"/>
     </row>
-    <row r="50" customHeight="1" spans="4:4">
+    <row r="50">
       <c r="D50" s="5"/>
     </row>
-    <row r="51" customHeight="1" spans="4:4">
+    <row r="51">
       <c r="D51" s="5"/>
     </row>
-    <row r="52" customHeight="1" spans="4:4">
+    <row r="52">
       <c r="D52" s="5"/>
     </row>
-    <row r="53" customHeight="1" spans="4:4">
+    <row r="53">
       <c r="D53" s="5"/>
     </row>
-    <row r="54" customHeight="1" spans="4:4">
+    <row r="54">
       <c r="D54" s="5"/>
     </row>
-    <row r="55" customHeight="1" spans="4:4">
+    <row r="55">
       <c r="D55" s="5"/>
     </row>
-    <row r="56" customHeight="1" spans="4:4">
+    <row r="56">
       <c r="D56" s="5"/>
     </row>
-    <row r="57" customHeight="1" spans="4:4">
+    <row r="57">
       <c r="D57" s="5"/>
     </row>
-    <row r="58" customHeight="1" spans="4:4">
+    <row r="58">
       <c r="D58" s="5"/>
     </row>
-    <row r="59" customHeight="1" spans="4:4">
+    <row r="59">
       <c r="D59" s="5"/>
     </row>
-    <row r="60" customHeight="1" spans="4:4">
+    <row r="60">
       <c r="D60" s="5"/>
     </row>
-    <row r="61" customHeight="1" spans="4:4">
+    <row r="61">
       <c r="D61" s="5"/>
     </row>
-    <row r="62" customHeight="1" spans="4:4">
+    <row r="62">
       <c r="D62" s="5"/>
     </row>
-    <row r="63" customHeight="1" spans="4:4">
+    <row r="63">
       <c r="D63" s="5"/>
     </row>
-    <row r="64" customHeight="1" spans="4:4">
+    <row r="64">
       <c r="D64" s="5"/>
     </row>
-    <row r="65" customHeight="1" spans="4:4">
+    <row r="65">
       <c r="D65" s="5"/>
     </row>
-    <row r="66" customHeight="1" spans="4:4">
+    <row r="66">
       <c r="D66" s="5"/>
     </row>
-    <row r="67" customHeight="1" spans="4:4">
+    <row r="67">
       <c r="D67" s="5"/>
     </row>
-    <row r="68" customHeight="1" spans="4:4">
+    <row r="68">
       <c r="D68" s="5"/>
     </row>
-    <row r="69" customHeight="1" spans="4:4">
+    <row r="69">
       <c r="D69" s="5"/>
     </row>
-    <row r="70" customHeight="1" spans="4:4">
+    <row r="70">
       <c r="D70" s="5"/>
     </row>
-    <row r="71" customHeight="1" spans="4:4">
+    <row r="71">
       <c r="D71" s="5"/>
     </row>
-    <row r="72" customHeight="1" spans="4:4">
+    <row r="72">
       <c r="D72" s="5"/>
     </row>
-    <row r="73" customHeight="1" spans="4:4">
+    <row r="73">
       <c r="D73" s="5"/>
     </row>
-    <row r="74" customHeight="1" spans="4:4">
+    <row r="74">
       <c r="D74" s="5"/>
     </row>
-    <row r="75" customHeight="1" spans="4:4">
+    <row r="75">
       <c r="D75" s="5"/>
     </row>
-    <row r="76" customHeight="1" spans="4:4">
+    <row r="76">
       <c r="D76" s="5"/>
     </row>
-    <row r="77" customHeight="1" spans="4:4">
+    <row r="77">
       <c r="D77" s="5"/>
     </row>
-    <row r="78" customHeight="1" spans="4:4">
+    <row r="78">
       <c r="D78" s="5"/>
     </row>
-    <row r="79" customHeight="1" spans="4:4">
+    <row r="79">
       <c r="D79" s="5"/>
     </row>
-    <row r="80" customHeight="1" spans="4:4">
+    <row r="80">
       <c r="D80" s="5"/>
     </row>
-    <row r="81" customHeight="1" spans="4:4">
+    <row r="81">
       <c r="D81" s="5"/>
     </row>
-    <row r="82" customHeight="1" spans="4:4">
+    <row r="82">
       <c r="D82" s="5"/>
     </row>
-    <row r="83" customHeight="1" spans="4:4">
+    <row r="83">
       <c r="D83" s="5"/>
     </row>
-    <row r="84" customHeight="1" spans="4:4">
+    <row r="84">
       <c r="D84" s="5"/>
     </row>
-    <row r="85" customHeight="1" spans="4:4">
+    <row r="85">
       <c r="D85" s="5"/>
     </row>
-    <row r="86" customHeight="1" spans="4:4">
+    <row r="86">
       <c r="D86" s="5"/>
     </row>
-    <row r="87" customHeight="1" spans="4:4">
+    <row r="87">
       <c r="D87" s="5"/>
     </row>
-    <row r="88" customHeight="1" spans="4:4">
+    <row r="88">
       <c r="D88" s="5"/>
     </row>
-    <row r="89" customHeight="1" spans="4:4">
+    <row r="89">
       <c r="D89" s="5"/>
     </row>
-    <row r="90" customHeight="1" spans="4:4">
+    <row r="90">
       <c r="D90" s="5"/>
     </row>
-    <row r="91" customHeight="1" spans="4:4">
+    <row r="91">
       <c r="D91" s="5"/>
     </row>
-    <row r="92" customHeight="1" spans="4:4">
+    <row r="92">
       <c r="D92" s="5"/>
     </row>
-    <row r="93" customHeight="1" spans="4:4">
+    <row r="93">
       <c r="D93" s="5"/>
     </row>
-    <row r="94" customHeight="1" spans="4:4">
+    <row r="94">
       <c r="D94" s="5"/>
     </row>
-    <row r="95" customHeight="1" spans="4:4">
+    <row r="95">
       <c r="D95" s="5"/>
     </row>
-    <row r="96" customHeight="1" spans="4:4">
+    <row r="96">
       <c r="D96" s="5"/>
     </row>
-    <row r="97" customHeight="1" spans="4:4">
+    <row r="97">
       <c r="D97" s="5"/>
     </row>
-    <row r="98" customHeight="1" spans="4:4">
+    <row r="98">
       <c r="D98" s="5"/>
     </row>
-    <row r="99" customHeight="1" spans="4:4">
+    <row r="99">
       <c r="D99" s="5"/>
     </row>
-    <row r="100" customHeight="1" spans="4:4">
+    <row r="100">
       <c r="D100" s="5"/>
     </row>
-    <row r="101" customHeight="1" spans="4:4">
+    <row r="101">
       <c r="D101" s="5"/>
     </row>
-    <row r="102" customHeight="1" spans="4:4">
+    <row r="102">
       <c r="D102" s="5"/>
     </row>
-    <row r="103" customHeight="1" spans="4:4">
+    <row r="103">
       <c r="D103" s="5"/>
     </row>
-    <row r="104" customHeight="1" spans="4:4">
+    <row r="104">
       <c r="D104" s="5"/>
     </row>
-    <row r="105" customHeight="1" spans="4:4">
+    <row r="105">
       <c r="D105" s="5"/>
     </row>
-    <row r="106" customHeight="1" spans="4:4">
+    <row r="106">
       <c r="D106" s="5"/>
     </row>
-    <row r="107" customHeight="1" spans="4:4">
+    <row r="107">
       <c r="D107" s="5"/>
     </row>
-    <row r="108" customHeight="1" spans="4:4">
+    <row r="108">
       <c r="D108" s="5"/>
     </row>
-    <row r="109" customHeight="1" spans="4:4">
+    <row r="109">
       <c r="D109" s="5"/>
     </row>
-    <row r="110" customHeight="1" spans="4:4">
+    <row r="110">
       <c r="D110" s="5"/>
     </row>
-    <row r="111" customHeight="1" spans="4:4">
+    <row r="111">
       <c r="D111" s="5"/>
     </row>
-    <row r="112" customHeight="1" spans="4:4">
+    <row r="112">
       <c r="D112" s="5"/>
     </row>
-    <row r="113" customHeight="1" spans="4:4">
+    <row r="113">
       <c r="D113" s="5"/>
     </row>
-    <row r="114" customHeight="1" spans="4:4">
+    <row r="114">
       <c r="D114" s="5"/>
     </row>
-    <row r="115" customHeight="1" spans="4:4">
+    <row r="115">
       <c r="D115" s="5"/>
     </row>
-    <row r="116" customHeight="1" spans="4:4">
+    <row r="116">
       <c r="D116" s="5"/>
     </row>
-    <row r="117" customHeight="1" spans="4:4">
+    <row r="117">
       <c r="D117" s="5"/>
     </row>
-    <row r="118" customHeight="1" spans="4:4">
+    <row r="118">
       <c r="D118" s="5"/>
     </row>
-    <row r="119" customHeight="1" spans="4:4">
+    <row r="119">
       <c r="D119" s="5"/>
     </row>
-    <row r="120" customHeight="1" spans="4:4">
+    <row r="120">
       <c r="D120" s="5"/>
     </row>
-    <row r="121" customHeight="1" spans="4:4">
+    <row r="121">
       <c r="D121" s="5"/>
     </row>
-    <row r="122" customHeight="1" spans="4:4">
+    <row r="122">
       <c r="D122" s="5"/>
     </row>
-    <row r="123" customHeight="1" spans="4:4">
+    <row r="123">
       <c r="D123" s="5"/>
     </row>
-    <row r="124" customHeight="1" spans="4:4">
+    <row r="124">
       <c r="D124" s="5"/>
     </row>
-    <row r="125" customHeight="1" spans="4:4">
+    <row r="125">
       <c r="D125" s="5"/>
     </row>
-    <row r="126" customHeight="1" spans="4:4">
+    <row r="126">
       <c r="D126" s="5"/>
     </row>
-    <row r="127" customHeight="1" spans="4:4">
+    <row r="127">
       <c r="D127" s="5"/>
     </row>
-    <row r="128" customHeight="1" spans="4:4">
+    <row r="128">
       <c r="D128" s="5"/>
     </row>
-    <row r="129" customHeight="1" spans="4:4">
+    <row r="129">
       <c r="D129" s="5"/>
     </row>
-    <row r="130" customHeight="1" spans="4:4">
+    <row r="130">
       <c r="D130" s="5"/>
     </row>
-    <row r="131" customHeight="1" spans="4:4">
+    <row r="131">
       <c r="D131" s="5"/>
     </row>
-    <row r="132" customHeight="1" spans="4:4">
+    <row r="132">
       <c r="D132" s="5"/>
     </row>
-    <row r="133" customHeight="1" spans="4:4">
+    <row r="133">
       <c r="D133" s="5"/>
     </row>
-    <row r="134" customHeight="1" spans="4:4">
+    <row r="134">
       <c r="D134" s="5"/>
     </row>
-    <row r="135" customHeight="1" spans="4:4">
+    <row r="135">
       <c r="D135" s="5"/>
     </row>
-    <row r="136" customHeight="1" spans="4:4">
+    <row r="136">
       <c r="D136" s="5"/>
     </row>
-    <row r="137" customHeight="1" spans="4:4">
+    <row r="137">
       <c r="D137" s="5"/>
     </row>
-    <row r="138" customHeight="1" spans="4:4">
+    <row r="138">
       <c r="D138" s="5"/>
     </row>
-    <row r="139" customHeight="1" spans="4:4">
+    <row r="139">
       <c r="D139" s="5"/>
     </row>
-    <row r="140" customHeight="1" spans="4:4">
+    <row r="140">
       <c r="D140" s="5"/>
     </row>
-    <row r="141" customHeight="1" spans="4:4">
+    <row r="141">
       <c r="D141" s="5"/>
     </row>
-    <row r="142" customHeight="1" spans="4:4">
+    <row r="142">
       <c r="D142" s="5"/>
     </row>
-    <row r="143" customHeight="1" spans="4:4">
+    <row r="143">
       <c r="D143" s="5"/>
     </row>
-    <row r="144" customHeight="1" spans="4:4">
+    <row r="144">
       <c r="D144" s="5"/>
     </row>
-    <row r="145" customHeight="1" spans="4:4">
+    <row r="145">
       <c r="D145" s="5"/>
     </row>
-    <row r="146" customHeight="1" spans="4:4">
+    <row r="146">
       <c r="D146" s="5"/>
     </row>
-    <row r="147" customHeight="1" spans="4:4">
+    <row r="147">
       <c r="D147" s="5"/>
     </row>
-    <row r="148" customHeight="1" spans="4:4">
+    <row r="148">
       <c r="D148" s="5"/>
     </row>
-    <row r="149" customHeight="1" spans="4:4">
+    <row r="149">
       <c r="D149" s="5"/>
     </row>
-    <row r="150" customHeight="1" spans="4:4">
+    <row r="150">
       <c r="D150" s="5"/>
     </row>
-    <row r="151" customHeight="1" spans="4:4">
+    <row r="151">
       <c r="D151" s="5"/>
     </row>
-    <row r="152" customHeight="1" spans="4:4">
+    <row r="152">
       <c r="D152" s="5"/>
     </row>
-    <row r="153" customHeight="1" spans="4:4">
+    <row r="153">
       <c r="D153" s="5"/>
     </row>
-    <row r="154" customHeight="1" spans="4:4">
+    <row r="154">
       <c r="D154" s="5"/>
     </row>
-    <row r="155" customHeight="1" spans="4:4">
+    <row r="155">
       <c r="D155" s="5"/>
     </row>
-    <row r="156" customHeight="1" spans="4:4">
+    <row r="156">
       <c r="D156" s="5"/>
     </row>
-    <row r="157" customHeight="1" spans="4:4">
+    <row r="157">
       <c r="D157" s="5"/>
     </row>
-    <row r="158" customHeight="1" spans="4:4">
+    <row r="158">
       <c r="D158" s="5"/>
     </row>
-    <row r="159" customHeight="1" spans="4:4">
+    <row r="159">
       <c r="D159" s="5"/>
     </row>
-    <row r="160" customHeight="1" spans="4:4">
+    <row r="160">
       <c r="D160" s="5"/>
     </row>
-    <row r="161" customHeight="1" spans="4:4">
+    <row r="161">
       <c r="D161" s="5"/>
     </row>
-    <row r="162" customHeight="1" spans="4:4">
+    <row r="162">
       <c r="D162" s="5"/>
     </row>
-    <row r="163" customHeight="1" spans="4:4">
+    <row r="163">
       <c r="D163" s="5"/>
     </row>
-    <row r="164" customHeight="1" spans="4:4">
+    <row r="164">
       <c r="D164" s="5"/>
     </row>
-    <row r="165" customHeight="1" spans="4:4">
+    <row r="165">
       <c r="D165" s="5"/>
     </row>
-    <row r="166" customHeight="1" spans="4:4">
+    <row r="166">
       <c r="D166" s="5"/>
     </row>
-    <row r="167" customHeight="1" spans="4:4">
+    <row r="167">
       <c r="D167" s="5"/>
     </row>
-    <row r="168" customHeight="1" spans="4:4">
+    <row r="168">
       <c r="D168" s="5"/>
     </row>
-    <row r="169" customHeight="1" spans="4:4">
+    <row r="169">
       <c r="D169" s="5"/>
     </row>
-    <row r="170" customHeight="1" spans="4:4">
+    <row r="170">
       <c r="D170" s="5"/>
     </row>
-    <row r="171" customHeight="1" spans="4:4">
+    <row r="171">
       <c r="D171" s="5"/>
     </row>
-    <row r="172" customHeight="1" spans="4:4">
+    <row r="172">
       <c r="D172" s="5"/>
     </row>
-    <row r="173" customHeight="1" spans="4:4">
+    <row r="173">
       <c r="D173" s="5"/>
     </row>
-    <row r="174" customHeight="1" spans="4:4">
+    <row r="174">
       <c r="D174" s="5"/>
     </row>
-    <row r="175" customHeight="1" spans="4:4">
+    <row r="175">
       <c r="D175" s="5"/>
     </row>
-    <row r="176" customHeight="1" spans="4:4">
+    <row r="176">
       <c r="D176" s="5"/>
     </row>
-    <row r="177" customHeight="1" spans="4:4">
+    <row r="177">
       <c r="D177" s="5"/>
     </row>
-    <row r="178" customHeight="1" spans="4:4">
+    <row r="178">
       <c r="D178" s="5"/>
     </row>
-    <row r="179" customHeight="1" spans="4:4">
+    <row r="179">
       <c r="D179" s="5"/>
     </row>
-    <row r="180" customHeight="1" spans="4:4">
+    <row r="180">
       <c r="D180" s="5"/>
     </row>
-    <row r="181" customHeight="1" spans="4:4">
+    <row r="181">
       <c r="D181" s="5"/>
     </row>
-    <row r="182" customHeight="1" spans="4:4">
+    <row r="182">
       <c r="D182" s="5"/>
     </row>
-    <row r="183" customHeight="1" spans="4:4">
+    <row r="183">
       <c r="D183" s="5"/>
     </row>
-    <row r="184" customHeight="1" spans="4:4">
+    <row r="184">
       <c r="D184" s="5"/>
     </row>
-    <row r="185" customHeight="1" spans="4:4">
+    <row r="185">
       <c r="D185" s="5"/>
     </row>
-    <row r="186" customHeight="1" spans="4:4">
+    <row r="186">
       <c r="D186" s="5"/>
     </row>
-    <row r="187" customHeight="1" spans="4:4">
+    <row r="187">
       <c r="D187" s="5"/>
     </row>
-    <row r="188" customHeight="1" spans="4:4">
+    <row r="188">
       <c r="D188" s="5"/>
     </row>
-    <row r="189" customHeight="1" spans="4:4">
+    <row r="189">
       <c r="D189" s="5"/>
     </row>
-    <row r="190" customHeight="1" spans="4:4">
+    <row r="190">
       <c r="D190" s="5"/>
     </row>
-    <row r="191" customHeight="1" spans="4:4">
+    <row r="191">
       <c r="D191" s="5"/>
     </row>
-    <row r="192" customHeight="1" spans="4:4">
+    <row r="192">
       <c r="D192" s="5"/>
     </row>
-    <row r="193" customHeight="1" spans="4:4">
+    <row r="193">
       <c r="D193" s="5"/>
     </row>
-    <row r="194" customHeight="1" spans="4:4">
+    <row r="194">
       <c r="D194" s="5"/>
     </row>
-    <row r="195" customHeight="1" spans="4:4">
+    <row r="195">
       <c r="D195" s="5"/>
     </row>
-    <row r="196" customHeight="1" spans="4:4">
+    <row r="196">
       <c r="D196" s="5"/>
     </row>
-    <row r="197" customHeight="1" spans="4:4">
+    <row r="197">
       <c r="D197" s="5"/>
     </row>
-    <row r="198" customHeight="1" spans="4:4">
+    <row r="198">
       <c r="D198" s="5"/>
     </row>
-    <row r="199" customHeight="1" spans="4:4">
+    <row r="199">
       <c r="D199" s="5"/>
     </row>
-    <row r="200" customHeight="1" spans="4:4">
+    <row r="200">
       <c r="D200" s="5"/>
     </row>
-    <row r="201" customHeight="1" spans="4:4">
+    <row r="201">
       <c r="D201" s="5"/>
     </row>
-    <row r="202" customHeight="1" spans="4:4">
+    <row r="202">
       <c r="D202" s="5"/>
     </row>
-    <row r="203" customHeight="1" spans="4:4">
+    <row r="203">
       <c r="D203" s="5"/>
     </row>
-    <row r="204" customHeight="1" spans="4:4">
+    <row r="204">
       <c r="D204" s="5"/>
     </row>
-    <row r="205" customHeight="1" spans="4:4">
+    <row r="205">
       <c r="D205" s="5"/>
     </row>
-    <row r="206" customHeight="1" spans="4:4">
+    <row r="206">
       <c r="D206" s="5"/>
     </row>
-    <row r="207" customHeight="1" spans="4:4">
+    <row r="207">
       <c r="D207" s="5"/>
     </row>
-    <row r="208" customHeight="1" spans="4:4">
+    <row r="208">
       <c r="D208" s="5"/>
     </row>
-    <row r="209" customHeight="1" spans="4:4">
+    <row r="209">
       <c r="D209" s="5"/>
     </row>
-    <row r="210" customHeight="1" spans="4:4">
+    <row r="210">
       <c r="D210" s="5"/>
     </row>
-    <row r="211" customHeight="1" spans="4:4">
+    <row r="211">
       <c r="D211" s="5"/>
     </row>
-    <row r="212" customHeight="1" spans="4:4">
+    <row r="212">
       <c r="D212" s="5"/>
     </row>
-    <row r="213" customHeight="1" spans="4:4">
+    <row r="213">
       <c r="D213" s="5"/>
     </row>
-    <row r="214" customHeight="1" spans="4:4">
+    <row r="214">
       <c r="D214" s="5"/>
     </row>
-    <row r="215" customHeight="1" spans="4:4">
+    <row r="215">
       <c r="D215" s="5"/>
     </row>
-    <row r="216" customHeight="1" spans="4:4">
+    <row r="216">
       <c r="D216" s="5"/>
     </row>
-    <row r="217" customHeight="1" spans="4:4">
+    <row r="217">
       <c r="D217" s="5"/>
     </row>
-    <row r="218" customHeight="1" spans="4:4">
+    <row r="218">
       <c r="D218" s="5"/>
     </row>
-    <row r="219" customHeight="1" spans="4:4">
+    <row r="219">
       <c r="D219" s="5"/>
     </row>
-    <row r="220" customHeight="1" spans="4:4">
+    <row r="220">
       <c r="D220" s="5"/>
     </row>
-    <row r="221" customHeight="1" spans="4:4">
+    <row r="221">
       <c r="D221" s="5"/>
     </row>
-    <row r="222" customHeight="1" spans="4:4">
+    <row r="222">
       <c r="D222" s="5"/>
     </row>
-    <row r="223" customHeight="1" spans="4:4">
+    <row r="223">
       <c r="D223" s="5"/>
     </row>
-    <row r="224" customHeight="1" spans="4:4">
+    <row r="224">
       <c r="D224" s="5"/>
     </row>
-    <row r="225" customHeight="1" spans="4:4">
+    <row r="225">
       <c r="D225" s="5"/>
     </row>
-    <row r="226" customHeight="1" spans="4:4">
+    <row r="226">
       <c r="D226" s="5"/>
     </row>
-    <row r="227" customHeight="1" spans="4:4">
+    <row r="227">
       <c r="D227" s="5"/>
     </row>
-    <row r="228" customHeight="1" spans="4:4">
+    <row r="228">
       <c r="D228" s="5"/>
     </row>
-    <row r="229" customHeight="1" spans="4:4">
+    <row r="229">
       <c r="D229" s="5"/>
     </row>
-    <row r="230" customHeight="1" spans="4:4">
+    <row r="230">
       <c r="D230" s="5"/>
     </row>
-    <row r="231" customHeight="1" spans="4:4">
+    <row r="231">
       <c r="D231" s="5"/>
     </row>
-    <row r="232" customHeight="1" spans="4:4">
+    <row r="232">
       <c r="D232" s="5"/>
     </row>
-    <row r="233" customHeight="1" spans="4:4">
+    <row r="233">
       <c r="D233" s="5"/>
     </row>
-    <row r="234" customHeight="1" spans="4:4">
+    <row r="234">
       <c r="D234" s="5"/>
     </row>
-    <row r="235" customHeight="1" spans="4:4">
+    <row r="235">
       <c r="D235" s="5"/>
     </row>
-    <row r="236" customHeight="1" spans="4:4">
+    <row r="236">
       <c r="D236" s="5"/>
     </row>
-    <row r="237" customHeight="1" spans="4:4">
+    <row r="237">
       <c r="D237" s="5"/>
     </row>
-    <row r="238" customHeight="1" spans="4:4">
+    <row r="238">
       <c r="D238" s="5"/>
     </row>
-    <row r="239" customHeight="1" spans="4:4">
+    <row r="239">
       <c r="D239" s="5"/>
     </row>
-    <row r="240" customHeight="1" spans="4:4">
+    <row r="240">
       <c r="D240" s="5"/>
     </row>
-    <row r="241" customHeight="1" spans="4:4">
+    <row r="241">
       <c r="D241" s="5"/>
     </row>
-    <row r="242" customHeight="1" spans="4:4">
+    <row r="242">
       <c r="D242" s="5"/>
     </row>
-    <row r="243" customHeight="1" spans="4:4">
+    <row r="243">
       <c r="D243" s="5"/>
     </row>
-    <row r="244" customHeight="1" spans="4:4">
+    <row r="244">
       <c r="D244" s="5"/>
     </row>
-    <row r="245" customHeight="1" spans="4:4">
+    <row r="245">
       <c r="D245" s="5"/>
     </row>
-    <row r="246" customHeight="1" spans="4:4">
+    <row r="246">
       <c r="D246" s="5"/>
     </row>
-    <row r="247" customHeight="1" spans="4:4">
+    <row r="247">
       <c r="D247" s="5"/>
     </row>
-    <row r="248" customHeight="1" spans="4:4">
+    <row r="248">
       <c r="D248" s="5"/>
     </row>
-    <row r="249" customHeight="1" spans="4:4">
+    <row r="249">
       <c r="D249" s="5"/>
     </row>
-    <row r="250" customHeight="1" spans="4:4">
+    <row r="250">
       <c r="D250" s="5"/>
     </row>
-    <row r="251" customHeight="1" spans="4:4">
+    <row r="251">
       <c r="D251" s="5"/>
     </row>
-    <row r="252" customHeight="1" spans="4:4">
+    <row r="252">
       <c r="D252" s="5"/>
     </row>
-    <row r="253" customHeight="1" spans="4:4">
+    <row r="253">
       <c r="D253" s="5"/>
     </row>
-    <row r="254" customHeight="1" spans="4:4">
+    <row r="254">
       <c r="D254" s="5"/>
     </row>
-    <row r="255" customHeight="1" spans="4:4">
+    <row r="255">
       <c r="D255" s="5"/>
     </row>
-    <row r="256" customHeight="1" spans="4:4">
+    <row r="256">
       <c r="D256" s="5"/>
     </row>
-    <row r="257" customHeight="1" spans="4:4">
+    <row r="257">
       <c r="D257" s="5"/>
     </row>
-    <row r="258" customHeight="1" spans="4:4">
+    <row r="258">
       <c r="D258" s="5"/>
     </row>
-    <row r="259" customHeight="1" spans="4:4">
+    <row r="259">
       <c r="D259" s="5"/>
     </row>
-    <row r="260" customHeight="1" spans="4:4">
+    <row r="260">
       <c r="D260" s="5"/>
     </row>
-    <row r="261" customHeight="1" spans="4:4">
+    <row r="261">
       <c r="D261" s="5"/>
     </row>
-    <row r="262" customHeight="1" spans="4:4">
+    <row r="262">
       <c r="D262" s="5"/>
     </row>
-    <row r="263" customHeight="1" spans="4:4">
+    <row r="263">
       <c r="D263" s="5"/>
     </row>
-    <row r="264" customHeight="1" spans="4:4">
+    <row r="264">
       <c r="D264" s="5"/>
     </row>
-    <row r="265" customHeight="1" spans="4:4">
+    <row r="265">
       <c r="D265" s="5"/>
     </row>
-    <row r="266" customHeight="1" spans="4:4">
+    <row r="266">
       <c r="D266" s="5"/>
     </row>
-    <row r="267" customHeight="1" spans="4:4">
+    <row r="267">
       <c r="D267" s="5"/>
     </row>
-    <row r="268" customHeight="1" spans="4:4">
+    <row r="268">
       <c r="D268" s="5"/>
     </row>
-    <row r="269" customHeight="1" spans="4:4">
+    <row r="269">
       <c r="D269" s="5"/>
     </row>
-    <row r="270" customHeight="1" spans="4:4">
+    <row r="270">
       <c r="D270" s="5"/>
     </row>
-    <row r="271" customHeight="1" spans="4:4">
+    <row r="271">
       <c r="D271" s="5"/>
     </row>
-    <row r="272" customHeight="1" spans="4:4">
+    <row r="272">
       <c r="D272" s="5"/>
     </row>
-    <row r="273" customHeight="1" spans="4:4">
+    <row r="273">
       <c r="D273" s="5"/>
     </row>
-    <row r="274" customHeight="1" spans="4:4">
+    <row r="274">
       <c r="D274" s="5"/>
     </row>
-    <row r="275" customHeight="1" spans="4:4">
+    <row r="275">
       <c r="D275" s="5"/>
     </row>
-    <row r="276" customHeight="1" spans="4:4">
+    <row r="276">
       <c r="D276" s="5"/>
     </row>
-    <row r="277" customHeight="1" spans="4:4">
+    <row r="277">
       <c r="D277" s="5"/>
     </row>
-    <row r="278" customHeight="1" spans="4:4">
+    <row r="278">
       <c r="D278" s="5"/>
     </row>
-    <row r="279" customHeight="1" spans="4:4">
+    <row r="279">
       <c r="D279" s="5"/>
     </row>
-    <row r="280" customHeight="1" spans="4:4">
+    <row r="280">
       <c r="D280" s="5"/>
     </row>
-    <row r="281" customHeight="1" spans="4:4">
+    <row r="281">
       <c r="D281" s="5"/>
     </row>
-    <row r="282" customHeight="1" spans="4:4">
+    <row r="282">
       <c r="D282" s="5"/>
     </row>
-    <row r="283" customHeight="1" spans="4:4">
+    <row r="283">
       <c r="D283" s="5"/>
     </row>
-    <row r="284" customHeight="1" spans="4:4">
+    <row r="284">
       <c r="D284" s="5"/>
     </row>
-    <row r="285" customHeight="1" spans="4:4">
+    <row r="285">
       <c r="D285" s="5"/>
     </row>
-    <row r="286" customHeight="1" spans="4:4">
+    <row r="286">
       <c r="D286" s="5"/>
     </row>
-    <row r="287" customHeight="1" spans="4:4">
+    <row r="287">
       <c r="D287" s="5"/>
     </row>
-    <row r="288" customHeight="1" spans="4:4">
+    <row r="288">
       <c r="D288" s="5"/>
     </row>
-    <row r="289" customHeight="1" spans="4:4">
+    <row r="289">
       <c r="D289" s="5"/>
     </row>
-    <row r="290" customHeight="1" spans="4:4">
+    <row r="290">
       <c r="D290" s="5"/>
     </row>
-    <row r="291" customHeight="1" spans="4:4">
+    <row r="291">
       <c r="D291" s="5"/>
     </row>
-    <row r="292" customHeight="1" spans="4:4">
+    <row r="292">
       <c r="D292" s="5"/>
     </row>
-    <row r="293" customHeight="1" spans="4:4">
+    <row r="293">
       <c r="D293" s="5"/>
     </row>
-    <row r="294" customHeight="1" spans="4:4">
+    <row r="294">
       <c r="D294" s="5"/>
     </row>
-    <row r="295" customHeight="1" spans="4:4">
+    <row r="295">
       <c r="D295" s="5"/>
     </row>
-    <row r="296" customHeight="1" spans="4:4">
+    <row r="296">
       <c r="D296" s="5"/>
     </row>
-    <row r="297" customHeight="1" spans="4:4">
+    <row r="297">
       <c r="D297" s="5"/>
     </row>
-    <row r="298" customHeight="1" spans="4:4">
+    <row r="298">
       <c r="D298" s="5"/>
     </row>
-    <row r="299" customHeight="1" spans="4:4">
+    <row r="299">
       <c r="D299" s="5"/>
     </row>
-    <row r="300" customHeight="1" spans="4:4">
+    <row r="300">
       <c r="D300" s="5"/>
     </row>
-    <row r="301" customHeight="1" spans="4:4">
+    <row r="301">
       <c r="D301" s="5"/>
     </row>
-    <row r="302" customHeight="1" spans="4:4">
+    <row r="302">
       <c r="D302" s="5"/>
     </row>
-    <row r="303" customHeight="1" spans="4:4">
+    <row r="303">
       <c r="D303" s="5"/>
     </row>
-    <row r="304" customHeight="1" spans="4:4">
+    <row r="304">
       <c r="D304" s="5"/>
     </row>
-    <row r="305" customHeight="1" spans="4:4">
+    <row r="305">
       <c r="D305" s="5"/>
     </row>
-    <row r="306" customHeight="1" spans="4:4">
+    <row r="306">
       <c r="D306" s="5"/>
     </row>
-    <row r="307" customHeight="1" spans="4:4">
+    <row r="307">
       <c r="D307" s="5"/>
     </row>
-    <row r="308" customHeight="1" spans="4:4">
+    <row r="308">
       <c r="D308" s="5"/>
     </row>
-    <row r="309" customHeight="1" spans="4:4">
+    <row r="309">
       <c r="D309" s="5"/>
     </row>
-    <row r="310" customHeight="1" spans="4:4">
+    <row r="310">
       <c r="D310" s="5"/>
     </row>
-    <row r="311" customHeight="1" spans="4:4">
+    <row r="311">
       <c r="D311" s="5"/>
     </row>
-    <row r="312" customHeight="1" spans="4:4">
+    <row r="312">
       <c r="D312" s="5"/>
     </row>
-    <row r="313" customHeight="1" spans="4:4">
+    <row r="313">
       <c r="D313" s="5"/>
     </row>
-    <row r="314" customHeight="1" spans="4:4">
+    <row r="314">
       <c r="D314" s="5"/>
     </row>
-    <row r="315" customHeight="1" spans="4:4">
+    <row r="315">
       <c r="D315" s="5"/>
     </row>
-    <row r="316" customHeight="1" spans="4:4">
+    <row r="316">
       <c r="D316" s="5"/>
     </row>
-    <row r="317" customHeight="1" spans="4:4">
+    <row r="317">
       <c r="D317" s="5"/>
     </row>
-    <row r="318" customHeight="1" spans="4:4">
+    <row r="318">
       <c r="D318" s="5"/>
     </row>
-    <row r="319" customHeight="1" spans="4:4">
+    <row r="319">
       <c r="D319" s="5"/>
     </row>
-    <row r="320" customHeight="1" spans="4:4">
+    <row r="320">
       <c r="D320" s="5"/>
     </row>
-    <row r="321" customHeight="1" spans="4:4">
+    <row r="321">
       <c r="D321" s="5"/>
     </row>
-    <row r="322" customHeight="1" spans="4:4">
+    <row r="322">
       <c r="D322" s="5"/>
     </row>
-    <row r="323" customHeight="1" spans="4:4">
+    <row r="323">
       <c r="D323" s="5"/>
     </row>
-    <row r="324" customHeight="1" spans="4:4">
+    <row r="324">
       <c r="D324" s="5"/>
     </row>
-    <row r="325" customHeight="1" spans="4:4">
+    <row r="325">
       <c r="D325" s="5"/>
     </row>
-    <row r="326" customHeight="1" spans="4:4">
+    <row r="326">
       <c r="D326" s="5"/>
     </row>
-    <row r="327" customHeight="1" spans="4:4">
+    <row r="327">
       <c r="D327" s="5"/>
     </row>
-    <row r="328" customHeight="1" spans="4:4">
+    <row r="328">
       <c r="D328" s="5"/>
     </row>
-    <row r="329" customHeight="1" spans="4:4">
+    <row r="329">
       <c r="D329" s="5"/>
     </row>
-    <row r="330" customHeight="1" spans="4:4">
+    <row r="330">
       <c r="D330" s="5"/>
     </row>
-    <row r="331" customHeight="1" spans="4:4">
+    <row r="331">
       <c r="D331" s="5"/>
     </row>
-    <row r="332" customHeight="1" spans="4:4">
+    <row r="332">
       <c r="D332" s="5"/>
     </row>
-    <row r="333" customHeight="1" spans="4:4">
+    <row r="333">
       <c r="D333" s="5"/>
     </row>
-    <row r="334" customHeight="1" spans="4:4">
+    <row r="334">
       <c r="D334" s="5"/>
     </row>
-    <row r="335" customHeight="1" spans="4:4">
+    <row r="335">
       <c r="D335" s="5"/>
     </row>
-    <row r="336" customHeight="1" spans="4:4">
+    <row r="336">
       <c r="D336" s="5"/>
     </row>
-    <row r="337" customHeight="1" spans="4:4">
+    <row r="337">
       <c r="D337" s="5"/>
     </row>
-    <row r="338" customHeight="1" spans="4:4">
+    <row r="338">
       <c r="D338" s="5"/>
     </row>
-    <row r="339" customHeight="1" spans="4:4">
+    <row r="339">
       <c r="D339" s="5"/>
     </row>
-    <row r="340" customHeight="1" spans="4:4">
+    <row r="340">
       <c r="D340" s="5"/>
     </row>
-    <row r="341" customHeight="1" spans="4:4">
+    <row r="341">
       <c r="D341" s="5"/>
     </row>
-    <row r="342" customHeight="1" spans="4:4">
+    <row r="342">
       <c r="D342" s="5"/>
     </row>
-    <row r="343" customHeight="1" spans="4:4">
+    <row r="343">
       <c r="D343" s="5"/>
     </row>
-    <row r="344" customHeight="1" spans="4:4">
+    <row r="344">
       <c r="D344" s="5"/>
     </row>
-    <row r="345" customHeight="1" spans="4:4">
+    <row r="345">
       <c r="D345" s="5"/>
     </row>
-    <row r="346" customHeight="1" spans="4:4">
+    <row r="346">
       <c r="D346" s="5"/>
     </row>
-    <row r="347" customHeight="1" spans="4:4">
+    <row r="347">
       <c r="D347" s="5"/>
     </row>
-    <row r="348" customHeight="1" spans="4:4">
+    <row r="348">
       <c r="D348" s="5"/>
     </row>
-    <row r="349" customHeight="1" spans="4:4">
+    <row r="349">
       <c r="D349" s="5"/>
     </row>
-    <row r="350" customHeight="1" spans="4:4">
+    <row r="350">
       <c r="D350" s="5"/>
     </row>
-    <row r="351" customHeight="1" spans="4:4">
+    <row r="351">
       <c r="D351" s="5"/>
     </row>
-    <row r="352" customHeight="1" spans="4:4">
+    <row r="352">
       <c r="D352" s="5"/>
     </row>
-    <row r="353" customHeight="1" spans="4:4">
+    <row r="353">
       <c r="D353" s="5"/>
     </row>
-    <row r="354" customHeight="1" spans="4:4">
+    <row r="354">
       <c r="D354" s="5"/>
     </row>
-    <row r="355" customHeight="1" spans="4:4">
+    <row r="355">
       <c r="D355" s="5"/>
     </row>
-    <row r="356" customHeight="1" spans="4:4">
+    <row r="356">
       <c r="D356" s="5"/>
     </row>
-    <row r="357" customHeight="1" spans="4:4">
+    <row r="357">
       <c r="D357" s="5"/>
     </row>
-    <row r="358" customHeight="1" spans="4:4">
+    <row r="358">
       <c r="D358" s="5"/>
     </row>
-    <row r="359" customHeight="1" spans="4:4">
+    <row r="359">
       <c r="D359" s="5"/>
     </row>
-    <row r="360" customHeight="1" spans="4:4">
+    <row r="360">
       <c r="D360" s="5"/>
     </row>
-    <row r="361" customHeight="1" spans="4:4">
+    <row r="361">
       <c r="D361" s="5"/>
     </row>
-    <row r="362" customHeight="1" spans="4:4">
+    <row r="362">
       <c r="D362" s="5"/>
     </row>
-    <row r="363" customHeight="1" spans="4:4">
+    <row r="363">
       <c r="D363" s="5"/>
     </row>
-    <row r="364" customHeight="1" spans="4:4">
+    <row r="364">
       <c r="D364" s="5"/>
     </row>
-    <row r="365" customHeight="1" spans="4:4">
+    <row r="365">
       <c r="D365" s="5"/>
     </row>
-    <row r="366" customHeight="1" spans="4:4">
+    <row r="366">
       <c r="D366" s="5"/>
     </row>
-    <row r="367" customHeight="1" spans="4:4">
+    <row r="367">
       <c r="D367" s="5"/>
     </row>
-    <row r="368" customHeight="1" spans="4:4">
+    <row r="368">
       <c r="D368" s="5"/>
     </row>
-    <row r="369" customHeight="1" spans="4:4">
+    <row r="369">
       <c r="D369" s="5"/>
     </row>
-    <row r="370" customHeight="1" spans="4:4">
+    <row r="370">
       <c r="D370" s="5"/>
     </row>
-    <row r="371" customHeight="1" spans="4:4">
+    <row r="371">
       <c r="D371" s="5"/>
     </row>
-    <row r="372" customHeight="1" spans="4:4">
+    <row r="372">
       <c r="D372" s="5"/>
     </row>
-    <row r="373" customHeight="1" spans="4:4">
+    <row r="373">
       <c r="D373" s="5"/>
     </row>
-    <row r="374" customHeight="1" spans="4:4">
+    <row r="374">
       <c r="D374" s="5"/>
     </row>
-    <row r="375" customHeight="1" spans="4:4">
+    <row r="375">
       <c r="D375" s="5"/>
     </row>
-    <row r="376" customHeight="1" spans="4:4">
+    <row r="376">
       <c r="D376" s="5"/>
     </row>
-    <row r="377" customHeight="1" spans="4:4">
+    <row r="377">
       <c r="D377" s="5"/>
     </row>
-    <row r="378" customHeight="1" spans="4:4">
+    <row r="378">
       <c r="D378" s="5"/>
     </row>
-    <row r="379" customHeight="1" spans="4:4">
+    <row r="379">
       <c r="D379" s="5"/>
     </row>
-    <row r="380" customHeight="1" spans="4:4">
+    <row r="380">
       <c r="D380" s="5"/>
     </row>
-    <row r="381" customHeight="1" spans="4:4">
+    <row r="381">
       <c r="D381" s="5"/>
     </row>
-    <row r="382" customHeight="1" spans="4:4">
+    <row r="382">
       <c r="D382" s="5"/>
     </row>
-    <row r="383" customHeight="1" spans="4:4">
+    <row r="383">
       <c r="D383" s="5"/>
     </row>
-    <row r="384" customHeight="1" spans="4:4">
+    <row r="384">
       <c r="D384" s="5"/>
     </row>
-    <row r="385" customHeight="1" spans="4:4">
+    <row r="385">
       <c r="D385" s="5"/>
     </row>
-    <row r="386" customHeight="1" spans="4:4">
+    <row r="386">
       <c r="D386" s="5"/>
     </row>
-    <row r="387" customHeight="1" spans="4:4">
+    <row r="387">
       <c r="D387" s="5"/>
     </row>
-    <row r="388" customHeight="1" spans="4:4">
+    <row r="388">
       <c r="D388" s="5"/>
     </row>
-    <row r="389" customHeight="1" spans="4:4">
+    <row r="389">
       <c r="D389" s="5"/>
     </row>
-    <row r="390" customHeight="1" spans="4:4">
+    <row r="390">
       <c r="D390" s="5"/>
     </row>
-    <row r="391" customHeight="1" spans="4:4">
+    <row r="391">
       <c r="D391" s="5"/>
     </row>
-    <row r="392" customHeight="1" spans="4:4">
+    <row r="392">
       <c r="D392" s="5"/>
     </row>
-    <row r="393" customHeight="1" spans="4:4">
+    <row r="393">
       <c r="D393" s="5"/>
     </row>
-    <row r="394" customHeight="1" spans="4:4">
+    <row r="394">
       <c r="D394" s="5"/>
     </row>
-    <row r="395" customHeight="1" spans="4:4">
+    <row r="395">
       <c r="D395" s="5"/>
     </row>
-    <row r="396" customHeight="1" spans="4:4">
+    <row r="396">
       <c r="D396" s="5"/>
     </row>
-    <row r="397" customHeight="1" spans="4:4">
+    <row r="397">
       <c r="D397" s="5"/>
     </row>
-    <row r="398" customHeight="1" spans="4:4">
+    <row r="398">
       <c r="D398" s="5"/>
     </row>
-    <row r="399" customHeight="1" spans="4:4">
+    <row r="399">
       <c r="D399" s="5"/>
     </row>
-    <row r="400" customHeight="1" spans="4:4">
+    <row r="400">
       <c r="D400" s="5"/>
     </row>
-    <row r="401" customHeight="1" spans="4:4">
+    <row r="401">
       <c r="D401" s="5"/>
     </row>
-    <row r="402" customHeight="1" spans="4:4">
+    <row r="402">
       <c r="D402" s="5"/>
     </row>
-    <row r="403" customHeight="1" spans="4:4">
+    <row r="403">
       <c r="D403" s="5"/>
     </row>
-    <row r="404" customHeight="1" spans="4:4">
+    <row r="404">
       <c r="D404" s="5"/>
     </row>
-    <row r="405" customHeight="1" spans="4:4">
+    <row r="405">
       <c r="D405" s="5"/>
     </row>
-    <row r="406" customHeight="1" spans="4:4">
+    <row r="406">
       <c r="D406" s="5"/>
     </row>
-    <row r="407" customHeight="1" spans="4:4">
+    <row r="407">
       <c r="D407" s="5"/>
     </row>
-    <row r="408" customHeight="1" spans="4:4">
+    <row r="408">
       <c r="D408" s="5"/>
     </row>
-    <row r="409" customHeight="1" spans="4:4">
+    <row r="409">
       <c r="D409" s="5"/>
     </row>
-    <row r="410" customHeight="1" spans="4:4">
+    <row r="410">
       <c r="D410" s="5"/>
     </row>
-    <row r="411" customHeight="1" spans="4:4">
+    <row r="411">
       <c r="D411" s="5"/>
     </row>
-    <row r="412" customHeight="1" spans="4:4">
+    <row r="412">
       <c r="D412" s="5"/>
     </row>
-    <row r="413" customHeight="1" spans="4:4">
+    <row r="413">
       <c r="D413" s="5"/>
     </row>
-    <row r="414" customHeight="1" spans="4:4">
+    <row r="414">
       <c r="D414" s="5"/>
     </row>
-    <row r="415" customHeight="1" spans="4:4">
+    <row r="415">
       <c r="D415" s="5"/>
     </row>
-    <row r="416" customHeight="1" spans="4:4">
+    <row r="416">
       <c r="D416" s="5"/>
     </row>
-    <row r="417" customHeight="1" spans="4:4">
+    <row r="417">
       <c r="D417" s="5"/>
     </row>
-    <row r="418" customHeight="1" spans="4:4">
+    <row r="418">
       <c r="D418" s="5"/>
     </row>
-    <row r="419" customHeight="1" spans="4:4">
+    <row r="419">
       <c r="D419" s="5"/>
     </row>
-    <row r="420" customHeight="1" spans="4:4">
+    <row r="420">
       <c r="D420" s="5"/>
     </row>
-    <row r="421" customHeight="1" spans="4:4">
+    <row r="421">
       <c r="D421" s="5"/>
     </row>
-    <row r="422" customHeight="1" spans="4:4">
+    <row r="422">
       <c r="D422" s="5"/>
     </row>
-    <row r="423" customHeight="1" spans="4:4">
+    <row r="423">
       <c r="D423" s="5"/>
     </row>
-    <row r="424" customHeight="1" spans="4:4">
+    <row r="424">
       <c r="D424" s="5"/>
     </row>
-    <row r="425" customHeight="1" spans="4:4">
+    <row r="425">
       <c r="D425" s="5"/>
     </row>
-    <row r="426" customHeight="1" spans="4:4">
+    <row r="426">
       <c r="D426" s="5"/>
     </row>
-    <row r="427" customHeight="1" spans="4:4">
+    <row r="427">
       <c r="D427" s="5"/>
     </row>
-    <row r="428" customHeight="1" spans="4:4">
+    <row r="428">
       <c r="D428" s="5"/>
     </row>
-    <row r="429" customHeight="1" spans="4:4">
+    <row r="429">
       <c r="D429" s="5"/>
     </row>
-    <row r="430" customHeight="1" spans="4:4">
+    <row r="430">
       <c r="D430" s="5"/>
     </row>
-    <row r="431" customHeight="1" spans="4:4">
+    <row r="431">
       <c r="D431" s="5"/>
     </row>
-    <row r="432" customHeight="1" spans="4:4">
+    <row r="432">
       <c r="D432" s="5"/>
     </row>
-    <row r="433" customHeight="1" spans="4:4">
+    <row r="433">
       <c r="D433" s="5"/>
     </row>
-    <row r="434" customHeight="1" spans="4:4">
+    <row r="434">
       <c r="D434" s="5"/>
     </row>
-    <row r="435" customHeight="1" spans="4:4">
+    <row r="435">
       <c r="D435" s="5"/>
     </row>
-    <row r="436" customHeight="1" spans="4:4">
+    <row r="436">
       <c r="D436" s="5"/>
     </row>
-    <row r="437" customHeight="1" spans="4:4">
+    <row r="437">
       <c r="D437" s="5"/>
     </row>
-    <row r="438" customHeight="1" spans="4:4">
+    <row r="438">
       <c r="D438" s="5"/>
     </row>
-    <row r="439" customHeight="1" spans="4:4">
+    <row r="439">
       <c r="D439" s="5"/>
     </row>
-    <row r="440" customHeight="1" spans="4:4">
+    <row r="440">
       <c r="D440" s="5"/>
     </row>
-    <row r="441" customHeight="1" spans="4:4">
+    <row r="441">
       <c r="D441" s="5"/>
     </row>
-    <row r="442" customHeight="1" spans="4:4">
+    <row r="442">
       <c r="D442" s="5"/>
     </row>
-    <row r="443" customHeight="1" spans="4:4">
+    <row r="443">
       <c r="D443" s="5"/>
     </row>
-    <row r="444" customHeight="1" spans="4:4">
+    <row r="444">
       <c r="D444" s="5"/>
     </row>
-    <row r="445" customHeight="1" spans="4:4">
+    <row r="445">
       <c r="D445" s="5"/>
     </row>
-    <row r="446" customHeight="1" spans="4:4">
+    <row r="446">
       <c r="D446" s="5"/>
     </row>
-    <row r="447" customHeight="1" spans="4:4">
+    <row r="447">
       <c r="D447" s="5"/>
     </row>
-    <row r="448" customHeight="1" spans="4:4">
+    <row r="448">
       <c r="D448" s="5"/>
     </row>
-    <row r="449" customHeight="1" spans="4:4">
+    <row r="449">
       <c r="D449" s="5"/>
     </row>
-    <row r="450" customHeight="1" spans="4:4">
+    <row r="450">
       <c r="D450" s="5"/>
     </row>
-    <row r="451" customHeight="1" spans="4:4">
+    <row r="451">
       <c r="D451" s="5"/>
     </row>
-    <row r="452" customHeight="1" spans="4:4">
+    <row r="452">
       <c r="D452" s="5"/>
     </row>
-    <row r="453" customHeight="1" spans="4:4">
+    <row r="453">
       <c r="D453" s="5"/>
     </row>
-    <row r="454" customHeight="1" spans="4:4">
+    <row r="454">
       <c r="D454" s="5"/>
     </row>
-    <row r="455" customHeight="1" spans="4:4">
+    <row r="455">
       <c r="D455" s="5"/>
     </row>
-    <row r="456" customHeight="1" spans="4:4">
+    <row r="456">
       <c r="D456" s="5"/>
     </row>
-    <row r="457" customHeight="1" spans="4:4">
+    <row r="457">
       <c r="D457" s="5"/>
     </row>
-    <row r="458" customHeight="1" spans="4:4">
+    <row r="458">
       <c r="D458" s="5"/>
     </row>
-    <row r="459" customHeight="1" spans="4:4">
+    <row r="459">
       <c r="D459" s="5"/>
     </row>
-    <row r="460" customHeight="1" spans="4:4">
+    <row r="460">
       <c r="D460" s="5"/>
     </row>
-    <row r="461" customHeight="1" spans="4:4">
+    <row r="461">
       <c r="D461" s="5"/>
     </row>
-    <row r="462" customHeight="1" spans="4:4">
+    <row r="462">
       <c r="D462" s="5"/>
     </row>
-    <row r="463" customHeight="1" spans="4:4">
+    <row r="463">
       <c r="D463" s="5"/>
     </row>
-    <row r="464" customHeight="1" spans="4:4">
+    <row r="464">
       <c r="D464" s="5"/>
     </row>
-    <row r="465" customHeight="1" spans="4:4">
+    <row r="465">
       <c r="D465" s="5"/>
     </row>
-    <row r="466" customHeight="1" spans="4:4">
+    <row r="466">
       <c r="D466" s="5"/>
     </row>
-    <row r="467" customHeight="1" spans="4:4">
+    <row r="467">
       <c r="D467" s="5"/>
     </row>
-    <row r="468" customHeight="1" spans="4:4">
+    <row r="468">
       <c r="D468" s="5"/>
     </row>
-    <row r="469" customHeight="1" spans="4:4">
+    <row r="469">
       <c r="D469" s="5"/>
     </row>
-    <row r="470" customHeight="1" spans="4:4">
+    <row r="470">
       <c r="D470" s="5"/>
     </row>
-    <row r="471" customHeight="1" spans="4:4">
+    <row r="471">
       <c r="D471" s="5"/>
     </row>
-    <row r="472" customHeight="1" spans="4:4">
+    <row r="472">
       <c r="D472" s="5"/>
     </row>
-    <row r="473" customHeight="1" spans="4:4">
+    <row r="473">
       <c r="D473" s="5"/>
     </row>
-    <row r="474" customHeight="1" spans="4:4">
+    <row r="474">
       <c r="D474" s="5"/>
     </row>
-    <row r="475" customHeight="1" spans="4:4">
+    <row r="475">
       <c r="D475" s="5"/>
     </row>
-    <row r="476" customHeight="1" spans="4:4">
+    <row r="476">
       <c r="D476" s="5"/>
     </row>
-    <row r="477" customHeight="1" spans="4:4">
+    <row r="477">
       <c r="D477" s="5"/>
     </row>
-    <row r="478" customHeight="1" spans="4:4">
+    <row r="478">
       <c r="D478" s="5"/>
     </row>
-    <row r="479" customHeight="1" spans="4:4">
+    <row r="479">
       <c r="D479" s="5"/>
     </row>
-    <row r="480" customHeight="1" spans="4:4">
+    <row r="480">
       <c r="D480" s="5"/>
     </row>
-    <row r="481" customHeight="1" spans="4:4">
+    <row r="481">
       <c r="D481" s="5"/>
     </row>
-    <row r="482" customHeight="1" spans="4:4">
+    <row r="482">
       <c r="D482" s="5"/>
     </row>
-    <row r="483" customHeight="1" spans="4:4">
+    <row r="483">
       <c r="D483" s="5"/>
     </row>
-    <row r="484" customHeight="1" spans="4:4">
+    <row r="484">
       <c r="D484" s="5"/>
     </row>
-    <row r="485" customHeight="1" spans="4:4">
+    <row r="485">
       <c r="D485" s="5"/>
     </row>
-    <row r="486" customHeight="1" spans="4:4">
+    <row r="486">
       <c r="D486" s="5"/>
     </row>
-    <row r="487" customHeight="1" spans="4:4">
+    <row r="487">
       <c r="D487" s="5"/>
     </row>
-    <row r="488" customHeight="1" spans="4:4">
+    <row r="488">
       <c r="D488" s="5"/>
     </row>
-    <row r="489" customHeight="1" spans="4:4">
+    <row r="489">
       <c r="D489" s="5"/>
     </row>
-    <row r="490" customHeight="1" spans="4:4">
+    <row r="490">
       <c r="D490" s="5"/>
     </row>
-    <row r="491" customHeight="1" spans="4:4">
+    <row r="491">
       <c r="D491" s="5"/>
     </row>
-    <row r="492" customHeight="1" spans="4:4">
+    <row r="492">
       <c r="D492" s="5"/>
     </row>
-    <row r="493" customHeight="1" spans="4:4">
+    <row r="493">
       <c r="D493" s="5"/>
     </row>
-    <row r="494" customHeight="1" spans="4:4">
+    <row r="494">
       <c r="D494" s="5"/>
     </row>
-    <row r="495" customHeight="1" spans="4:4">
+    <row r="495">
       <c r="D495" s="5"/>
     </row>
-    <row r="496" customHeight="1" spans="4:4">
+    <row r="496">
       <c r="D496" s="5"/>
     </row>
-    <row r="497" customHeight="1" spans="4:4">
+    <row r="497">
       <c r="D497" s="5"/>
     </row>
-    <row r="498" customHeight="1" spans="4:4">
+    <row r="498">
       <c r="D498" s="5"/>
     </row>
-    <row r="499" customHeight="1" spans="4:4">
+    <row r="499">
       <c r="D499" s="5"/>
     </row>
-    <row r="500" customHeight="1" spans="4:4">
+    <row r="500">
       <c r="D500" s="5"/>
     </row>
-    <row r="501" customHeight="1" spans="4:4">
+    <row r="501">
       <c r="D501" s="5"/>
     </row>
-    <row r="502" customHeight="1" spans="4:4">
+    <row r="502">
       <c r="D502" s="5"/>
     </row>
-    <row r="503" customHeight="1" spans="4:4">
+    <row r="503">
       <c r="D503" s="5"/>
     </row>
-    <row r="504" customHeight="1" spans="4:4">
+    <row r="504">
       <c r="D504" s="5"/>
     </row>
-    <row r="505" customHeight="1" spans="4:4">
+    <row r="505">
       <c r="D505" s="5"/>
     </row>
-    <row r="506" customHeight="1" spans="4:4">
+    <row r="506">
       <c r="D506" s="5"/>
     </row>
-    <row r="507" customHeight="1" spans="4:4">
+    <row r="507">
       <c r="D507" s="5"/>
     </row>
-    <row r="508" customHeight="1" spans="4:4">
+    <row r="508">
       <c r="D508" s="5"/>
     </row>
-    <row r="509" customHeight="1" spans="4:4">
+    <row r="509">
       <c r="D509" s="5"/>
     </row>
-    <row r="510" customHeight="1" spans="4:4">
+    <row r="510">
       <c r="D510" s="5"/>
     </row>
-    <row r="511" customHeight="1" spans="4:4">
+    <row r="511">
       <c r="D511" s="5"/>
     </row>
-    <row r="512" customHeight="1" spans="4:4">
+    <row r="512">
       <c r="D512" s="5"/>
     </row>
-    <row r="513" customHeight="1" spans="4:4">
+    <row r="513">
       <c r="D513" s="5"/>
     </row>
-    <row r="514" customHeight="1" spans="4:4">
+    <row r="514">
       <c r="D514" s="5"/>
     </row>
-    <row r="515" customHeight="1" spans="4:4">
+    <row r="515">
       <c r="D515" s="5"/>
     </row>
-    <row r="516" customHeight="1" spans="4:4">
+    <row r="516">
       <c r="D516" s="5"/>
     </row>
-    <row r="517" customHeight="1" spans="4:4">
+    <row r="517">
       <c r="D517" s="5"/>
     </row>
-    <row r="518" customHeight="1" spans="4:4">
+    <row r="518">
       <c r="D518" s="5"/>
     </row>
-    <row r="519" customHeight="1" spans="4:4">
+    <row r="519">
       <c r="D519" s="5"/>
     </row>
-    <row r="520" customHeight="1" spans="4:4">
+    <row r="520">
       <c r="D520" s="5"/>
     </row>
-    <row r="521" customHeight="1" spans="4:4">
+    <row r="521">
       <c r="D521" s="5"/>
     </row>
-    <row r="522" customHeight="1" spans="4:4">
+    <row r="522">
       <c r="D522" s="5"/>
     </row>
-    <row r="523" customHeight="1" spans="4:4">
+    <row r="523">
       <c r="D523" s="5"/>
     </row>
-    <row r="524" customHeight="1" spans="4:4">
+    <row r="524">
       <c r="D524" s="5"/>
     </row>
-    <row r="525" customHeight="1" spans="4:4">
+    <row r="525">
       <c r="D525" s="5"/>
     </row>
-    <row r="526" customHeight="1" spans="4:4">
+    <row r="526">
       <c r="D526" s="5"/>
     </row>
-    <row r="527" customHeight="1" spans="4:4">
+    <row r="527">
       <c r="D527" s="5"/>
     </row>
-    <row r="528" customHeight="1" spans="4:4">
+    <row r="528">
       <c r="D528" s="5"/>
     </row>
-    <row r="529" customHeight="1" spans="4:4">
+    <row r="529">
       <c r="D529" s="5"/>
     </row>
-    <row r="530" customHeight="1" spans="4:4">
+    <row r="530">
       <c r="D530" s="5"/>
     </row>
-    <row r="531" customHeight="1" spans="4:4">
+    <row r="531">
       <c r="D531" s="5"/>
     </row>
-    <row r="532" customHeight="1" spans="4:4">
+    <row r="532">
       <c r="D532" s="5"/>
     </row>
-    <row r="533" customHeight="1" spans="4:4">
+    <row r="533">
       <c r="D533" s="5"/>
     </row>
-    <row r="534" customHeight="1" spans="4:4">
+    <row r="534">
       <c r="D534" s="5"/>
     </row>
-    <row r="535" customHeight="1" spans="4:4">
+    <row r="535">
       <c r="D535" s="5"/>
     </row>
-    <row r="536" customHeight="1" spans="4:4">
+    <row r="536">
       <c r="D536" s="5"/>
     </row>
-    <row r="537" customHeight="1" spans="4:4">
+    <row r="537">
       <c r="D537" s="5"/>
     </row>
-    <row r="538" customHeight="1" spans="4:4">
+    <row r="538">
       <c r="D538" s="5"/>
     </row>
-    <row r="539" customHeight="1" spans="4:4">
+    <row r="539">
       <c r="D539" s="5"/>
     </row>
-    <row r="540" customHeight="1" spans="4:4">
+    <row r="540">
       <c r="D540" s="5"/>
     </row>
-    <row r="541" customHeight="1" spans="4:4">
+    <row r="541">
       <c r="D541" s="5"/>
     </row>
-    <row r="542" customHeight="1" spans="4:4">
+    <row r="542">
       <c r="D542" s="5"/>
     </row>
-    <row r="543" customHeight="1" spans="4:4">
+    <row r="543">
       <c r="D543" s="5"/>
     </row>
-    <row r="544" customHeight="1" spans="4:4">
+    <row r="544">
       <c r="D544" s="5"/>
     </row>
-    <row r="545" customHeight="1" spans="4:4">
+    <row r="545">
       <c r="D545" s="5"/>
     </row>
-    <row r="546" customHeight="1" spans="4:4">
+    <row r="546">
       <c r="D546" s="5"/>
     </row>
-    <row r="547" customHeight="1" spans="4:4">
+    <row r="547">
       <c r="D547" s="5"/>
     </row>
-    <row r="548" customHeight="1" spans="4:4">
+    <row r="548">
       <c r="D548" s="5"/>
     </row>
-    <row r="549" customHeight="1" spans="4:4">
+    <row r="549">
       <c r="D549" s="5"/>
     </row>
-    <row r="550" customHeight="1" spans="4:4">
+    <row r="550">
       <c r="D550" s="5"/>
     </row>
-    <row r="551" customHeight="1" spans="4:4">
+    <row r="551">
       <c r="D551" s="5"/>
     </row>
-    <row r="552" customHeight="1" spans="4:4">
+    <row r="552">
       <c r="D552" s="5"/>
     </row>
-    <row r="553" customHeight="1" spans="4:4">
+    <row r="553">
       <c r="D553" s="5"/>
     </row>
-    <row r="554" customHeight="1" spans="4:4">
+    <row r="554">
       <c r="D554" s="5"/>
     </row>
-    <row r="555" customHeight="1" spans="4:4">
+    <row r="555">
       <c r="D555" s="5"/>
     </row>
-    <row r="556" customHeight="1" spans="4:4">
+    <row r="556">
       <c r="D556" s="5"/>
     </row>
-    <row r="557" customHeight="1" spans="4:4">
+    <row r="557">
       <c r="D557" s="5"/>
     </row>
-    <row r="558" customHeight="1" spans="4:4">
+    <row r="558">
       <c r="D558" s="5"/>
     </row>
-    <row r="559" customHeight="1" spans="4:4">
+    <row r="559">
       <c r="D559" s="5"/>
     </row>
-    <row r="560" customHeight="1" spans="4:4">
+    <row r="560">
       <c r="D560" s="5"/>
     </row>
-    <row r="561" customHeight="1" spans="4:4">
+    <row r="561">
       <c r="D561" s="5"/>
     </row>
-    <row r="562" customHeight="1" spans="4:4">
+    <row r="562">
       <c r="D562" s="5"/>
     </row>
-    <row r="563" customHeight="1" spans="4:4">
+    <row r="563">
       <c r="D563" s="5"/>
     </row>
-    <row r="564" customHeight="1" spans="4:4">
+    <row r="564">
       <c r="D564" s="5"/>
     </row>
-    <row r="565" customHeight="1" spans="4:4">
+    <row r="565">
       <c r="D565" s="5"/>
     </row>
-    <row r="566" customHeight="1" spans="4:4">
+    <row r="566">
       <c r="D566" s="5"/>
     </row>
-    <row r="567" customHeight="1" spans="4:4">
+    <row r="567">
       <c r="D567" s="5"/>
     </row>
-    <row r="568" customHeight="1" spans="4:4">
+    <row r="568">
       <c r="D568" s="5"/>
     </row>
-    <row r="569" customHeight="1" spans="4:4">
+    <row r="569">
       <c r="D569" s="5"/>
     </row>
-    <row r="570" customHeight="1" spans="4:4">
+    <row r="570">
       <c r="D570" s="5"/>
     </row>
-    <row r="571" customHeight="1" spans="4:4">
+    <row r="571">
       <c r="D571" s="5"/>
     </row>
-    <row r="572" customHeight="1" spans="4:4">
+    <row r="572">
       <c r="D572" s="5"/>
     </row>
-    <row r="573" customHeight="1" spans="4:4">
+    <row r="573">
       <c r="D573" s="5"/>
     </row>
-    <row r="574" customHeight="1" spans="4:4">
+    <row r="574">
       <c r="D574" s="5"/>
     </row>
-    <row r="575" customHeight="1" spans="4:4">
+    <row r="575">
       <c r="D575" s="5"/>
     </row>
-    <row r="576" customHeight="1" spans="4:4">
+    <row r="576">
       <c r="D576" s="5"/>
     </row>
-    <row r="577" customHeight="1" spans="4:4">
+    <row r="577">
       <c r="D577" s="5"/>
     </row>
-    <row r="578" customHeight="1" spans="4:4">
+    <row r="578">
       <c r="D578" s="5"/>
     </row>
-    <row r="579" customHeight="1" spans="4:4">
+    <row r="579">
       <c r="D579" s="5"/>
     </row>
-    <row r="580" customHeight="1" spans="4:4">
+    <row r="580">
       <c r="D580" s="5"/>
     </row>
-    <row r="581" customHeight="1" spans="4:4">
+    <row r="581">
       <c r="D581" s="5"/>
     </row>
-    <row r="582" customHeight="1" spans="4:4">
+    <row r="582">
       <c r="D582" s="5"/>
     </row>
-    <row r="583" customHeight="1" spans="4:4">
+    <row r="583">
       <c r="D583" s="5"/>
     </row>
-    <row r="584" customHeight="1" spans="4:4">
+    <row r="584">
       <c r="D584" s="5"/>
     </row>
-    <row r="585" customHeight="1" spans="4:4">
+    <row r="585">
       <c r="D585" s="5"/>
     </row>
-    <row r="586" customHeight="1" spans="4:4">
+    <row r="586">
       <c r="D586" s="5"/>
     </row>
-    <row r="587" customHeight="1" spans="4:4">
+    <row r="587">
       <c r="D587" s="5"/>
     </row>
-    <row r="588" customHeight="1" spans="4:4">
+    <row r="588">
       <c r="D588" s="5"/>
     </row>
-    <row r="589" customHeight="1" spans="4:4">
+    <row r="589">
       <c r="D589" s="5"/>
     </row>
-    <row r="590" customHeight="1" spans="4:4">
+    <row r="590">
       <c r="D590" s="5"/>
     </row>
-    <row r="591" customHeight="1" spans="4:4">
+    <row r="591">
       <c r="D591" s="5"/>
     </row>
-    <row r="592" customHeight="1" spans="4:4">
+    <row r="592">
       <c r="D592" s="5"/>
     </row>
-    <row r="593" customHeight="1" spans="4:4">
+    <row r="593">
       <c r="D593" s="5"/>
     </row>
-    <row r="594" customHeight="1" spans="4:4">
+    <row r="594">
       <c r="D594" s="5"/>
     </row>
-    <row r="595" customHeight="1" spans="4:4">
+    <row r="595">
       <c r="D595" s="5"/>
     </row>
-    <row r="596" customHeight="1" spans="4:4">
+    <row r="596">
       <c r="D596" s="5"/>
     </row>
-    <row r="597" customHeight="1" spans="4:4">
+    <row r="597">
       <c r="D597" s="5"/>
     </row>
-    <row r="598" customHeight="1" spans="4:4">
+    <row r="598">
       <c r="D598" s="5"/>
     </row>
-    <row r="599" customHeight="1" spans="4:4">
+    <row r="599">
       <c r="D599" s="5"/>
     </row>
-    <row r="600" customHeight="1" spans="4:4">
+    <row r="600">
       <c r="D600" s="5"/>
     </row>
-    <row r="601" customHeight="1" spans="4:4">
+    <row r="601">
       <c r="D601" s="5"/>
     </row>
-    <row r="602" customHeight="1" spans="4:4">
+    <row r="602">
       <c r="D602" s="5"/>
     </row>
-    <row r="603" customHeight="1" spans="4:4">
+    <row r="603">
       <c r="D603" s="5"/>
     </row>
-    <row r="604" customHeight="1" spans="4:4">
+    <row r="604">
       <c r="D604" s="5"/>
     </row>
-    <row r="605" customHeight="1" spans="4:4">
+    <row r="605">
       <c r="D605" s="5"/>
     </row>
-    <row r="606" customHeight="1" spans="4:4">
+    <row r="606">
       <c r="D606" s="5"/>
     </row>
-    <row r="607" customHeight="1" spans="4:4">
+    <row r="607">
       <c r="D607" s="5"/>
     </row>
-    <row r="608" customHeight="1" spans="4:4">
+    <row r="608">
       <c r="D608" s="5"/>
     </row>
-    <row r="609" customHeight="1" spans="4:4">
+    <row r="609">
       <c r="D609" s="5"/>
     </row>
-    <row r="610" customHeight="1" spans="4:4">
+    <row r="610">
       <c r="D610" s="5"/>
     </row>
-    <row r="611" customHeight="1" spans="4:4">
+    <row r="611">
       <c r="D611" s="5"/>
     </row>
-    <row r="612" customHeight="1" spans="4:4">
+    <row r="612">
       <c r="D612" s="5"/>
     </row>
-    <row r="613" customHeight="1" spans="4:4">
+    <row r="613">
       <c r="D613" s="5"/>
     </row>
-    <row r="614" customHeight="1" spans="4:4">
+    <row r="614">
       <c r="D614" s="5"/>
     </row>
-    <row r="615" customHeight="1" spans="4:4">
+    <row r="615">
       <c r="D615" s="5"/>
     </row>
-    <row r="616" customHeight="1" spans="4:4">
+    <row r="616">
       <c r="D616" s="5"/>
     </row>
-    <row r="617" customHeight="1" spans="4:4">
+    <row r="617">
       <c r="D617" s="5"/>
     </row>
-    <row r="618" customHeight="1" spans="4:4">
+    <row r="618">
       <c r="D618" s="5"/>
     </row>
-    <row r="619" customHeight="1" spans="4:4">
+    <row r="619">
       <c r="D619" s="5"/>
     </row>
-    <row r="620" customHeight="1" spans="4:4">
+    <row r="620">
       <c r="D620" s="5"/>
     </row>
-    <row r="621" customHeight="1" spans="4:4">
+    <row r="621">
       <c r="D621" s="5"/>
     </row>
-    <row r="622" customHeight="1" spans="4:4">
+    <row r="622">
       <c r="D622" s="5"/>
     </row>
-    <row r="623" customHeight="1" spans="4:4">
+    <row r="623">
       <c r="D623" s="5"/>
     </row>
-    <row r="624" customHeight="1" spans="4:4">
+    <row r="624">
       <c r="D624" s="5"/>
     </row>
-    <row r="625" customHeight="1" spans="4:4">
+    <row r="625">
       <c r="D625" s="5"/>
     </row>
-    <row r="626" customHeight="1" spans="4:4">
+    <row r="626">
       <c r="D626" s="5"/>
     </row>
-    <row r="627" customHeight="1" spans="4:4">
+    <row r="627">
       <c r="D627" s="5"/>
     </row>
-    <row r="628" customHeight="1" spans="4:4">
+    <row r="628">
       <c r="D628" s="5"/>
     </row>
-    <row r="629" customHeight="1" spans="4:4">
+    <row r="629">
       <c r="D629" s="5"/>
     </row>
-    <row r="630" customHeight="1" spans="4:4">
+    <row r="630">
       <c r="D630" s="5"/>
     </row>
-    <row r="631" customHeight="1" spans="4:4">
+    <row r="631">
       <c r="D631" s="5"/>
     </row>
-    <row r="632" customHeight="1" spans="4:4">
+    <row r="632">
       <c r="D632" s="5"/>
     </row>
-    <row r="633" customHeight="1" spans="4:4">
+    <row r="633">
       <c r="D633" s="5"/>
     </row>
-    <row r="634" customHeight="1" spans="4:4">
+    <row r="634">
       <c r="D634" s="5"/>
     </row>
-    <row r="635" customHeight="1" spans="4:4">
+    <row r="635">
       <c r="D635" s="5"/>
     </row>
-    <row r="636" customHeight="1" spans="4:4">
+    <row r="636">
       <c r="D636" s="5"/>
     </row>
-    <row r="637" customHeight="1" spans="4:4">
+    <row r="637">
       <c r="D637" s="5"/>
     </row>
-    <row r="638" customHeight="1" spans="4:4">
+    <row r="638">
       <c r="D638" s="5"/>
     </row>
-    <row r="639" customHeight="1" spans="4:4">
+    <row r="639">
       <c r="D639" s="5"/>
     </row>
-    <row r="640" customHeight="1" spans="4:4">
+    <row r="640">
       <c r="D640" s="5"/>
     </row>
-    <row r="641" customHeight="1" spans="4:4">
+    <row r="641">
       <c r="D641" s="5"/>
     </row>
-    <row r="642" customHeight="1" spans="4:4">
+    <row r="642">
       <c r="D642" s="5"/>
     </row>
-    <row r="643" customHeight="1" spans="4:4">
+    <row r="643">
       <c r="D643" s="5"/>
     </row>
-    <row r="644" customHeight="1" spans="4:4">
+    <row r="644">
       <c r="D644" s="5"/>
     </row>
-    <row r="645" customHeight="1" spans="4:4">
+    <row r="645">
       <c r="D645" s="5"/>
     </row>
-    <row r="646" customHeight="1" spans="4:4">
+    <row r="646">
       <c r="D646" s="5"/>
     </row>
-    <row r="647" customHeight="1" spans="4:4">
+    <row r="647">
       <c r="D647" s="5"/>
     </row>
-    <row r="648" customHeight="1" spans="4:4">
+    <row r="648">
       <c r="D648" s="5"/>
     </row>
-    <row r="649" customHeight="1" spans="4:4">
+    <row r="649">
       <c r="D649" s="5"/>
     </row>
-    <row r="650" customHeight="1" spans="4:4">
+    <row r="650">
       <c r="D650" s="5"/>
     </row>
-    <row r="651" customHeight="1" spans="4:4">
+    <row r="651">
       <c r="D651" s="5"/>
     </row>
-    <row r="652" customHeight="1" spans="4:4">
+    <row r="652">
       <c r="D652" s="5"/>
     </row>
-    <row r="653" customHeight="1" spans="4:4">
+    <row r="653">
       <c r="D653" s="5"/>
     </row>
-    <row r="654" customHeight="1" spans="4:4">
+    <row r="654">
       <c r="D654" s="5"/>
     </row>
-    <row r="655" customHeight="1" spans="4:4">
+    <row r="655">
       <c r="D655" s="5"/>
     </row>
-    <row r="656" customHeight="1" spans="4:4">
+    <row r="656">
       <c r="D656" s="5"/>
     </row>
-    <row r="657" customHeight="1" spans="4:4">
+    <row r="657">
       <c r="D657" s="5"/>
     </row>
-    <row r="658" customHeight="1" spans="4:4">
+    <row r="658">
       <c r="D658" s="5"/>
     </row>
-    <row r="659" customHeight="1" spans="4:4">
+    <row r="659">
       <c r="D659" s="5"/>
     </row>
-    <row r="660" customHeight="1" spans="4:4">
+    <row r="660">
       <c r="D660" s="5"/>
     </row>
-    <row r="661" customHeight="1" spans="4:4">
+    <row r="661">
       <c r="D661" s="5"/>
     </row>
-    <row r="662" customHeight="1" spans="4:4">
+    <row r="662">
       <c r="D662" s="5"/>
     </row>
-    <row r="663" customHeight="1" spans="4:4">
+    <row r="663">
       <c r="D663" s="5"/>
     </row>
-    <row r="664" customHeight="1" spans="4:4">
+    <row r="664">
       <c r="D664" s="5"/>
     </row>
-    <row r="665" customHeight="1" spans="4:4">
+    <row r="665">
       <c r="D665" s="5"/>
     </row>
-    <row r="666" customHeight="1" spans="4:4">
+    <row r="666">
       <c r="D666" s="5"/>
     </row>
-    <row r="667" customHeight="1" spans="4:4">
+    <row r="667">
       <c r="D667" s="5"/>
     </row>
-    <row r="668" customHeight="1" spans="4:4">
+    <row r="668">
       <c r="D668" s="5"/>
     </row>
-    <row r="669" customHeight="1" spans="4:4">
+    <row r="669">
       <c r="D669" s="5"/>
     </row>
-    <row r="670" customHeight="1" spans="4:4">
+    <row r="670">
       <c r="D670" s="5"/>
     </row>
-    <row r="671" customHeight="1" spans="4:4">
+    <row r="671">
       <c r="D671" s="5"/>
     </row>
-    <row r="672" customHeight="1" spans="4:4">
+    <row r="672">
       <c r="D672" s="5"/>
     </row>
-    <row r="673" customHeight="1" spans="4:4">
+    <row r="673">
       <c r="D673" s="5"/>
     </row>
-    <row r="674" customHeight="1" spans="4:4">
+    <row r="674">
       <c r="D674" s="5"/>
     </row>
-    <row r="675" customHeight="1" spans="4:4">
+    <row r="675">
       <c r="D675" s="5"/>
     </row>
-    <row r="676" customHeight="1" spans="4:4">
+    <row r="676">
       <c r="D676" s="5"/>
     </row>
-    <row r="677" customHeight="1" spans="4:4">
+    <row r="677">
       <c r="D677" s="5"/>
     </row>
-    <row r="678" customHeight="1" spans="4:4">
+    <row r="678">
       <c r="D678" s="5"/>
     </row>
-    <row r="679" customHeight="1" spans="4:4">
+    <row r="679">
       <c r="D679" s="5"/>
     </row>
-    <row r="680" customHeight="1" spans="4:4">
+    <row r="680">
       <c r="D680" s="5"/>
     </row>
-    <row r="681" customHeight="1" spans="4:4">
+    <row r="681">
       <c r="D681" s="5"/>
     </row>
-    <row r="682" customHeight="1" spans="4:4">
+    <row r="682">
       <c r="D682" s="5"/>
     </row>
-    <row r="683" customHeight="1" spans="4:4">
+    <row r="683">
       <c r="D683" s="5"/>
     </row>
-    <row r="684" customHeight="1" spans="4:4">
+    <row r="684">
       <c r="D684" s="5"/>
     </row>
-    <row r="685" customHeight="1" spans="4:4">
+    <row r="685">
       <c r="D685" s="5"/>
     </row>
-    <row r="686" customHeight="1" spans="4:4">
+    <row r="686">
       <c r="D686" s="5"/>
     </row>
-    <row r="687" customHeight="1" spans="4:4">
+    <row r="687">
       <c r="D687" s="5"/>
     </row>
-    <row r="688" customHeight="1" spans="4:4">
+    <row r="688">
       <c r="D688" s="5"/>
     </row>
-    <row r="689" customHeight="1" spans="4:4">
+    <row r="689">
       <c r="D689" s="5"/>
     </row>
-    <row r="690" customHeight="1" spans="4:4">
+    <row r="690">
       <c r="D690" s="5"/>
     </row>
-    <row r="691" customHeight="1" spans="4:4">
+    <row r="691">
       <c r="D691" s="5"/>
     </row>
-    <row r="692" customHeight="1" spans="4:4">
+    <row r="692">
       <c r="D692" s="5"/>
     </row>
-    <row r="693" customHeight="1" spans="4:4">
+    <row r="693">
       <c r="D693" s="5"/>
     </row>
-    <row r="694" customHeight="1" spans="4:4">
+    <row r="694">
       <c r="D694" s="5"/>
     </row>
-    <row r="695" customHeight="1" spans="4:4">
+    <row r="695">
       <c r="D695" s="5"/>
     </row>
-    <row r="696" customHeight="1" spans="4:4">
+    <row r="696">
       <c r="D696" s="5"/>
     </row>
-    <row r="697" customHeight="1" spans="4:4">
+    <row r="697">
       <c r="D697" s="5"/>
     </row>
-    <row r="698" customHeight="1" spans="4:4">
+    <row r="698">
       <c r="D698" s="5"/>
     </row>
-    <row r="699" customHeight="1" spans="4:4">
+    <row r="699">
       <c r="D699" s="5"/>
     </row>
-    <row r="700" customHeight="1" spans="4:4">
+    <row r="700">
       <c r="D700" s="5"/>
     </row>
-    <row r="701" customHeight="1" spans="4:4">
+    <row r="701">
       <c r="D701" s="5"/>
     </row>
-    <row r="702" customHeight="1" spans="4:4">
+    <row r="702">
       <c r="D702" s="5"/>
     </row>
-    <row r="703" customHeight="1" spans="4:4">
+    <row r="703">
       <c r="D703" s="5"/>
     </row>
-    <row r="704" customHeight="1" spans="4:4">
+    <row r="704">
       <c r="D704" s="5"/>
     </row>
-    <row r="705" customHeight="1" spans="4:4">
+    <row r="705">
       <c r="D705" s="5"/>
     </row>
-    <row r="706" customHeight="1" spans="4:4">
+    <row r="706">
       <c r="D706" s="5"/>
     </row>
-    <row r="707" customHeight="1" spans="4:4">
+    <row r="707">
       <c r="D707" s="5"/>
     </row>
-    <row r="708" customHeight="1" spans="4:4">
+    <row r="708">
       <c r="D708" s="5"/>
     </row>
-    <row r="709" customHeight="1" spans="4:4">
+    <row r="709">
       <c r="D709" s="5"/>
     </row>
-    <row r="710" customHeight="1" spans="4:4">
+    <row r="710">
       <c r="D710" s="5"/>
     </row>
-    <row r="711" customHeight="1" spans="4:4">
+    <row r="711">
       <c r="D711" s="5"/>
     </row>
-    <row r="712" customHeight="1" spans="4:4">
+    <row r="712">
       <c r="D712" s="5"/>
     </row>
-    <row r="713" customHeight="1" spans="4:4">
+    <row r="713">
       <c r="D713" s="5"/>
     </row>
-    <row r="714" customHeight="1" spans="4:4">
+    <row r="714">
       <c r="D714" s="5"/>
     </row>
-    <row r="715" customHeight="1" spans="4:4">
+    <row r="715">
       <c r="D715" s="5"/>
     </row>
-    <row r="716" customHeight="1" spans="4:4">
+    <row r="716">
       <c r="D716" s="5"/>
     </row>
-    <row r="717" customHeight="1" spans="4:4">
+    <row r="717">
       <c r="D717" s="5"/>
     </row>
-    <row r="718" customHeight="1" spans="4:4">
+    <row r="718">
       <c r="D718" s="5"/>
     </row>
-    <row r="719" customHeight="1" spans="4:4">
+    <row r="719">
       <c r="D719" s="5"/>
     </row>
-    <row r="720" customHeight="1" spans="4:4">
+    <row r="720">
       <c r="D720" s="5"/>
     </row>
-    <row r="721" customHeight="1" spans="4:4">
+    <row r="721">
       <c r="D721" s="5"/>
     </row>
-    <row r="722" customHeight="1" spans="4:4">
+    <row r="722">
       <c r="D722" s="5"/>
     </row>
-    <row r="723" customHeight="1" spans="4:4">
+    <row r="723">
       <c r="D723" s="5"/>
     </row>
-    <row r="724" customHeight="1" spans="4:4">
+    <row r="724">
       <c r="D724" s="5"/>
     </row>
-    <row r="725" customHeight="1" spans="4:4">
+    <row r="725">
       <c r="D725" s="5"/>
     </row>
-    <row r="726" customHeight="1" spans="4:4">
+    <row r="726">
       <c r="D726" s="5"/>
     </row>
-    <row r="727" customHeight="1" spans="4:4">
+    <row r="727">
       <c r="D727" s="5"/>
     </row>
-    <row r="728" customHeight="1" spans="4:4">
+    <row r="728">
       <c r="D728" s="5"/>
     </row>
-    <row r="729" customHeight="1" spans="4:4">
+    <row r="729">
       <c r="D729" s="5"/>
     </row>
-    <row r="730" customHeight="1" spans="4:4">
+    <row r="730">
       <c r="D730" s="5"/>
     </row>
-    <row r="731" customHeight="1" spans="4:4">
+    <row r="731">
       <c r="D731" s="5"/>
     </row>
-    <row r="732" customHeight="1" spans="4:4">
+    <row r="732">
       <c r="D732" s="5"/>
     </row>
-    <row r="733" customHeight="1" spans="4:4">
+    <row r="733">
       <c r="D733" s="5"/>
     </row>
-    <row r="734" customHeight="1" spans="4:4">
+    <row r="734">
       <c r="D734" s="5"/>
     </row>
-    <row r="735" customHeight="1" spans="4:4">
+    <row r="735">
       <c r="D735" s="5"/>
     </row>
-    <row r="736" customHeight="1" spans="4:4">
+    <row r="736">
       <c r="D736" s="5"/>
     </row>
-    <row r="737" customHeight="1" spans="4:4">
+    <row r="737">
       <c r="D737" s="5"/>
     </row>
-    <row r="738" customHeight="1" spans="4:4">
+    <row r="738">
       <c r="D738" s="5"/>
     </row>
-    <row r="739" customHeight="1" spans="4:4">
+    <row r="739">
       <c r="D739" s="5"/>
     </row>
-    <row r="740" customHeight="1" spans="4:4">
+    <row r="740">
       <c r="D740" s="5"/>
     </row>
-    <row r="741" customHeight="1" spans="4:4">
+    <row r="741">
       <c r="D741" s="5"/>
     </row>
-    <row r="742" customHeight="1" spans="4:4">
+    <row r="742">
       <c r="D742" s="5"/>
     </row>
-    <row r="743" customHeight="1" spans="4:4">
+    <row r="743">
       <c r="D743" s="5"/>
     </row>
-    <row r="744" customHeight="1" spans="4:4">
+    <row r="744">
       <c r="D744" s="5"/>
     </row>
-    <row r="745" customHeight="1" spans="4:4">
+    <row r="745">
       <c r="D745" s="5"/>
     </row>
-    <row r="746" customHeight="1" spans="4:4">
+    <row r="746">
       <c r="D746" s="5"/>
     </row>
-    <row r="747" customHeight="1" spans="4:4">
+    <row r="747">
       <c r="D747" s="5"/>
     </row>
-    <row r="748" customHeight="1" spans="4:4">
+    <row r="748">
       <c r="D748" s="5"/>
     </row>
-    <row r="749" customHeight="1" spans="4:4">
+    <row r="749">
       <c r="D749" s="5"/>
     </row>
-    <row r="750" customHeight="1" spans="4:4">
+    <row r="750">
       <c r="D750" s="5"/>
     </row>
-    <row r="751" customHeight="1" spans="4:4">
+    <row r="751">
       <c r="D751" s="5"/>
     </row>
-    <row r="752" customHeight="1" spans="4:4">
+    <row r="752">
       <c r="D752" s="5"/>
     </row>
-    <row r="753" customHeight="1" spans="4:4">
+    <row r="753">
       <c r="D753" s="5"/>
     </row>
-    <row r="754" customHeight="1" spans="4:4">
+    <row r="754">
       <c r="D754" s="5"/>
     </row>
-    <row r="755" customHeight="1" spans="4:4">
+    <row r="755">
       <c r="D755" s="5"/>
     </row>
-    <row r="756" customHeight="1" spans="4:4">
+    <row r="756">
       <c r="D756" s="5"/>
     </row>
-    <row r="757" customHeight="1" spans="4:4">
+    <row r="757">
       <c r="D757" s="5"/>
     </row>
-    <row r="758" customHeight="1" spans="4:4">
+    <row r="758">
       <c r="D758" s="5"/>
     </row>
-    <row r="759" customHeight="1" spans="4:4">
+    <row r="759">
       <c r="D759" s="5"/>
     </row>
-    <row r="760" customHeight="1" spans="4:4">
+    <row r="760">
       <c r="D760" s="5"/>
     </row>
-    <row r="761" customHeight="1" spans="4:4">
+    <row r="761">
       <c r="D761" s="5"/>
     </row>
-    <row r="762" customHeight="1" spans="4:4">
+    <row r="762">
       <c r="D762" s="5"/>
     </row>
-    <row r="763" customHeight="1" spans="4:4">
+    <row r="763">
       <c r="D763" s="5"/>
     </row>
-    <row r="764" customHeight="1" spans="4:4">
+    <row r="764">
       <c r="D764" s="5"/>
     </row>
-    <row r="765" customHeight="1" spans="4:4">
+    <row r="765">
       <c r="D765" s="5"/>
     </row>
-    <row r="766" customHeight="1" spans="4:4">
+    <row r="766">
       <c r="D766" s="5"/>
     </row>
-    <row r="767" customHeight="1" spans="4:4">
+    <row r="767">
       <c r="D767" s="5"/>
     </row>
-    <row r="768" customHeight="1" spans="4:4">
+    <row r="768">
       <c r="D768" s="5"/>
     </row>
-    <row r="769" customHeight="1" spans="4:4">
+    <row r="769">
       <c r="D769" s="5"/>
     </row>
-    <row r="770" customHeight="1" spans="4:4">
+    <row r="770">
       <c r="D770" s="5"/>
     </row>
-    <row r="771" customHeight="1" spans="4:4">
+    <row r="771">
       <c r="D771" s="5"/>
     </row>
-    <row r="772" customHeight="1" spans="4:4">
+    <row r="772">
       <c r="D772" s="5"/>
     </row>
-    <row r="773" customHeight="1" spans="4:4">
+    <row r="773">
       <c r="D773" s="5"/>
     </row>
-    <row r="774" customHeight="1" spans="4:4">
+    <row r="774">
       <c r="D774" s="5"/>
     </row>
-    <row r="775" customHeight="1" spans="4:4">
+    <row r="775">
       <c r="D775" s="5"/>
     </row>
-    <row r="776" customHeight="1" spans="4:4">
+    <row r="776">
       <c r="D776" s="5"/>
     </row>
-    <row r="777" customHeight="1" spans="4:4">
+    <row r="777">
       <c r="D777" s="5"/>
     </row>
-    <row r="778" customHeight="1" spans="4:4">
+    <row r="778">
       <c r="D778" s="5"/>
     </row>
-    <row r="779" customHeight="1" spans="4:4">
+    <row r="779">
       <c r="D779" s="5"/>
     </row>
-    <row r="780" customHeight="1" spans="4:4">
+    <row r="780">
       <c r="D780" s="5"/>
     </row>
-    <row r="781" customHeight="1" spans="4:4">
+    <row r="781">
       <c r="D781" s="5"/>
     </row>
-    <row r="782" customHeight="1" spans="4:4">
+    <row r="782">
       <c r="D782" s="5"/>
     </row>
-    <row r="783" customHeight="1" spans="4:4">
+    <row r="783">
       <c r="D783" s="5"/>
     </row>
-    <row r="784" customHeight="1" spans="4:4">
+    <row r="784">
       <c r="D784" s="5"/>
     </row>
-    <row r="785" customHeight="1" spans="4:4">
+    <row r="785">
       <c r="D785" s="5"/>
     </row>
-    <row r="786" customHeight="1" spans="4:4">
+    <row r="786">
       <c r="D786" s="5"/>
     </row>
-    <row r="787" customHeight="1" spans="4:4">
+    <row r="787">
       <c r="D787" s="5"/>
     </row>
-    <row r="788" customHeight="1" spans="4:4">
+    <row r="788">
       <c r="D788" s="5"/>
     </row>
-    <row r="789" customHeight="1" spans="4:4">
+    <row r="789">
       <c r="D789" s="5"/>
     </row>
-    <row r="790" customHeight="1" spans="4:4">
+    <row r="790">
       <c r="D790" s="5"/>
     </row>
-    <row r="791" customHeight="1" spans="4:4">
+    <row r="791">
       <c r="D791" s="5"/>
     </row>
-    <row r="792" customHeight="1" spans="4:4">
+    <row r="792">
       <c r="D792" s="5"/>
     </row>
-    <row r="793" customHeight="1" spans="4:4">
+    <row r="793">
       <c r="D793" s="5"/>
     </row>
-    <row r="794" customHeight="1" spans="4:4">
+    <row r="794">
       <c r="D794" s="5"/>
     </row>
-    <row r="795" customHeight="1" spans="4:4">
+    <row r="795">
       <c r="D795" s="5"/>
     </row>
-    <row r="796" customHeight="1" spans="4:4">
+    <row r="796">
       <c r="D796" s="5"/>
     </row>
-    <row r="797" customHeight="1" spans="4:4">
+    <row r="797">
       <c r="D797" s="5"/>
     </row>
-    <row r="798" customHeight="1" spans="4:4">
+    <row r="798">
       <c r="D798" s="5"/>
     </row>
-    <row r="799" customHeight="1" spans="4:4">
+    <row r="799">
       <c r="D799" s="5"/>
     </row>
-    <row r="800" customHeight="1" spans="4:4">
+    <row r="800">
       <c r="D800" s="5"/>
     </row>
-    <row r="801" customHeight="1" spans="4:4">
+    <row r="801">
       <c r="D801" s="5"/>
     </row>
-    <row r="802" customHeight="1" spans="4:4">
+    <row r="802">
       <c r="D802" s="5"/>
     </row>
-    <row r="803" customHeight="1" spans="4:4">
+    <row r="803">
       <c r="D803" s="5"/>
     </row>
-    <row r="804" customHeight="1" spans="4:4">
+    <row r="804">
       <c r="D804" s="5"/>
     </row>
-    <row r="805" customHeight="1" spans="4:4">
+    <row r="805">
       <c r="D805" s="5"/>
     </row>
-    <row r="806" customHeight="1" spans="4:4">
+    <row r="806">
       <c r="D806" s="5"/>
     </row>
-    <row r="807" customHeight="1" spans="4:4">
+    <row r="807">
       <c r="D807" s="5"/>
     </row>
-    <row r="808" customHeight="1" spans="4:4">
+    <row r="808">
       <c r="D808" s="5"/>
     </row>
-    <row r="809" customHeight="1" spans="4:4">
+    <row r="809">
       <c r="D809" s="5"/>
     </row>
-    <row r="810" customHeight="1" spans="4:4">
+    <row r="810">
       <c r="D810" s="5"/>
     </row>
-    <row r="811" customHeight="1" spans="4:4">
+    <row r="811">
       <c r="D811" s="5"/>
     </row>
-    <row r="812" customHeight="1" spans="4:4">
+    <row r="812">
       <c r="D812" s="5"/>
     </row>
-    <row r="813" customHeight="1" spans="4:4">
+    <row r="813">
       <c r="D813" s="5"/>
     </row>
-    <row r="814" customHeight="1" spans="4:4">
+    <row r="814">
       <c r="D814" s="5"/>
     </row>
-    <row r="815" customHeight="1" spans="4:4">
+    <row r="815">
       <c r="D815" s="5"/>
     </row>
-    <row r="816" customHeight="1" spans="4:4">
+    <row r="816">
       <c r="D816" s="5"/>
     </row>
-    <row r="817" customHeight="1" spans="4:4">
+    <row r="817">
       <c r="D817" s="5"/>
     </row>
-    <row r="818" customHeight="1" spans="4:4">
+    <row r="818">
       <c r="D818" s="5"/>
     </row>
-    <row r="819" customHeight="1" spans="4:4">
+    <row r="819">
       <c r="D819" s="5"/>
     </row>
-    <row r="820" customHeight="1" spans="4:4">
+    <row r="820">
       <c r="D820" s="5"/>
     </row>
-    <row r="821" customHeight="1" spans="4:4">
+    <row r="821">
       <c r="D821" s="5"/>
     </row>
-    <row r="822" customHeight="1" spans="4:4">
+    <row r="822">
       <c r="D822" s="5"/>
     </row>
-    <row r="823" customHeight="1" spans="4:4">
+    <row r="823">
       <c r="D823" s="5"/>
     </row>
-    <row r="824" customHeight="1" spans="4:4">
+    <row r="824">
       <c r="D824" s="5"/>
     </row>
-    <row r="825" customHeight="1" spans="4:4">
+    <row r="825">
       <c r="D825" s="5"/>
     </row>
-    <row r="826" customHeight="1" spans="4:4">
+    <row r="826">
       <c r="D826" s="5"/>
     </row>
-    <row r="827" customHeight="1" spans="4:4">
+    <row r="827">
       <c r="D827" s="5"/>
     </row>
-    <row r="828" customHeight="1" spans="4:4">
+    <row r="828">
       <c r="D828" s="5"/>
     </row>
-    <row r="829" customHeight="1" spans="4:4">
+    <row r="829">
       <c r="D829" s="5"/>
     </row>
-    <row r="830" customHeight="1" spans="4:4">
+    <row r="830">
       <c r="D830" s="5"/>
     </row>
-    <row r="831" customHeight="1" spans="4:4">
+    <row r="831">
       <c r="D831" s="5"/>
     </row>
-    <row r="832" customHeight="1" spans="4:4">
+    <row r="832">
       <c r="D832" s="5"/>
     </row>
-    <row r="833" customHeight="1" spans="4:4">
+    <row r="833">
       <c r="D833" s="5"/>
     </row>
-    <row r="834" customHeight="1" spans="4:4">
+    <row r="834">
       <c r="D834" s="5"/>
     </row>
-    <row r="835" customHeight="1" spans="4:4">
+    <row r="835">
       <c r="D835" s="5"/>
     </row>
-    <row r="836" customHeight="1" spans="4:4">
+    <row r="836">
       <c r="D836" s="5"/>
     </row>
-    <row r="837" customHeight="1" spans="4:4">
+    <row r="837">
       <c r="D837" s="5"/>
     </row>
-    <row r="838" customHeight="1" spans="4:4">
+    <row r="838">
       <c r="D838" s="5"/>
     </row>
-    <row r="839" customHeight="1" spans="4:4">
+    <row r="839">
       <c r="D839" s="5"/>
     </row>
-    <row r="840" customHeight="1" spans="4:4">
+    <row r="840">
       <c r="D840" s="5"/>
     </row>
-    <row r="841" customHeight="1" spans="4:4">
+    <row r="841">
       <c r="D841" s="5"/>
     </row>
-    <row r="842" customHeight="1" spans="4:4">
+    <row r="842">
       <c r="D842" s="5"/>
     </row>
-    <row r="843" customHeight="1" spans="4:4">
+    <row r="843">
       <c r="D843" s="5"/>
     </row>
-    <row r="844" customHeight="1" spans="4:4">
+    <row r="844">
       <c r="D844" s="5"/>
     </row>
-    <row r="845" customHeight="1" spans="4:4">
+    <row r="845">
       <c r="D845" s="5"/>
     </row>
-    <row r="846" customHeight="1" spans="4:4">
+    <row r="846">
       <c r="D846" s="5"/>
     </row>
-    <row r="847" customHeight="1" spans="4:4">
+    <row r="847">
       <c r="D847" s="5"/>
     </row>
-    <row r="848" customHeight="1" spans="4:4">
+    <row r="848">
       <c r="D848" s="5"/>
     </row>
-    <row r="849" customHeight="1" spans="4:4">
+    <row r="849">
       <c r="D849" s="5"/>
     </row>
-    <row r="850" customHeight="1" spans="4:4">
+    <row r="850">
       <c r="D850" s="5"/>
     </row>
-    <row r="851" customHeight="1" spans="4:4">
+    <row r="851">
       <c r="D851" s="5"/>
     </row>
-    <row r="852" customHeight="1" spans="4:4">
+    <row r="852">
       <c r="D852" s="5"/>
     </row>
-    <row r="853" customHeight="1" spans="4:4">
+    <row r="853">
       <c r="D853" s="5"/>
     </row>
-    <row r="854" customHeight="1" spans="4:4">
+    <row r="854">
       <c r="D854" s="5"/>
     </row>
-    <row r="855" customHeight="1" spans="4:4">
+    <row r="855">
       <c r="D855" s="5"/>
     </row>
-    <row r="856" customHeight="1" spans="4:4">
+    <row r="856">
       <c r="D856" s="5"/>
     </row>
-    <row r="857" customHeight="1" spans="4:4">
+    <row r="857">
       <c r="D857" s="5"/>
     </row>
-    <row r="858" customHeight="1" spans="4:4">
+    <row r="858">
       <c r="D858" s="5"/>
     </row>
-    <row r="859" customHeight="1" spans="4:4">
+    <row r="859">
       <c r="D859" s="5"/>
     </row>
-    <row r="860" customHeight="1" spans="4:4">
+    <row r="860">
       <c r="D860" s="5"/>
     </row>
-    <row r="861" customHeight="1" spans="4:4">
+    <row r="861">
       <c r="D861" s="5"/>
     </row>
-    <row r="862" customHeight="1" spans="4:4">
+    <row r="862">
       <c r="D862" s="5"/>
     </row>
-    <row r="863" customHeight="1" spans="4:4">
+    <row r="863">
       <c r="D863" s="5"/>
     </row>
-    <row r="864" customHeight="1" spans="4:4">
+    <row r="864">
       <c r="D864" s="5"/>
     </row>
-    <row r="865" customHeight="1" spans="4:4">
+    <row r="865">
       <c r="D865" s="5"/>
     </row>
-    <row r="866" customHeight="1" spans="4:4">
+    <row r="866">
       <c r="D866" s="5"/>
     </row>
-    <row r="867" customHeight="1" spans="4:4">
+    <row r="867">
       <c r="D867" s="5"/>
     </row>
-    <row r="868" customHeight="1" spans="4:4">
+    <row r="868">
       <c r="D868" s="5"/>
     </row>
-    <row r="869" customHeight="1" spans="4:4">
+    <row r="869">
       <c r="D869" s="5"/>
     </row>
-    <row r="870" customHeight="1" spans="4:4">
+    <row r="870">
       <c r="D870" s="5"/>
     </row>
-    <row r="871" customHeight="1" spans="4:4">
+    <row r="871">
       <c r="D871" s="5"/>
     </row>
-    <row r="872" customHeight="1" spans="4:4">
+    <row r="872">
       <c r="D872" s="5"/>
     </row>
-    <row r="873" customHeight="1" spans="4:4">
+    <row r="873">
       <c r="D873" s="5"/>
     </row>
-    <row r="874" customHeight="1" spans="4:4">
+    <row r="874">
       <c r="D874" s="5"/>
     </row>
-    <row r="875" customHeight="1" spans="4:4">
+    <row r="875">
       <c r="D875" s="5"/>
     </row>
-    <row r="876" customHeight="1" spans="4:4">
+    <row r="876">
       <c r="D876" s="5"/>
     </row>
-    <row r="877" customHeight="1" spans="4:4">
+    <row r="877">
       <c r="D877" s="5"/>
     </row>
-    <row r="878" customHeight="1" spans="4:4">
+    <row r="878">
       <c r="D878" s="5"/>
     </row>
-    <row r="879" customHeight="1" spans="4:4">
+    <row r="879">
       <c r="D879" s="5"/>
     </row>
-    <row r="880" customHeight="1" spans="4:4">
+    <row r="880">
       <c r="D880" s="5"/>
     </row>
-    <row r="881" customHeight="1" spans="4:4">
+    <row r="881">
       <c r="D881" s="5"/>
     </row>
-    <row r="882" customHeight="1" spans="4:4">
+    <row r="882">
       <c r="D882" s="5"/>
     </row>
-    <row r="883" customHeight="1" spans="4:4">
+    <row r="883">
       <c r="D883" s="5"/>
     </row>
-    <row r="884" customHeight="1" spans="4:4">
+    <row r="884">
       <c r="D884" s="5"/>
     </row>
-    <row r="885" customHeight="1" spans="4:4">
+    <row r="885">
       <c r="D885" s="5"/>
     </row>
-    <row r="886" customHeight="1" spans="4:4">
+    <row r="886">
       <c r="D886" s="5"/>
     </row>
-    <row r="887" customHeight="1" spans="4:4">
+    <row r="887">
       <c r="D887" s="5"/>
     </row>
-    <row r="888" customHeight="1" spans="4:4">
+    <row r="888">
       <c r="D888" s="5"/>
     </row>
-    <row r="889" customHeight="1" spans="4:4">
+    <row r="889">
       <c r="D889" s="5"/>
     </row>
-    <row r="890" customHeight="1" spans="4:4">
+    <row r="890">
       <c r="D890" s="5"/>
     </row>
-    <row r="891" customHeight="1" spans="4:4">
+    <row r="891">
       <c r="D891" s="5"/>
     </row>
-    <row r="892" customHeight="1" spans="4:4">
+    <row r="892">
       <c r="D892" s="5"/>
     </row>
-    <row r="893" customHeight="1" spans="4:4">
+    <row r="893">
       <c r="D893" s="5"/>
     </row>
-    <row r="894" customHeight="1" spans="4:4">
+    <row r="894">
       <c r="D894" s="5"/>
     </row>
-    <row r="895" customHeight="1" spans="4:4">
+    <row r="895">
       <c r="D895" s="5"/>
     </row>
-    <row r="896" customHeight="1" spans="4:4">
+    <row r="896">
       <c r="D896" s="5"/>
     </row>
-    <row r="897" customHeight="1" spans="4:4">
+    <row r="897">
       <c r="D897" s="5"/>
     </row>
-    <row r="898" customHeight="1" spans="4:4">
+    <row r="898">
       <c r="D898" s="5"/>
     </row>
-    <row r="899" customHeight="1" spans="4:4">
+    <row r="899">
       <c r="D899" s="5"/>
     </row>
-    <row r="900" customHeight="1" spans="4:4">
+    <row r="900">
       <c r="D900" s="5"/>
     </row>
-    <row r="901" customHeight="1" spans="4:4">
+    <row r="901">
       <c r="D901" s="5"/>
     </row>
-    <row r="902" customHeight="1" spans="4:4">
+    <row r="902">
       <c r="D902" s="5"/>
     </row>
-    <row r="903" customHeight="1" spans="4:4">
+    <row r="903">
       <c r="D903" s="5"/>
     </row>
-    <row r="904" customHeight="1" spans="4:4">
+    <row r="904">
       <c r="D904" s="5"/>
     </row>
-    <row r="905" customHeight="1" spans="4:4">
+    <row r="905">
       <c r="D905" s="5"/>
     </row>
-    <row r="906" customHeight="1" spans="4:4">
+    <row r="906">
       <c r="D906" s="5"/>
     </row>
-    <row r="907" customHeight="1" spans="4:4">
+    <row r="907">
       <c r="D907" s="5"/>
     </row>
-    <row r="908" customHeight="1" spans="4:4">
+    <row r="908">
       <c r="D908" s="5"/>
     </row>
-    <row r="909" customHeight="1" spans="4:4">
+    <row r="909">
       <c r="D909" s="5"/>
     </row>
-    <row r="910" customHeight="1" spans="4:4">
+    <row r="910">
       <c r="D910" s="5"/>
     </row>
-    <row r="911" customHeight="1" spans="4:4">
+    <row r="911">
       <c r="D911" s="5"/>
     </row>
-    <row r="912" customHeight="1" spans="4:4">
+    <row r="912">
       <c r="D912" s="5"/>
     </row>
-    <row r="913" customHeight="1" spans="4:4">
+    <row r="913">
       <c r="D913" s="5"/>
     </row>
-    <row r="914" customHeight="1" spans="4:4">
+    <row r="914">
       <c r="D914" s="5"/>
     </row>
-    <row r="915" customHeight="1" spans="4:4">
+    <row r="915">
       <c r="D915" s="5"/>
     </row>
-    <row r="916" customHeight="1" spans="4:4">
+    <row r="916">
       <c r="D916" s="5"/>
     </row>
-    <row r="917" customHeight="1" spans="4:4">
+    <row r="917">
       <c r="D917" s="5"/>
     </row>
-    <row r="918" customHeight="1" spans="4:4">
+    <row r="918">
       <c r="D918" s="5"/>
     </row>
-    <row r="919" customHeight="1" spans="4:4">
+    <row r="919">
       <c r="D919" s="5"/>
     </row>
-    <row r="920" customHeight="1" spans="4:4">
+    <row r="920">
       <c r="D920" s="5"/>
     </row>
-    <row r="921" customHeight="1" spans="4:4">
+    <row r="921">
       <c r="D921" s="5"/>
     </row>
-    <row r="922" customHeight="1" spans="4:4">
+    <row r="922">
       <c r="D922" s="5"/>
     </row>
-    <row r="923" customHeight="1" spans="4:4">
+    <row r="923">
       <c r="D923" s="5"/>
     </row>
-    <row r="924" customHeight="1" spans="4:4">
+    <row r="924">
       <c r="D924" s="5"/>
     </row>
-    <row r="925" customHeight="1" spans="4:4">
+    <row r="925">
       <c r="D925" s="5"/>
     </row>
-    <row r="926" customHeight="1" spans="4:4">
+    <row r="926">
       <c r="D926" s="5"/>
     </row>
-    <row r="927" customHeight="1" spans="4:4">
+    <row r="927">
       <c r="D927" s="5"/>
     </row>
-    <row r="928" customHeight="1" spans="4:4">
+    <row r="928">
       <c r="D928" s="5"/>
     </row>
-    <row r="929" customHeight="1" spans="4:4">
+    <row r="929">
       <c r="D929" s="5"/>
     </row>
-    <row r="930" customHeight="1" spans="4:4">
+    <row r="930">
       <c r="D930" s="5"/>
     </row>
-    <row r="931" customHeight="1" spans="4:4">
+    <row r="931">
       <c r="D931" s="5"/>
     </row>
-    <row r="932" customHeight="1" spans="4:4">
+    <row r="932">
       <c r="D932" s="5"/>
     </row>
-    <row r="933" customHeight="1" spans="4:4">
+    <row r="933">
       <c r="D933" s="5"/>
     </row>
-    <row r="934" customHeight="1" spans="4:4">
+    <row r="934">
       <c r="D934" s="5"/>
     </row>
-    <row r="935" customHeight="1" spans="4:4">
+    <row r="935">
       <c r="D935" s="5"/>
     </row>
-    <row r="936" customHeight="1" spans="4:4">
+    <row r="936">
       <c r="D936" s="5"/>
     </row>
-    <row r="937" customHeight="1" spans="4:4">
+    <row r="937">
       <c r="D937" s="5"/>
     </row>
-    <row r="938" customHeight="1" spans="4:4">
+    <row r="938">
       <c r="D938" s="5"/>
     </row>
-    <row r="939" customHeight="1" spans="4:4">
+    <row r="939">
       <c r="D939" s="5"/>
     </row>
-    <row r="940" customHeight="1" spans="4:4">
+    <row r="940">
       <c r="D940" s="5"/>
     </row>
-    <row r="941" customHeight="1" spans="4:4">
+    <row r="941">
       <c r="D941" s="5"/>
     </row>
-    <row r="942" customHeight="1" spans="4:4">
+    <row r="942">
       <c r="D942" s="5"/>
     </row>
-    <row r="943" customHeight="1" spans="4:4">
+    <row r="943">
       <c r="D943" s="5"/>
     </row>
-    <row r="944" customHeight="1" spans="4:4">
+    <row r="944">
       <c r="D944" s="5"/>
     </row>
-    <row r="945" customHeight="1" spans="4:4">
+    <row r="945">
       <c r="D945" s="5"/>
     </row>
-    <row r="946" customHeight="1" spans="4:4">
+    <row r="946">
       <c r="D946" s="5"/>
     </row>
-    <row r="947" customHeight="1" spans="4:4">
+    <row r="947">
       <c r="D947" s="5"/>
     </row>
-    <row r="948" customHeight="1" spans="4:4">
+    <row r="948">
       <c r="D948" s="5"/>
     </row>
-    <row r="949" customHeight="1" spans="4:4">
+    <row r="949">
       <c r="D949" s="5"/>
     </row>
-    <row r="950" customHeight="1" spans="4:4">
+    <row r="950">
       <c r="D950" s="5"/>
     </row>
-    <row r="951" customHeight="1" spans="4:4">
+    <row r="951">
       <c r="D951" s="5"/>
     </row>
-    <row r="952" customHeight="1" spans="4:4">
+    <row r="952">
       <c r="D952" s="5"/>
     </row>
-    <row r="953" customHeight="1" spans="4:4">
+    <row r="953">
       <c r="D953" s="5"/>
     </row>
-    <row r="954" customHeight="1" spans="4:4">
+    <row r="954">
       <c r="D954" s="5"/>
     </row>
-    <row r="955" customHeight="1" spans="4:4">
+    <row r="955">
       <c r="D955" s="5"/>
     </row>
-    <row r="956" customHeight="1" spans="4:4">
+    <row r="956">
       <c r="D956" s="5"/>
     </row>
-    <row r="957" customHeight="1" spans="4:4">
+    <row r="957">
       <c r="D957" s="5"/>
     </row>
-    <row r="958" customHeight="1" spans="4:4">
+    <row r="958">
       <c r="D958" s="5"/>
     </row>
-    <row r="959" customHeight="1" spans="4:4">
+    <row r="959">
       <c r="D959" s="5"/>
     </row>
-    <row r="960" customHeight="1" spans="4:4">
+    <row r="960">
       <c r="D960" s="5"/>
     </row>
-    <row r="961" customHeight="1" spans="4:4">
+    <row r="961">
       <c r="D961" s="5"/>
     </row>
-    <row r="962" customHeight="1" spans="4:4">
+    <row r="962">
       <c r="D962" s="5"/>
     </row>
-    <row r="963" customHeight="1" spans="4:4">
+    <row r="963">
       <c r="D963" s="5"/>
     </row>
-    <row r="964" customHeight="1" spans="4:4">
+    <row r="964">
       <c r="D964" s="5"/>
     </row>
-    <row r="965" customHeight="1" spans="4:4">
+    <row r="965">
       <c r="D965" s="5"/>
     </row>
-    <row r="966" customHeight="1" spans="4:4">
+    <row r="966">
       <c r="D966" s="5"/>
     </row>
-    <row r="967" customHeight="1" spans="4:4">
+    <row r="967">
       <c r="D967" s="5"/>
     </row>
-    <row r="968" customHeight="1" spans="4:4">
+    <row r="968">
       <c r="D968" s="5"/>
     </row>
-    <row r="969" customHeight="1" spans="4:4">
+    <row r="969">
       <c r="D969" s="5"/>
     </row>
-    <row r="970" customHeight="1" spans="4:4">
+    <row r="970">
       <c r="D970" s="5"/>
     </row>
-    <row r="971" customHeight="1" spans="4:4">
+    <row r="971">
       <c r="D971" s="5"/>
     </row>
-    <row r="972" customHeight="1" spans="4:4">
+    <row r="972">
       <c r="D972" s="5"/>
     </row>
-    <row r="973" customHeight="1" spans="4:4">
+    <row r="973">
       <c r="D973" s="5"/>
     </row>
-    <row r="974" customHeight="1" spans="4:4">
+    <row r="974">
       <c r="D974" s="5"/>
     </row>
-    <row r="975" customHeight="1" spans="4:4">
+    <row r="975">
       <c r="D975" s="5"/>
     </row>
-    <row r="976" customHeight="1" spans="4:4">
+    <row r="976">
       <c r="D976" s="5"/>
     </row>
-    <row r="977" customHeight="1" spans="4:4">
+    <row r="977">
       <c r="D977" s="5"/>
     </row>
-    <row r="978" customHeight="1" spans="4:4">
+    <row r="978">
       <c r="D978" s="5"/>
     </row>
-    <row r="979" customHeight="1" spans="4:4">
+    <row r="979">
       <c r="D979" s="5"/>
     </row>
-    <row r="980" customHeight="1" spans="4:4">
+    <row r="980">
       <c r="D980" s="5"/>
     </row>
-    <row r="981" customHeight="1" spans="4:4">
+    <row r="981">
       <c r="D981" s="5"/>
     </row>
-    <row r="982" customHeight="1" spans="4:4">
+    <row r="982">
       <c r="D982" s="5"/>
     </row>
-    <row r="983" customHeight="1" spans="4:4">
+    <row r="983">
       <c r="D983" s="5"/>
     </row>
-    <row r="984" customHeight="1" spans="4:4">
+    <row r="984">
       <c r="D984" s="5"/>
     </row>
-    <row r="985" customHeight="1" spans="4:4">
+    <row r="985">
       <c r="D985" s="5"/>
     </row>
-    <row r="986" customHeight="1" spans="4:4">
+    <row r="986">
       <c r="D986" s="5"/>
     </row>
-    <row r="987" customHeight="1" spans="4:4">
+    <row r="987">
       <c r="D987" s="5"/>
     </row>
-    <row r="988" customHeight="1" spans="4:4">
+    <row r="988">
       <c r="D988" s="5"/>
     </row>
-    <row r="989" customHeight="1" spans="4:4">
+    <row r="989">
       <c r="D989" s="5"/>
     </row>
-    <row r="990" customHeight="1" spans="4:4">
+    <row r="990">
       <c r="D990" s="5"/>
     </row>
-    <row r="991" customHeight="1" spans="4:4">
+    <row r="991">
       <c r="D991" s="5"/>
     </row>
-    <row r="992" customHeight="1" spans="4:4">
+    <row r="992">
       <c r="D992" s="5"/>
     </row>
-    <row r="993" customHeight="1" spans="4:4">
+    <row r="993">
       <c r="D993" s="5"/>
     </row>
-    <row r="994" customHeight="1" spans="4:4">
+    <row r="994">
       <c r="D994" s="5"/>
     </row>
-    <row r="995" customHeight="1" spans="4:4">
+    <row r="995">
       <c r="D995" s="5"/>
     </row>
-    <row r="996" customHeight="1" spans="4:4">
+    <row r="996">
       <c r="D996" s="5"/>
     </row>
-    <row r="997" customHeight="1" spans="4:4">
+    <row r="997">
       <c r="D997" s="5"/>
     </row>
-    <row r="998" customHeight="1" spans="4:4">
+    <row r="998">
       <c r="D998" s="5"/>
     </row>
-    <row r="999" customHeight="1" spans="4:4">
+    <row r="999">
       <c r="D999" s="5"/>
     </row>
-    <row r="1000" customHeight="1" spans="4:4">
+    <row r="1000">
       <c r="D1000" s="5"/>
     </row>
-    <row r="1001" customHeight="1" spans="4:4">
+    <row r="1001">
       <c r="D1001" s="5"/>
     </row>
   </sheetData>
@@ -4722,7 +3858,6 @@
       <formula>LEN(TRIM(D1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>